--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="88" t="n">
-        <v>7.35</v>
+        <v>7.36</v>
       </c>
       <c r="C25" s="88" t="n">
         <v>7.34</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="89" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="C26" s="89" t="n">
         <v>0.04</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="89" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="C27" s="89" t="n">
         <v>0.86</v>
@@ -8281,9 +8281,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B18" s="94" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C18" s="92" t="inlineStr">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>3.03</v>
+        <v>3.33</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>3.03</v>
@@ -8534,7 +8534,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>4.51</v>
+        <v>5.53</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>4.51</v>
@@ -8625,13 +8625,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="86" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>6.03</v>
+        <v>74.91</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>6.03</v>
@@ -8727,9 +8727,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B22" s="94" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C22" s="92" t="inlineStr">
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>1.04</v>
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>5.98</v>
+        <v>6.27</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>5.98</v>
@@ -9071,13 +9071,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="86" t="inlineStr">
+      <c r="A25" s="76" t="inlineStr">
         <is>
           <t>us30:RS3</t>
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>15.8</v>
+        <v>54.91</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>15.8</v>
@@ -9173,9 +9173,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B26" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C26" s="92" t="inlineStr">
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>7.57</v>
+        <v>7.91</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>7.57</v>
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>4.8</v>
+        <v>6.22</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>4.8</v>
@@ -9517,13 +9517,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="86" t="inlineStr">
+      <c r="A29" s="76" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>5.68</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>5.68</v>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="B35" s="95" t="n">
-        <v>-1.96</v>
+        <v>-2.47</v>
       </c>
       <c r="C35" s="95" t="n">
         <v>-0.95</v>
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="B36" s="95" t="n">
-        <v>-1.56</v>
+        <v>-2.08</v>
       </c>
       <c r="C36" s="95" t="n">
         <v>-0.79</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="B37" s="95" t="n">
-        <v>24.2</v>
+        <v>17.28</v>
       </c>
       <c r="C37" s="95" t="n">
         <v>51.04</v>
@@ -10667,7 +10667,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>-2.86</v>
+        <v>-2.95</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>-1.36</v>
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>-1.51</v>
+        <v>-1.61</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>0.06</v>
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>49.1</v>
+        <v>48.38</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>55.82</v>
@@ -10957,9 +10957,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B42" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C42" s="93" t="inlineStr">
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-2.41</v>
+        <v>-3.18</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-2.41</v>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-3.13</v>
+        <v>-3.93</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-3.13</v>
@@ -11307,7 +11307,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>65.84</v>
+        <v>37.52</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>65.84</v>
@@ -11403,9 +11403,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B46" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C46" s="94" t="inlineStr">
@@ -11559,7 +11559,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>4.24</v>
+        <v>4.11</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>5.31</v>
@@ -11656,7 +11656,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>6.31</v>
+        <v>6.18</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>8.039999999999999</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>40.81</v>
+        <v>39.09</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>48.84</v>
@@ -11846,7 +11846,7 @@
     <row r="51">
       <c r="A51" s="91" t="inlineStr">
         <is>
-          <t>今日买报：sh:RS3:4.21&lt;=8;kc:RS5:16.9&lt;=21;cy:RS3:2.51&lt;=4;us500:RS2:6.03&lt;=22;us30:RS3:15.8&lt;=25;ixic:RS2:5.68&lt;=38;vn:RS3:24.2&lt;=25</t>
+          <t>今日买报：sh:RS3:4.21&lt;=8;kc:RS5:16.9&lt;=21;cy:RS3:2.51&lt;=4;vn:RS3:17.28&lt;=25</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.12</v>
+        <v>-0.16</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.25</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.3</v>
@@ -8289,9 +8289,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C18" s="93" t="inlineStr">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>3.33</v>
+        <v>3.17</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>3.33</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>5.53</v>
+        <v>5.44</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>5.53</v>
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>74.91</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>74.91</v>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>1.55</v>
+        <v>0.46</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>1.55</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>6.27</v>
+        <v>4.28</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>6.27</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>54.91</v>
+        <v>52.18</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>54.91</v>
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="B35" s="94" t="n">
-        <v>-2.5</v>
+        <v>-3.26</v>
       </c>
       <c r="C35" s="94" t="n">
         <v>-2.47</v>
@@ -10336,7 +10336,7 @@
         </is>
       </c>
       <c r="B36" s="94" t="n">
-        <v>-0.98</v>
+        <v>-1.76</v>
       </c>
       <c r="C36" s="94" t="n">
         <v>-2.08</v>
@@ -10427,13 +10427,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="76" t="inlineStr">
+      <c r="A37" s="95" t="inlineStr">
         <is>
           <t>vn:RS3</t>
         </is>
       </c>
       <c r="B37" s="94" t="n">
-        <v>25.18</v>
+        <v>11.22</v>
       </c>
       <c r="C37" s="94" t="n">
         <v>17.28</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-4.25</v>
+        <v>-4.3</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>-2.95</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>-3.29</v>
+        <v>-3.35</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>-1.61</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>38.72</v>
+        <v>38.45</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>48.38</v>
@@ -10977,9 +10977,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="91" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C42" s="91" t="inlineStr">
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>-3.18</v>
+        <v>-1.51</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>-3.18</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>-3.93</v>
+        <v>-1.65</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>-3.93</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>37.52</v>
+        <v>65.06</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>37.52</v>
@@ -11425,9 +11425,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="91" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C46" s="91" t="inlineStr">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>4.11</v>
+        <v>5.82</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>4.11</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>6.18</v>
+        <v>8.74</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>6.18</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>39.09</v>
+        <v>62.55</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>39.09</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：sh:RS3:4.01&lt;=8;kc:RS5:16.15&lt;=21;cy:RS3:2.46&lt;=4;sensex:RS10:38.72&lt;=39</t>
+          <t>今日买报：sh:RS3:4.01&lt;=8;kc:RS5:16.15&lt;=21;cy:RS3:2.46&lt;=4;vn:RS3:11.22&lt;=25;sensex:RS10:38.45&lt;=39</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.33</v>
+        <v>7.34</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.35</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.16</v>
+        <v>-0.06</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.16</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.93</v>
+        <v>1.03</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.88</v>
@@ -8289,9 +8289,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B18" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C18" s="93" t="inlineStr">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>3.17</v>
+        <v>2.23</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>3.17</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>5.44</v>
+        <v>5.74</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>5.44</v>
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>84.81999999999999</v>
+        <v>32.72</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>84.81999999999999</v>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>0.46</v>
+        <v>0.17</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>0.46</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>4.28</v>
+        <v>3.23</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>4.28</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>52.18</v>
+        <v>34.31</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>52.18</v>
@@ -9185,9 +9185,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B26" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C26" s="93" t="inlineStr">
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>8.6</v>
+        <v>6.61</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>8.6</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>7.32</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>7.32</v>
@@ -9531,13 +9531,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="76" t="inlineStr">
+      <c r="A29" s="96" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>88.52</v>
+        <v>34.13</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>88.52</v>
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="B35" s="94" t="n">
-        <v>-3.26</v>
+        <v>-3.06</v>
       </c>
       <c r="C35" s="94" t="n">
         <v>-3.26</v>
@@ -10336,7 +10336,7 @@
         </is>
       </c>
       <c r="B36" s="94" t="n">
-        <v>-1.76</v>
+        <v>-2.16</v>
       </c>
       <c r="C36" s="94" t="n">
         <v>-1.76</v>
@@ -10433,7 +10433,7 @@
         </is>
       </c>
       <c r="B37" s="94" t="n">
-        <v>11.22</v>
+        <v>14.49</v>
       </c>
       <c r="C37" s="94" t="n">
         <v>11.22</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-4.21</v>
+        <v>-4.18</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>-4.3</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>-3.15</v>
+        <v>-3.12</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>-3.35</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>40.69</v>
+        <v>40.95</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>38.45</v>
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>-1.22</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>-1.51</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>-1.8</v>
+        <v>-1.28</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>-1.65</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>65.52</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>65.06</v>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>5.82</v>
+        <v>6.73</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>5.82</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>8.74</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>8.74</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>62.55</v>
+        <v>68.78</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>62.55</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：hk50:RS4:21.65&lt;=22;vn:RS3:11.22&lt;=25</t>
+          <t>今日买报：hk50:RS4:21.65&lt;=22;ixic:RS2:34.13&lt;=38;vn:RS3:14.49&lt;=25</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.06</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.03</v>
@@ -8289,9 +8289,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C18" s="92" t="inlineStr">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>2.23</v>
+        <v>1.78</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>2.23</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>5.74</v>
+        <v>6.74</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>5.74</v>
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>32.72</v>
+        <v>42.53</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>32.72</v>
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="B35" s="94" t="n">
-        <v>-2.98</v>
+        <v>-2.35</v>
       </c>
       <c r="C35" s="94" t="n">
         <v>-3.06</v>
@@ -10336,7 +10336,7 @@
         </is>
       </c>
       <c r="B36" s="94" t="n">
-        <v>-1.73</v>
+        <v>-1.09</v>
       </c>
       <c r="C36" s="94" t="n">
         <v>-2.16</v>
@@ -10427,13 +10427,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="96" t="inlineStr">
+      <c r="A37" s="76" t="inlineStr">
         <is>
           <t>vn:RS3</t>
         </is>
       </c>
       <c r="B37" s="94" t="n">
-        <v>10.52</v>
+        <v>37.84</v>
       </c>
       <c r="C37" s="94" t="n">
         <v>14.49</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-3.94</v>
+        <v>-3.97</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>-4.18</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>-3.9</v>
+        <v>-3.93</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>-3.12</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>40.74</v>
+        <v>40.56</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>40.95</v>
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.66</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>-0.6899999999999999</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>-1.28</v>
+        <v>-1.09</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>-1.28</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>69.54000000000001</v>
+        <v>61.23</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>69.54000000000001</v>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>6.68</v>
+        <v>5.58</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>6.68</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>9.84</v>
+        <v>10.27</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>9.84</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>68.40000000000001</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>68.40000000000001</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：hk50:RS4:16.18&lt;=22;ixic:RS2:34.13&lt;=38;vn:RS3:10.52&lt;=25</t>
+          <t>今日买报：hk50:RS4:16.18&lt;=22;ixic:RS2:34.13&lt;=38</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-5.34</v>
+        <v>-5.31</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>-3.97</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>-3.73</v>
+        <v>-3.7</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>-3.93</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>36.29</v>
+        <v>36.46</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>40.56</v>
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>-1.66</v>
+        <v>-1.47</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>-1.66</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>-1.09</v>
+        <v>-1.73</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>-1.09</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>61.23</v>
+        <v>66.38</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>61.23</v>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>5.74</v>
+        <v>5.76</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>5.58</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>10.67</v>
+        <v>10.69</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>10.27</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>65.33</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>67.31999999999999</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：hk50:RS4:15.01&lt;=22;ixic:RS2:32.97&lt;=38;vn:RS3:24.76&lt;=25;sensex:RS10:36.29&lt;=39</t>
+          <t>今日买报：hk50:RS4:15.01&lt;=22;ixic:RS2:32.97&lt;=38;vn:RS3:24.76&lt;=25;sensex:RS10:36.46&lt;=39</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="B25" s="88" t="n">
-        <v>7.35</v>
+        <v>7.36</v>
       </c>
       <c r="C25" s="88" t="n">
         <v>7.36</v>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="B26" s="89" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="C26" s="89" t="n">
         <v>0.03</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="B27" s="89" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="C27" s="89" t="n">
         <v>1.06</v>
@@ -8280,9 +8280,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B18" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C18" s="93" t="inlineStr">
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>1.78</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>1.78</v>
@@ -8533,7 +8533,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>6.74</v>
+        <v>5.85</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>6.74</v>
@@ -8624,13 +8624,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="86" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>42.53</v>
+        <v>10.95</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>42.53</v>
@@ -8726,9 +8726,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B22" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C22" s="93" t="inlineStr">
@@ -8882,7 +8882,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>-0.53</v>
+        <v>-2.62</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>-0.53</v>
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>4.84</v>
+        <v>4.1</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>4.84</v>
@@ -9070,13 +9070,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="76" t="inlineStr">
+      <c r="A25" s="86" t="inlineStr">
         <is>
           <t>us30:RS3</t>
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>49.78</v>
+        <v>15.07</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>49.78</v>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>6.19</v>
+        <v>3.56</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>6.19</v>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>9</v>
+        <v>8.09</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>9</v>
@@ -9522,7 +9522,7 @@
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>32.97</v>
+        <v>10.96</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>32.97</v>
@@ -10220,7 +10220,7 @@
         </is>
       </c>
       <c r="B35" s="95" t="n">
-        <v>-3.56</v>
+        <v>-4.36</v>
       </c>
       <c r="C35" s="95" t="n">
         <v>-2.63</v>
@@ -10317,7 +10317,7 @@
         </is>
       </c>
       <c r="B36" s="95" t="n">
-        <v>0.73</v>
+        <v>-0.11</v>
       </c>
       <c r="C36" s="95" t="n">
         <v>-0.71</v>
@@ -10414,7 +10414,7 @@
         </is>
       </c>
       <c r="B37" s="95" t="n">
-        <v>16.56</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="C37" s="95" t="n">
         <v>24.76</v>
@@ -10666,7 +10666,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>-5.49</v>
+        <v>-5.43</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>-5.31</v>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>-3.94</v>
+        <v>-3.88</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>-3.7</v>
@@ -10860,7 +10860,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>34.33</v>
+        <v>34.68</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>36.46</v>
@@ -10956,9 +10956,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="94" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B42" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C42" s="94" t="inlineStr">
@@ -11112,7 +11112,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-0.36</v>
+        <v>-1.21</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-1.47</v>
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-1.37</v>
+        <v>-2.21</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-1.73</v>
@@ -11306,7 +11306,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>67.01000000000001</v>
+        <v>52.7</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>66.38</v>
@@ -11402,9 +11402,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="94" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B46" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C46" s="94" t="inlineStr">
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>5.76</v>
+        <v>4.34</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>5.76</v>
@@ -11655,7 +11655,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>10.69</v>
+        <v>11.24</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>10.69</v>
@@ -11752,7 +11752,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>65.81999999999999</v>
+        <v>54.22</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>65.81999999999999</v>
@@ -11845,7 +11845,7 @@
     <row r="51">
       <c r="A51" s="91" t="inlineStr">
         <is>
-          <t>今日买报：hk50:RS4:10.43&lt;=22;ixic:RS2:32.97&lt;=38;vn:RS3:16.56&lt;=25;sensex:RS10:34.33&lt;=39</t>
+          <t>今日买报：hk50:RS4:10.43&lt;=22;us500:RS2:10.95&lt;=22;us30:RS3:15.07&lt;=25;ixic:RS2:10.96&lt;=38;vn:RS3:9.86&lt;=25;sensex:RS10:34.68&lt;=39</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="88" t="n">
-        <v>7.36</v>
+        <v>7.35</v>
       </c>
       <c r="C25" s="88" t="n">
         <v>7.36</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="89" t="n">
-        <v>-0.1</v>
+        <v>-0.21</v>
       </c>
       <c r="C26" s="89" t="n">
         <v>0.1</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="89" t="n">
-        <v>1.03</v>
+        <v>0.92</v>
       </c>
       <c r="C27" s="89" t="n">
         <v>1.2</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>-0.5600000000000001</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>5.85</v>
+        <v>4.88</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>5.85</v>
@@ -8635,13 +8635,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="87" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>10.95</v>
+        <v>22.53</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>10.95</v>
@@ -8737,9 +8737,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B22" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C22" s="93" t="inlineStr">
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>-2.62</v>
+        <v>-1.04</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>-2.62</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>4.1</v>
+        <v>4.66</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>4.1</v>
@@ -9083,13 +9083,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="87" t="inlineStr">
+      <c r="A25" s="76" t="inlineStr">
         <is>
           <t>us30:RS3</t>
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>15.07</v>
+        <v>44.79</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>15.07</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>3.56</v>
+        <v>4.22</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>3.56</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>8.09</v>
+        <v>6</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>8.09</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>10.96</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>10.96</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>-6.2</v>
+        <v>-6.35</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>-5.43</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>-4.95</v>
+        <v>-5.1</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>-3.88</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>28.68</v>
+        <v>28.07</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>34.68</v>
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-1.17</v>
+        <v>-1.11</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-1.21</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-1.46</v>
+        <v>-1.4</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-2.21</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>47.19</v>
+        <v>48.02</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>52.7</v>
@@ -11425,9 +11425,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C46" s="92" t="inlineStr">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>4.34</v>
+        <v>3.2</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>4.34</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>11.24</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>11.24</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>54.22</v>
+        <v>46.37</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>54.22</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="91" t="inlineStr">
         <is>
-          <t>今日买报：hk50:RS4:7.26&lt;=22;us500:RS2:10.95&lt;=22;us30:RS3:15.07&lt;=25;ixic:RS2:10.96&lt;=38;sensex:RS10:28.68&lt;=39</t>
+          <t>今日买报：hk50:RS4:7.26&lt;=22;ixic:RS2:8.38&lt;=38;sensex:RS10:28.07&lt;=39</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.35</v>
+        <v>7.34</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.35</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.21</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.77</v>
+        <v>0.7</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.92</v>
@@ -8289,9 +8289,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C18" s="92" t="inlineStr">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>0.36</v>
+        <v>0.01</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>0.36</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>4.88</v>
+        <v>5.17</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>4.88</v>
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>22.53</v>
+        <v>34.87</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>22.53</v>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>-1.04</v>
+        <v>-1.3</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>-1.04</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>4.66</v>
+        <v>5.35</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>4.66</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>44.79</v>
+        <v>58.29</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>44.79</v>
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="B35" s="94" t="n">
-        <v>-3.88</v>
+        <v>-3.96</v>
       </c>
       <c r="C35" s="94" t="n">
         <v>-3.87</v>
@@ -10336,7 +10336,7 @@
         </is>
       </c>
       <c r="B36" s="94" t="n">
-        <v>-0.25</v>
+        <v>-0.33</v>
       </c>
       <c r="C36" s="94" t="n">
         <v>-0.23</v>
@@ -10433,7 +10433,7 @@
         </is>
       </c>
       <c r="B37" s="94" t="n">
-        <v>22.53</v>
+        <v>21.39</v>
       </c>
       <c r="C37" s="94" t="n">
         <v>30.94</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-5.41</v>
+        <v>-5.56</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>-6.35</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>-4.4</v>
+        <v>-4.55</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>-5.1</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>32.12</v>
+        <v>30.45</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>28.07</v>
@@ -10977,9 +10977,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C42" s="91" t="inlineStr">
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>-1.32</v>
+        <v>-2.11</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>-1.11</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>0.76</v>
+        <v>-0.05</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>-1.4</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>62.06</v>
+        <v>51.62</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>48.02</v>
@@ -11425,9 +11425,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C46" s="92" t="inlineStr">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>3.2</v>
+        <v>4.03</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>3.2</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>9.380000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>9.380000000000001</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>46.37</v>
+        <v>58.54</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>46.37</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：ixic:RS2:8.38&lt;=38;vn:RS3:22.53&lt;=25;sensex:RS10:32.12&lt;=39</t>
+          <t>今日买报：ixic:RS2:8.38&lt;=38;vn:RS3:21.39&lt;=25;sensex:RS10:30.45&lt;=39</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.06</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.7</v>
@@ -8289,9 +8289,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B18" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C18" s="91" t="inlineStr">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>0.01</v>
+        <v>1.86</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>0.01</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>5.17</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>5.17</v>
@@ -8635,13 +8635,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="95" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>34.87</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>34.87</v>
@@ -8737,9 +8737,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B22" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C22" s="91" t="inlineStr">
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>-1.3</v>
+        <v>-0.04</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>-1.3</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>5.35</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>5.35</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>58.29</v>
+        <v>80.75</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>58.29</v>
@@ -9185,9 +9185,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B26" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C26" s="92" t="inlineStr">
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>3.69</v>
+        <v>6.19</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>3.69</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>5.82</v>
+        <v>12.51</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>5.82</v>
@@ -9531,13 +9531,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="96" t="inlineStr">
+      <c r="A29" s="76" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>6.54</v>
+        <v>83.56</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>6.54</v>
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="B31" s="94" t="n">
-        <v>-1.67</v>
+        <v>-1.88</v>
       </c>
       <c r="C31" s="94" t="n">
         <v>-3.6</v>
@@ -9888,7 +9888,7 @@
         </is>
       </c>
       <c r="B32" s="94" t="n">
-        <v>-2.71</v>
+        <v>-2.92</v>
       </c>
       <c r="C32" s="94" t="n">
         <v>-3.97</v>
@@ -9985,7 +9985,7 @@
         </is>
       </c>
       <c r="B33" s="94" t="n">
-        <v>37.47</v>
+        <v>36.1</v>
       </c>
       <c r="C33" s="94" t="n">
         <v>36.44</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-5.71</v>
+        <v>-5.54</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>-5.56</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>-4.32</v>
+        <v>-4.14</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>-4.55</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>31.7</v>
+        <v>33.68</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>30.45</v>
@@ -10977,9 +10977,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B42" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C42" s="91" t="inlineStr">
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>-2.21</v>
+        <v>-1.82</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>-2.11</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>-0.97</v>
+        <v>-0.57</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>-0.05</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>56.88</v>
+        <v>62.6</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>51.62</v>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>4.03</v>
+        <v>5.88</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>4.03</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>9.23</v>
+        <v>11.9</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>9.23</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>58.54</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>58.54</v>
@@ -11870,14 +11870,14 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：ixic:RS2:6.54&lt;=38;sensex:RS10:31.7&lt;=39</t>
+          <t>今日买报：sensex:RS10:33.68&lt;=39</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：kc:RNG120:30.45&gt;=30</t>
+          <t>今日卖报：kc:RNG120:30.45&gt;=30;us500:RS2:89.32&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -800,7 +800,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1062,7 +1062,6 @@
     <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3988,7 +3987,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.08</v>
@@ -4085,7 +4084,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.84</v>
@@ -8447,7 +8446,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>1.86</v>
+        <v>1.24</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>1.86</v>
@@ -8544,7 +8543,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>9.630000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>9.630000000000001</v>
@@ -8635,13 +8634,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="95" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>89.31999999999999</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>89.31999999999999</v>
@@ -8895,7 +8894,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>-0.04</v>
+        <v>-0.28</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>-0.04</v>
@@ -8992,7 +8991,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>8.449999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>8.449999999999999</v>
@@ -9089,7 +9088,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>80.75</v>
+        <v>74.87</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>80.75</v>
@@ -9185,9 +9184,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C26" s="93" t="inlineStr">
@@ -9343,7 +9342,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>6.19</v>
+        <v>4.59</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>6.19</v>
@@ -9440,7 +9439,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>12.51</v>
+        <v>12.55</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>12.51</v>
@@ -9537,7 +9536,7 @@
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>83.56</v>
+        <v>51.88</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>83.56</v>
@@ -10687,7 +10686,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-5.11</v>
+        <v>-5.06</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>-5.54</v>
@@ -10784,7 +10783,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>-5.32</v>
+        <v>-5.27</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>-4.14</v>
@@ -10875,13 +10874,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="96" t="inlineStr">
+      <c r="A41" s="95" t="inlineStr">
         <is>
           <t>sensex:RS10</t>
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>37.71</v>
+        <v>38.21</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>33.68</v>
@@ -11135,7 +11134,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>-0.01</v>
+        <v>1.31</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>-1.82</v>
@@ -11232,7 +11231,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>1.23</v>
+        <v>2.56</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>-0.57</v>
@@ -11329,7 +11328,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>72.05</v>
+        <v>80.23</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>62.6</v>
@@ -11583,7 +11582,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>5.14</v>
+        <v>5.47</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>5.88</v>
@@ -11680,7 +11679,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>12.52</v>
+        <v>12.88</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>11.9</v>
@@ -11777,7 +11776,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>74.59</v>
+        <v>76.81</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>74.04000000000001</v>
@@ -11870,14 +11869,14 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：sensex:RS10:37.71&lt;=39</t>
+          <t>今日买报：sensex:RS10:38.21&lt;=39</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：us500:RS2:89.32&gt;=85</t>
+          <t>今日卖报：</t>
         </is>
       </c>
     </row>
@@ -15478,13 +15477,13 @@
       <c r="G2" s="36" t="n">
         <v>66</v>
       </c>
-      <c r="H2" s="97" t="n">
+      <c r="H2" s="96" t="n">
         <v>22.3514585</v>
       </c>
       <c r="I2" s="36" t="n">
         <v>7.06</v>
       </c>
-      <c r="J2" s="98">
+      <c r="J2" s="97">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -15516,13 +15515,13 @@
       <c r="G3" s="39" t="n">
         <v>73</v>
       </c>
-      <c r="H3" s="99" t="n">
+      <c r="H3" s="98" t="n">
         <v>35.0298984</v>
       </c>
       <c r="I3" s="39" t="n">
         <v>11.41</v>
       </c>
-      <c r="J3" s="98">
+      <c r="J3" s="97">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -15554,13 +15553,13 @@
       <c r="G4" s="39" t="n">
         <v>85</v>
       </c>
-      <c r="H4" s="99" t="n">
+      <c r="H4" s="98" t="n">
         <v>122.4911655</v>
       </c>
       <c r="I4" s="39" t="n">
         <v>76.98</v>
       </c>
-      <c r="J4" s="100">
+      <c r="J4" s="99">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -15592,13 +15591,13 @@
       <c r="G5" s="39" t="n">
         <v>96</v>
       </c>
-      <c r="H5" s="99" t="n">
+      <c r="H5" s="98" t="n">
         <v>136.13543</v>
       </c>
       <c r="I5" s="39" t="n">
         <v>100.05</v>
       </c>
-      <c r="J5" s="100">
+      <c r="J5" s="99">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -15630,13 +15629,13 @@
       <c r="G6" s="39" t="n">
         <v>95</v>
       </c>
-      <c r="H6" s="99" t="n">
+      <c r="H6" s="98" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I6" s="39" t="n">
         <v>44.37</v>
       </c>
-      <c r="J6" s="100">
+      <c r="J6" s="99">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -15668,13 +15667,13 @@
       <c r="G7" s="39" t="n">
         <v>86</v>
       </c>
-      <c r="H7" s="99" t="n">
+      <c r="H7" s="98" t="n">
         <v>123.8525927</v>
       </c>
       <c r="I7" s="39" t="n">
         <v>63.41</v>
       </c>
-      <c r="J7" s="100">
+      <c r="J7" s="99">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -15706,13 +15705,13 @@
       <c r="G8" s="39" t="n">
         <v>87</v>
       </c>
-      <c r="H8" s="99" t="n">
+      <c r="H8" s="98" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I8" s="39" t="n">
         <v>26.39</v>
       </c>
-      <c r="J8" s="100">
+      <c r="J8" s="99">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -15744,13 +15743,13 @@
       <c r="G9" s="39" t="n">
         <v>83</v>
       </c>
-      <c r="H9" s="99" t="n">
+      <c r="H9" s="98" t="n">
         <v>47.02060524</v>
       </c>
       <c r="I9" s="39" t="n">
         <v>37.82</v>
       </c>
-      <c r="J9" s="100">
+      <c r="J9" s="99">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -15781,13 +15780,13 @@
       <c r="G10" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="H10" s="101" t="n">
+      <c r="H10" s="100" t="n">
         <v>27.8860732</v>
       </c>
       <c r="I10" s="24" t="n">
         <v>-10.97</v>
       </c>
-      <c r="J10" s="102" t="n">
+      <c r="J10" s="101" t="n">
         <v>0.278860732</v>
       </c>
     </row>
@@ -15818,13 +15817,13 @@
       <c r="G11" s="24" t="n">
         <v>93</v>
       </c>
-      <c r="H11" s="101" t="n">
+      <c r="H11" s="100" t="n">
         <v>17.4948656</v>
       </c>
       <c r="I11" s="24" t="n">
         <v>-7.7</v>
       </c>
-      <c r="J11" s="102">
+      <c r="J11" s="101">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.35</v>
+        <v>7.34</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.35</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.03</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.59</v>
+        <v>0.44</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.31</v>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>1.24</v>
+        <v>2.44</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>1.24</v>
@@ -8534,7 +8534,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>9.970000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>9.970000000000001</v>
@@ -8625,13 +8625,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="95" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>74.65000000000001</v>
+        <v>90.06</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>74.65000000000001</v>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>-0.28</v>
+        <v>1.3</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>-0.28</v>
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>8.06</v>
+        <v>7.14</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>8.06</v>
@@ -9077,7 +9077,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>74.87</v>
+        <v>83.62</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>74.87</v>
@@ -9173,9 +9173,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B26" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C26" s="91" t="inlineStr">
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>4.59</v>
+        <v>5.88</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>4.59</v>
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>12.55</v>
+        <v>13.09</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>12.55</v>
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>51.88</v>
+        <v>78.89</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>51.88</v>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>1.31</v>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>2.56</v>
@@ -11307,7 +11307,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>84.2</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>80.23</v>
@@ -11559,7 +11559,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>5.47</v>
+        <v>6.34</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>5.47</v>
@@ -11656,7 +11656,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>12.88</v>
+        <v>13.5</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>12.88</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>76.81</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>76.81</v>
@@ -11853,7 +11853,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RS3:67.65&gt;=66;kc:RNG120:33.95&gt;=30</t>
+          <t>今日卖报：sh:RS3:67.65&gt;=66;kc:RNG120:33.95&gt;=30;us500:RS2:90.06&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.27</v>
+        <v>7.28</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.27</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.03</v>
+        <v>0.19</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.07000000000000001</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>-0.5</v>
+        <v>-0.35</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>-0.54</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>3.38</v>
+        <v>4.98</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>3.38</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>10.72</v>
+        <v>11.96</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>10.72</v>
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>95.22</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>95.22</v>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>2.56</v>
+        <v>3.86</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>2.56</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>8.6</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>8.6</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>91.09999999999999</v>
+        <v>92.37</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>91.09999999999999</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>6.37</v>
+        <v>9.48</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>6.37</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>13.74</v>
+        <v>16.69</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>13.74</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>85.8</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>85.8</v>
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="B31" s="94" t="n">
-        <v>3.51</v>
+        <v>4.05</v>
       </c>
       <c r="C31" s="94" t="n">
         <v>1.6</v>
@@ -9888,7 +9888,7 @@
         </is>
       </c>
       <c r="B32" s="94" t="n">
-        <v>2.53</v>
+        <v>3.06</v>
       </c>
       <c r="C32" s="94" t="n">
         <v>3.61</v>
@@ -9985,7 +9985,7 @@
         </is>
       </c>
       <c r="B33" s="94" t="n">
-        <v>56.63</v>
+        <v>59.51</v>
       </c>
       <c r="C33" s="94" t="n">
         <v>49.22</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>38.87</v>
+        <v>38.85</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>31.71</v>
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>3.57</v>
+        <v>4.53</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>3.57</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>5.43</v>
+        <v>8.08</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>5.43</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>87.65000000000001</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>87.65000000000001</v>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>9.220000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>8.34</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>14.34</v>
+        <v>14.86</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>14.29</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>88.45999999999999</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>86.16</v>
@@ -11870,14 +11870,14 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：sensex:RS10:38.87&lt;=39</t>
+          <t>今日买报：sensex:RS10:38.85&lt;=39</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：kc:RNG120:35.49&gt;=30;us500:RS2:95.22&gt;=85;us30:RS3:91.1&gt;=85;fr40:RS5:87.65&gt;=87</t>
+          <t>今日卖报：kc:RNG120:35.49&gt;=30;us500:RS2:97.24&gt;=85;us30:RS3:92.37&gt;=85;fr40:RS5:90.49&gt;=87</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.19</v>
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>4.98</v>
+        <v>5.32</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>4.98</v>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>11.96</v>
+        <v>10.8</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>11.96</v>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>97.23999999999999</v>
+        <v>98.41</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>97.23999999999999</v>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>3.86</v>
+        <v>5.17</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>3.86</v>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>8.380000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>8.380000000000001</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>92.37</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>92.37</v>
@@ -9342,7 +9342,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>9.48</v>
+        <v>8.9</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>9.48</v>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>16.69</v>
+        <v>13.95</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>16.69</v>
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>93.84999999999999</v>
+        <v>94.87</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>93.84999999999999</v>
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>3.84</v>
+        <v>4.44</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>4.53</v>
@@ -11231,7 +11231,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>9.77</v>
+        <v>10.4</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>8.08</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>90.87</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>90.48999999999999</v>
@@ -11576,13 +11576,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="76" t="inlineStr">
+      <c r="A47" s="95" t="inlineStr">
         <is>
           <t>dax30:RNG60</t>
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>9.57</v>
+        <v>10.12</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>9.68</v>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>17.81</v>
+        <v>18.41</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>14.83</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>90.42</v>
+        <v>91.64</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>89.73</v>
@@ -11876,7 +11876,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：kc:RNG120:36.53&gt;=30;us500:RS2:97.24&gt;=85;us30:RS3:92.37&gt;=85;fr40:RS5:90.87&gt;=87</t>
+          <t>今日卖报：kc:RNG120:36.53&gt;=30;us500:RS2:98.41&gt;=85;us30:RS3:95.43&gt;=85;fr40:RS5:92.32&gt;=87;dax30:RNG60:10.12&gt;=10</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.25</v>
+        <v>7.24</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.29</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.49</v>
+        <v>-0.59</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.08</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>-0.71</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="C27" s="88" t="n">
         <v/>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>5.32</v>
+        <v>5.05</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>5.32</v>
@@ -8534,7 +8534,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>10.8</v>
+        <v>12.02</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>10.8</v>
@@ -8625,13 +8625,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="95" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>98.41</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>98.41</v>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>5.17</v>
+        <v>5.48</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>5.17</v>
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>9.109999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>9.109999999999999</v>
@@ -9071,13 +9071,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="95" t="inlineStr">
+      <c r="A25" s="76" t="inlineStr">
         <is>
           <t>us30:RS3</t>
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>95.43000000000001</v>
+        <v>79.05</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>95.43000000000001</v>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>8.9</v>
+        <v>7.75</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>8.9</v>
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>13.95</v>
+        <v>16.05</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>13.95</v>
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>94.87</v>
+        <v>54.41</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>94.87</v>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>5.91</v>
+        <v>5.55</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>4.44</v>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>11.57</v>
+        <v>11.19</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>10.4</v>
@@ -11307,7 +11307,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>93.97</v>
+        <v>93.34</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>92.31999999999999</v>
@@ -11403,9 +11403,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B46" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C46" s="91" t="inlineStr">
@@ -11553,13 +11553,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="95" t="inlineStr">
+      <c r="A47" s="76" t="inlineStr">
         <is>
           <t>dax30:RNG60</t>
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>10.34</v>
+        <v>9.92</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>10.12</v>
@@ -11656,7 +11656,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>21.6</v>
+        <v>21.14</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>18.41</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>92.34</v>
+        <v>89.53</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>91.64</v>
@@ -11853,7 +11853,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RS3:71.19&gt;=66;kc:RNG120:37.3&gt;=30;us500:RS2:98.41&gt;=85;us30:RS3:95.43&gt;=85;vn:RS3:85.3&gt;=85;fr40:RS5:93.97&gt;=87;dax30:RNG60:10.34&gt;=10;dax30:RNG120:21.6&gt;=20</t>
+          <t>今日卖报：sh:RS3:71.19&gt;=66;kc:RNG120:37.3&gt;=30;vn:RS3:85.3&gt;=85;fr40:RS5:93.34&gt;=87;dax30:RNG120:21.14&gt;=20</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.26</v>
+        <v>7.25</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.24</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.59</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>-0.58</v>
+        <v>-0.67</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>-0.8100000000000001</v>
@@ -8289,9 +8289,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B18" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C18" s="91" t="inlineStr">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>5.05</v>
+        <v>3.24</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>5.05</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>12.02</v>
+        <v>12.45</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>12.02</v>
@@ -8635,13 +8635,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="96" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>67.48999999999999</v>
+        <v>16.07</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>67.48999999999999</v>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>5.48</v>
+        <v>5.49</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>5.48</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>10.1</v>
+        <v>12.52</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>10.1</v>
@@ -9083,13 +9083,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="76" t="inlineStr">
+      <c r="A25" s="95" t="inlineStr">
         <is>
           <t>us30:RS3</t>
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>79.05</v>
+        <v>86.3</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>79.05</v>
@@ -9185,9 +9185,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C26" s="91" t="inlineStr">
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>7.75</v>
+        <v>4.17</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>7.75</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>16.05</v>
+        <v>15.29</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>16.05</v>
@@ -9531,13 +9531,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="76" t="inlineStr">
+      <c r="A29" s="96" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>54.41</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>54.41</v>
@@ -10977,9 +10977,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B42" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C42" s="91" t="inlineStr">
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>5.55</v>
+        <v>6.44</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>5.55</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>11.19</v>
+        <v>8.82</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>11.19</v>
@@ -11323,13 +11323,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="95" t="inlineStr">
+      <c r="A45" s="76" t="inlineStr">
         <is>
           <t>fr40:RS5</t>
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>93.34</v>
+        <v>84.89</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>93.34</v>
@@ -11577,7 +11577,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>8.32</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>9.92</v>
@@ -11674,7 +11674,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>22.01</v>
+        <v>22.74</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>21.14</v>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>64.04000000000001</v>
+        <v>75.37</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>89.53</v>
@@ -11864,14 +11864,14 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：sensex:RS10:31.52&lt;=39</t>
+          <t>今日买报：us500:RS2:16.07&lt;=22;ixic:RS2:8.7&lt;=38;sensex:RS10:31.52&lt;=39</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:74.31&gt;=73;vn:RS3:85.3&gt;=85;fr40:RS5:93.34&gt;=87;dax30:RNG120:22.01&gt;=20</t>
+          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:74.31&gt;=73;us30:RS3:86.3&gt;=85;vn:RS3:85.3&gt;=85;dax30:RNG120:22.74&gt;=20</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -6342,152 +6342,152 @@
       </c>
       <c r="B1" s="77" t="inlineStr">
         <is>
+          <t>250128</t>
+        </is>
+      </c>
+      <c r="C1" s="77" t="inlineStr">
+        <is>
           <t>250127</t>
         </is>
       </c>
-      <c r="C1" s="77" t="inlineStr">
+      <c r="D1" s="77" t="inlineStr">
         <is>
           <t>250126</t>
         </is>
       </c>
-      <c r="D1" s="77" t="inlineStr">
+      <c r="E1" s="77" t="inlineStr">
         <is>
           <t>250124</t>
         </is>
       </c>
-      <c r="E1" s="77" t="inlineStr">
+      <c r="F1" s="77" t="inlineStr">
         <is>
           <t>250123</t>
         </is>
       </c>
-      <c r="F1" s="77" t="inlineStr">
+      <c r="G1" s="77" t="inlineStr">
         <is>
           <t>250122</t>
         </is>
       </c>
-      <c r="G1" s="77" t="inlineStr">
+      <c r="H1" s="77" t="inlineStr">
         <is>
           <t>250121</t>
         </is>
       </c>
-      <c r="H1" s="77" t="inlineStr">
+      <c r="I1" s="77" t="inlineStr">
         <is>
           <t>250120</t>
         </is>
       </c>
-      <c r="I1" s="77" t="inlineStr">
+      <c r="J1" s="77" t="inlineStr">
         <is>
           <t>250119</t>
         </is>
       </c>
-      <c r="J1" s="77" t="inlineStr">
+      <c r="K1" s="77" t="inlineStr">
         <is>
           <t>250117</t>
         </is>
       </c>
-      <c r="K1" s="77" t="inlineStr">
+      <c r="L1" s="77" t="inlineStr">
         <is>
           <t>250116</t>
         </is>
       </c>
-      <c r="L1" s="77" t="inlineStr">
+      <c r="M1" s="77" t="inlineStr">
         <is>
           <t>250115</t>
         </is>
       </c>
-      <c r="M1" s="77" t="inlineStr">
+      <c r="N1" s="77" t="inlineStr">
         <is>
           <t>250114</t>
         </is>
       </c>
-      <c r="N1" s="77" t="inlineStr">
+      <c r="O1" s="77" t="inlineStr">
         <is>
           <t>250113</t>
         </is>
       </c>
-      <c r="O1" s="77" t="inlineStr">
+      <c r="P1" s="77" t="inlineStr">
         <is>
           <t>250112</t>
         </is>
       </c>
-      <c r="P1" s="77" t="inlineStr">
+      <c r="Q1" s="77" t="inlineStr">
         <is>
           <t>250110</t>
         </is>
       </c>
-      <c r="Q1" s="77" t="inlineStr">
+      <c r="R1" s="77" t="inlineStr">
         <is>
           <t>250109</t>
         </is>
       </c>
-      <c r="R1" s="77" t="inlineStr">
+      <c r="S1" s="77" t="inlineStr">
         <is>
           <t>250108</t>
         </is>
       </c>
-      <c r="S1" s="77" t="inlineStr">
+      <c r="T1" s="77" t="inlineStr">
         <is>
           <t>250107</t>
         </is>
       </c>
-      <c r="T1" s="77" t="inlineStr">
+      <c r="U1" s="77" t="inlineStr">
         <is>
           <t>250106</t>
         </is>
       </c>
-      <c r="U1" s="77" t="inlineStr">
+      <c r="V1" s="77" t="inlineStr">
         <is>
           <t>250105</t>
         </is>
       </c>
-      <c r="V1" s="77" t="inlineStr">
+      <c r="W1" s="77" t="inlineStr">
         <is>
           <t>250103</t>
         </is>
       </c>
-      <c r="W1" s="77" t="inlineStr">
+      <c r="X1" s="77" t="inlineStr">
         <is>
           <t>250102</t>
         </is>
       </c>
-      <c r="X1" s="77" t="inlineStr">
+      <c r="Y1" s="77" t="inlineStr">
         <is>
           <t>250101</t>
         </is>
       </c>
-      <c r="Y1" s="77" t="inlineStr">
+      <c r="Z1" s="77" t="inlineStr">
         <is>
           <t>241231</t>
         </is>
       </c>
-      <c r="Z1" s="77" t="inlineStr">
+      <c r="AA1" s="77" t="inlineStr">
         <is>
           <t>241230</t>
         </is>
       </c>
-      <c r="AA1" s="77" t="inlineStr">
+      <c r="AB1" s="77" t="inlineStr">
         <is>
           <t>241229</t>
         </is>
       </c>
-      <c r="AB1" s="77" t="inlineStr">
+      <c r="AC1" s="77" t="inlineStr">
         <is>
           <t>241227</t>
         </is>
       </c>
-      <c r="AC1" s="77" t="inlineStr">
+      <c r="AD1" s="77" t="inlineStr">
         <is>
           <t>241226</t>
         </is>
       </c>
-      <c r="AD1" s="77" t="inlineStr">
+      <c r="AE1" s="77" t="inlineStr">
         <is>
           <t>241225</t>
-        </is>
-      </c>
-      <c r="AE1" s="77" t="inlineStr">
-        <is>
-          <t>241224</t>
         </is>
       </c>
     </row>
@@ -6512,114 +6512,114 @@
           <t>red</t>
         </is>
       </c>
-      <c r="E2" s="92" t="inlineStr">
+      <c r="E2" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F2" s="93" t="inlineStr">
+      <c r="G2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G2" s="92" t="inlineStr">
+      <c r="H2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H2" s="92" t="inlineStr">
+      <c r="I2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I2" s="92" t="inlineStr">
+      <c r="J2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J2" s="92" t="inlineStr">
+      <c r="K2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K2" s="92" t="inlineStr">
+      <c r="L2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L2" s="92" t="inlineStr">
+      <c r="M2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M2" s="92" t="inlineStr">
+      <c r="N2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N2" s="92" t="inlineStr">
+      <c r="O2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O2" s="93" t="inlineStr">
+      <c r="P2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P2" s="93" t="inlineStr">
+      <c r="Q2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q2" s="92" t="inlineStr">
+      <c r="R2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R2" s="92" t="inlineStr">
+      <c r="S2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S2" s="92" t="inlineStr">
+      <c r="T2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T2" s="93" t="inlineStr">
+      <c r="U2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U2" s="93" t="inlineStr">
+      <c r="V2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V2" s="93" t="inlineStr">
+      <c r="W2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W2" s="93" t="inlineStr">
+      <c r="X2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X2" s="93" t="inlineStr">
+      <c r="Y2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y2" s="93" t="inlineStr">
+      <c r="Z2" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="Z2" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AA2" s="91" t="inlineStr">
@@ -6658,91 +6658,91 @@
         <v>-0.65</v>
       </c>
       <c r="C3" s="94" t="n">
-        <v>-0.83</v>
+        <v>-0.65</v>
       </c>
       <c r="D3" s="94" t="n">
         <v>-0.83</v>
       </c>
       <c r="E3" s="94" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="F3" s="94" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F3" s="94" t="n">
+      <c r="G3" s="94" t="n">
         <v>-2.21</v>
       </c>
-      <c r="G3" s="94" t="n">
+      <c r="H3" s="94" t="n">
         <v>-2.4</v>
       </c>
-      <c r="H3" s="94" t="n">
+      <c r="I3" s="94" t="n">
         <v>-1.68</v>
-      </c>
-      <c r="I3" s="94" t="n">
-        <v>-1.17</v>
       </c>
       <c r="J3" s="94" t="n">
         <v>-1.17</v>
       </c>
       <c r="K3" s="94" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="L3" s="94" t="n">
         <v>-2.02</v>
       </c>
-      <c r="L3" s="94" t="n">
+      <c r="M3" s="94" t="n">
         <v>-1.79</v>
       </c>
-      <c r="M3" s="94" t="n">
+      <c r="N3" s="94" t="n">
         <v>-0.83</v>
       </c>
-      <c r="N3" s="94" t="n">
+      <c r="O3" s="94" t="n">
         <v>-3.09</v>
-      </c>
-      <c r="O3" s="94" t="n">
-        <v>-0.03</v>
       </c>
       <c r="P3" s="94" t="n">
         <v>-0.03</v>
       </c>
       <c r="Q3" s="94" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="R3" s="94" t="n">
         <v>0.26</v>
       </c>
-      <c r="R3" s="94" t="n">
+      <c r="S3" s="94" t="n">
         <v>0.9</v>
       </c>
-      <c r="S3" s="94" t="n">
+      <c r="T3" s="94" t="n">
         <v>-1.66</v>
       </c>
-      <c r="T3" s="94" t="n">
+      <c r="U3" s="94" t="n">
         <v>-0.34</v>
-      </c>
-      <c r="U3" s="94" t="n">
-        <v>-2.74</v>
       </c>
       <c r="V3" s="94" t="n">
         <v>-2.74</v>
       </c>
       <c r="W3" s="94" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="X3" s="94" t="n">
         <v>0.11</v>
-      </c>
-      <c r="X3" s="94" t="n">
-        <v>-3.95</v>
       </c>
       <c r="Y3" s="94" t="n">
         <v>-3.95</v>
       </c>
       <c r="Z3" s="94" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="AA3" s="94" t="n">
         <v>2.12</v>
-      </c>
-      <c r="AA3" s="94" t="n">
-        <v>10.12</v>
       </c>
       <c r="AB3" s="94" t="n">
         <v>10.12</v>
       </c>
       <c r="AC3" s="94" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="AD3" s="94" t="n">
         <v>13.23</v>
       </c>
-      <c r="AD3" s="94" t="n">
+      <c r="AE3" s="94" t="n">
         <v>17.16</v>
-      </c>
-      <c r="AE3" s="94" t="n">
-        <v>18.53</v>
       </c>
     </row>
     <row r="4">
@@ -6755,91 +6755,91 @@
         <v>10.61</v>
       </c>
       <c r="C4" s="94" t="n">
-        <v>12.97</v>
+        <v>10.61</v>
       </c>
       <c r="D4" s="94" t="n">
         <v>12.97</v>
       </c>
       <c r="E4" s="94" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="F4" s="94" t="n">
         <v>11.7</v>
       </c>
-      <c r="F4" s="94" t="n">
+      <c r="G4" s="94" t="n">
         <v>11.16</v>
       </c>
-      <c r="G4" s="94" t="n">
+      <c r="H4" s="94" t="n">
         <v>12.33</v>
       </c>
-      <c r="H4" s="94" t="n">
+      <c r="I4" s="94" t="n">
         <v>11.8</v>
-      </c>
-      <c r="I4" s="94" t="n">
-        <v>11.2</v>
       </c>
       <c r="J4" s="94" t="n">
         <v>11.2</v>
       </c>
       <c r="K4" s="94" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="L4" s="94" t="n">
         <v>9.17</v>
       </c>
-      <c r="L4" s="94" t="n">
+      <c r="M4" s="94" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="M4" s="94" t="n">
+      <c r="N4" s="94" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="N4" s="94" t="n">
+      <c r="O4" s="94" t="n">
         <v>6.68</v>
-      </c>
-      <c r="O4" s="94" t="n">
-        <v>6.46</v>
       </c>
       <c r="P4" s="94" t="n">
         <v>6.46</v>
       </c>
       <c r="Q4" s="94" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="R4" s="94" t="n">
         <v>7.98</v>
       </c>
-      <c r="R4" s="94" t="n">
+      <c r="S4" s="94" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="S4" s="94" t="n">
+      <c r="T4" s="94" t="n">
         <v>8.73</v>
       </c>
-      <c r="T4" s="94" t="n">
+      <c r="U4" s="94" t="n">
         <v>9.1</v>
-      </c>
-      <c r="U4" s="94" t="n">
-        <v>8.52</v>
       </c>
       <c r="V4" s="94" t="n">
         <v>8.52</v>
       </c>
       <c r="W4" s="94" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="X4" s="94" t="n">
         <v>11.64</v>
-      </c>
-      <c r="X4" s="94" t="n">
-        <v>13.62</v>
       </c>
       <c r="Y4" s="94" t="n">
         <v>13.62</v>
       </c>
       <c r="Z4" s="94" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="AA4" s="94" t="n">
         <v>15.21</v>
-      </c>
-      <c r="AA4" s="94" t="n">
-        <v>14.01</v>
       </c>
       <c r="AB4" s="94" t="n">
         <v>14.01</v>
       </c>
       <c r="AC4" s="94" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="AD4" s="94" t="n">
         <v>13.38</v>
       </c>
-      <c r="AD4" s="94" t="n">
+      <c r="AE4" s="94" t="n">
         <v>13.31</v>
-      </c>
-      <c r="AE4" s="94" t="n">
-        <v>14.36</v>
       </c>
     </row>
     <row r="5">
@@ -6852,91 +6852,91 @@
         <v>67.42</v>
       </c>
       <c r="C5" s="94" t="n">
-        <v>71.19</v>
+        <v>67.42</v>
       </c>
       <c r="D5" s="94" t="n">
         <v>71.19</v>
       </c>
       <c r="E5" s="94" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="F5" s="94" t="n">
         <v>50.98</v>
       </c>
-      <c r="F5" s="94" t="n">
+      <c r="G5" s="94" t="n">
         <v>25.28</v>
       </c>
-      <c r="G5" s="94" t="n">
+      <c r="H5" s="94" t="n">
         <v>65.31999999999999</v>
       </c>
-      <c r="H5" s="94" t="n">
+      <c r="I5" s="94" t="n">
         <v>69.8</v>
-      </c>
-      <c r="I5" s="94" t="n">
-        <v>67.65000000000001</v>
       </c>
       <c r="J5" s="94" t="n">
         <v>67.65000000000001</v>
       </c>
       <c r="K5" s="94" t="n">
+        <v>67.65000000000001</v>
+      </c>
+      <c r="L5" s="94" t="n">
         <v>63.76</v>
       </c>
-      <c r="L5" s="94" t="n">
+      <c r="M5" s="94" t="n">
         <v>58.67</v>
       </c>
-      <c r="M5" s="94" t="n">
+      <c r="N5" s="94" t="n">
         <v>68.65000000000001</v>
       </c>
-      <c r="N5" s="94" t="n">
+      <c r="O5" s="94" t="n">
         <v>8.279999999999999</v>
-      </c>
-      <c r="O5" s="94" t="n">
-        <v>9.460000000000001</v>
       </c>
       <c r="P5" s="94" t="n">
         <v>9.460000000000001</v>
       </c>
       <c r="Q5" s="94" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="R5" s="94" t="n">
         <v>19.81</v>
       </c>
-      <c r="R5" s="94" t="n">
+      <c r="S5" s="94" t="n">
         <v>29.11</v>
       </c>
-      <c r="S5" s="94" t="n">
+      <c r="T5" s="94" t="n">
         <v>28.48</v>
       </c>
-      <c r="T5" s="94" t="n">
+      <c r="U5" s="94" t="n">
         <v>4.01</v>
-      </c>
-      <c r="U5" s="94" t="n">
-        <v>4.21</v>
       </c>
       <c r="V5" s="94" t="n">
         <v>4.21</v>
       </c>
       <c r="W5" s="94" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="X5" s="94" t="n">
         <v>6.55</v>
-      </c>
-      <c r="X5" s="94" t="n">
-        <v>18.7</v>
       </c>
       <c r="Y5" s="94" t="n">
         <v>18.7</v>
       </c>
       <c r="Z5" s="94" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AA5" s="94" t="n">
         <v>81.11</v>
-      </c>
-      <c r="AA5" s="94" t="n">
-        <v>73.47</v>
       </c>
       <c r="AB5" s="94" t="n">
         <v>73.47</v>
       </c>
       <c r="AC5" s="94" t="n">
+        <v>73.47</v>
+      </c>
+      <c r="AD5" s="94" t="n">
         <v>71.25</v>
       </c>
-      <c r="AD5" s="94" t="n">
+      <c r="AE5" s="94" t="n">
         <v>67.02</v>
-      </c>
-      <c r="AE5" s="94" t="n">
-        <v>67.27</v>
       </c>
     </row>
     <row r="6">
@@ -6950,124 +6950,124 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C6" s="91" t="inlineStr">
+      <c r="C6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D6" s="91" t="inlineStr">
+      <c r="E6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E6" s="93" t="inlineStr">
+      <c r="F6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F6" s="91" t="inlineStr">
+      <c r="G6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G6" s="91" t="inlineStr">
+      <c r="H6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H6" s="92" t="inlineStr">
+      <c r="I6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I6" s="92" t="inlineStr">
+      <c r="J6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J6" s="92" t="inlineStr">
+      <c r="K6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K6" s="93" t="inlineStr">
+      <c r="L6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L6" s="91" t="inlineStr">
+      <c r="M6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M6" s="91" t="inlineStr">
+      <c r="N6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N6" s="92" t="inlineStr">
+      <c r="O6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O6" s="92" t="inlineStr">
+      <c r="P6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P6" s="92" t="inlineStr">
+      <c r="Q6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q6" s="92" t="inlineStr">
+      <c r="R6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R6" s="92" t="inlineStr">
+      <c r="S6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S6" s="92" t="inlineStr">
+      <c r="T6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T6" s="93" t="inlineStr">
+      <c r="U6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U6" s="93" t="inlineStr">
+      <c r="V6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V6" s="93" t="inlineStr">
+      <c r="W6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W6" s="93" t="inlineStr">
+      <c r="X6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X6" s="93" t="inlineStr">
+      <c r="Y6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y6" s="93" t="inlineStr">
+      <c r="Z6" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="Z6" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AA6" s="91" t="inlineStr">
@@ -7106,91 +7106,91 @@
         <v>1.63</v>
       </c>
       <c r="C7" s="94" t="n">
-        <v>0.55</v>
+        <v>1.63</v>
       </c>
       <c r="D7" s="94" t="n">
         <v>0.55</v>
       </c>
       <c r="E7" s="94" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F7" s="94" t="n">
         <v>0.76</v>
       </c>
-      <c r="F7" s="94" t="n">
+      <c r="G7" s="94" t="n">
         <v>-0</v>
       </c>
-      <c r="G7" s="94" t="n">
+      <c r="H7" s="94" t="n">
         <v>-1.04</v>
       </c>
-      <c r="H7" s="94" t="n">
+      <c r="I7" s="94" t="n">
         <v>-2.32</v>
-      </c>
-      <c r="I7" s="94" t="n">
-        <v>-1.2</v>
       </c>
       <c r="J7" s="94" t="n">
         <v>-1.2</v>
       </c>
       <c r="K7" s="94" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="L7" s="94" t="n">
         <v>-2.32</v>
       </c>
-      <c r="L7" s="94" t="n">
+      <c r="M7" s="94" t="n">
         <v>-0.83</v>
       </c>
-      <c r="M7" s="94" t="n">
+      <c r="N7" s="94" t="n">
         <v>-1.86</v>
       </c>
-      <c r="N7" s="94" t="n">
+      <c r="O7" s="94" t="n">
         <v>-2.7</v>
-      </c>
-      <c r="O7" s="94" t="n">
-        <v>8.130000000000001</v>
       </c>
       <c r="P7" s="94" t="n">
         <v>8.130000000000001</v>
       </c>
       <c r="Q7" s="94" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="R7" s="94" t="n">
         <v>9.789999999999999</v>
       </c>
-      <c r="R7" s="94" t="n">
+      <c r="S7" s="94" t="n">
         <v>7.38</v>
       </c>
-      <c r="S7" s="94" t="n">
+      <c r="T7" s="94" t="n">
         <v>4.27</v>
       </c>
-      <c r="T7" s="94" t="n">
+      <c r="U7" s="94" t="n">
         <v>4.43</v>
-      </c>
-      <c r="U7" s="94" t="n">
-        <v>-1.29</v>
       </c>
       <c r="V7" s="94" t="n">
         <v>-1.29</v>
       </c>
       <c r="W7" s="94" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="X7" s="94" t="n">
         <v>-4.26</v>
-      </c>
-      <c r="X7" s="94" t="n">
-        <v>-3.42</v>
       </c>
       <c r="Y7" s="94" t="n">
         <v>-3.42</v>
       </c>
       <c r="Z7" s="94" t="n">
+        <v>-3.42</v>
+      </c>
+      <c r="AA7" s="94" t="n">
         <v>17</v>
-      </c>
-      <c r="AA7" s="94" t="n">
-        <v>37.64</v>
       </c>
       <c r="AB7" s="94" t="n">
         <v>37.64</v>
       </c>
       <c r="AC7" s="94" t="n">
+        <v>37.64</v>
+      </c>
+      <c r="AD7" s="94" t="n">
         <v>48.17</v>
       </c>
-      <c r="AD7" s="94" t="n">
+      <c r="AE7" s="94" t="n">
         <v>52.45</v>
-      </c>
-      <c r="AE7" s="94" t="n">
-        <v>52.02</v>
       </c>
     </row>
     <row r="8">
@@ -7203,91 +7203,91 @@
         <v>28.48</v>
       </c>
       <c r="C8" s="94" t="n">
-        <v>37.3</v>
+        <v>28.48</v>
       </c>
       <c r="D8" s="94" t="n">
         <v>37.3</v>
       </c>
       <c r="E8" s="94" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="F8" s="94" t="n">
         <v>36.53</v>
       </c>
-      <c r="F8" s="94" t="n">
+      <c r="G8" s="94" t="n">
         <v>35.49</v>
       </c>
-      <c r="G8" s="94" t="n">
+      <c r="H8" s="94" t="n">
         <v>36.76</v>
       </c>
-      <c r="H8" s="94" t="n">
+      <c r="I8" s="94" t="n">
         <v>35.74</v>
-      </c>
-      <c r="I8" s="94" t="n">
-        <v>33.95</v>
       </c>
       <c r="J8" s="94" t="n">
         <v>33.95</v>
       </c>
       <c r="K8" s="94" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="L8" s="94" t="n">
         <v>27.18</v>
       </c>
-      <c r="L8" s="94" t="n">
+      <c r="M8" s="94" t="n">
         <v>30.45</v>
       </c>
-      <c r="M8" s="94" t="n">
+      <c r="N8" s="94" t="n">
         <v>33.5</v>
       </c>
-      <c r="N8" s="94" t="n">
+      <c r="O8" s="94" t="n">
         <v>30.62</v>
-      </c>
-      <c r="O8" s="94" t="n">
-        <v>29.85</v>
       </c>
       <c r="P8" s="94" t="n">
         <v>29.85</v>
       </c>
       <c r="Q8" s="94" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="R8" s="94" t="n">
         <v>34.31</v>
       </c>
-      <c r="R8" s="94" t="n">
+      <c r="S8" s="94" t="n">
         <v>34.35</v>
       </c>
-      <c r="S8" s="94" t="n">
+      <c r="T8" s="94" t="n">
         <v>34.47</v>
       </c>
-      <c r="T8" s="94" t="n">
+      <c r="U8" s="94" t="n">
         <v>32.14</v>
-      </c>
-      <c r="U8" s="94" t="n">
-        <v>32.67</v>
       </c>
       <c r="V8" s="94" t="n">
         <v>32.67</v>
       </c>
       <c r="W8" s="94" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="X8" s="94" t="n">
         <v>37.96</v>
-      </c>
-      <c r="X8" s="94" t="n">
-        <v>41.51</v>
       </c>
       <c r="Y8" s="94" t="n">
         <v>41.51</v>
       </c>
       <c r="Z8" s="94" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="AA8" s="94" t="n">
         <v>47.84</v>
-      </c>
-      <c r="AA8" s="94" t="n">
-        <v>45.14</v>
       </c>
       <c r="AB8" s="94" t="n">
         <v>45.14</v>
       </c>
       <c r="AC8" s="94" t="n">
+        <v>45.14</v>
+      </c>
+      <c r="AD8" s="94" t="n">
         <v>46.9</v>
       </c>
-      <c r="AD8" s="94" t="n">
+      <c r="AE8" s="94" t="n">
         <v>43.37</v>
-      </c>
-      <c r="AE8" s="94" t="n">
-        <v>42.4</v>
       </c>
     </row>
     <row r="9">
@@ -7300,91 +7300,91 @@
         <v>35.78</v>
       </c>
       <c r="C9" s="94" t="n">
-        <v>56.52</v>
+        <v>35.78</v>
       </c>
       <c r="D9" s="94" t="n">
         <v>56.52</v>
       </c>
       <c r="E9" s="94" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="F9" s="94" t="n">
         <v>45.32</v>
       </c>
-      <c r="F9" s="94" t="n">
+      <c r="G9" s="94" t="n">
         <v>57.96</v>
       </c>
-      <c r="G9" s="94" t="n">
+      <c r="H9" s="94" t="n">
         <v>59.34</v>
       </c>
-      <c r="H9" s="94" t="n">
+      <c r="I9" s="94" t="n">
         <v>51.65</v>
-      </c>
-      <c r="I9" s="94" t="n">
-        <v>49.39</v>
       </c>
       <c r="J9" s="94" t="n">
         <v>49.39</v>
       </c>
       <c r="K9" s="94" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="L9" s="94" t="n">
         <v>40.47</v>
       </c>
-      <c r="L9" s="94" t="n">
+      <c r="M9" s="94" t="n">
         <v>59.12</v>
       </c>
-      <c r="M9" s="94" t="n">
+      <c r="N9" s="94" t="n">
         <v>63.67</v>
       </c>
-      <c r="N9" s="94" t="n">
+      <c r="O9" s="94" t="n">
         <v>34.88</v>
-      </c>
-      <c r="O9" s="94" t="n">
-        <v>32.56</v>
       </c>
       <c r="P9" s="94" t="n">
         <v>32.56</v>
       </c>
       <c r="Q9" s="94" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="R9" s="94" t="n">
         <v>40.33</v>
       </c>
-      <c r="R9" s="94" t="n">
+      <c r="S9" s="94" t="n">
         <v>43.12</v>
       </c>
-      <c r="S9" s="94" t="n">
+      <c r="T9" s="94" t="n">
         <v>43.39</v>
       </c>
-      <c r="T9" s="94" t="n">
+      <c r="U9" s="94" t="n">
         <v>16.15</v>
-      </c>
-      <c r="U9" s="94" t="n">
-        <v>16.9</v>
       </c>
       <c r="V9" s="94" t="n">
         <v>16.9</v>
       </c>
       <c r="W9" s="94" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="X9" s="94" t="n">
         <v>20.18</v>
-      </c>
-      <c r="X9" s="94" t="n">
-        <v>32.85</v>
       </c>
       <c r="Y9" s="94" t="n">
         <v>32.85</v>
       </c>
       <c r="Z9" s="94" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="AA9" s="94" t="n">
         <v>62.46</v>
-      </c>
-      <c r="AA9" s="94" t="n">
-        <v>60.63</v>
       </c>
       <c r="AB9" s="94" t="n">
         <v>60.63</v>
       </c>
       <c r="AC9" s="94" t="n">
+        <v>60.63</v>
+      </c>
+      <c r="AD9" s="94" t="n">
         <v>72.27</v>
       </c>
-      <c r="AD9" s="94" t="n">
+      <c r="AE9" s="94" t="n">
         <v>66.34999999999999</v>
-      </c>
-      <c r="AE9" s="94" t="n">
-        <v>64.23999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -7398,124 +7398,124 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C10" s="91" t="inlineStr">
+      <c r="C10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D10" s="91" t="inlineStr">
+      <c r="E10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E10" s="91" t="inlineStr">
+      <c r="F10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F10" s="91" t="inlineStr">
+      <c r="G10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G10" s="91" t="inlineStr">
+      <c r="H10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H10" s="91" t="inlineStr">
+      <c r="I10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I10" s="91" t="inlineStr">
+      <c r="J10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J10" s="91" t="inlineStr">
+      <c r="K10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K10" s="92" t="inlineStr">
+      <c r="L10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L10" s="92" t="inlineStr">
+      <c r="M10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M10" s="91" t="inlineStr">
+      <c r="N10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N10" s="92" t="inlineStr">
+      <c r="O10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O10" s="92" t="inlineStr">
+      <c r="P10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P10" s="92" t="inlineStr">
+      <c r="Q10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q10" s="92" t="inlineStr">
+      <c r="R10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R10" s="92" t="inlineStr">
+      <c r="S10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S10" s="92" t="inlineStr">
+      <c r="T10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T10" s="93" t="inlineStr">
+      <c r="U10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U10" s="93" t="inlineStr">
+      <c r="V10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V10" s="93" t="inlineStr">
+      <c r="W10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W10" s="93" t="inlineStr">
+      <c r="X10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X10" s="93" t="inlineStr">
+      <c r="Y10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y10" s="93" t="inlineStr">
+      <c r="Z10" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="Z10" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AA10" s="92" t="inlineStr">
@@ -7554,91 +7554,91 @@
         <v>-2.82</v>
       </c>
       <c r="C11" s="94" t="n">
-        <v>-1.97</v>
+        <v>-2.82</v>
       </c>
       <c r="D11" s="94" t="n">
         <v>-1.97</v>
       </c>
       <c r="E11" s="94" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="F11" s="94" t="n">
         <v>-2.71</v>
       </c>
-      <c r="F11" s="94" t="n">
+      <c r="G11" s="94" t="n">
         <v>-3.5</v>
       </c>
-      <c r="G11" s="94" t="n">
+      <c r="H11" s="94" t="n">
         <v>-5.24</v>
       </c>
-      <c r="H11" s="94" t="n">
+      <c r="I11" s="94" t="n">
         <v>-5.99</v>
-      </c>
-      <c r="I11" s="94" t="n">
-        <v>-4.96</v>
       </c>
       <c r="J11" s="94" t="n">
         <v>-4.96</v>
       </c>
       <c r="K11" s="94" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="L11" s="94" t="n">
         <v>-6.98</v>
       </c>
-      <c r="L11" s="94" t="n">
+      <c r="M11" s="94" t="n">
         <v>-8.08</v>
       </c>
-      <c r="M11" s="94" t="n">
+      <c r="N11" s="94" t="n">
         <v>-6.09</v>
       </c>
-      <c r="N11" s="94" t="n">
+      <c r="O11" s="94" t="n">
         <v>-9.69</v>
-      </c>
-      <c r="O11" s="94" t="n">
-        <v>-2.86</v>
       </c>
       <c r="P11" s="94" t="n">
         <v>-2.86</v>
       </c>
       <c r="Q11" s="94" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="R11" s="94" t="n">
         <v>-1.44</v>
       </c>
-      <c r="R11" s="94" t="n">
+      <c r="S11" s="94" t="n">
         <v>-3.72</v>
       </c>
-      <c r="S11" s="94" t="n">
+      <c r="T11" s="94" t="n">
         <v>-5.89</v>
       </c>
-      <c r="T11" s="94" t="n">
+      <c r="U11" s="94" t="n">
         <v>-4.13</v>
-      </c>
-      <c r="U11" s="94" t="n">
-        <v>-8.9</v>
       </c>
       <c r="V11" s="94" t="n">
         <v>-8.9</v>
       </c>
       <c r="W11" s="94" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="X11" s="94" t="n">
         <v>-9.630000000000001</v>
-      </c>
-      <c r="X11" s="94" t="n">
-        <v>-16.02</v>
       </c>
       <c r="Y11" s="94" t="n">
         <v>-16.02</v>
       </c>
       <c r="Z11" s="94" t="n">
+        <v>-16.02</v>
+      </c>
+      <c r="AA11" s="94" t="n">
         <v>1.43</v>
-      </c>
-      <c r="AA11" s="94" t="n">
-        <v>16.94</v>
       </c>
       <c r="AB11" s="94" t="n">
         <v>16.94</v>
       </c>
       <c r="AC11" s="94" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="AD11" s="94" t="n">
         <v>28.92</v>
       </c>
-      <c r="AD11" s="94" t="n">
+      <c r="AE11" s="94" t="n">
         <v>34.1</v>
-      </c>
-      <c r="AE11" s="94" t="n">
-        <v>37.03</v>
       </c>
     </row>
     <row r="12">
@@ -7651,91 +7651,91 @@
         <v>22.25</v>
       </c>
       <c r="C12" s="94" t="n">
-        <v>30.1</v>
+        <v>22.25</v>
       </c>
       <c r="D12" s="94" t="n">
         <v>30.1</v>
       </c>
       <c r="E12" s="94" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="F12" s="94" t="n">
         <v>27.98</v>
       </c>
-      <c r="F12" s="94" t="n">
+      <c r="G12" s="94" t="n">
         <v>26.6</v>
       </c>
-      <c r="G12" s="94" t="n">
+      <c r="H12" s="94" t="n">
         <v>28.46</v>
       </c>
-      <c r="H12" s="94" t="n">
+      <c r="I12" s="94" t="n">
         <v>27.49</v>
-      </c>
-      <c r="I12" s="94" t="n">
-        <v>23.68</v>
       </c>
       <c r="J12" s="94" t="n">
         <v>23.68</v>
       </c>
       <c r="K12" s="94" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="L12" s="94" t="n">
         <v>18.99</v>
       </c>
-      <c r="L12" s="94" t="n">
+      <c r="M12" s="94" t="n">
         <v>18.11</v>
       </c>
-      <c r="M12" s="94" t="n">
+      <c r="N12" s="94" t="n">
         <v>20.84</v>
       </c>
-      <c r="N12" s="94" t="n">
+      <c r="O12" s="94" t="n">
         <v>16.86</v>
-      </c>
-      <c r="O12" s="94" t="n">
-        <v>16.44</v>
       </c>
       <c r="P12" s="94" t="n">
         <v>16.44</v>
       </c>
       <c r="Q12" s="94" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="R12" s="94" t="n">
         <v>20.18</v>
       </c>
-      <c r="R12" s="94" t="n">
+      <c r="S12" s="94" t="n">
         <v>19.29</v>
       </c>
-      <c r="S12" s="94" t="n">
+      <c r="T12" s="94" t="n">
         <v>20.37</v>
       </c>
-      <c r="T12" s="94" t="n">
+      <c r="U12" s="94" t="n">
         <v>21.99</v>
-      </c>
-      <c r="U12" s="94" t="n">
-        <v>22.02</v>
       </c>
       <c r="V12" s="94" t="n">
         <v>22.02</v>
       </c>
       <c r="W12" s="94" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="X12" s="94" t="n">
         <v>26.5</v>
-      </c>
-      <c r="X12" s="94" t="n">
-        <v>29.36</v>
       </c>
       <c r="Y12" s="94" t="n">
         <v>29.36</v>
       </c>
       <c r="Z12" s="94" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="AA12" s="94" t="n">
         <v>33.94</v>
-      </c>
-      <c r="AA12" s="94" t="n">
-        <v>32.82</v>
       </c>
       <c r="AB12" s="94" t="n">
         <v>32.82</v>
       </c>
       <c r="AC12" s="94" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="AD12" s="94" t="n">
         <v>32.72</v>
       </c>
-      <c r="AD12" s="94" t="n">
+      <c r="AE12" s="94" t="n">
         <v>30.82</v>
-      </c>
-      <c r="AE12" s="94" t="n">
-        <v>31.49</v>
       </c>
     </row>
     <row r="13">
@@ -7748,91 +7748,91 @@
         <v>31.12</v>
       </c>
       <c r="C13" s="94" t="n">
-        <v>77.11</v>
+        <v>31.12</v>
       </c>
       <c r="D13" s="94" t="n">
         <v>77.11</v>
       </c>
       <c r="E13" s="94" t="n">
+        <v>77.11</v>
+      </c>
+      <c r="F13" s="94" t="n">
         <v>55.59</v>
       </c>
-      <c r="F13" s="94" t="n">
+      <c r="G13" s="94" t="n">
         <v>66.94</v>
       </c>
-      <c r="G13" s="94" t="n">
+      <c r="H13" s="94" t="n">
         <v>83.7</v>
       </c>
-      <c r="H13" s="94" t="n">
+      <c r="I13" s="94" t="n">
         <v>81.64</v>
-      </c>
-      <c r="I13" s="94" t="n">
-        <v>68.69</v>
       </c>
       <c r="J13" s="94" t="n">
         <v>68.69</v>
       </c>
       <c r="K13" s="94" t="n">
+        <v>68.69</v>
+      </c>
+      <c r="L13" s="94" t="n">
         <v>60.87</v>
       </c>
-      <c r="L13" s="94" t="n">
+      <c r="M13" s="94" t="n">
         <v>54.48</v>
       </c>
-      <c r="M13" s="94" t="n">
+      <c r="N13" s="94" t="n">
         <v>78.59</v>
       </c>
-      <c r="N13" s="94" t="n">
+      <c r="O13" s="94" t="n">
         <v>21.44</v>
-      </c>
-      <c r="O13" s="94" t="n">
-        <v>9.02</v>
       </c>
       <c r="P13" s="94" t="n">
         <v>9.02</v>
       </c>
       <c r="Q13" s="94" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="R13" s="94" t="n">
         <v>18.81</v>
       </c>
-      <c r="R13" s="94" t="n">
+      <c r="S13" s="94" t="n">
         <v>14.94</v>
       </c>
-      <c r="S13" s="94" t="n">
+      <c r="T13" s="94" t="n">
         <v>20.9</v>
       </c>
-      <c r="T13" s="94" t="n">
+      <c r="U13" s="94" t="n">
         <v>2.46</v>
-      </c>
-      <c r="U13" s="94" t="n">
-        <v>2.51</v>
       </c>
       <c r="V13" s="94" t="n">
         <v>2.51</v>
       </c>
       <c r="W13" s="94" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="X13" s="94" t="n">
         <v>3.75</v>
-      </c>
-      <c r="X13" s="94" t="n">
-        <v>9.470000000000001</v>
       </c>
       <c r="Y13" s="94" t="n">
         <v>9.470000000000001</v>
       </c>
       <c r="Z13" s="94" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="AA13" s="94" t="n">
         <v>49.72</v>
-      </c>
-      <c r="AA13" s="94" t="n">
-        <v>46.46</v>
       </c>
       <c r="AB13" s="94" t="n">
         <v>46.46</v>
       </c>
       <c r="AC13" s="94" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="AD13" s="94" t="n">
         <v>54.92</v>
       </c>
-      <c r="AD13" s="94" t="n">
+      <c r="AE13" s="94" t="n">
         <v>42.96</v>
-      </c>
-      <c r="AE13" s="94" t="n">
-        <v>57.53</v>
       </c>
     </row>
     <row r="14">
@@ -7856,140 +7856,136 @@
           <t>red</t>
         </is>
       </c>
-      <c r="E14" s="92" t="inlineStr">
+      <c r="E14" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F14" s="92" t="inlineStr">
+      <c r="G14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G14" s="91" t="inlineStr">
+      <c r="H14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H14" s="91" t="inlineStr">
+      <c r="I14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I14" s="91" t="inlineStr">
+      <c r="J14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J14" s="91" t="inlineStr">
+      <c r="K14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K14" s="91" t="inlineStr">
+      <c r="L14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L14" s="92" t="inlineStr">
+      <c r="M14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M14" s="92" t="inlineStr">
+      <c r="N14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N14" s="93" t="inlineStr">
+      <c r="O14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O14" s="93" t="inlineStr">
+      <c r="P14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P14" s="93" t="inlineStr">
+      <c r="Q14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q14" s="93" t="inlineStr">
+      <c r="R14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R14" s="93" t="inlineStr">
+      <c r="S14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S14" s="93" t="inlineStr">
+      <c r="T14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T14" s="93" t="inlineStr">
+      <c r="U14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U14" s="93" t="inlineStr">
+      <c r="V14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V14" s="93" t="inlineStr">
+      <c r="W14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W14" s="93" t="inlineStr">
+      <c r="X14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X14" s="91" t="inlineStr">
+      <c r="Y14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y14" s="91" t="inlineStr">
+      <c r="Z14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z14" s="91" t="inlineStr">
+      <c r="AA14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA14" s="91" t="inlineStr">
+      <c r="AB14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB14" s="91" t="inlineStr">
+      <c r="AC14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC14" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD14" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE14" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
+      <c r="AD14" s="92" t="n">
+        <v/>
+      </c>
+      <c r="AE14" s="92" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -7999,94 +7995,94 @@
         </is>
       </c>
       <c r="B15" s="94" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="C15" s="94" t="n">
         <v>-0.9</v>
-      </c>
-      <c r="C15" s="94" t="n">
-        <v>-3.07</v>
       </c>
       <c r="D15" s="94" t="n">
         <v>-3.07</v>
       </c>
       <c r="E15" s="94" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="F15" s="94" t="n">
         <v>-4.36</v>
       </c>
-      <c r="F15" s="94" t="n">
+      <c r="G15" s="94" t="n">
         <v>-3.94</v>
       </c>
-      <c r="G15" s="94" t="n">
+      <c r="H15" s="94" t="n">
         <v>-1.87</v>
       </c>
-      <c r="H15" s="94" t="n">
+      <c r="I15" s="94" t="n">
         <v>-4.02</v>
-      </c>
-      <c r="I15" s="94" t="n">
-        <v>-4.46</v>
       </c>
       <c r="J15" s="94" t="n">
         <v>-4.46</v>
       </c>
       <c r="K15" s="94" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="L15" s="94" t="n">
         <v>-4.67</v>
       </c>
-      <c r="L15" s="94" t="n">
+      <c r="M15" s="94" t="n">
         <v>-7.3</v>
       </c>
-      <c r="M15" s="94" t="n">
+      <c r="N15" s="94" t="n">
         <v>-4.28</v>
       </c>
-      <c r="N15" s="94" t="n">
+      <c r="O15" s="94" t="n">
         <v>-6.96</v>
-      </c>
-      <c r="O15" s="94" t="n">
-        <v>-6.17</v>
       </c>
       <c r="P15" s="94" t="n">
         <v>-6.17</v>
       </c>
       <c r="Q15" s="94" t="n">
+        <v>-6.17</v>
+      </c>
+      <c r="R15" s="94" t="n">
         <v>-8.779999999999999</v>
       </c>
-      <c r="R15" s="94" t="n">
+      <c r="S15" s="94" t="n">
         <v>-9.279999999999999</v>
       </c>
-      <c r="S15" s="94" t="n">
+      <c r="T15" s="94" t="n">
         <v>-5.76</v>
       </c>
-      <c r="T15" s="94" t="n">
+      <c r="U15" s="94" t="n">
         <v>-5.92</v>
-      </c>
-      <c r="U15" s="94" t="n">
-        <v>-14.46</v>
       </c>
       <c r="V15" s="94" t="n">
         <v>-14.46</v>
       </c>
       <c r="W15" s="94" t="n">
+        <v>-14.46</v>
+      </c>
+      <c r="X15" s="94" t="n">
         <v>-13.69</v>
-      </c>
-      <c r="X15" s="94" t="n">
-        <v>-9.289999999999999</v>
       </c>
       <c r="Y15" s="94" t="n">
         <v>-9.289999999999999</v>
       </c>
       <c r="Z15" s="94" t="n">
+        <v>-9.289999999999999</v>
+      </c>
+      <c r="AA15" s="94" t="n">
         <v>-10.7</v>
-      </c>
-      <c r="AA15" s="94" t="n">
-        <v>-4.94</v>
       </c>
       <c r="AB15" s="94" t="n">
         <v>-4.94</v>
       </c>
       <c r="AC15" s="94" t="n">
-        <v>-2.59</v>
+        <v>-4.94</v>
       </c>
       <c r="AD15" s="94" t="n">
-        <v>-2.59</v>
+        <v/>
       </c>
       <c r="AE15" s="94" t="n">
-        <v>-2.59</v>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -8096,94 +8092,94 @@
         </is>
       </c>
       <c r="B16" s="94" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="C16" s="94" t="n">
         <v>16.72</v>
-      </c>
-      <c r="C16" s="94" t="n">
-        <v>15.69</v>
       </c>
       <c r="D16" s="94" t="n">
         <v>15.69</v>
       </c>
       <c r="E16" s="94" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="F16" s="94" t="n">
         <v>15.87</v>
       </c>
-      <c r="F16" s="94" t="n">
+      <c r="G16" s="94" t="n">
         <v>14.74</v>
       </c>
-      <c r="G16" s="94" t="n">
+      <c r="H16" s="94" t="n">
         <v>18.13</v>
       </c>
-      <c r="H16" s="94" t="n">
+      <c r="I16" s="94" t="n">
         <v>17.18</v>
-      </c>
-      <c r="I16" s="94" t="n">
-        <v>13.13</v>
       </c>
       <c r="J16" s="94" t="n">
         <v>13.13</v>
       </c>
       <c r="K16" s="94" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="L16" s="94" t="n">
         <v>11.76</v>
       </c>
-      <c r="L16" s="94" t="n">
+      <c r="M16" s="94" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="M16" s="94" t="n">
+      <c r="N16" s="94" t="n">
         <v>10.35</v>
       </c>
-      <c r="N16" s="94" t="n">
+      <c r="O16" s="94" t="n">
         <v>6.16</v>
-      </c>
-      <c r="O16" s="94" t="n">
-        <v>7.47</v>
       </c>
       <c r="P16" s="94" t="n">
         <v>7.47</v>
       </c>
       <c r="Q16" s="94" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="R16" s="94" t="n">
         <v>8.529999999999999</v>
       </c>
-      <c r="R16" s="94" t="n">
+      <c r="S16" s="94" t="n">
         <v>7.02</v>
       </c>
-      <c r="S16" s="94" t="n">
+      <c r="T16" s="94" t="n">
         <v>6.31</v>
       </c>
-      <c r="T16" s="94" t="n">
+      <c r="U16" s="94" t="n">
         <v>10.41</v>
-      </c>
-      <c r="U16" s="94" t="n">
-        <v>13.1</v>
       </c>
       <c r="V16" s="94" t="n">
         <v>13.1</v>
       </c>
       <c r="W16" s="94" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="X16" s="94" t="n">
         <v>11.98</v>
-      </c>
-      <c r="X16" s="94" t="n">
-        <v>14.47</v>
       </c>
       <c r="Y16" s="94" t="n">
         <v>14.47</v>
       </c>
       <c r="Z16" s="94" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="AA16" s="94" t="n">
         <v>12.59</v>
-      </c>
-      <c r="AA16" s="94" t="n">
-        <v>11.44</v>
       </c>
       <c r="AB16" s="94" t="n">
         <v>11.44</v>
       </c>
       <c r="AC16" s="94" t="n">
-        <v>11.79</v>
+        <v>11.44</v>
       </c>
       <c r="AD16" s="94" t="n">
-        <v>11.79</v>
+        <v/>
       </c>
       <c r="AE16" s="94" t="n">
-        <v>11.79</v>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -8193,94 +8189,94 @@
         </is>
       </c>
       <c r="B17" s="94" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="C17" s="94" t="n">
         <v>74.31</v>
-      </c>
-      <c r="C17" s="94" t="n">
-        <v>69.52</v>
       </c>
       <c r="D17" s="94" t="n">
         <v>69.52</v>
       </c>
       <c r="E17" s="94" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F17" s="94" t="n">
         <v>50.12</v>
       </c>
-      <c r="F17" s="94" t="n">
+      <c r="G17" s="94" t="n">
         <v>55.82</v>
       </c>
-      <c r="G17" s="94" t="n">
+      <c r="H17" s="94" t="n">
         <v>86.87</v>
       </c>
-      <c r="H17" s="94" t="n">
+      <c r="I17" s="94" t="n">
         <v>82.95</v>
-      </c>
-      <c r="I17" s="94" t="n">
-        <v>70.41</v>
       </c>
       <c r="J17" s="94" t="n">
         <v>70.41</v>
       </c>
       <c r="K17" s="94" t="n">
+        <v>70.41</v>
+      </c>
+      <c r="L17" s="94" t="n">
         <v>67.17</v>
       </c>
-      <c r="L17" s="94" t="n">
+      <c r="M17" s="94" t="n">
         <v>51.86</v>
       </c>
-      <c r="M17" s="94" t="n">
+      <c r="N17" s="94" t="n">
         <v>46.63</v>
       </c>
-      <c r="N17" s="94" t="n">
+      <c r="O17" s="94" t="n">
         <v>7.26</v>
-      </c>
-      <c r="O17" s="94" t="n">
-        <v>10.43</v>
       </c>
       <c r="P17" s="94" t="n">
         <v>10.43</v>
       </c>
       <c r="Q17" s="94" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="R17" s="94" t="n">
         <v>15.01</v>
       </c>
-      <c r="R17" s="94" t="n">
+      <c r="S17" s="94" t="n">
         <v>16.18</v>
       </c>
-      <c r="S17" s="94" t="n">
+      <c r="T17" s="94" t="n">
         <v>21.65</v>
       </c>
-      <c r="T17" s="94" t="n">
+      <c r="U17" s="94" t="n">
         <v>34.02</v>
-      </c>
-      <c r="U17" s="94" t="n">
-        <v>39.01</v>
       </c>
       <c r="V17" s="94" t="n">
         <v>39.01</v>
       </c>
       <c r="W17" s="94" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="X17" s="94" t="n">
         <v>22.83</v>
-      </c>
-      <c r="X17" s="94" t="n">
-        <v>62.48</v>
       </c>
       <c r="Y17" s="94" t="n">
         <v>62.48</v>
       </c>
       <c r="Z17" s="94" t="n">
+        <v>62.48</v>
+      </c>
+      <c r="AA17" s="94" t="n">
         <v>60.29</v>
-      </c>
-      <c r="AA17" s="94" t="n">
-        <v>68.20999999999999</v>
       </c>
       <c r="AB17" s="94" t="n">
         <v>68.20999999999999</v>
       </c>
       <c r="AC17" s="94" t="n">
-        <v>69.3</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="AD17" s="94" t="n">
-        <v>69.3</v>
+        <v/>
       </c>
       <c r="AE17" s="94" t="n">
-        <v>69.3</v>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -8294,150 +8290,148 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="C18" s="91" t="inlineStr">
+      <c r="C18" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D18" s="91" t="inlineStr">
+      <c r="E18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E18" s="91" t="inlineStr">
+      <c r="F18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F18" s="91" t="inlineStr">
+      <c r="G18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G18" s="91" t="inlineStr">
+      <c r="H18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H18" s="91" t="inlineStr">
+      <c r="I18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I18" s="91" t="inlineStr">
+      <c r="J18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J18" s="91" t="inlineStr">
+      <c r="K18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K18" s="91" t="inlineStr">
+      <c r="L18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L18" s="91" t="inlineStr">
+      <c r="M18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M18" s="92" t="inlineStr">
+      <c r="N18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N18" s="93" t="inlineStr">
+      <c r="O18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O18" s="93" t="inlineStr">
+      <c r="P18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P18" s="93" t="inlineStr">
+      <c r="Q18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q18" s="92" t="inlineStr">
+      <c r="R18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R18" s="92" t="inlineStr">
+      <c r="S18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S18" s="93" t="inlineStr">
+      <c r="T18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T18" s="91" t="inlineStr">
+      <c r="U18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U18" s="92" t="inlineStr">
+      <c r="V18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V18" s="92" t="inlineStr">
+      <c r="W18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W18" s="93" t="inlineStr">
+      <c r="X18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X18" s="93" t="inlineStr">
+      <c r="Y18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y18" s="93" t="inlineStr">
+      <c r="Z18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z18" s="93" t="inlineStr">
+      <c r="AA18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA18" s="93" t="inlineStr">
+      <c r="AB18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB18" s="93" t="inlineStr">
+      <c r="AC18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC18" s="91" t="inlineStr">
+      <c r="AD18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD18" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE18" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
+      <c r="AE18" s="92" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -8450,22 +8444,22 @@
         <v>3.24</v>
       </c>
       <c r="C19" s="94" t="n">
-        <v>5.05</v>
+        <v>3.24</v>
       </c>
       <c r="D19" s="94" t="n">
         <v>5.05</v>
       </c>
       <c r="E19" s="94" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="F19" s="94" t="n">
         <v>5.32</v>
       </c>
-      <c r="F19" s="94" t="n">
+      <c r="G19" s="94" t="n">
         <v>4.98</v>
       </c>
-      <c r="G19" s="94" t="n">
+      <c r="H19" s="94" t="n">
         <v>3.38</v>
-      </c>
-      <c r="H19" s="94" t="n">
-        <v>2.44</v>
       </c>
       <c r="I19" s="94" t="n">
         <v>2.44</v>
@@ -8474,67 +8468,67 @@
         <v>2.44</v>
       </c>
       <c r="K19" s="94" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="L19" s="94" t="n">
         <v>1.24</v>
       </c>
-      <c r="L19" s="94" t="n">
+      <c r="M19" s="94" t="n">
         <v>1.86</v>
       </c>
-      <c r="M19" s="94" t="n">
+      <c r="N19" s="94" t="n">
         <v>0.01</v>
       </c>
-      <c r="N19" s="94" t="n">
+      <c r="O19" s="94" t="n">
         <v>0.36</v>
-      </c>
-      <c r="O19" s="94" t="n">
-        <v>-0.5600000000000001</v>
       </c>
       <c r="P19" s="94" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="Q19" s="94" t="n">
-        <v>1.78</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="R19" s="94" t="n">
         <v>1.78</v>
       </c>
       <c r="S19" s="94" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T19" s="94" t="n">
         <v>2.23</v>
       </c>
-      <c r="T19" s="94" t="n">
+      <c r="U19" s="94" t="n">
         <v>3.17</v>
-      </c>
-      <c r="U19" s="94" t="n">
-        <v>3.33</v>
       </c>
       <c r="V19" s="94" t="n">
         <v>3.33</v>
       </c>
       <c r="W19" s="94" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="X19" s="94" t="n">
         <v>3.03</v>
-      </c>
-      <c r="X19" s="94" t="n">
-        <v>2.27</v>
       </c>
       <c r="Y19" s="94" t="n">
         <v>2.27</v>
       </c>
       <c r="Z19" s="94" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA19" s="94" t="n">
         <v>3.63</v>
-      </c>
-      <c r="AA19" s="94" t="n">
-        <v>4.58</v>
       </c>
       <c r="AB19" s="94" t="n">
         <v>4.58</v>
       </c>
       <c r="AC19" s="94" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AD19" s="94" t="n">
         <v>5.76</v>
       </c>
-      <c r="AD19" s="94" t="n">
-        <v>4.82</v>
-      </c>
       <c r="AE19" s="94" t="n">
-        <v>4.82</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -8547,22 +8541,22 @@
         <v>12.45</v>
       </c>
       <c r="C20" s="94" t="n">
-        <v>12.02</v>
+        <v>12.45</v>
       </c>
       <c r="D20" s="94" t="n">
         <v>12.02</v>
       </c>
       <c r="E20" s="94" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="F20" s="94" t="n">
         <v>10.8</v>
       </c>
-      <c r="F20" s="94" t="n">
+      <c r="G20" s="94" t="n">
         <v>11.96</v>
       </c>
-      <c r="G20" s="94" t="n">
+      <c r="H20" s="94" t="n">
         <v>10.72</v>
-      </c>
-      <c r="H20" s="94" t="n">
-        <v>9.85</v>
       </c>
       <c r="I20" s="94" t="n">
         <v>9.85</v>
@@ -8571,67 +8565,67 @@
         <v>9.85</v>
       </c>
       <c r="K20" s="94" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="L20" s="94" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="L20" s="94" t="n">
+      <c r="M20" s="94" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="M20" s="94" t="n">
+      <c r="N20" s="94" t="n">
         <v>5.17</v>
       </c>
-      <c r="N20" s="94" t="n">
+      <c r="O20" s="94" t="n">
         <v>4.88</v>
-      </c>
-      <c r="O20" s="94" t="n">
-        <v>5.85</v>
       </c>
       <c r="P20" s="94" t="n">
         <v>5.85</v>
       </c>
       <c r="Q20" s="94" t="n">
-        <v>6.74</v>
+        <v>5.85</v>
       </c>
       <c r="R20" s="94" t="n">
         <v>6.74</v>
       </c>
       <c r="S20" s="94" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="T20" s="94" t="n">
         <v>5.74</v>
       </c>
-      <c r="T20" s="94" t="n">
+      <c r="U20" s="94" t="n">
         <v>5.44</v>
-      </c>
-      <c r="U20" s="94" t="n">
-        <v>5.53</v>
       </c>
       <c r="V20" s="94" t="n">
         <v>5.53</v>
       </c>
       <c r="W20" s="94" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="X20" s="94" t="n">
         <v>4.51</v>
-      </c>
-      <c r="X20" s="94" t="n">
-        <v>5.32</v>
       </c>
       <c r="Y20" s="94" t="n">
         <v>5.32</v>
       </c>
       <c r="Z20" s="94" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="AA20" s="94" t="n">
         <v>4.85</v>
-      </c>
-      <c r="AA20" s="94" t="n">
-        <v>7.06</v>
       </c>
       <c r="AB20" s="94" t="n">
         <v>7.06</v>
       </c>
       <c r="AC20" s="94" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="AD20" s="94" t="n">
         <v>8.34</v>
       </c>
-      <c r="AD20" s="94" t="n">
-        <v>8.49</v>
-      </c>
       <c r="AE20" s="94" t="n">
-        <v>8.49</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -8644,22 +8638,22 @@
         <v>16.07</v>
       </c>
       <c r="C21" s="94" t="n">
-        <v>67.48999999999999</v>
+        <v>16.07</v>
       </c>
       <c r="D21" s="94" t="n">
         <v>67.48999999999999</v>
       </c>
       <c r="E21" s="94" t="n">
+        <v>67.48999999999999</v>
+      </c>
+      <c r="F21" s="94" t="n">
         <v>98.41</v>
       </c>
-      <c r="F21" s="94" t="n">
+      <c r="G21" s="94" t="n">
         <v>97.23999999999999</v>
       </c>
-      <c r="G21" s="94" t="n">
+      <c r="H21" s="94" t="n">
         <v>95.22</v>
-      </c>
-      <c r="H21" s="94" t="n">
-        <v>90.06</v>
       </c>
       <c r="I21" s="94" t="n">
         <v>90.06</v>
@@ -8668,67 +8662,67 @@
         <v>90.06</v>
       </c>
       <c r="K21" s="94" t="n">
+        <v>90.06</v>
+      </c>
+      <c r="L21" s="94" t="n">
         <v>74.65000000000001</v>
       </c>
-      <c r="L21" s="94" t="n">
+      <c r="M21" s="94" t="n">
         <v>89.31999999999999</v>
       </c>
-      <c r="M21" s="94" t="n">
+      <c r="N21" s="94" t="n">
         <v>34.87</v>
       </c>
-      <c r="N21" s="94" t="n">
+      <c r="O21" s="94" t="n">
         <v>22.53</v>
-      </c>
-      <c r="O21" s="94" t="n">
-        <v>10.95</v>
       </c>
       <c r="P21" s="94" t="n">
         <v>10.95</v>
       </c>
       <c r="Q21" s="94" t="n">
-        <v>42.53</v>
+        <v>10.95</v>
       </c>
       <c r="R21" s="94" t="n">
         <v>42.53</v>
       </c>
       <c r="S21" s="94" t="n">
+        <v>42.53</v>
+      </c>
+      <c r="T21" s="94" t="n">
         <v>32.72</v>
       </c>
-      <c r="T21" s="94" t="n">
+      <c r="U21" s="94" t="n">
         <v>84.81999999999999</v>
-      </c>
-      <c r="U21" s="94" t="n">
-        <v>74.91</v>
       </c>
       <c r="V21" s="94" t="n">
         <v>74.91</v>
       </c>
       <c r="W21" s="94" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="X21" s="94" t="n">
         <v>6.03</v>
-      </c>
-      <c r="X21" s="94" t="n">
-        <v>7.97</v>
       </c>
       <c r="Y21" s="94" t="n">
         <v>7.97</v>
       </c>
       <c r="Z21" s="94" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="AA21" s="94" t="n">
         <v>11.56</v>
-      </c>
-      <c r="AA21" s="94" t="n">
-        <v>26.76</v>
       </c>
       <c r="AB21" s="94" t="n">
         <v>26.76</v>
       </c>
       <c r="AC21" s="94" t="n">
+        <v>26.76</v>
+      </c>
+      <c r="AD21" s="94" t="n">
         <v>85.53</v>
       </c>
-      <c r="AD21" s="94" t="n">
-        <v>89.12</v>
-      </c>
       <c r="AE21" s="94" t="n">
-        <v>89.12</v>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -8792,100 +8786,98 @@
           <t>red</t>
         </is>
       </c>
-      <c r="M22" s="92" t="inlineStr">
+      <c r="M22" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N22" s="92" t="inlineStr">
+      <c r="O22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O22" s="93" t="inlineStr">
+      <c r="P22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P22" s="93" t="inlineStr">
+      <c r="Q22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q22" s="92" t="inlineStr">
+      <c r="R22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R22" s="92" t="inlineStr">
+      <c r="S22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S22" s="92" t="inlineStr">
+      <c r="T22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T22" s="92" t="inlineStr">
+      <c r="U22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U22" s="92" t="inlineStr">
+      <c r="V22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V22" s="92" t="inlineStr">
+      <c r="W22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W22" s="93" t="inlineStr">
+      <c r="X22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X22" s="92" t="inlineStr">
+      <c r="Y22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y22" s="92" t="inlineStr">
+      <c r="Z22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z22" s="93" t="inlineStr">
+      <c r="AA22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA22" s="92" t="inlineStr">
+      <c r="AB22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB22" s="92" t="inlineStr">
+      <c r="AC22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC22" s="92" t="inlineStr">
+      <c r="AD22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD22" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE22" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
+      <c r="AE22" s="92" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -8898,22 +8890,22 @@
         <v>5.49</v>
       </c>
       <c r="C23" s="94" t="n">
-        <v>5.48</v>
+        <v>5.49</v>
       </c>
       <c r="D23" s="94" t="n">
         <v>5.48</v>
       </c>
       <c r="E23" s="94" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="F23" s="94" t="n">
         <v>5.17</v>
       </c>
-      <c r="F23" s="94" t="n">
+      <c r="G23" s="94" t="n">
         <v>3.86</v>
       </c>
-      <c r="G23" s="94" t="n">
+      <c r="H23" s="94" t="n">
         <v>2.56</v>
-      </c>
-      <c r="H23" s="94" t="n">
-        <v>1.3</v>
       </c>
       <c r="I23" s="94" t="n">
         <v>1.3</v>
@@ -8922,67 +8914,67 @@
         <v>1.3</v>
       </c>
       <c r="K23" s="94" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L23" s="94" t="n">
         <v>-0.28</v>
       </c>
-      <c r="L23" s="94" t="n">
+      <c r="M23" s="94" t="n">
         <v>-0.04</v>
       </c>
-      <c r="M23" s="94" t="n">
+      <c r="N23" s="94" t="n">
         <v>-1.3</v>
       </c>
-      <c r="N23" s="94" t="n">
+      <c r="O23" s="94" t="n">
         <v>-1.04</v>
-      </c>
-      <c r="O23" s="94" t="n">
-        <v>-2.62</v>
       </c>
       <c r="P23" s="94" t="n">
         <v>-2.62</v>
       </c>
       <c r="Q23" s="94" t="n">
-        <v>-0.53</v>
+        <v>-2.62</v>
       </c>
       <c r="R23" s="94" t="n">
         <v>-0.53</v>
       </c>
       <c r="S23" s="94" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="T23" s="94" t="n">
         <v>0.17</v>
       </c>
-      <c r="T23" s="94" t="n">
+      <c r="U23" s="94" t="n">
         <v>0.46</v>
-      </c>
-      <c r="U23" s="94" t="n">
-        <v>1.55</v>
       </c>
       <c r="V23" s="94" t="n">
         <v>1.55</v>
       </c>
       <c r="W23" s="94" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X23" s="94" t="n">
         <v>1.04</v>
-      </c>
-      <c r="X23" s="94" t="n">
-        <v>0.45</v>
       </c>
       <c r="Y23" s="94" t="n">
         <v>0.45</v>
       </c>
       <c r="Z23" s="94" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AA23" s="94" t="n">
         <v>1.34</v>
-      </c>
-      <c r="AA23" s="94" t="n">
-        <v>1.89</v>
       </c>
       <c r="AB23" s="94" t="n">
         <v>1.89</v>
       </c>
       <c r="AC23" s="94" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD23" s="94" t="n">
         <v>2.77</v>
       </c>
-      <c r="AD23" s="94" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AE23" s="94" t="n">
-        <v>2.28</v>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -8995,22 +8987,22 @@
         <v>12.52</v>
       </c>
       <c r="C24" s="94" t="n">
-        <v>10.1</v>
+        <v>12.52</v>
       </c>
       <c r="D24" s="94" t="n">
         <v>10.1</v>
       </c>
       <c r="E24" s="94" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F24" s="94" t="n">
         <v>9.109999999999999</v>
       </c>
-      <c r="F24" s="94" t="n">
+      <c r="G24" s="94" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="G24" s="94" t="n">
+      <c r="H24" s="94" t="n">
         <v>8.6</v>
-      </c>
-      <c r="H24" s="94" t="n">
-        <v>7.14</v>
       </c>
       <c r="I24" s="94" t="n">
         <v>7.14</v>
@@ -9019,67 +9011,67 @@
         <v>7.14</v>
       </c>
       <c r="K24" s="94" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="L24" s="94" t="n">
         <v>8.06</v>
       </c>
-      <c r="L24" s="94" t="n">
+      <c r="M24" s="94" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="M24" s="94" t="n">
+      <c r="N24" s="94" t="n">
         <v>5.35</v>
       </c>
-      <c r="N24" s="94" t="n">
+      <c r="O24" s="94" t="n">
         <v>4.66</v>
-      </c>
-      <c r="O24" s="94" t="n">
-        <v>4.1</v>
       </c>
       <c r="P24" s="94" t="n">
         <v>4.1</v>
       </c>
       <c r="Q24" s="94" t="n">
-        <v>4.84</v>
+        <v>4.1</v>
       </c>
       <c r="R24" s="94" t="n">
         <v>4.84</v>
       </c>
       <c r="S24" s="94" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="T24" s="94" t="n">
         <v>3.23</v>
       </c>
-      <c r="T24" s="94" t="n">
+      <c r="U24" s="94" t="n">
         <v>4.28</v>
-      </c>
-      <c r="U24" s="94" t="n">
-        <v>6.27</v>
       </c>
       <c r="V24" s="94" t="n">
         <v>6.27</v>
       </c>
       <c r="W24" s="94" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="X24" s="94" t="n">
         <v>5.98</v>
-      </c>
-      <c r="X24" s="94" t="n">
-        <v>7.02</v>
       </c>
       <c r="Y24" s="94" t="n">
         <v>7.02</v>
       </c>
       <c r="Z24" s="94" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="AA24" s="94" t="n">
         <v>7.18</v>
-      </c>
-      <c r="AA24" s="94" t="n">
-        <v>9.42</v>
       </c>
       <c r="AB24" s="94" t="n">
         <v>9.42</v>
       </c>
       <c r="AC24" s="94" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="AD24" s="94" t="n">
         <v>10.12</v>
       </c>
-      <c r="AD24" s="94" t="n">
-        <v>9.960000000000001</v>
-      </c>
       <c r="AE24" s="94" t="n">
-        <v>9.960000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -9092,22 +9084,22 @@
         <v>86.3</v>
       </c>
       <c r="C25" s="94" t="n">
-        <v>79.05</v>
+        <v>86.3</v>
       </c>
       <c r="D25" s="94" t="n">
         <v>79.05</v>
       </c>
       <c r="E25" s="94" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="F25" s="94" t="n">
         <v>95.43000000000001</v>
       </c>
-      <c r="F25" s="94" t="n">
+      <c r="G25" s="94" t="n">
         <v>92.37</v>
       </c>
-      <c r="G25" s="94" t="n">
+      <c r="H25" s="94" t="n">
         <v>91.09999999999999</v>
-      </c>
-      <c r="H25" s="94" t="n">
-        <v>83.62</v>
       </c>
       <c r="I25" s="94" t="n">
         <v>83.62</v>
@@ -9116,67 +9108,67 @@
         <v>83.62</v>
       </c>
       <c r="K25" s="94" t="n">
+        <v>83.62</v>
+      </c>
+      <c r="L25" s="94" t="n">
         <v>74.87</v>
       </c>
-      <c r="L25" s="94" t="n">
+      <c r="M25" s="94" t="n">
         <v>80.75</v>
       </c>
-      <c r="M25" s="94" t="n">
+      <c r="N25" s="94" t="n">
         <v>58.29</v>
       </c>
-      <c r="N25" s="94" t="n">
+      <c r="O25" s="94" t="n">
         <v>44.79</v>
-      </c>
-      <c r="O25" s="94" t="n">
-        <v>15.07</v>
       </c>
       <c r="P25" s="94" t="n">
         <v>15.07</v>
       </c>
       <c r="Q25" s="94" t="n">
-        <v>49.78</v>
+        <v>15.07</v>
       </c>
       <c r="R25" s="94" t="n">
         <v>49.78</v>
       </c>
       <c r="S25" s="94" t="n">
+        <v>49.78</v>
+      </c>
+      <c r="T25" s="94" t="n">
         <v>34.31</v>
       </c>
-      <c r="T25" s="94" t="n">
+      <c r="U25" s="94" t="n">
         <v>52.18</v>
-      </c>
-      <c r="U25" s="94" t="n">
-        <v>54.91</v>
       </c>
       <c r="V25" s="94" t="n">
         <v>54.91</v>
       </c>
       <c r="W25" s="94" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="X25" s="94" t="n">
         <v>15.8</v>
-      </c>
-      <c r="X25" s="94" t="n">
-        <v>21.31</v>
       </c>
       <c r="Y25" s="94" t="n">
         <v>21.31</v>
       </c>
       <c r="Z25" s="94" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="AA25" s="94" t="n">
         <v>22.32</v>
-      </c>
-      <c r="AA25" s="94" t="n">
-        <v>40.35</v>
       </c>
       <c r="AB25" s="94" t="n">
         <v>40.35</v>
       </c>
       <c r="AC25" s="94" t="n">
+        <v>40.35</v>
+      </c>
+      <c r="AD25" s="94" t="n">
         <v>70.73999999999999</v>
       </c>
-      <c r="AD25" s="94" t="n">
-        <v>69.41</v>
-      </c>
       <c r="AE25" s="94" t="n">
-        <v>69.41</v>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -9190,150 +9182,148 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C26" s="91" t="inlineStr">
+      <c r="C26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D26" s="91" t="inlineStr">
+      <c r="E26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E26" s="91" t="inlineStr">
+      <c r="F26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F26" s="91" t="inlineStr">
+      <c r="G26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G26" s="91" t="inlineStr">
+      <c r="H26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H26" s="91" t="inlineStr">
+      <c r="I26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I26" s="91" t="inlineStr">
+      <c r="J26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J26" s="91" t="inlineStr">
+      <c r="K26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K26" s="92" t="inlineStr">
+      <c r="L26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L26" s="91" t="inlineStr">
+      <c r="M26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M26" s="93" t="inlineStr">
+      <c r="N26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N26" s="93" t="inlineStr">
+      <c r="O26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O26" s="93" t="inlineStr">
+      <c r="P26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P26" s="93" t="inlineStr">
+      <c r="Q26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q26" s="93" t="inlineStr">
+      <c r="R26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R26" s="93" t="inlineStr">
+      <c r="S26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S26" s="93" t="inlineStr">
+      <c r="T26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T26" s="91" t="inlineStr">
+      <c r="U26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U26" s="91" t="inlineStr">
+      <c r="V26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V26" s="91" t="inlineStr">
+      <c r="W26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W26" s="93" t="inlineStr">
+      <c r="X26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X26" s="93" t="inlineStr">
+      <c r="Y26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y26" s="93" t="inlineStr">
+      <c r="Z26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z26" s="93" t="inlineStr">
+      <c r="AA26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA26" s="93" t="inlineStr">
+      <c r="AB26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB26" s="93" t="inlineStr">
+      <c r="AC26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC26" s="91" t="inlineStr">
+      <c r="AD26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD26" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE26" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
+      <c r="AE26" s="92" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -9346,22 +9336,22 @@
         <v>4.17</v>
       </c>
       <c r="C27" s="94" t="n">
-        <v>7.75</v>
+        <v>4.17</v>
       </c>
       <c r="D27" s="94" t="n">
         <v>7.75</v>
       </c>
       <c r="E27" s="94" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="F27" s="94" t="n">
         <v>8.9</v>
       </c>
-      <c r="F27" s="94" t="n">
+      <c r="G27" s="94" t="n">
         <v>9.48</v>
       </c>
-      <c r="G27" s="94" t="n">
+      <c r="H27" s="94" t="n">
         <v>6.37</v>
-      </c>
-      <c r="H27" s="94" t="n">
-        <v>5.88</v>
       </c>
       <c r="I27" s="94" t="n">
         <v>5.88</v>
@@ -9370,67 +9360,67 @@
         <v>5.88</v>
       </c>
       <c r="K27" s="94" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="L27" s="94" t="n">
         <v>4.59</v>
       </c>
-      <c r="L27" s="94" t="n">
+      <c r="M27" s="94" t="n">
         <v>6.19</v>
       </c>
-      <c r="M27" s="94" t="n">
+      <c r="N27" s="94" t="n">
         <v>3.69</v>
       </c>
-      <c r="N27" s="94" t="n">
+      <c r="O27" s="94" t="n">
         <v>4.22</v>
-      </c>
-      <c r="O27" s="94" t="n">
-        <v>3.56</v>
       </c>
       <c r="P27" s="94" t="n">
         <v>3.56</v>
       </c>
       <c r="Q27" s="94" t="n">
-        <v>6.19</v>
+        <v>3.56</v>
       </c>
       <c r="R27" s="94" t="n">
         <v>6.19</v>
       </c>
       <c r="S27" s="94" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="T27" s="94" t="n">
         <v>6.61</v>
       </c>
-      <c r="T27" s="94" t="n">
+      <c r="U27" s="94" t="n">
         <v>8.6</v>
-      </c>
-      <c r="U27" s="94" t="n">
-        <v>7.91</v>
       </c>
       <c r="V27" s="94" t="n">
         <v>7.91</v>
       </c>
       <c r="W27" s="94" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="X27" s="94" t="n">
         <v>7.57</v>
-      </c>
-      <c r="X27" s="94" t="n">
-        <v>6.47</v>
       </c>
       <c r="Y27" s="94" t="n">
         <v>6.47</v>
       </c>
       <c r="Z27" s="94" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="AA27" s="94" t="n">
         <v>8.75</v>
-      </c>
-      <c r="AA27" s="94" t="n">
-        <v>10.02</v>
       </c>
       <c r="AB27" s="94" t="n">
         <v>10.02</v>
       </c>
       <c r="AC27" s="94" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="AD27" s="94" t="n">
         <v>11.78</v>
       </c>
-      <c r="AD27" s="94" t="n">
-        <v>10.13</v>
-      </c>
       <c r="AE27" s="94" t="n">
-        <v>10.13</v>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -9443,22 +9433,22 @@
         <v>15.29</v>
       </c>
       <c r="C28" s="94" t="n">
-        <v>16.05</v>
+        <v>15.29</v>
       </c>
       <c r="D28" s="94" t="n">
         <v>16.05</v>
       </c>
       <c r="E28" s="94" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="F28" s="94" t="n">
         <v>13.95</v>
       </c>
-      <c r="F28" s="94" t="n">
+      <c r="G28" s="94" t="n">
         <v>16.69</v>
       </c>
-      <c r="G28" s="94" t="n">
+      <c r="H28" s="94" t="n">
         <v>13.74</v>
-      </c>
-      <c r="H28" s="94" t="n">
-        <v>13.09</v>
       </c>
       <c r="I28" s="94" t="n">
         <v>13.09</v>
@@ -9467,67 +9457,67 @@
         <v>13.09</v>
       </c>
       <c r="K28" s="94" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="L28" s="94" t="n">
         <v>12.55</v>
       </c>
-      <c r="L28" s="94" t="n">
+      <c r="M28" s="94" t="n">
         <v>12.51</v>
       </c>
-      <c r="M28" s="94" t="n">
+      <c r="N28" s="94" t="n">
         <v>5.82</v>
       </c>
-      <c r="N28" s="94" t="n">
+      <c r="O28" s="94" t="n">
         <v>6</v>
-      </c>
-      <c r="O28" s="94" t="n">
-        <v>8.09</v>
       </c>
       <c r="P28" s="94" t="n">
         <v>8.09</v>
       </c>
       <c r="Q28" s="94" t="n">
-        <v>9</v>
+        <v>8.09</v>
       </c>
       <c r="R28" s="94" t="n">
         <v>9</v>
       </c>
       <c r="S28" s="94" t="n">
+        <v>9</v>
+      </c>
+      <c r="T28" s="94" t="n">
         <v>8.289999999999999</v>
       </c>
-      <c r="T28" s="94" t="n">
+      <c r="U28" s="94" t="n">
         <v>7.32</v>
-      </c>
-      <c r="U28" s="94" t="n">
-        <v>6.22</v>
       </c>
       <c r="V28" s="94" t="n">
         <v>6.22</v>
       </c>
       <c r="W28" s="94" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="X28" s="94" t="n">
         <v>4.8</v>
-      </c>
-      <c r="X28" s="94" t="n">
-        <v>5.62</v>
       </c>
       <c r="Y28" s="94" t="n">
         <v>5.62</v>
       </c>
       <c r="Z28" s="94" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="AA28" s="94" t="n">
         <v>4.5</v>
-      </c>
-      <c r="AA28" s="94" t="n">
-        <v>7.01</v>
       </c>
       <c r="AB28" s="94" t="n">
         <v>7.01</v>
       </c>
       <c r="AC28" s="94" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="AD28" s="94" t="n">
         <v>8.779999999999999</v>
       </c>
-      <c r="AD28" s="94" t="n">
-        <v>9.15</v>
-      </c>
       <c r="AE28" s="94" t="n">
-        <v>9.15</v>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -9540,22 +9530,22 @@
         <v>8.699999999999999</v>
       </c>
       <c r="C29" s="94" t="n">
-        <v>54.41</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D29" s="94" t="n">
         <v>54.41</v>
       </c>
       <c r="E29" s="94" t="n">
+        <v>54.41</v>
+      </c>
+      <c r="F29" s="94" t="n">
         <v>94.87</v>
       </c>
-      <c r="F29" s="94" t="n">
+      <c r="G29" s="94" t="n">
         <v>93.84999999999999</v>
       </c>
-      <c r="G29" s="94" t="n">
+      <c r="H29" s="94" t="n">
         <v>85.8</v>
-      </c>
-      <c r="H29" s="94" t="n">
-        <v>78.89</v>
       </c>
       <c r="I29" s="94" t="n">
         <v>78.89</v>
@@ -9564,67 +9554,67 @@
         <v>78.89</v>
       </c>
       <c r="K29" s="94" t="n">
+        <v>78.89</v>
+      </c>
+      <c r="L29" s="94" t="n">
         <v>51.88</v>
       </c>
-      <c r="L29" s="94" t="n">
+      <c r="M29" s="94" t="n">
         <v>83.56</v>
       </c>
-      <c r="M29" s="94" t="n">
+      <c r="N29" s="94" t="n">
         <v>6.54</v>
       </c>
-      <c r="N29" s="94" t="n">
+      <c r="O29" s="94" t="n">
         <v>8.380000000000001</v>
-      </c>
-      <c r="O29" s="94" t="n">
-        <v>10.96</v>
       </c>
       <c r="P29" s="94" t="n">
         <v>10.96</v>
       </c>
       <c r="Q29" s="94" t="n">
-        <v>32.97</v>
+        <v>10.96</v>
       </c>
       <c r="R29" s="94" t="n">
         <v>32.97</v>
       </c>
       <c r="S29" s="94" t="n">
+        <v>32.97</v>
+      </c>
+      <c r="T29" s="94" t="n">
         <v>34.13</v>
       </c>
-      <c r="T29" s="94" t="n">
+      <c r="U29" s="94" t="n">
         <v>88.52</v>
-      </c>
-      <c r="U29" s="94" t="n">
-        <v>76.26000000000001</v>
       </c>
       <c r="V29" s="94" t="n">
         <v>76.26000000000001</v>
       </c>
       <c r="W29" s="94" t="n">
+        <v>76.26000000000001</v>
+      </c>
+      <c r="X29" s="94" t="n">
         <v>5.68</v>
-      </c>
-      <c r="X29" s="94" t="n">
-        <v>6.54</v>
       </c>
       <c r="Y29" s="94" t="n">
         <v>6.54</v>
       </c>
       <c r="Z29" s="94" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="AA29" s="94" t="n">
         <v>11.7</v>
-      </c>
-      <c r="AA29" s="94" t="n">
-        <v>24.8</v>
       </c>
       <c r="AB29" s="94" t="n">
         <v>24.8</v>
       </c>
       <c r="AC29" s="94" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AD29" s="94" t="n">
         <v>85.38</v>
       </c>
-      <c r="AD29" s="94" t="n">
-        <v>89.31</v>
-      </c>
       <c r="AE29" s="94" t="n">
-        <v>89.31</v>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -9633,154 +9623,154 @@
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B30" s="92" t="inlineStr">
+      <c r="B30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C30" s="91" t="inlineStr">
+      <c r="D30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D30" s="91" t="inlineStr">
+      <c r="E30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E30" s="91" t="inlineStr">
+      <c r="F30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F30" s="91" t="inlineStr">
+      <c r="G30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G30" s="91" t="inlineStr">
+      <c r="H30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H30" s="92" t="inlineStr">
+      <c r="I30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I30" s="93" t="inlineStr">
+      <c r="J30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J30" s="93" t="inlineStr">
+      <c r="K30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K30" s="93" t="inlineStr">
+      <c r="L30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L30" s="93" t="inlineStr">
+      <c r="M30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M30" s="93" t="inlineStr">
+      <c r="N30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N30" s="93" t="inlineStr">
+      <c r="O30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O30" s="93" t="inlineStr">
+      <c r="P30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P30" s="93" t="inlineStr">
+      <c r="Q30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q30" s="92" t="inlineStr">
+      <c r="R30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R30" s="91" t="inlineStr">
+      <c r="S30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S30" s="91" t="inlineStr">
+      <c r="T30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T30" s="93" t="inlineStr">
+      <c r="U30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U30" s="91" t="inlineStr">
+      <c r="V30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V30" s="91" t="inlineStr">
+      <c r="W30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W30" s="91" t="inlineStr">
+      <c r="X30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X30" s="91" t="inlineStr">
+      <c r="Y30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y30" s="91" t="inlineStr">
+      <c r="Z30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z30" s="91" t="inlineStr">
+      <c r="AA30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA30" s="91" t="inlineStr">
+      <c r="AB30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB30" s="91" t="inlineStr">
+      <c r="AC30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC30" s="91" t="inlineStr">
+      <c r="AD30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD30" s="91" t="inlineStr">
+      <c r="AE30" s="91" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AE30" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -9791,43 +9781,43 @@
         </is>
       </c>
       <c r="B31" s="94" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="C31" s="94" t="n">
         <v>2.49</v>
-      </c>
-      <c r="C31" s="94" t="n">
-        <v>5.32</v>
       </c>
       <c r="D31" s="94" t="n">
         <v>5.32</v>
       </c>
       <c r="E31" s="94" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="F31" s="94" t="n">
         <v>4.76</v>
       </c>
-      <c r="F31" s="94" t="n">
+      <c r="G31" s="94" t="n">
         <v>4.05</v>
       </c>
-      <c r="G31" s="94" t="n">
+      <c r="H31" s="94" t="n">
         <v>1.6</v>
       </c>
-      <c r="H31" s="94" t="n">
+      <c r="I31" s="94" t="n">
         <v>-0.13</v>
-      </c>
-      <c r="I31" s="94" t="n">
-        <v>-1.36</v>
       </c>
       <c r="J31" s="94" t="n">
         <v>-1.36</v>
       </c>
       <c r="K31" s="94" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="L31" s="94" t="n">
         <v>-0.87</v>
       </c>
-      <c r="L31" s="94" t="n">
+      <c r="M31" s="94" t="n">
         <v>-1.88</v>
       </c>
-      <c r="M31" s="94" t="n">
+      <c r="N31" s="94" t="n">
         <v>-3.6</v>
-      </c>
-      <c r="N31" s="94" t="n">
-        <v>-1.05</v>
       </c>
       <c r="O31" s="94" t="n">
         <v>-1.05</v>
@@ -9836,19 +9826,19 @@
         <v>-1.05</v>
       </c>
       <c r="Q31" s="94" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="R31" s="94" t="n">
         <v>0.57</v>
       </c>
-      <c r="R31" s="94" t="n">
+      <c r="S31" s="94" t="n">
         <v>1.79</v>
       </c>
-      <c r="S31" s="94" t="n">
+      <c r="T31" s="94" t="n">
         <v>2.94</v>
       </c>
-      <c r="T31" s="94" t="n">
+      <c r="U31" s="94" t="n">
         <v>-0.07000000000000001</v>
-      </c>
-      <c r="U31" s="94" t="n">
-        <v>3.26</v>
       </c>
       <c r="V31" s="94" t="n">
         <v>3.26</v>
@@ -9866,19 +9856,19 @@
         <v>3.26</v>
       </c>
       <c r="AA31" s="94" t="n">
-        <v>4.49</v>
+        <v>3.26</v>
       </c>
       <c r="AB31" s="94" t="n">
         <v>4.49</v>
       </c>
       <c r="AC31" s="94" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="AD31" s="94" t="n">
         <v>4.65</v>
       </c>
-      <c r="AD31" s="94" t="n">
+      <c r="AE31" s="94" t="n">
         <v>1.24</v>
-      </c>
-      <c r="AE31" s="94" t="n">
-        <v>2.95</v>
       </c>
     </row>
     <row r="32">
@@ -9888,43 +9878,43 @@
         </is>
       </c>
       <c r="B32" s="94" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="C32" s="94" t="n">
         <v>3.78</v>
-      </c>
-      <c r="C32" s="94" t="n">
-        <v>2.12</v>
       </c>
       <c r="D32" s="94" t="n">
         <v>2.12</v>
       </c>
       <c r="E32" s="94" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F32" s="94" t="n">
         <v>3.72</v>
       </c>
-      <c r="F32" s="94" t="n">
+      <c r="G32" s="94" t="n">
         <v>3.06</v>
       </c>
-      <c r="G32" s="94" t="n">
+      <c r="H32" s="94" t="n">
         <v>3.61</v>
       </c>
-      <c r="H32" s="94" t="n">
+      <c r="I32" s="94" t="n">
         <v>2.73</v>
-      </c>
-      <c r="I32" s="94" t="n">
-        <v>-1.8</v>
       </c>
       <c r="J32" s="94" t="n">
         <v>-1.8</v>
       </c>
       <c r="K32" s="94" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="L32" s="94" t="n">
         <v>-2.58</v>
       </c>
-      <c r="L32" s="94" t="n">
+      <c r="M32" s="94" t="n">
         <v>-2.92</v>
       </c>
-      <c r="M32" s="94" t="n">
+      <c r="N32" s="94" t="n">
         <v>-3.97</v>
-      </c>
-      <c r="N32" s="94" t="n">
-        <v>-2.33</v>
       </c>
       <c r="O32" s="94" t="n">
         <v>-2.33</v>
@@ -9933,19 +9923,19 @@
         <v>-2.33</v>
       </c>
       <c r="Q32" s="94" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="R32" s="94" t="n">
         <v>-3.63</v>
       </c>
-      <c r="R32" s="94" t="n">
+      <c r="S32" s="94" t="n">
         <v>-3.14</v>
       </c>
-      <c r="S32" s="94" t="n">
+      <c r="T32" s="94" t="n">
         <v>-2.69</v>
       </c>
-      <c r="T32" s="94" t="n">
+      <c r="U32" s="94" t="n">
         <v>-6.91</v>
-      </c>
-      <c r="U32" s="94" t="n">
-        <v>-4.63</v>
       </c>
       <c r="V32" s="94" t="n">
         <v>-4.63</v>
@@ -9963,19 +9953,19 @@
         <v>-4.63</v>
       </c>
       <c r="AA32" s="94" t="n">
-        <v>-3.12</v>
+        <v>-4.63</v>
       </c>
       <c r="AB32" s="94" t="n">
         <v>-3.12</v>
       </c>
       <c r="AC32" s="94" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="AD32" s="94" t="n">
         <v>-2.97</v>
       </c>
-      <c r="AD32" s="94" t="n">
+      <c r="AE32" s="94" t="n">
         <v>-4.36</v>
-      </c>
-      <c r="AE32" s="94" t="n">
-        <v>-4.59</v>
       </c>
     </row>
     <row r="33">
@@ -9985,43 +9975,43 @@
         </is>
       </c>
       <c r="B33" s="94" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="C33" s="94" t="n">
         <v>54.76</v>
-      </c>
-      <c r="C33" s="94" t="n">
-        <v>63.06</v>
       </c>
       <c r="D33" s="94" t="n">
         <v>63.06</v>
       </c>
       <c r="E33" s="94" t="n">
+        <v>63.06</v>
+      </c>
+      <c r="F33" s="94" t="n">
         <v>63.69</v>
       </c>
-      <c r="F33" s="94" t="n">
+      <c r="G33" s="94" t="n">
         <v>59.51</v>
       </c>
-      <c r="G33" s="94" t="n">
+      <c r="H33" s="94" t="n">
         <v>49.22</v>
       </c>
-      <c r="H33" s="94" t="n">
+      <c r="I33" s="94" t="n">
         <v>46.79</v>
-      </c>
-      <c r="I33" s="94" t="n">
-        <v>37.14</v>
       </c>
       <c r="J33" s="94" t="n">
         <v>37.14</v>
       </c>
       <c r="K33" s="94" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="L33" s="94" t="n">
         <v>38.82</v>
       </c>
-      <c r="L33" s="94" t="n">
+      <c r="M33" s="94" t="n">
         <v>36.1</v>
       </c>
-      <c r="M33" s="94" t="n">
+      <c r="N33" s="94" t="n">
         <v>36.44</v>
-      </c>
-      <c r="N33" s="94" t="n">
-        <v>45.43</v>
       </c>
       <c r="O33" s="94" t="n">
         <v>45.43</v>
@@ -10030,19 +10020,19 @@
         <v>45.43</v>
       </c>
       <c r="Q33" s="94" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="R33" s="94" t="n">
         <v>52.04</v>
       </c>
-      <c r="R33" s="94" t="n">
+      <c r="S33" s="94" t="n">
         <v>58.96</v>
       </c>
-      <c r="S33" s="94" t="n">
+      <c r="T33" s="94" t="n">
         <v>60.92</v>
       </c>
-      <c r="T33" s="94" t="n">
+      <c r="U33" s="94" t="n">
         <v>49.64</v>
-      </c>
-      <c r="U33" s="94" t="n">
-        <v>61.59</v>
       </c>
       <c r="V33" s="94" t="n">
         <v>61.59</v>
@@ -10060,19 +10050,19 @@
         <v>61.59</v>
       </c>
       <c r="AA33" s="94" t="n">
-        <v>71.7</v>
+        <v>61.59</v>
       </c>
       <c r="AB33" s="94" t="n">
         <v>71.7</v>
       </c>
       <c r="AC33" s="94" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="AD33" s="94" t="n">
         <v>61.28</v>
       </c>
-      <c r="AD33" s="94" t="n">
+      <c r="AE33" s="94" t="n">
         <v>51.56</v>
-      </c>
-      <c r="AE33" s="94" t="n">
-        <v>49.14</v>
       </c>
     </row>
     <row r="34">
@@ -10101,134 +10091,134 @@
           <t>red</t>
         </is>
       </c>
-      <c r="F34" s="92" t="inlineStr">
+      <c r="F34" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G34" s="92" t="inlineStr">
+      <c r="H34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H34" s="91" t="inlineStr">
+      <c r="I34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I34" s="91" t="inlineStr">
+      <c r="J34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J34" s="91" t="inlineStr">
+      <c r="K34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K34" s="92" t="inlineStr">
+      <c r="L34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L34" s="92" t="inlineStr">
+      <c r="M34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M34" s="93" t="inlineStr">
+      <c r="N34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N34" s="93" t="inlineStr">
+      <c r="O34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O34" s="93" t="inlineStr">
+      <c r="P34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P34" s="93" t="inlineStr">
+      <c r="Q34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q34" s="93" t="inlineStr">
+      <c r="R34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R34" s="93" t="inlineStr">
+      <c r="S34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S34" s="93" t="inlineStr">
+      <c r="T34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T34" s="93" t="inlineStr">
+      <c r="U34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U34" s="93" t="inlineStr">
+      <c r="V34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V34" s="93" t="inlineStr">
+      <c r="W34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W34" s="92" t="inlineStr">
+      <c r="X34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X34" s="92" t="inlineStr">
+      <c r="Y34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y34" s="92" t="inlineStr">
+      <c r="Z34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z34" s="92" t="inlineStr">
+      <c r="AA34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA34" s="91" t="inlineStr">
+      <c r="AB34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB34" s="91" t="inlineStr">
+      <c r="AC34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC34" s="91" t="inlineStr">
+      <c r="AD34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD34" s="91" t="inlineStr">
+      <c r="AE34" s="91" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AE34" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -10248,85 +10238,85 @@
         <v>0.05</v>
       </c>
       <c r="E35" s="94" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F35" s="94" t="n">
         <v>0.08</v>
       </c>
-      <c r="F35" s="94" t="n">
+      <c r="G35" s="94" t="n">
         <v>-1.53</v>
       </c>
-      <c r="G35" s="94" t="n">
+      <c r="H35" s="94" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="H35" s="94" t="n">
+      <c r="I35" s="94" t="n">
         <v>-0.25</v>
-      </c>
-      <c r="I35" s="94" t="n">
-        <v>-0.66</v>
       </c>
       <c r="J35" s="94" t="n">
         <v>-0.66</v>
       </c>
       <c r="K35" s="94" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="L35" s="94" t="n">
         <v>-2.25</v>
       </c>
-      <c r="L35" s="94" t="n">
+      <c r="M35" s="94" t="n">
         <v>-2.65</v>
       </c>
-      <c r="M35" s="94" t="n">
+      <c r="N35" s="94" t="n">
         <v>-3.96</v>
       </c>
-      <c r="N35" s="94" t="n">
+      <c r="O35" s="94" t="n">
         <v>-3.87</v>
-      </c>
-      <c r="O35" s="94" t="n">
-        <v>-4.36</v>
       </c>
       <c r="P35" s="94" t="n">
         <v>-4.36</v>
       </c>
       <c r="Q35" s="94" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="R35" s="94" t="n">
         <v>-2.63</v>
       </c>
-      <c r="R35" s="94" t="n">
+      <c r="S35" s="94" t="n">
         <v>-2.35</v>
       </c>
-      <c r="S35" s="94" t="n">
+      <c r="T35" s="94" t="n">
         <v>-3.06</v>
       </c>
-      <c r="T35" s="94" t="n">
+      <c r="U35" s="94" t="n">
         <v>-3.26</v>
-      </c>
-      <c r="U35" s="94" t="n">
-        <v>-2.47</v>
       </c>
       <c r="V35" s="94" t="n">
         <v>-2.47</v>
       </c>
       <c r="W35" s="94" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="X35" s="94" t="n">
         <v>-0.95</v>
-      </c>
-      <c r="X35" s="94" t="n">
-        <v>-0.41</v>
       </c>
       <c r="Y35" s="94" t="n">
         <v>-0.41</v>
       </c>
       <c r="Z35" s="94" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="AA35" s="94" t="n">
         <v>0.16</v>
-      </c>
-      <c r="AA35" s="94" t="n">
-        <v>0.36</v>
       </c>
       <c r="AB35" s="94" t="n">
         <v>0.36</v>
       </c>
       <c r="AC35" s="94" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AD35" s="94" t="n">
         <v>-0.41</v>
       </c>
-      <c r="AD35" s="94" t="n">
+      <c r="AE35" s="94" t="n">
         <v>-1.07</v>
-      </c>
-      <c r="AE35" s="94" t="n">
-        <v>-2.46</v>
       </c>
     </row>
     <row r="36">
@@ -10345,85 +10335,85 @@
         <v>4.53</v>
       </c>
       <c r="E36" s="94" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="F36" s="94" t="n">
         <v>6.02</v>
       </c>
-      <c r="F36" s="94" t="n">
+      <c r="G36" s="94" t="n">
         <v>0.48</v>
       </c>
-      <c r="G36" s="94" t="n">
+      <c r="H36" s="94" t="n">
         <v>1.56</v>
       </c>
-      <c r="H36" s="94" t="n">
+      <c r="I36" s="94" t="n">
         <v>-0.16</v>
-      </c>
-      <c r="I36" s="94" t="n">
-        <v>0.33</v>
       </c>
       <c r="J36" s="94" t="n">
         <v>0.33</v>
       </c>
       <c r="K36" s="94" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L36" s="94" t="n">
         <v>-0.34</v>
       </c>
-      <c r="L36" s="94" t="n">
+      <c r="M36" s="94" t="n">
         <v>-0.48</v>
       </c>
-      <c r="M36" s="94" t="n">
+      <c r="N36" s="94" t="n">
         <v>-0.33</v>
       </c>
-      <c r="N36" s="94" t="n">
+      <c r="O36" s="94" t="n">
         <v>-0.23</v>
-      </c>
-      <c r="O36" s="94" t="n">
-        <v>-0.11</v>
       </c>
       <c r="P36" s="94" t="n">
         <v>-0.11</v>
       </c>
       <c r="Q36" s="94" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="R36" s="94" t="n">
         <v>-0.71</v>
       </c>
-      <c r="R36" s="94" t="n">
+      <c r="S36" s="94" t="n">
         <v>-1.09</v>
       </c>
-      <c r="S36" s="94" t="n">
+      <c r="T36" s="94" t="n">
         <v>-2.16</v>
       </c>
-      <c r="T36" s="94" t="n">
+      <c r="U36" s="94" t="n">
         <v>-1.76</v>
-      </c>
-      <c r="U36" s="94" t="n">
-        <v>-2.08</v>
       </c>
       <c r="V36" s="94" t="n">
         <v>-2.08</v>
       </c>
       <c r="W36" s="94" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="X36" s="94" t="n">
         <v>-0.79</v>
-      </c>
-      <c r="X36" s="94" t="n">
-        <v>-1.09</v>
       </c>
       <c r="Y36" s="94" t="n">
         <v>-1.09</v>
       </c>
       <c r="Z36" s="94" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="AA36" s="94" t="n">
         <v>-0.92</v>
-      </c>
-      <c r="AA36" s="94" t="n">
-        <v>-0.84</v>
       </c>
       <c r="AB36" s="94" t="n">
         <v>-0.84</v>
       </c>
       <c r="AC36" s="94" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="AD36" s="94" t="n">
         <v>-1.61</v>
       </c>
-      <c r="AD36" s="94" t="n">
+      <c r="AE36" s="94" t="n">
         <v>-0.74</v>
-      </c>
-      <c r="AE36" s="94" t="n">
-        <v>-1.77</v>
       </c>
     </row>
     <row r="37">
@@ -10442,85 +10432,85 @@
         <v>85.3</v>
       </c>
       <c r="E37" s="94" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="F37" s="94" t="n">
         <v>80.56</v>
       </c>
-      <c r="F37" s="94" t="n">
+      <c r="G37" s="94" t="n">
         <v>39.31</v>
       </c>
-      <c r="G37" s="94" t="n">
+      <c r="H37" s="94" t="n">
         <v>55.71</v>
       </c>
-      <c r="H37" s="94" t="n">
+      <c r="I37" s="94" t="n">
         <v>76.36</v>
-      </c>
-      <c r="I37" s="94" t="n">
-        <v>75.59</v>
       </c>
       <c r="J37" s="94" t="n">
         <v>75.59</v>
       </c>
       <c r="K37" s="94" t="n">
+        <v>75.59</v>
+      </c>
+      <c r="L37" s="94" t="n">
         <v>63.48</v>
       </c>
-      <c r="L37" s="94" t="n">
+      <c r="M37" s="94" t="n">
         <v>47.6</v>
       </c>
-      <c r="M37" s="94" t="n">
+      <c r="N37" s="94" t="n">
         <v>21.39</v>
       </c>
-      <c r="N37" s="94" t="n">
+      <c r="O37" s="94" t="n">
         <v>30.94</v>
-      </c>
-      <c r="O37" s="94" t="n">
-        <v>9.859999999999999</v>
       </c>
       <c r="P37" s="94" t="n">
         <v>9.859999999999999</v>
       </c>
       <c r="Q37" s="94" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="R37" s="94" t="n">
         <v>24.76</v>
       </c>
-      <c r="R37" s="94" t="n">
+      <c r="S37" s="94" t="n">
         <v>37.84</v>
       </c>
-      <c r="S37" s="94" t="n">
+      <c r="T37" s="94" t="n">
         <v>14.49</v>
       </c>
-      <c r="T37" s="94" t="n">
+      <c r="U37" s="94" t="n">
         <v>11.22</v>
-      </c>
-      <c r="U37" s="94" t="n">
-        <v>17.28</v>
       </c>
       <c r="V37" s="94" t="n">
         <v>17.28</v>
       </c>
       <c r="W37" s="94" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="X37" s="94" t="n">
         <v>51.04</v>
-      </c>
-      <c r="X37" s="94" t="n">
-        <v>34.51</v>
       </c>
       <c r="Y37" s="94" t="n">
         <v>34.51</v>
       </c>
       <c r="Z37" s="94" t="n">
+        <v>34.51</v>
+      </c>
+      <c r="AA37" s="94" t="n">
         <v>57.76</v>
-      </c>
-      <c r="AA37" s="94" t="n">
-        <v>78.84999999999999</v>
       </c>
       <c r="AB37" s="94" t="n">
         <v>78.84999999999999</v>
       </c>
       <c r="AC37" s="94" t="n">
+        <v>78.84999999999999</v>
+      </c>
+      <c r="AD37" s="94" t="n">
         <v>74.3</v>
       </c>
-      <c r="AD37" s="94" t="n">
+      <c r="AE37" s="94" t="n">
         <v>80.23</v>
-      </c>
-      <c r="AE37" s="94" t="n">
-        <v>47.65</v>
       </c>
     </row>
     <row r="38">
@@ -10529,155 +10519,153 @@
           <t>sensex:EIDE</t>
         </is>
       </c>
-      <c r="B38" s="93" t="inlineStr">
+      <c r="B38" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C38" s="92" t="inlineStr">
+      <c r="D38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D38" s="92" t="inlineStr">
+      <c r="E38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E38" s="92" t="inlineStr">
+      <c r="F38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F38" s="92" t="inlineStr">
+      <c r="G38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G38" s="93" t="inlineStr">
+      <c r="H38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H38" s="92" t="inlineStr">
+      <c r="I38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I38" s="92" t="inlineStr">
+      <c r="J38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J38" s="92" t="inlineStr">
+      <c r="K38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K38" s="92" t="inlineStr">
+      <c r="L38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L38" s="92" t="inlineStr">
+      <c r="M38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M38" s="93" t="inlineStr">
+      <c r="N38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N38" s="93" t="inlineStr">
+      <c r="O38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O38" s="93" t="inlineStr">
+      <c r="P38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P38" s="93" t="inlineStr">
+      <c r="Q38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q38" s="93" t="inlineStr">
+      <c r="R38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R38" s="92" t="inlineStr">
+      <c r="S38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S38" s="93" t="inlineStr">
+      <c r="T38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T38" s="93" t="inlineStr">
+      <c r="U38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U38" s="91" t="inlineStr">
+      <c r="V38" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V38" s="91" t="inlineStr">
+      <c r="W38" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W38" s="91" t="inlineStr">
+      <c r="X38" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X38" s="92" t="inlineStr">
+      <c r="Y38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y38" s="92" t="inlineStr">
+      <c r="Z38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z38" s="92" t="inlineStr">
+      <c r="AA38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA38" s="92" t="inlineStr">
+      <c r="AB38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB38" s="92" t="inlineStr">
+      <c r="AC38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC38" s="92" t="inlineStr">
+      <c r="AD38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD38" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE38" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
+      <c r="AE38" s="92" t="n">
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -10687,94 +10675,94 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
+        <v>-3.92</v>
+      </c>
+      <c r="C39" s="94" t="n">
         <v>-5.72</v>
-      </c>
-      <c r="C39" s="94" t="n">
-        <v>-5.2</v>
       </c>
       <c r="D39" s="94" t="n">
         <v>-5.2</v>
       </c>
       <c r="E39" s="94" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="F39" s="94" t="n">
         <v>-4.36</v>
       </c>
-      <c r="F39" s="94" t="n">
+      <c r="G39" s="94" t="n">
         <v>-3.77</v>
       </c>
-      <c r="G39" s="94" t="n">
+      <c r="H39" s="94" t="n">
         <v>-5.28</v>
       </c>
-      <c r="H39" s="94" t="n">
+      <c r="I39" s="94" t="n">
         <v>-3.76</v>
-      </c>
-      <c r="I39" s="94" t="n">
-        <v>-4.49</v>
       </c>
       <c r="J39" s="94" t="n">
         <v>-4.49</v>
       </c>
       <c r="K39" s="94" t="n">
+        <v>-4.49</v>
+      </c>
+      <c r="L39" s="94" t="n">
         <v>-5.06</v>
       </c>
-      <c r="L39" s="94" t="n">
+      <c r="M39" s="94" t="n">
         <v>-5.54</v>
       </c>
-      <c r="M39" s="94" t="n">
+      <c r="N39" s="94" t="n">
         <v>-5.56</v>
       </c>
-      <c r="N39" s="94" t="n">
+      <c r="O39" s="94" t="n">
         <v>-6.35</v>
-      </c>
-      <c r="O39" s="94" t="n">
-        <v>-5.43</v>
       </c>
       <c r="P39" s="94" t="n">
         <v>-5.43</v>
       </c>
       <c r="Q39" s="94" t="n">
+        <v>-5.43</v>
+      </c>
+      <c r="R39" s="94" t="n">
         <v>-5.31</v>
       </c>
-      <c r="R39" s="94" t="n">
+      <c r="S39" s="94" t="n">
         <v>-3.97</v>
       </c>
-      <c r="S39" s="94" t="n">
+      <c r="T39" s="94" t="n">
         <v>-4.18</v>
       </c>
-      <c r="T39" s="94" t="n">
+      <c r="U39" s="94" t="n">
         <v>-4.3</v>
-      </c>
-      <c r="U39" s="94" t="n">
-        <v>-2.95</v>
       </c>
       <c r="V39" s="94" t="n">
         <v>-2.95</v>
       </c>
       <c r="W39" s="94" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="X39" s="94" t="n">
         <v>-1.36</v>
       </c>
-      <c r="X39" s="94" t="n">
+      <c r="Y39" s="94" t="n">
         <v>-3.89</v>
       </c>
-      <c r="Y39" s="94" t="n">
+      <c r="Z39" s="94" t="n">
         <v>-5.28</v>
       </c>
-      <c r="Z39" s="94" t="n">
+      <c r="AA39" s="94" t="n">
         <v>-7.14</v>
-      </c>
-      <c r="AA39" s="94" t="n">
-        <v>-6.64</v>
       </c>
       <c r="AB39" s="94" t="n">
         <v>-6.64</v>
       </c>
       <c r="AC39" s="94" t="n">
+        <v>-6.64</v>
+      </c>
+      <c r="AD39" s="94" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="AD39" s="94" t="n">
-        <v>-8.58</v>
-      </c>
       <c r="AE39" s="94" t="n">
-        <v>-8.58</v>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -10784,191 +10772,191 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="C40" s="94" t="n">
         <v>-4.11</v>
-      </c>
-      <c r="C40" s="94" t="n">
-        <v>-3.26</v>
       </c>
       <c r="D40" s="94" t="n">
         <v>-3.26</v>
       </c>
       <c r="E40" s="94" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="F40" s="94" t="n">
         <v>-5.51</v>
       </c>
-      <c r="F40" s="94" t="n">
+      <c r="G40" s="94" t="n">
         <v>-6.67</v>
       </c>
-      <c r="G40" s="94" t="n">
+      <c r="H40" s="94" t="n">
         <v>-7.22</v>
       </c>
-      <c r="H40" s="94" t="n">
+      <c r="I40" s="94" t="n">
         <v>-5.38</v>
-      </c>
-      <c r="I40" s="94" t="n">
-        <v>-5.82</v>
       </c>
       <c r="J40" s="94" t="n">
         <v>-5.82</v>
       </c>
       <c r="K40" s="94" t="n">
+        <v>-5.82</v>
+      </c>
+      <c r="L40" s="94" t="n">
         <v>-5.27</v>
       </c>
-      <c r="L40" s="94" t="n">
+      <c r="M40" s="94" t="n">
         <v>-4.14</v>
       </c>
-      <c r="M40" s="94" t="n">
+      <c r="N40" s="94" t="n">
         <v>-4.55</v>
       </c>
-      <c r="N40" s="94" t="n">
+      <c r="O40" s="94" t="n">
         <v>-5.1</v>
-      </c>
-      <c r="O40" s="94" t="n">
-        <v>-3.88</v>
       </c>
       <c r="P40" s="94" t="n">
         <v>-3.88</v>
       </c>
       <c r="Q40" s="94" t="n">
+        <v>-3.88</v>
+      </c>
+      <c r="R40" s="94" t="n">
         <v>-3.7</v>
       </c>
-      <c r="R40" s="94" t="n">
+      <c r="S40" s="94" t="n">
         <v>-3.93</v>
       </c>
-      <c r="S40" s="94" t="n">
+      <c r="T40" s="94" t="n">
         <v>-3.12</v>
       </c>
-      <c r="T40" s="94" t="n">
+      <c r="U40" s="94" t="n">
         <v>-3.35</v>
-      </c>
-      <c r="U40" s="94" t="n">
-        <v>-1.61</v>
       </c>
       <c r="V40" s="94" t="n">
         <v>-1.61</v>
       </c>
       <c r="W40" s="94" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="X40" s="94" t="n">
         <v>0.06</v>
       </c>
-      <c r="X40" s="94" t="n">
+      <c r="Y40" s="94" t="n">
         <v>-1.77</v>
       </c>
-      <c r="Y40" s="94" t="n">
+      <c r="Z40" s="94" t="n">
         <v>-2.75</v>
       </c>
-      <c r="Z40" s="94" t="n">
+      <c r="AA40" s="94" t="n">
         <v>-2.14</v>
-      </c>
-      <c r="AA40" s="94" t="n">
-        <v>-1.62</v>
       </c>
       <c r="AB40" s="94" t="n">
         <v>-1.62</v>
       </c>
       <c r="AC40" s="94" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="AD40" s="94" t="n">
         <v>-1.97</v>
       </c>
-      <c r="AD40" s="94" t="n">
-        <v>-1.89</v>
-      </c>
       <c r="AE40" s="94" t="n">
-        <v>-1.89</v>
+        <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="96" t="inlineStr">
+      <c r="A41" s="76" t="inlineStr">
         <is>
           <t>sensex:RS10</t>
         </is>
       </c>
       <c r="B41" s="94" t="n">
+        <v>42.74</v>
+      </c>
+      <c r="C41" s="94" t="n">
         <v>31.52</v>
-      </c>
-      <c r="C41" s="94" t="n">
-        <v>37.51</v>
       </c>
       <c r="D41" s="94" t="n">
         <v>37.51</v>
       </c>
       <c r="E41" s="94" t="n">
+        <v>37.51</v>
+      </c>
+      <c r="F41" s="94" t="n">
         <v>40.26</v>
       </c>
-      <c r="F41" s="94" t="n">
+      <c r="G41" s="94" t="n">
         <v>38.85</v>
       </c>
-      <c r="G41" s="94" t="n">
+      <c r="H41" s="94" t="n">
         <v>31.71</v>
       </c>
-      <c r="H41" s="94" t="n">
+      <c r="I41" s="94" t="n">
         <v>41.13</v>
-      </c>
-      <c r="I41" s="94" t="n">
-        <v>34.71</v>
       </c>
       <c r="J41" s="94" t="n">
         <v>34.71</v>
       </c>
       <c r="K41" s="94" t="n">
+        <v>34.71</v>
+      </c>
+      <c r="L41" s="94" t="n">
         <v>38.21</v>
       </c>
-      <c r="L41" s="94" t="n">
+      <c r="M41" s="94" t="n">
         <v>33.68</v>
       </c>
-      <c r="M41" s="94" t="n">
+      <c r="N41" s="94" t="n">
         <v>30.45</v>
       </c>
-      <c r="N41" s="94" t="n">
+      <c r="O41" s="94" t="n">
         <v>28.07</v>
-      </c>
-      <c r="O41" s="94" t="n">
-        <v>34.68</v>
       </c>
       <c r="P41" s="94" t="n">
         <v>34.68</v>
       </c>
       <c r="Q41" s="94" t="n">
+        <v>34.68</v>
+      </c>
+      <c r="R41" s="94" t="n">
         <v>36.46</v>
       </c>
-      <c r="R41" s="94" t="n">
+      <c r="S41" s="94" t="n">
         <v>40.56</v>
       </c>
-      <c r="S41" s="94" t="n">
+      <c r="T41" s="94" t="n">
         <v>40.95</v>
       </c>
-      <c r="T41" s="94" t="n">
+      <c r="U41" s="94" t="n">
         <v>38.45</v>
-      </c>
-      <c r="U41" s="94" t="n">
-        <v>48.38</v>
       </c>
       <c r="V41" s="94" t="n">
         <v>48.38</v>
       </c>
       <c r="W41" s="94" t="n">
+        <v>48.38</v>
+      </c>
+      <c r="X41" s="94" t="n">
         <v>55.82</v>
       </c>
-      <c r="X41" s="94" t="n">
+      <c r="Y41" s="94" t="n">
         <v>39</v>
       </c>
-      <c r="Y41" s="94" t="n">
+      <c r="Z41" s="94" t="n">
         <v>33.12</v>
       </c>
-      <c r="Z41" s="94" t="n">
+      <c r="AA41" s="94" t="n">
         <v>34</v>
-      </c>
-      <c r="AA41" s="94" t="n">
-        <v>37.69</v>
       </c>
       <c r="AB41" s="94" t="n">
         <v>37.69</v>
       </c>
       <c r="AC41" s="94" t="n">
-        <v>34.47</v>
+        <v>37.69</v>
       </c>
       <c r="AD41" s="94" t="n">
         <v>34.47</v>
       </c>
       <c r="AE41" s="94" t="n">
-        <v>34.47</v>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -10982,150 +10970,146 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="C42" s="91" t="inlineStr">
+      <c r="C42" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D42" s="91" t="inlineStr">
+      <c r="E42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E42" s="91" t="inlineStr">
+      <c r="F42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F42" s="91" t="inlineStr">
+      <c r="G42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G42" s="91" t="inlineStr">
+      <c r="H42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H42" s="91" t="inlineStr">
+      <c r="I42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I42" s="91" t="inlineStr">
+      <c r="J42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J42" s="91" t="inlineStr">
+      <c r="K42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K42" s="91" t="inlineStr">
+      <c r="L42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L42" s="91" t="inlineStr">
+      <c r="M42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M42" s="92" t="inlineStr">
+      <c r="N42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N42" s="92" t="inlineStr">
+      <c r="O42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O42" s="92" t="inlineStr">
+      <c r="P42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P42" s="92" t="inlineStr">
+      <c r="Q42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q42" s="91" t="inlineStr">
+      <c r="R42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R42" s="91" t="inlineStr">
+      <c r="S42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S42" s="91" t="inlineStr">
+      <c r="T42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T42" s="91" t="inlineStr">
+      <c r="U42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U42" s="93" t="inlineStr">
+      <c r="V42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V42" s="93" t="inlineStr">
+      <c r="W42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W42" s="91" t="inlineStr">
+      <c r="X42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X42" s="91" t="inlineStr">
+      <c r="Y42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y42" s="91" t="inlineStr">
+      <c r="Z42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z42" s="92" t="inlineStr">
+      <c r="AA42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA42" s="91" t="inlineStr">
+      <c r="AB42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB42" s="91" t="inlineStr">
+      <c r="AC42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
+      <c r="AD42" s="92" t="n">
+        <v/>
+      </c>
+      <c r="AE42" s="92" t="n">
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -11135,94 +11119,94 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C43" s="94" t="n">
         <v>6.44</v>
-      </c>
-      <c r="C43" s="94" t="n">
-        <v>5.55</v>
       </c>
       <c r="D43" s="94" t="n">
         <v>5.55</v>
       </c>
       <c r="E43" s="94" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="F43" s="94" t="n">
         <v>4.44</v>
       </c>
-      <c r="F43" s="94" t="n">
+      <c r="G43" s="94" t="n">
         <v>4.53</v>
       </c>
-      <c r="G43" s="94" t="n">
+      <c r="H43" s="94" t="n">
         <v>3.57</v>
       </c>
-      <c r="H43" s="94" t="n">
+      <c r="I43" s="94" t="n">
         <v>3.15</v>
-      </c>
-      <c r="I43" s="94" t="n">
-        <v>2.32</v>
       </c>
       <c r="J43" s="94" t="n">
         <v>2.32</v>
       </c>
       <c r="K43" s="94" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="L43" s="94" t="n">
         <v>1.31</v>
       </c>
-      <c r="L43" s="94" t="n">
+      <c r="M43" s="94" t="n">
         <v>-1.82</v>
       </c>
-      <c r="M43" s="94" t="n">
+      <c r="N43" s="94" t="n">
         <v>-2.11</v>
       </c>
-      <c r="N43" s="94" t="n">
+      <c r="O43" s="94" t="n">
         <v>-1.11</v>
-      </c>
-      <c r="O43" s="94" t="n">
-        <v>-1.21</v>
       </c>
       <c r="P43" s="94" t="n">
         <v>-1.21</v>
       </c>
       <c r="Q43" s="94" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="R43" s="94" t="n">
         <v>-1.47</v>
       </c>
-      <c r="R43" s="94" t="n">
+      <c r="S43" s="94" t="n">
         <v>-1.66</v>
       </c>
-      <c r="S43" s="94" t="n">
+      <c r="T43" s="94" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="T43" s="94" t="n">
+      <c r="U43" s="94" t="n">
         <v>-1.51</v>
-      </c>
-      <c r="U43" s="94" t="n">
-        <v>-3.18</v>
       </c>
       <c r="V43" s="94" t="n">
         <v>-3.18</v>
       </c>
       <c r="W43" s="94" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="X43" s="94" t="n">
         <v>-2.41</v>
-      </c>
-      <c r="X43" s="94" t="n">
-        <v>-2.13</v>
       </c>
       <c r="Y43" s="94" t="n">
         <v>-2.13</v>
       </c>
       <c r="Z43" s="94" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="AA43" s="94" t="n">
         <v>-2.2</v>
-      </c>
-      <c r="AA43" s="94" t="n">
-        <v>-2.93</v>
       </c>
       <c r="AB43" s="94" t="n">
         <v>-2.93</v>
       </c>
       <c r="AC43" s="94" t="n">
-        <v>-3.85</v>
+        <v>-2.93</v>
       </c>
       <c r="AD43" s="94" t="n">
-        <v>-3.85</v>
+        <v/>
       </c>
       <c r="AE43" s="94" t="n">
-        <v>-3.85</v>
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -11232,94 +11216,94 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="C44" s="94" t="n">
         <v>8.82</v>
-      </c>
-      <c r="C44" s="94" t="n">
-        <v>11.19</v>
       </c>
       <c r="D44" s="94" t="n">
         <v>11.19</v>
       </c>
       <c r="E44" s="94" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="F44" s="94" t="n">
         <v>10.4</v>
       </c>
-      <c r="F44" s="94" t="n">
+      <c r="G44" s="94" t="n">
         <v>8.08</v>
       </c>
-      <c r="G44" s="94" t="n">
+      <c r="H44" s="94" t="n">
         <v>5.43</v>
       </c>
-      <c r="H44" s="94" t="n">
+      <c r="I44" s="94" t="n">
         <v>2.68</v>
-      </c>
-      <c r="I44" s="94" t="n">
-        <v>3.14</v>
       </c>
       <c r="J44" s="94" t="n">
         <v>3.14</v>
       </c>
       <c r="K44" s="94" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="L44" s="94" t="n">
         <v>2.56</v>
       </c>
-      <c r="L44" s="94" t="n">
+      <c r="M44" s="94" t="n">
         <v>-0.57</v>
       </c>
-      <c r="M44" s="94" t="n">
+      <c r="N44" s="94" t="n">
         <v>-0.05</v>
       </c>
-      <c r="N44" s="94" t="n">
+      <c r="O44" s="94" t="n">
         <v>-1.4</v>
-      </c>
-      <c r="O44" s="94" t="n">
-        <v>-2.21</v>
       </c>
       <c r="P44" s="94" t="n">
         <v>-2.21</v>
       </c>
       <c r="Q44" s="94" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="R44" s="94" t="n">
         <v>-1.73</v>
       </c>
-      <c r="R44" s="94" t="n">
+      <c r="S44" s="94" t="n">
         <v>-1.09</v>
       </c>
-      <c r="S44" s="94" t="n">
+      <c r="T44" s="94" t="n">
         <v>-1.28</v>
       </c>
-      <c r="T44" s="94" t="n">
+      <c r="U44" s="94" t="n">
         <v>-1.65</v>
-      </c>
-      <c r="U44" s="94" t="n">
-        <v>-3.93</v>
       </c>
       <c r="V44" s="94" t="n">
         <v>-3.93</v>
       </c>
       <c r="W44" s="94" t="n">
+        <v>-3.93</v>
+      </c>
+      <c r="X44" s="94" t="n">
         <v>-3.13</v>
-      </c>
-      <c r="X44" s="94" t="n">
-        <v>-4.45</v>
       </c>
       <c r="Y44" s="94" t="n">
         <v>-4.45</v>
       </c>
       <c r="Z44" s="94" t="n">
+        <v>-4.45</v>
+      </c>
+      <c r="AA44" s="94" t="n">
         <v>-4.11</v>
-      </c>
-      <c r="AA44" s="94" t="n">
-        <v>-2.88</v>
       </c>
       <c r="AB44" s="94" t="n">
         <v>-2.88</v>
       </c>
       <c r="AC44" s="94" t="n">
-        <v>-3.01</v>
+        <v>-2.88</v>
       </c>
       <c r="AD44" s="94" t="n">
-        <v>-3.01</v>
+        <v/>
       </c>
       <c r="AE44" s="94" t="n">
-        <v>-3.01</v>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -11329,94 +11313,94 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
+        <v>79.53</v>
+      </c>
+      <c r="C45" s="94" t="n">
         <v>84.89</v>
-      </c>
-      <c r="C45" s="94" t="n">
-        <v>93.34</v>
       </c>
       <c r="D45" s="94" t="n">
         <v>93.34</v>
       </c>
       <c r="E45" s="94" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="F45" s="94" t="n">
         <v>92.31999999999999</v>
       </c>
-      <c r="F45" s="94" t="n">
+      <c r="G45" s="94" t="n">
         <v>90.48999999999999</v>
       </c>
-      <c r="G45" s="94" t="n">
+      <c r="H45" s="94" t="n">
         <v>87.65000000000001</v>
       </c>
-      <c r="H45" s="94" t="n">
+      <c r="I45" s="94" t="n">
         <v>85.73</v>
-      </c>
-      <c r="I45" s="94" t="n">
-        <v>84.51000000000001</v>
       </c>
       <c r="J45" s="94" t="n">
         <v>84.51000000000001</v>
       </c>
       <c r="K45" s="94" t="n">
+        <v>84.51000000000001</v>
+      </c>
+      <c r="L45" s="94" t="n">
         <v>80.23</v>
       </c>
-      <c r="L45" s="94" t="n">
+      <c r="M45" s="94" t="n">
         <v>62.6</v>
       </c>
-      <c r="M45" s="94" t="n">
+      <c r="N45" s="94" t="n">
         <v>51.62</v>
       </c>
-      <c r="N45" s="94" t="n">
+      <c r="O45" s="94" t="n">
         <v>48.02</v>
-      </c>
-      <c r="O45" s="94" t="n">
-        <v>52.7</v>
       </c>
       <c r="P45" s="94" t="n">
         <v>52.7</v>
       </c>
       <c r="Q45" s="94" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="R45" s="94" t="n">
         <v>66.38</v>
       </c>
-      <c r="R45" s="94" t="n">
+      <c r="S45" s="94" t="n">
         <v>61.23</v>
       </c>
-      <c r="S45" s="94" t="n">
+      <c r="T45" s="94" t="n">
         <v>69.54000000000001</v>
       </c>
-      <c r="T45" s="94" t="n">
+      <c r="U45" s="94" t="n">
         <v>65.06</v>
-      </c>
-      <c r="U45" s="94" t="n">
-        <v>37.52</v>
       </c>
       <c r="V45" s="94" t="n">
         <v>37.52</v>
       </c>
       <c r="W45" s="94" t="n">
+        <v>37.52</v>
+      </c>
+      <c r="X45" s="94" t="n">
         <v>65.84</v>
-      </c>
-      <c r="X45" s="94" t="n">
-        <v>63.25</v>
       </c>
       <c r="Y45" s="94" t="n">
         <v>63.25</v>
       </c>
       <c r="Z45" s="94" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="AA45" s="94" t="n">
         <v>46.49</v>
-      </c>
-      <c r="AA45" s="94" t="n">
-        <v>60.14</v>
       </c>
       <c r="AB45" s="94" t="n">
         <v>60.14</v>
       </c>
       <c r="AC45" s="94" t="n">
-        <v>32.65</v>
+        <v>60.14</v>
       </c>
       <c r="AD45" s="94" t="n">
-        <v>32.65</v>
+        <v/>
       </c>
       <c r="AE45" s="94" t="n">
-        <v>32.65</v>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -11440,128 +11424,130 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="E46" s="91" t="inlineStr">
+      <c r="E46" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F46" s="91" t="inlineStr">
+      <c r="G46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G46" s="91" t="inlineStr">
+      <c r="H46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H46" s="91" t="inlineStr">
+      <c r="I46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I46" s="91" t="inlineStr">
+      <c r="J46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J46" s="91" t="inlineStr">
+      <c r="K46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K46" s="91" t="inlineStr">
+      <c r="L46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L46" s="91" t="inlineStr">
+      <c r="M46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M46" s="91" t="inlineStr">
+      <c r="N46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N46" s="93" t="inlineStr">
+      <c r="O46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O46" s="92" t="inlineStr">
+      <c r="P46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P46" s="92" t="inlineStr">
+      <c r="Q46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q46" s="91" t="inlineStr">
+      <c r="R46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R46" s="91" t="inlineStr">
+      <c r="S46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S46" s="91" t="inlineStr">
+      <c r="T46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T46" s="91" t="inlineStr">
+      <c r="U46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U46" s="93" t="inlineStr">
+      <c r="V46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V46" s="93" t="inlineStr">
+      <c r="W46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W46" s="92" t="inlineStr">
+      <c r="X46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X46" s="93" t="inlineStr">
+      <c r="Y46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y46" s="93" t="inlineStr">
+      <c r="Z46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z46" s="93" t="inlineStr">
+      <c r="AA46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA46" s="93" t="inlineStr">
+      <c r="AB46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB46" s="93" t="inlineStr">
+      <c r="AC46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
-      </c>
-      <c r="AC46" s="92" t="n">
-        <v/>
       </c>
       <c r="AD46" s="92" t="n">
         <v/>
@@ -11580,70 +11566,70 @@
         <v>8.960000000000001</v>
       </c>
       <c r="C47" s="94" t="n">
-        <v>9.92</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="D47" s="94" t="n">
         <v>9.92</v>
       </c>
       <c r="E47" s="94" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="F47" s="94" t="n">
         <v>10.12</v>
       </c>
-      <c r="F47" s="94" t="n">
+      <c r="G47" s="94" t="n">
         <v>9.68</v>
       </c>
-      <c r="G47" s="94" t="n">
+      <c r="H47" s="94" t="n">
         <v>8.34</v>
       </c>
-      <c r="H47" s="94" t="n">
+      <c r="I47" s="94" t="n">
         <v>7.86</v>
-      </c>
-      <c r="I47" s="94" t="n">
-        <v>6.34</v>
       </c>
       <c r="J47" s="94" t="n">
         <v>6.34</v>
       </c>
       <c r="K47" s="94" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="L47" s="94" t="n">
         <v>5.47</v>
       </c>
-      <c r="L47" s="94" t="n">
+      <c r="M47" s="94" t="n">
         <v>5.88</v>
       </c>
-      <c r="M47" s="94" t="n">
+      <c r="N47" s="94" t="n">
         <v>4.03</v>
       </c>
-      <c r="N47" s="94" t="n">
+      <c r="O47" s="94" t="n">
         <v>3.2</v>
-      </c>
-      <c r="O47" s="94" t="n">
-        <v>4.34</v>
       </c>
       <c r="P47" s="94" t="n">
         <v>4.34</v>
       </c>
       <c r="Q47" s="94" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="R47" s="94" t="n">
         <v>5.76</v>
       </c>
-      <c r="R47" s="94" t="n">
+      <c r="S47" s="94" t="n">
         <v>5.58</v>
       </c>
-      <c r="S47" s="94" t="n">
+      <c r="T47" s="94" t="n">
         <v>6.68</v>
       </c>
-      <c r="T47" s="94" t="n">
+      <c r="U47" s="94" t="n">
         <v>5.82</v>
-      </c>
-      <c r="U47" s="94" t="n">
-        <v>4.11</v>
       </c>
       <c r="V47" s="94" t="n">
         <v>4.11</v>
       </c>
       <c r="W47" s="94" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="X47" s="94" t="n">
         <v>5.31</v>
-      </c>
-      <c r="X47" s="94" t="n">
-        <v>3.88</v>
       </c>
       <c r="Y47" s="94" t="n">
         <v>3.88</v>
@@ -11652,13 +11638,13 @@
         <v>3.88</v>
       </c>
       <c r="AA47" s="94" t="n">
-        <v>4.01</v>
+        <v>3.88</v>
       </c>
       <c r="AB47" s="94" t="n">
         <v>4.01</v>
       </c>
       <c r="AC47" s="94" t="n">
-        <v/>
+        <v>4.01</v>
       </c>
       <c r="AD47" s="94" t="n">
         <v/>
@@ -11677,70 +11663,70 @@
         <v>22.74</v>
       </c>
       <c r="C48" s="94" t="n">
-        <v>21.14</v>
+        <v>22.74</v>
       </c>
       <c r="D48" s="94" t="n">
         <v>21.14</v>
       </c>
       <c r="E48" s="94" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="F48" s="94" t="n">
         <v>18.41</v>
       </c>
-      <c r="F48" s="94" t="n">
+      <c r="G48" s="94" t="n">
         <v>14.83</v>
       </c>
-      <c r="G48" s="94" t="n">
+      <c r="H48" s="94" t="n">
         <v>14.29</v>
       </c>
-      <c r="H48" s="94" t="n">
+      <c r="I48" s="94" t="n">
         <v>14.57</v>
-      </c>
-      <c r="I48" s="94" t="n">
-        <v>13.5</v>
       </c>
       <c r="J48" s="94" t="n">
         <v>13.5</v>
       </c>
       <c r="K48" s="94" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L48" s="94" t="n">
         <v>12.88</v>
       </c>
-      <c r="L48" s="94" t="n">
+      <c r="M48" s="94" t="n">
         <v>11.9</v>
       </c>
-      <c r="M48" s="94" t="n">
+      <c r="N48" s="94" t="n">
         <v>9.23</v>
       </c>
-      <c r="N48" s="94" t="n">
+      <c r="O48" s="94" t="n">
         <v>9.380000000000001</v>
-      </c>
-      <c r="O48" s="94" t="n">
-        <v>11.24</v>
       </c>
       <c r="P48" s="94" t="n">
         <v>11.24</v>
       </c>
       <c r="Q48" s="94" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="R48" s="94" t="n">
         <v>10.69</v>
       </c>
-      <c r="R48" s="94" t="n">
+      <c r="S48" s="94" t="n">
         <v>10.27</v>
       </c>
-      <c r="S48" s="94" t="n">
+      <c r="T48" s="94" t="n">
         <v>9.84</v>
       </c>
-      <c r="T48" s="94" t="n">
+      <c r="U48" s="94" t="n">
         <v>8.74</v>
-      </c>
-      <c r="U48" s="94" t="n">
-        <v>6.18</v>
       </c>
       <c r="V48" s="94" t="n">
         <v>6.18</v>
       </c>
       <c r="W48" s="94" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="X48" s="94" t="n">
         <v>8.039999999999999</v>
-      </c>
-      <c r="X48" s="94" t="n">
-        <v>8.16</v>
       </c>
       <c r="Y48" s="94" t="n">
         <v>8.16</v>
@@ -11749,13 +11735,13 @@
         <v>8.16</v>
       </c>
       <c r="AA48" s="94" t="n">
-        <v>9.59</v>
+        <v>8.16</v>
       </c>
       <c r="AB48" s="94" t="n">
         <v>9.59</v>
       </c>
       <c r="AC48" s="94" t="n">
-        <v/>
+        <v>9.59</v>
       </c>
       <c r="AD48" s="94" t="n">
         <v/>
@@ -11774,70 +11760,70 @@
         <v>75.37</v>
       </c>
       <c r="C49" s="94" t="n">
-        <v>89.53</v>
+        <v>75.37</v>
       </c>
       <c r="D49" s="94" t="n">
         <v>89.53</v>
       </c>
       <c r="E49" s="94" t="n">
+        <v>89.53</v>
+      </c>
+      <c r="F49" s="94" t="n">
         <v>91.64</v>
       </c>
-      <c r="F49" s="94" t="n">
+      <c r="G49" s="94" t="n">
         <v>89.73</v>
       </c>
-      <c r="G49" s="94" t="n">
+      <c r="H49" s="94" t="n">
         <v>86.16</v>
       </c>
-      <c r="H49" s="94" t="n">
+      <c r="I49" s="94" t="n">
         <v>85.12</v>
-      </c>
-      <c r="I49" s="94" t="n">
-        <v>83.34999999999999</v>
       </c>
       <c r="J49" s="94" t="n">
         <v>83.34999999999999</v>
       </c>
       <c r="K49" s="94" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="L49" s="94" t="n">
         <v>76.81</v>
       </c>
-      <c r="L49" s="94" t="n">
+      <c r="M49" s="94" t="n">
         <v>74.04000000000001</v>
       </c>
-      <c r="M49" s="94" t="n">
+      <c r="N49" s="94" t="n">
         <v>58.54</v>
       </c>
-      <c r="N49" s="94" t="n">
+      <c r="O49" s="94" t="n">
         <v>46.37</v>
-      </c>
-      <c r="O49" s="94" t="n">
-        <v>54.22</v>
       </c>
       <c r="P49" s="94" t="n">
         <v>54.22</v>
       </c>
       <c r="Q49" s="94" t="n">
+        <v>54.22</v>
+      </c>
+      <c r="R49" s="94" t="n">
         <v>65.81999999999999</v>
       </c>
-      <c r="R49" s="94" t="n">
+      <c r="S49" s="94" t="n">
         <v>67.31999999999999</v>
       </c>
-      <c r="S49" s="94" t="n">
+      <c r="T49" s="94" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="T49" s="94" t="n">
+      <c r="U49" s="94" t="n">
         <v>62.55</v>
-      </c>
-      <c r="U49" s="94" t="n">
-        <v>39.09</v>
       </c>
       <c r="V49" s="94" t="n">
         <v>39.09</v>
       </c>
       <c r="W49" s="94" t="n">
+        <v>39.09</v>
+      </c>
+      <c r="X49" s="94" t="n">
         <v>48.84</v>
-      </c>
-      <c r="X49" s="94" t="n">
-        <v>35.85</v>
       </c>
       <c r="Y49" s="94" t="n">
         <v>35.85</v>
@@ -11846,13 +11832,13 @@
         <v>35.85</v>
       </c>
       <c r="AA49" s="94" t="n">
-        <v>41.58</v>
+        <v>35.85</v>
       </c>
       <c r="AB49" s="94" t="n">
         <v>41.58</v>
       </c>
       <c r="AC49" s="94" t="n">
-        <v/>
+        <v>41.58</v>
       </c>
       <c r="AD49" s="94" t="n">
         <v/>
@@ -11864,14 +11850,14 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：us500:RS2:16.07&lt;=22;ixic:RS2:8.7&lt;=38;sensex:RS10:31.52&lt;=39</t>
+          <t>今日买报：us500:RS2:16.07&lt;=22;ixic:RS2:8.7&lt;=38</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:74.31&gt;=73;us30:RS3:86.3&gt;=85;vn:RS3:85.3&gt;=85;dax30:RNG120:22.74&gt;=20</t>
+          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:75.39&gt;=73;us30:RS3:86.3&gt;=85;vn:RS3:85.3&gt;=85;dax30:RNG120:22.74&gt;=20</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -8731,9 +8731,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B22" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C22" s="91" t="inlineStr">
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>5.49</v>
+        <v>6.2</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>5.49</v>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>12.52</v>
+        <v>15.88</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>12.52</v>
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>86.3</v>
+        <v>89</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>86.3</v>
@@ -9177,9 +9177,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B26" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C26" s="93" t="inlineStr">
@@ -9333,7 +9333,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>4.17</v>
+        <v>5.46</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>4.17</v>
@@ -9430,7 +9430,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>15.29</v>
+        <v>21.81</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>15.29</v>
@@ -9521,13 +9521,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="96" t="inlineStr">
+      <c r="A29" s="76" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>8.699999999999999</v>
+        <v>55.99</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>8.699999999999999</v>
@@ -9781,7 +9781,7 @@
         </is>
       </c>
       <c r="B31" s="94" t="n">
-        <v>0.57</v>
+        <v>0.29</v>
       </c>
       <c r="C31" s="94" t="n">
         <v>2.49</v>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="B32" s="94" t="n">
-        <v>8.949999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="C32" s="94" t="n">
         <v>3.78</v>
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="B33" s="94" t="n">
-        <v>46.45</v>
+        <v>44.81</v>
       </c>
       <c r="C33" s="94" t="n">
         <v>54.76</v>
@@ -10675,7 +10675,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-3.92</v>
+        <v>-4.39</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>-5.72</v>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>-4.02</v>
+        <v>-4.49</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>-4.11</v>
@@ -10863,13 +10863,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="76" t="inlineStr">
+      <c r="A41" s="96" t="inlineStr">
         <is>
           <t>sensex:RS10</t>
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>42.74</v>
+        <v>38.59</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>31.52</v>
@@ -11119,7 +11119,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>7.4</v>
+        <v>7.44</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>6.44</v>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>8.92</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>8.82</v>
@@ -11313,7 +11313,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>79.53</v>
+        <v>80.88</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>84.89</v>
@@ -11557,13 +11557,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="76" t="inlineStr">
+      <c r="A47" s="95" t="inlineStr">
         <is>
           <t>dax30:RNG60</t>
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>8.960000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>8.960000000000001</v>
@@ -11660,7 +11660,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>22.74</v>
+        <v>23.49</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>22.74</v>
@@ -11757,7 +11757,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>75.37</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>75.37</v>
@@ -11850,14 +11850,14 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：us500:RS2:16.07&lt;=22;ixic:RS2:8.7&lt;=38</t>
+          <t>今日买报：us500:RS2:16.07&lt;=22;sensex:RS10:38.59&lt;=39</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:75.39&gt;=73;us30:RS3:86.3&gt;=85;vn:RS3:85.3&gt;=85;dax30:RNG120:22.74&gt;=20</t>
+          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:75.39&gt;=73;us30:RS3:89.0&gt;=85;vn:RS3:85.3&gt;=85;dax30:RNG60:10.02&gt;=10;dax30:RNG120:23.49&gt;=20</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -800,7 +800,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1063,7 +1063,6 @@
     <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6342,152 +6341,152 @@
       </c>
       <c r="B1" s="77" t="inlineStr">
         <is>
+          <t>250129</t>
+        </is>
+      </c>
+      <c r="C1" s="77" t="inlineStr">
+        <is>
           <t>250128</t>
         </is>
       </c>
-      <c r="C1" s="77" t="inlineStr">
+      <c r="D1" s="77" t="inlineStr">
         <is>
           <t>250127</t>
         </is>
       </c>
-      <c r="D1" s="77" t="inlineStr">
+      <c r="E1" s="77" t="inlineStr">
         <is>
           <t>250126</t>
         </is>
       </c>
-      <c r="E1" s="77" t="inlineStr">
+      <c r="F1" s="77" t="inlineStr">
         <is>
           <t>250124</t>
         </is>
       </c>
-      <c r="F1" s="77" t="inlineStr">
+      <c r="G1" s="77" t="inlineStr">
         <is>
           <t>250123</t>
         </is>
       </c>
-      <c r="G1" s="77" t="inlineStr">
+      <c r="H1" s="77" t="inlineStr">
         <is>
           <t>250122</t>
         </is>
       </c>
-      <c r="H1" s="77" t="inlineStr">
+      <c r="I1" s="77" t="inlineStr">
         <is>
           <t>250121</t>
         </is>
       </c>
-      <c r="I1" s="77" t="inlineStr">
+      <c r="J1" s="77" t="inlineStr">
         <is>
           <t>250120</t>
         </is>
       </c>
-      <c r="J1" s="77" t="inlineStr">
+      <c r="K1" s="77" t="inlineStr">
         <is>
           <t>250119</t>
         </is>
       </c>
-      <c r="K1" s="77" t="inlineStr">
+      <c r="L1" s="77" t="inlineStr">
         <is>
           <t>250117</t>
         </is>
       </c>
-      <c r="L1" s="77" t="inlineStr">
+      <c r="M1" s="77" t="inlineStr">
         <is>
           <t>250116</t>
         </is>
       </c>
-      <c r="M1" s="77" t="inlineStr">
+      <c r="N1" s="77" t="inlineStr">
         <is>
           <t>250115</t>
         </is>
       </c>
-      <c r="N1" s="77" t="inlineStr">
+      <c r="O1" s="77" t="inlineStr">
         <is>
           <t>250114</t>
         </is>
       </c>
-      <c r="O1" s="77" t="inlineStr">
+      <c r="P1" s="77" t="inlineStr">
         <is>
           <t>250113</t>
         </is>
       </c>
-      <c r="P1" s="77" t="inlineStr">
+      <c r="Q1" s="77" t="inlineStr">
         <is>
           <t>250112</t>
         </is>
       </c>
-      <c r="Q1" s="77" t="inlineStr">
+      <c r="R1" s="77" t="inlineStr">
         <is>
           <t>250110</t>
         </is>
       </c>
-      <c r="R1" s="77" t="inlineStr">
+      <c r="S1" s="77" t="inlineStr">
         <is>
           <t>250109</t>
         </is>
       </c>
-      <c r="S1" s="77" t="inlineStr">
+      <c r="T1" s="77" t="inlineStr">
         <is>
           <t>250108</t>
         </is>
       </c>
-      <c r="T1" s="77" t="inlineStr">
+      <c r="U1" s="77" t="inlineStr">
         <is>
           <t>250107</t>
         </is>
       </c>
-      <c r="U1" s="77" t="inlineStr">
+      <c r="V1" s="77" t="inlineStr">
         <is>
           <t>250106</t>
         </is>
       </c>
-      <c r="V1" s="77" t="inlineStr">
+      <c r="W1" s="77" t="inlineStr">
         <is>
           <t>250105</t>
         </is>
       </c>
-      <c r="W1" s="77" t="inlineStr">
+      <c r="X1" s="77" t="inlineStr">
         <is>
           <t>250103</t>
         </is>
       </c>
-      <c r="X1" s="77" t="inlineStr">
+      <c r="Y1" s="77" t="inlineStr">
         <is>
           <t>250102</t>
         </is>
       </c>
-      <c r="Y1" s="77" t="inlineStr">
+      <c r="Z1" s="77" t="inlineStr">
         <is>
           <t>250101</t>
         </is>
       </c>
-      <c r="Z1" s="77" t="inlineStr">
+      <c r="AA1" s="77" t="inlineStr">
         <is>
           <t>241231</t>
         </is>
       </c>
-      <c r="AA1" s="77" t="inlineStr">
+      <c r="AB1" s="77" t="inlineStr">
         <is>
           <t>241230</t>
         </is>
       </c>
-      <c r="AB1" s="77" t="inlineStr">
+      <c r="AC1" s="77" t="inlineStr">
         <is>
           <t>241229</t>
         </is>
       </c>
-      <c r="AC1" s="77" t="inlineStr">
+      <c r="AD1" s="77" t="inlineStr">
         <is>
           <t>241227</t>
         </is>
       </c>
-      <c r="AD1" s="77" t="inlineStr">
+      <c r="AE1" s="77" t="inlineStr">
         <is>
           <t>241226</t>
-        </is>
-      </c>
-      <c r="AE1" s="77" t="inlineStr">
-        <is>
-          <t>241225</t>
         </is>
       </c>
     </row>
@@ -6517,114 +6516,114 @@
           <t>red</t>
         </is>
       </c>
-      <c r="F2" s="92" t="inlineStr">
+      <c r="F2" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G2" s="93" t="inlineStr">
+      <c r="H2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H2" s="92" t="inlineStr">
+      <c r="I2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I2" s="92" t="inlineStr">
+      <c r="J2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J2" s="92" t="inlineStr">
+      <c r="K2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K2" s="92" t="inlineStr">
+      <c r="L2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L2" s="92" t="inlineStr">
+      <c r="M2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M2" s="92" t="inlineStr">
+      <c r="N2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N2" s="92" t="inlineStr">
+      <c r="O2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O2" s="92" t="inlineStr">
+      <c r="P2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P2" s="93" t="inlineStr">
+      <c r="Q2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q2" s="93" t="inlineStr">
+      <c r="R2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R2" s="92" t="inlineStr">
+      <c r="S2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S2" s="92" t="inlineStr">
+      <c r="T2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T2" s="92" t="inlineStr">
+      <c r="U2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U2" s="93" t="inlineStr">
+      <c r="V2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V2" s="93" t="inlineStr">
+      <c r="W2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W2" s="93" t="inlineStr">
+      <c r="X2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X2" s="93" t="inlineStr">
+      <c r="Y2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y2" s="93" t="inlineStr">
+      <c r="Z2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z2" s="93" t="inlineStr">
+      <c r="AA2" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AA2" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AB2" s="91" t="inlineStr">
@@ -6661,88 +6660,88 @@
         <v>-0.65</v>
       </c>
       <c r="D3" s="94" t="n">
-        <v>-0.83</v>
+        <v>-0.65</v>
       </c>
       <c r="E3" s="94" t="n">
         <v>-0.83</v>
       </c>
       <c r="F3" s="94" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="G3" s="94" t="n">
         <v>-1.1</v>
       </c>
-      <c r="G3" s="94" t="n">
+      <c r="H3" s="94" t="n">
         <v>-2.21</v>
       </c>
-      <c r="H3" s="94" t="n">
+      <c r="I3" s="94" t="n">
         <v>-2.4</v>
       </c>
-      <c r="I3" s="94" t="n">
+      <c r="J3" s="94" t="n">
         <v>-1.68</v>
-      </c>
-      <c r="J3" s="94" t="n">
-        <v>-1.17</v>
       </c>
       <c r="K3" s="94" t="n">
         <v>-1.17</v>
       </c>
       <c r="L3" s="94" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="M3" s="94" t="n">
         <v>-2.02</v>
       </c>
-      <c r="M3" s="94" t="n">
+      <c r="N3" s="94" t="n">
         <v>-1.79</v>
       </c>
-      <c r="N3" s="94" t="n">
+      <c r="O3" s="94" t="n">
         <v>-0.83</v>
       </c>
-      <c r="O3" s="94" t="n">
+      <c r="P3" s="94" t="n">
         <v>-3.09</v>
-      </c>
-      <c r="P3" s="94" t="n">
-        <v>-0.03</v>
       </c>
       <c r="Q3" s="94" t="n">
         <v>-0.03</v>
       </c>
       <c r="R3" s="94" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="S3" s="94" t="n">
         <v>0.26</v>
       </c>
-      <c r="S3" s="94" t="n">
+      <c r="T3" s="94" t="n">
         <v>0.9</v>
       </c>
-      <c r="T3" s="94" t="n">
+      <c r="U3" s="94" t="n">
         <v>-1.66</v>
       </c>
-      <c r="U3" s="94" t="n">
+      <c r="V3" s="94" t="n">
         <v>-0.34</v>
-      </c>
-      <c r="V3" s="94" t="n">
-        <v>-2.74</v>
       </c>
       <c r="W3" s="94" t="n">
         <v>-2.74</v>
       </c>
       <c r="X3" s="94" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="Y3" s="94" t="n">
         <v>0.11</v>
-      </c>
-      <c r="Y3" s="94" t="n">
-        <v>-3.95</v>
       </c>
       <c r="Z3" s="94" t="n">
         <v>-3.95</v>
       </c>
       <c r="AA3" s="94" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="AB3" s="94" t="n">
         <v>2.12</v>
-      </c>
-      <c r="AB3" s="94" t="n">
-        <v>10.12</v>
       </c>
       <c r="AC3" s="94" t="n">
         <v>10.12</v>
       </c>
       <c r="AD3" s="94" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="AE3" s="94" t="n">
         <v>13.23</v>
-      </c>
-      <c r="AE3" s="94" t="n">
-        <v>17.16</v>
       </c>
     </row>
     <row r="4">
@@ -6758,88 +6757,88 @@
         <v>10.61</v>
       </c>
       <c r="D4" s="94" t="n">
-        <v>12.97</v>
+        <v>10.61</v>
       </c>
       <c r="E4" s="94" t="n">
         <v>12.97</v>
       </c>
       <c r="F4" s="94" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="G4" s="94" t="n">
         <v>11.7</v>
       </c>
-      <c r="G4" s="94" t="n">
+      <c r="H4" s="94" t="n">
         <v>11.16</v>
       </c>
-      <c r="H4" s="94" t="n">
+      <c r="I4" s="94" t="n">
         <v>12.33</v>
       </c>
-      <c r="I4" s="94" t="n">
+      <c r="J4" s="94" t="n">
         <v>11.8</v>
-      </c>
-      <c r="J4" s="94" t="n">
-        <v>11.2</v>
       </c>
       <c r="K4" s="94" t="n">
         <v>11.2</v>
       </c>
       <c r="L4" s="94" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="M4" s="94" t="n">
         <v>9.17</v>
       </c>
-      <c r="M4" s="94" t="n">
+      <c r="N4" s="94" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="N4" s="94" t="n">
+      <c r="O4" s="94" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="O4" s="94" t="n">
+      <c r="P4" s="94" t="n">
         <v>6.68</v>
-      </c>
-      <c r="P4" s="94" t="n">
-        <v>6.46</v>
       </c>
       <c r="Q4" s="94" t="n">
         <v>6.46</v>
       </c>
       <c r="R4" s="94" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="S4" s="94" t="n">
         <v>7.98</v>
       </c>
-      <c r="S4" s="94" t="n">
+      <c r="T4" s="94" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="T4" s="94" t="n">
+      <c r="U4" s="94" t="n">
         <v>8.73</v>
       </c>
-      <c r="U4" s="94" t="n">
+      <c r="V4" s="94" t="n">
         <v>9.1</v>
-      </c>
-      <c r="V4" s="94" t="n">
-        <v>8.52</v>
       </c>
       <c r="W4" s="94" t="n">
         <v>8.52</v>
       </c>
       <c r="X4" s="94" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="Y4" s="94" t="n">
         <v>11.64</v>
-      </c>
-      <c r="Y4" s="94" t="n">
-        <v>13.62</v>
       </c>
       <c r="Z4" s="94" t="n">
         <v>13.62</v>
       </c>
       <c r="AA4" s="94" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="AB4" s="94" t="n">
         <v>15.21</v>
-      </c>
-      <c r="AB4" s="94" t="n">
-        <v>14.01</v>
       </c>
       <c r="AC4" s="94" t="n">
         <v>14.01</v>
       </c>
       <c r="AD4" s="94" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="AE4" s="94" t="n">
         <v>13.38</v>
-      </c>
-      <c r="AE4" s="94" t="n">
-        <v>13.31</v>
       </c>
     </row>
     <row r="5">
@@ -6855,88 +6854,88 @@
         <v>67.42</v>
       </c>
       <c r="D5" s="94" t="n">
-        <v>71.19</v>
+        <v>67.42</v>
       </c>
       <c r="E5" s="94" t="n">
         <v>71.19</v>
       </c>
       <c r="F5" s="94" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="G5" s="94" t="n">
         <v>50.98</v>
       </c>
-      <c r="G5" s="94" t="n">
+      <c r="H5" s="94" t="n">
         <v>25.28</v>
       </c>
-      <c r="H5" s="94" t="n">
+      <c r="I5" s="94" t="n">
         <v>65.31999999999999</v>
       </c>
-      <c r="I5" s="94" t="n">
+      <c r="J5" s="94" t="n">
         <v>69.8</v>
-      </c>
-      <c r="J5" s="94" t="n">
-        <v>67.65000000000001</v>
       </c>
       <c r="K5" s="94" t="n">
         <v>67.65000000000001</v>
       </c>
       <c r="L5" s="94" t="n">
+        <v>67.65000000000001</v>
+      </c>
+      <c r="M5" s="94" t="n">
         <v>63.76</v>
       </c>
-      <c r="M5" s="94" t="n">
+      <c r="N5" s="94" t="n">
         <v>58.67</v>
       </c>
-      <c r="N5" s="94" t="n">
+      <c r="O5" s="94" t="n">
         <v>68.65000000000001</v>
       </c>
-      <c r="O5" s="94" t="n">
+      <c r="P5" s="94" t="n">
         <v>8.279999999999999</v>
-      </c>
-      <c r="P5" s="94" t="n">
-        <v>9.460000000000001</v>
       </c>
       <c r="Q5" s="94" t="n">
         <v>9.460000000000001</v>
       </c>
       <c r="R5" s="94" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="S5" s="94" t="n">
         <v>19.81</v>
       </c>
-      <c r="S5" s="94" t="n">
+      <c r="T5" s="94" t="n">
         <v>29.11</v>
       </c>
-      <c r="T5" s="94" t="n">
+      <c r="U5" s="94" t="n">
         <v>28.48</v>
       </c>
-      <c r="U5" s="94" t="n">
+      <c r="V5" s="94" t="n">
         <v>4.01</v>
-      </c>
-      <c r="V5" s="94" t="n">
-        <v>4.21</v>
       </c>
       <c r="W5" s="94" t="n">
         <v>4.21</v>
       </c>
       <c r="X5" s="94" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="Y5" s="94" t="n">
         <v>6.55</v>
-      </c>
-      <c r="Y5" s="94" t="n">
-        <v>18.7</v>
       </c>
       <c r="Z5" s="94" t="n">
         <v>18.7</v>
       </c>
       <c r="AA5" s="94" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AB5" s="94" t="n">
         <v>81.11</v>
-      </c>
-      <c r="AB5" s="94" t="n">
-        <v>73.47</v>
       </c>
       <c r="AC5" s="94" t="n">
         <v>73.47</v>
       </c>
       <c r="AD5" s="94" t="n">
+        <v>73.47</v>
+      </c>
+      <c r="AE5" s="94" t="n">
         <v>71.25</v>
-      </c>
-      <c r="AE5" s="94" t="n">
-        <v>67.02</v>
       </c>
     </row>
     <row r="6">
@@ -6955,124 +6954,124 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D6" s="91" t="inlineStr">
+      <c r="D6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E6" s="91" t="inlineStr">
+      <c r="F6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F6" s="93" t="inlineStr">
+      <c r="G6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G6" s="91" t="inlineStr">
+      <c r="H6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H6" s="91" t="inlineStr">
+      <c r="I6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I6" s="92" t="inlineStr">
+      <c r="J6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J6" s="92" t="inlineStr">
+      <c r="K6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K6" s="92" t="inlineStr">
+      <c r="L6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L6" s="93" t="inlineStr">
+      <c r="M6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M6" s="91" t="inlineStr">
+      <c r="N6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N6" s="91" t="inlineStr">
+      <c r="O6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O6" s="92" t="inlineStr">
+      <c r="P6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P6" s="92" t="inlineStr">
+      <c r="Q6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q6" s="92" t="inlineStr">
+      <c r="R6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R6" s="92" t="inlineStr">
+      <c r="S6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S6" s="92" t="inlineStr">
+      <c r="T6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T6" s="92" t="inlineStr">
+      <c r="U6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U6" s="93" t="inlineStr">
+      <c r="V6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V6" s="93" t="inlineStr">
+      <c r="W6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W6" s="93" t="inlineStr">
+      <c r="X6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X6" s="93" t="inlineStr">
+      <c r="Y6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y6" s="93" t="inlineStr">
+      <c r="Z6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z6" s="93" t="inlineStr">
+      <c r="AA6" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AA6" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AB6" s="91" t="inlineStr">
@@ -7109,88 +7108,88 @@
         <v>1.63</v>
       </c>
       <c r="D7" s="94" t="n">
-        <v>0.55</v>
+        <v>1.63</v>
       </c>
       <c r="E7" s="94" t="n">
         <v>0.55</v>
       </c>
       <c r="F7" s="94" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G7" s="94" t="n">
         <v>0.76</v>
       </c>
-      <c r="G7" s="94" t="n">
+      <c r="H7" s="94" t="n">
         <v>-0</v>
       </c>
-      <c r="H7" s="94" t="n">
+      <c r="I7" s="94" t="n">
         <v>-1.04</v>
       </c>
-      <c r="I7" s="94" t="n">
+      <c r="J7" s="94" t="n">
         <v>-2.32</v>
-      </c>
-      <c r="J7" s="94" t="n">
-        <v>-1.2</v>
       </c>
       <c r="K7" s="94" t="n">
         <v>-1.2</v>
       </c>
       <c r="L7" s="94" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="M7" s="94" t="n">
         <v>-2.32</v>
       </c>
-      <c r="M7" s="94" t="n">
+      <c r="N7" s="94" t="n">
         <v>-0.83</v>
       </c>
-      <c r="N7" s="94" t="n">
+      <c r="O7" s="94" t="n">
         <v>-1.86</v>
       </c>
-      <c r="O7" s="94" t="n">
+      <c r="P7" s="94" t="n">
         <v>-2.7</v>
-      </c>
-      <c r="P7" s="94" t="n">
-        <v>8.130000000000001</v>
       </c>
       <c r="Q7" s="94" t="n">
         <v>8.130000000000001</v>
       </c>
       <c r="R7" s="94" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="S7" s="94" t="n">
         <v>9.789999999999999</v>
       </c>
-      <c r="S7" s="94" t="n">
+      <c r="T7" s="94" t="n">
         <v>7.38</v>
       </c>
-      <c r="T7" s="94" t="n">
+      <c r="U7" s="94" t="n">
         <v>4.27</v>
       </c>
-      <c r="U7" s="94" t="n">
+      <c r="V7" s="94" t="n">
         <v>4.43</v>
-      </c>
-      <c r="V7" s="94" t="n">
-        <v>-1.29</v>
       </c>
       <c r="W7" s="94" t="n">
         <v>-1.29</v>
       </c>
       <c r="X7" s="94" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="Y7" s="94" t="n">
         <v>-4.26</v>
-      </c>
-      <c r="Y7" s="94" t="n">
-        <v>-3.42</v>
       </c>
       <c r="Z7" s="94" t="n">
         <v>-3.42</v>
       </c>
       <c r="AA7" s="94" t="n">
+        <v>-3.42</v>
+      </c>
+      <c r="AB7" s="94" t="n">
         <v>17</v>
-      </c>
-      <c r="AB7" s="94" t="n">
-        <v>37.64</v>
       </c>
       <c r="AC7" s="94" t="n">
         <v>37.64</v>
       </c>
       <c r="AD7" s="94" t="n">
+        <v>37.64</v>
+      </c>
+      <c r="AE7" s="94" t="n">
         <v>48.17</v>
-      </c>
-      <c r="AE7" s="94" t="n">
-        <v>52.45</v>
       </c>
     </row>
     <row r="8">
@@ -7206,88 +7205,88 @@
         <v>28.48</v>
       </c>
       <c r="D8" s="94" t="n">
-        <v>37.3</v>
+        <v>28.48</v>
       </c>
       <c r="E8" s="94" t="n">
         <v>37.3</v>
       </c>
       <c r="F8" s="94" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="G8" s="94" t="n">
         <v>36.53</v>
       </c>
-      <c r="G8" s="94" t="n">
+      <c r="H8" s="94" t="n">
         <v>35.49</v>
       </c>
-      <c r="H8" s="94" t="n">
+      <c r="I8" s="94" t="n">
         <v>36.76</v>
       </c>
-      <c r="I8" s="94" t="n">
+      <c r="J8" s="94" t="n">
         <v>35.74</v>
-      </c>
-      <c r="J8" s="94" t="n">
-        <v>33.95</v>
       </c>
       <c r="K8" s="94" t="n">
         <v>33.95</v>
       </c>
       <c r="L8" s="94" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="M8" s="94" t="n">
         <v>27.18</v>
       </c>
-      <c r="M8" s="94" t="n">
+      <c r="N8" s="94" t="n">
         <v>30.45</v>
       </c>
-      <c r="N8" s="94" t="n">
+      <c r="O8" s="94" t="n">
         <v>33.5</v>
       </c>
-      <c r="O8" s="94" t="n">
+      <c r="P8" s="94" t="n">
         <v>30.62</v>
-      </c>
-      <c r="P8" s="94" t="n">
-        <v>29.85</v>
       </c>
       <c r="Q8" s="94" t="n">
         <v>29.85</v>
       </c>
       <c r="R8" s="94" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="S8" s="94" t="n">
         <v>34.31</v>
       </c>
-      <c r="S8" s="94" t="n">
+      <c r="T8" s="94" t="n">
         <v>34.35</v>
       </c>
-      <c r="T8" s="94" t="n">
+      <c r="U8" s="94" t="n">
         <v>34.47</v>
       </c>
-      <c r="U8" s="94" t="n">
+      <c r="V8" s="94" t="n">
         <v>32.14</v>
-      </c>
-      <c r="V8" s="94" t="n">
-        <v>32.67</v>
       </c>
       <c r="W8" s="94" t="n">
         <v>32.67</v>
       </c>
       <c r="X8" s="94" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="Y8" s="94" t="n">
         <v>37.96</v>
-      </c>
-      <c r="Y8" s="94" t="n">
-        <v>41.51</v>
       </c>
       <c r="Z8" s="94" t="n">
         <v>41.51</v>
       </c>
       <c r="AA8" s="94" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="AB8" s="94" t="n">
         <v>47.84</v>
-      </c>
-      <c r="AB8" s="94" t="n">
-        <v>45.14</v>
       </c>
       <c r="AC8" s="94" t="n">
         <v>45.14</v>
       </c>
       <c r="AD8" s="94" t="n">
+        <v>45.14</v>
+      </c>
+      <c r="AE8" s="94" t="n">
         <v>46.9</v>
-      </c>
-      <c r="AE8" s="94" t="n">
-        <v>43.37</v>
       </c>
     </row>
     <row r="9">
@@ -7303,88 +7302,88 @@
         <v>35.78</v>
       </c>
       <c r="D9" s="94" t="n">
-        <v>56.52</v>
+        <v>35.78</v>
       </c>
       <c r="E9" s="94" t="n">
         <v>56.52</v>
       </c>
       <c r="F9" s="94" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="G9" s="94" t="n">
         <v>45.32</v>
       </c>
-      <c r="G9" s="94" t="n">
+      <c r="H9" s="94" t="n">
         <v>57.96</v>
       </c>
-      <c r="H9" s="94" t="n">
+      <c r="I9" s="94" t="n">
         <v>59.34</v>
       </c>
-      <c r="I9" s="94" t="n">
+      <c r="J9" s="94" t="n">
         <v>51.65</v>
-      </c>
-      <c r="J9" s="94" t="n">
-        <v>49.39</v>
       </c>
       <c r="K9" s="94" t="n">
         <v>49.39</v>
       </c>
       <c r="L9" s="94" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="M9" s="94" t="n">
         <v>40.47</v>
       </c>
-      <c r="M9" s="94" t="n">
+      <c r="N9" s="94" t="n">
         <v>59.12</v>
       </c>
-      <c r="N9" s="94" t="n">
+      <c r="O9" s="94" t="n">
         <v>63.67</v>
       </c>
-      <c r="O9" s="94" t="n">
+      <c r="P9" s="94" t="n">
         <v>34.88</v>
-      </c>
-      <c r="P9" s="94" t="n">
-        <v>32.56</v>
       </c>
       <c r="Q9" s="94" t="n">
         <v>32.56</v>
       </c>
       <c r="R9" s="94" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="S9" s="94" t="n">
         <v>40.33</v>
       </c>
-      <c r="S9" s="94" t="n">
+      <c r="T9" s="94" t="n">
         <v>43.12</v>
       </c>
-      <c r="T9" s="94" t="n">
+      <c r="U9" s="94" t="n">
         <v>43.39</v>
       </c>
-      <c r="U9" s="94" t="n">
+      <c r="V9" s="94" t="n">
         <v>16.15</v>
-      </c>
-      <c r="V9" s="94" t="n">
-        <v>16.9</v>
       </c>
       <c r="W9" s="94" t="n">
         <v>16.9</v>
       </c>
       <c r="X9" s="94" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="Y9" s="94" t="n">
         <v>20.18</v>
-      </c>
-      <c r="Y9" s="94" t="n">
-        <v>32.85</v>
       </c>
       <c r="Z9" s="94" t="n">
         <v>32.85</v>
       </c>
       <c r="AA9" s="94" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="AB9" s="94" t="n">
         <v>62.46</v>
-      </c>
-      <c r="AB9" s="94" t="n">
-        <v>60.63</v>
       </c>
       <c r="AC9" s="94" t="n">
         <v>60.63</v>
       </c>
       <c r="AD9" s="94" t="n">
+        <v>60.63</v>
+      </c>
+      <c r="AE9" s="94" t="n">
         <v>72.27</v>
-      </c>
-      <c r="AE9" s="94" t="n">
-        <v>66.34999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -7403,124 +7402,124 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D10" s="91" t="inlineStr">
+      <c r="D10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E10" s="91" t="inlineStr">
+      <c r="F10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F10" s="91" t="inlineStr">
+      <c r="G10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G10" s="91" t="inlineStr">
+      <c r="H10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H10" s="91" t="inlineStr">
+      <c r="I10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I10" s="91" t="inlineStr">
+      <c r="J10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J10" s="91" t="inlineStr">
+      <c r="K10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K10" s="91" t="inlineStr">
+      <c r="L10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L10" s="92" t="inlineStr">
+      <c r="M10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M10" s="92" t="inlineStr">
+      <c r="N10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N10" s="91" t="inlineStr">
+      <c r="O10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O10" s="92" t="inlineStr">
+      <c r="P10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P10" s="92" t="inlineStr">
+      <c r="Q10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q10" s="92" t="inlineStr">
+      <c r="R10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R10" s="92" t="inlineStr">
+      <c r="S10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S10" s="92" t="inlineStr">
+      <c r="T10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T10" s="92" t="inlineStr">
+      <c r="U10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U10" s="93" t="inlineStr">
+      <c r="V10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V10" s="93" t="inlineStr">
+      <c r="W10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W10" s="93" t="inlineStr">
+      <c r="X10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X10" s="93" t="inlineStr">
+      <c r="Y10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y10" s="93" t="inlineStr">
+      <c r="Z10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z10" s="93" t="inlineStr">
+      <c r="AA10" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AA10" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AB10" s="92" t="inlineStr">
@@ -7557,88 +7556,88 @@
         <v>-2.82</v>
       </c>
       <c r="D11" s="94" t="n">
-        <v>-1.97</v>
+        <v>-2.82</v>
       </c>
       <c r="E11" s="94" t="n">
         <v>-1.97</v>
       </c>
       <c r="F11" s="94" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="G11" s="94" t="n">
         <v>-2.71</v>
       </c>
-      <c r="G11" s="94" t="n">
+      <c r="H11" s="94" t="n">
         <v>-3.5</v>
       </c>
-      <c r="H11" s="94" t="n">
+      <c r="I11" s="94" t="n">
         <v>-5.24</v>
       </c>
-      <c r="I11" s="94" t="n">
+      <c r="J11" s="94" t="n">
         <v>-5.99</v>
-      </c>
-      <c r="J11" s="94" t="n">
-        <v>-4.96</v>
       </c>
       <c r="K11" s="94" t="n">
         <v>-4.96</v>
       </c>
       <c r="L11" s="94" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="M11" s="94" t="n">
         <v>-6.98</v>
       </c>
-      <c r="M11" s="94" t="n">
+      <c r="N11" s="94" t="n">
         <v>-8.08</v>
       </c>
-      <c r="N11" s="94" t="n">
+      <c r="O11" s="94" t="n">
         <v>-6.09</v>
       </c>
-      <c r="O11" s="94" t="n">
+      <c r="P11" s="94" t="n">
         <v>-9.69</v>
-      </c>
-      <c r="P11" s="94" t="n">
-        <v>-2.86</v>
       </c>
       <c r="Q11" s="94" t="n">
         <v>-2.86</v>
       </c>
       <c r="R11" s="94" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="S11" s="94" t="n">
         <v>-1.44</v>
       </c>
-      <c r="S11" s="94" t="n">
+      <c r="T11" s="94" t="n">
         <v>-3.72</v>
       </c>
-      <c r="T11" s="94" t="n">
+      <c r="U11" s="94" t="n">
         <v>-5.89</v>
       </c>
-      <c r="U11" s="94" t="n">
+      <c r="V11" s="94" t="n">
         <v>-4.13</v>
-      </c>
-      <c r="V11" s="94" t="n">
-        <v>-8.9</v>
       </c>
       <c r="W11" s="94" t="n">
         <v>-8.9</v>
       </c>
       <c r="X11" s="94" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="Y11" s="94" t="n">
         <v>-9.630000000000001</v>
-      </c>
-      <c r="Y11" s="94" t="n">
-        <v>-16.02</v>
       </c>
       <c r="Z11" s="94" t="n">
         <v>-16.02</v>
       </c>
       <c r="AA11" s="94" t="n">
+        <v>-16.02</v>
+      </c>
+      <c r="AB11" s="94" t="n">
         <v>1.43</v>
-      </c>
-      <c r="AB11" s="94" t="n">
-        <v>16.94</v>
       </c>
       <c r="AC11" s="94" t="n">
         <v>16.94</v>
       </c>
       <c r="AD11" s="94" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="AE11" s="94" t="n">
         <v>28.92</v>
-      </c>
-      <c r="AE11" s="94" t="n">
-        <v>34.1</v>
       </c>
     </row>
     <row r="12">
@@ -7654,88 +7653,88 @@
         <v>22.25</v>
       </c>
       <c r="D12" s="94" t="n">
-        <v>30.1</v>
+        <v>22.25</v>
       </c>
       <c r="E12" s="94" t="n">
         <v>30.1</v>
       </c>
       <c r="F12" s="94" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="G12" s="94" t="n">
         <v>27.98</v>
       </c>
-      <c r="G12" s="94" t="n">
+      <c r="H12" s="94" t="n">
         <v>26.6</v>
       </c>
-      <c r="H12" s="94" t="n">
+      <c r="I12" s="94" t="n">
         <v>28.46</v>
       </c>
-      <c r="I12" s="94" t="n">
+      <c r="J12" s="94" t="n">
         <v>27.49</v>
-      </c>
-      <c r="J12" s="94" t="n">
-        <v>23.68</v>
       </c>
       <c r="K12" s="94" t="n">
         <v>23.68</v>
       </c>
       <c r="L12" s="94" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="M12" s="94" t="n">
         <v>18.99</v>
       </c>
-      <c r="M12" s="94" t="n">
+      <c r="N12" s="94" t="n">
         <v>18.11</v>
       </c>
-      <c r="N12" s="94" t="n">
+      <c r="O12" s="94" t="n">
         <v>20.84</v>
       </c>
-      <c r="O12" s="94" t="n">
+      <c r="P12" s="94" t="n">
         <v>16.86</v>
-      </c>
-      <c r="P12" s="94" t="n">
-        <v>16.44</v>
       </c>
       <c r="Q12" s="94" t="n">
         <v>16.44</v>
       </c>
       <c r="R12" s="94" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="S12" s="94" t="n">
         <v>20.18</v>
       </c>
-      <c r="S12" s="94" t="n">
+      <c r="T12" s="94" t="n">
         <v>19.29</v>
       </c>
-      <c r="T12" s="94" t="n">
+      <c r="U12" s="94" t="n">
         <v>20.37</v>
       </c>
-      <c r="U12" s="94" t="n">
+      <c r="V12" s="94" t="n">
         <v>21.99</v>
-      </c>
-      <c r="V12" s="94" t="n">
-        <v>22.02</v>
       </c>
       <c r="W12" s="94" t="n">
         <v>22.02</v>
       </c>
       <c r="X12" s="94" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="Y12" s="94" t="n">
         <v>26.5</v>
-      </c>
-      <c r="Y12" s="94" t="n">
-        <v>29.36</v>
       </c>
       <c r="Z12" s="94" t="n">
         <v>29.36</v>
       </c>
       <c r="AA12" s="94" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="AB12" s="94" t="n">
         <v>33.94</v>
-      </c>
-      <c r="AB12" s="94" t="n">
-        <v>32.82</v>
       </c>
       <c r="AC12" s="94" t="n">
         <v>32.82</v>
       </c>
       <c r="AD12" s="94" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="AE12" s="94" t="n">
         <v>32.72</v>
-      </c>
-      <c r="AE12" s="94" t="n">
-        <v>30.82</v>
       </c>
     </row>
     <row r="13">
@@ -7751,88 +7750,88 @@
         <v>31.12</v>
       </c>
       <c r="D13" s="94" t="n">
-        <v>77.11</v>
+        <v>31.12</v>
       </c>
       <c r="E13" s="94" t="n">
         <v>77.11</v>
       </c>
       <c r="F13" s="94" t="n">
+        <v>77.11</v>
+      </c>
+      <c r="G13" s="94" t="n">
         <v>55.59</v>
       </c>
-      <c r="G13" s="94" t="n">
+      <c r="H13" s="94" t="n">
         <v>66.94</v>
       </c>
-      <c r="H13" s="94" t="n">
+      <c r="I13" s="94" t="n">
         <v>83.7</v>
       </c>
-      <c r="I13" s="94" t="n">
+      <c r="J13" s="94" t="n">
         <v>81.64</v>
-      </c>
-      <c r="J13" s="94" t="n">
-        <v>68.69</v>
       </c>
       <c r="K13" s="94" t="n">
         <v>68.69</v>
       </c>
       <c r="L13" s="94" t="n">
+        <v>68.69</v>
+      </c>
+      <c r="M13" s="94" t="n">
         <v>60.87</v>
       </c>
-      <c r="M13" s="94" t="n">
+      <c r="N13" s="94" t="n">
         <v>54.48</v>
       </c>
-      <c r="N13" s="94" t="n">
+      <c r="O13" s="94" t="n">
         <v>78.59</v>
       </c>
-      <c r="O13" s="94" t="n">
+      <c r="P13" s="94" t="n">
         <v>21.44</v>
-      </c>
-      <c r="P13" s="94" t="n">
-        <v>9.02</v>
       </c>
       <c r="Q13" s="94" t="n">
         <v>9.02</v>
       </c>
       <c r="R13" s="94" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="S13" s="94" t="n">
         <v>18.81</v>
       </c>
-      <c r="S13" s="94" t="n">
+      <c r="T13" s="94" t="n">
         <v>14.94</v>
       </c>
-      <c r="T13" s="94" t="n">
+      <c r="U13" s="94" t="n">
         <v>20.9</v>
       </c>
-      <c r="U13" s="94" t="n">
+      <c r="V13" s="94" t="n">
         <v>2.46</v>
-      </c>
-      <c r="V13" s="94" t="n">
-        <v>2.51</v>
       </c>
       <c r="W13" s="94" t="n">
         <v>2.51</v>
       </c>
       <c r="X13" s="94" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Y13" s="94" t="n">
         <v>3.75</v>
-      </c>
-      <c r="Y13" s="94" t="n">
-        <v>9.470000000000001</v>
       </c>
       <c r="Z13" s="94" t="n">
         <v>9.470000000000001</v>
       </c>
       <c r="AA13" s="94" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="AB13" s="94" t="n">
         <v>49.72</v>
-      </c>
-      <c r="AB13" s="94" t="n">
-        <v>46.46</v>
       </c>
       <c r="AC13" s="94" t="n">
         <v>46.46</v>
       </c>
       <c r="AD13" s="94" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="AE13" s="94" t="n">
         <v>54.92</v>
-      </c>
-      <c r="AE13" s="94" t="n">
-        <v>42.96</v>
       </c>
     </row>
     <row r="14">
@@ -7861,128 +7860,130 @@
           <t>red</t>
         </is>
       </c>
-      <c r="F14" s="92" t="inlineStr">
+      <c r="F14" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G14" s="92" t="inlineStr">
+      <c r="H14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H14" s="91" t="inlineStr">
+      <c r="I14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I14" s="91" t="inlineStr">
+      <c r="J14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J14" s="91" t="inlineStr">
+      <c r="K14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K14" s="91" t="inlineStr">
+      <c r="L14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L14" s="91" t="inlineStr">
+      <c r="M14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M14" s="92" t="inlineStr">
+      <c r="N14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N14" s="92" t="inlineStr">
+      <c r="O14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O14" s="93" t="inlineStr">
+      <c r="P14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P14" s="93" t="inlineStr">
+      <c r="Q14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q14" s="93" t="inlineStr">
+      <c r="R14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R14" s="93" t="inlineStr">
+      <c r="S14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S14" s="93" t="inlineStr">
+      <c r="T14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T14" s="93" t="inlineStr">
+      <c r="U14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U14" s="93" t="inlineStr">
+      <c r="V14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V14" s="93" t="inlineStr">
+      <c r="W14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W14" s="93" t="inlineStr">
+      <c r="X14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X14" s="93" t="inlineStr">
+      <c r="Y14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y14" s="91" t="inlineStr">
+      <c r="Z14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z14" s="91" t="inlineStr">
+      <c r="AA14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA14" s="91" t="inlineStr">
+      <c r="AB14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB14" s="91" t="inlineStr">
+      <c r="AC14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC14" s="91" t="inlineStr">
+      <c r="AD14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
-      </c>
-      <c r="AD14" s="92" t="n">
-        <v/>
       </c>
       <c r="AE14" s="92" t="n">
         <v/>
@@ -7998,88 +7999,88 @@
         <v>-0.45</v>
       </c>
       <c r="C15" s="94" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="D15" s="94" t="n">
         <v>-0.9</v>
-      </c>
-      <c r="D15" s="94" t="n">
-        <v>-3.07</v>
       </c>
       <c r="E15" s="94" t="n">
         <v>-3.07</v>
       </c>
       <c r="F15" s="94" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="G15" s="94" t="n">
         <v>-4.36</v>
       </c>
-      <c r="G15" s="94" t="n">
+      <c r="H15" s="94" t="n">
         <v>-3.94</v>
       </c>
-      <c r="H15" s="94" t="n">
+      <c r="I15" s="94" t="n">
         <v>-1.87</v>
       </c>
-      <c r="I15" s="94" t="n">
+      <c r="J15" s="94" t="n">
         <v>-4.02</v>
-      </c>
-      <c r="J15" s="94" t="n">
-        <v>-4.46</v>
       </c>
       <c r="K15" s="94" t="n">
         <v>-4.46</v>
       </c>
       <c r="L15" s="94" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="M15" s="94" t="n">
         <v>-4.67</v>
       </c>
-      <c r="M15" s="94" t="n">
+      <c r="N15" s="94" t="n">
         <v>-7.3</v>
       </c>
-      <c r="N15" s="94" t="n">
+      <c r="O15" s="94" t="n">
         <v>-4.28</v>
       </c>
-      <c r="O15" s="94" t="n">
+      <c r="P15" s="94" t="n">
         <v>-6.96</v>
-      </c>
-      <c r="P15" s="94" t="n">
-        <v>-6.17</v>
       </c>
       <c r="Q15" s="94" t="n">
         <v>-6.17</v>
       </c>
       <c r="R15" s="94" t="n">
+        <v>-6.17</v>
+      </c>
+      <c r="S15" s="94" t="n">
         <v>-8.779999999999999</v>
       </c>
-      <c r="S15" s="94" t="n">
+      <c r="T15" s="94" t="n">
         <v>-9.279999999999999</v>
       </c>
-      <c r="T15" s="94" t="n">
+      <c r="U15" s="94" t="n">
         <v>-5.76</v>
       </c>
-      <c r="U15" s="94" t="n">
+      <c r="V15" s="94" t="n">
         <v>-5.92</v>
-      </c>
-      <c r="V15" s="94" t="n">
-        <v>-14.46</v>
       </c>
       <c r="W15" s="94" t="n">
         <v>-14.46</v>
       </c>
       <c r="X15" s="94" t="n">
+        <v>-14.46</v>
+      </c>
+      <c r="Y15" s="94" t="n">
         <v>-13.69</v>
-      </c>
-      <c r="Y15" s="94" t="n">
-        <v>-9.289999999999999</v>
       </c>
       <c r="Z15" s="94" t="n">
         <v>-9.289999999999999</v>
       </c>
       <c r="AA15" s="94" t="n">
+        <v>-9.289999999999999</v>
+      </c>
+      <c r="AB15" s="94" t="n">
         <v>-10.7</v>
-      </c>
-      <c r="AB15" s="94" t="n">
-        <v>-4.94</v>
       </c>
       <c r="AC15" s="94" t="n">
         <v>-4.94</v>
       </c>
       <c r="AD15" s="94" t="n">
-        <v/>
+        <v>-4.94</v>
       </c>
       <c r="AE15" s="94" t="n">
         <v/>
@@ -8095,88 +8096,88 @@
         <v>19.35</v>
       </c>
       <c r="C16" s="94" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="D16" s="94" t="n">
         <v>16.72</v>
-      </c>
-      <c r="D16" s="94" t="n">
-        <v>15.69</v>
       </c>
       <c r="E16" s="94" t="n">
         <v>15.69</v>
       </c>
       <c r="F16" s="94" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="G16" s="94" t="n">
         <v>15.87</v>
       </c>
-      <c r="G16" s="94" t="n">
+      <c r="H16" s="94" t="n">
         <v>14.74</v>
       </c>
-      <c r="H16" s="94" t="n">
+      <c r="I16" s="94" t="n">
         <v>18.13</v>
       </c>
-      <c r="I16" s="94" t="n">
+      <c r="J16" s="94" t="n">
         <v>17.18</v>
-      </c>
-      <c r="J16" s="94" t="n">
-        <v>13.13</v>
       </c>
       <c r="K16" s="94" t="n">
         <v>13.13</v>
       </c>
       <c r="L16" s="94" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="M16" s="94" t="n">
         <v>11.76</v>
       </c>
-      <c r="M16" s="94" t="n">
+      <c r="N16" s="94" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="N16" s="94" t="n">
+      <c r="O16" s="94" t="n">
         <v>10.35</v>
       </c>
-      <c r="O16" s="94" t="n">
+      <c r="P16" s="94" t="n">
         <v>6.16</v>
-      </c>
-      <c r="P16" s="94" t="n">
-        <v>7.47</v>
       </c>
       <c r="Q16" s="94" t="n">
         <v>7.47</v>
       </c>
       <c r="R16" s="94" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="S16" s="94" t="n">
         <v>8.529999999999999</v>
       </c>
-      <c r="S16" s="94" t="n">
+      <c r="T16" s="94" t="n">
         <v>7.02</v>
       </c>
-      <c r="T16" s="94" t="n">
+      <c r="U16" s="94" t="n">
         <v>6.31</v>
       </c>
-      <c r="U16" s="94" t="n">
+      <c r="V16" s="94" t="n">
         <v>10.41</v>
-      </c>
-      <c r="V16" s="94" t="n">
-        <v>13.1</v>
       </c>
       <c r="W16" s="94" t="n">
         <v>13.1</v>
       </c>
       <c r="X16" s="94" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="Y16" s="94" t="n">
         <v>11.98</v>
-      </c>
-      <c r="Y16" s="94" t="n">
-        <v>14.47</v>
       </c>
       <c r="Z16" s="94" t="n">
         <v>14.47</v>
       </c>
       <c r="AA16" s="94" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="AB16" s="94" t="n">
         <v>12.59</v>
-      </c>
-      <c r="AB16" s="94" t="n">
-        <v>11.44</v>
       </c>
       <c r="AC16" s="94" t="n">
         <v>11.44</v>
       </c>
       <c r="AD16" s="94" t="n">
-        <v/>
+        <v>11.44</v>
       </c>
       <c r="AE16" s="94" t="n">
         <v/>
@@ -8192,88 +8193,88 @@
         <v>75.39</v>
       </c>
       <c r="C17" s="94" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="D17" s="94" t="n">
         <v>74.31</v>
-      </c>
-      <c r="D17" s="94" t="n">
-        <v>69.52</v>
       </c>
       <c r="E17" s="94" t="n">
         <v>69.52</v>
       </c>
       <c r="F17" s="94" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="G17" s="94" t="n">
         <v>50.12</v>
       </c>
-      <c r="G17" s="94" t="n">
+      <c r="H17" s="94" t="n">
         <v>55.82</v>
       </c>
-      <c r="H17" s="94" t="n">
+      <c r="I17" s="94" t="n">
         <v>86.87</v>
       </c>
-      <c r="I17" s="94" t="n">
+      <c r="J17" s="94" t="n">
         <v>82.95</v>
-      </c>
-      <c r="J17" s="94" t="n">
-        <v>70.41</v>
       </c>
       <c r="K17" s="94" t="n">
         <v>70.41</v>
       </c>
       <c r="L17" s="94" t="n">
+        <v>70.41</v>
+      </c>
+      <c r="M17" s="94" t="n">
         <v>67.17</v>
       </c>
-      <c r="M17" s="94" t="n">
+      <c r="N17" s="94" t="n">
         <v>51.86</v>
       </c>
-      <c r="N17" s="94" t="n">
+      <c r="O17" s="94" t="n">
         <v>46.63</v>
       </c>
-      <c r="O17" s="94" t="n">
+      <c r="P17" s="94" t="n">
         <v>7.26</v>
-      </c>
-      <c r="P17" s="94" t="n">
-        <v>10.43</v>
       </c>
       <c r="Q17" s="94" t="n">
         <v>10.43</v>
       </c>
       <c r="R17" s="94" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="S17" s="94" t="n">
         <v>15.01</v>
       </c>
-      <c r="S17" s="94" t="n">
+      <c r="T17" s="94" t="n">
         <v>16.18</v>
       </c>
-      <c r="T17" s="94" t="n">
+      <c r="U17" s="94" t="n">
         <v>21.65</v>
       </c>
-      <c r="U17" s="94" t="n">
+      <c r="V17" s="94" t="n">
         <v>34.02</v>
-      </c>
-      <c r="V17" s="94" t="n">
-        <v>39.01</v>
       </c>
       <c r="W17" s="94" t="n">
         <v>39.01</v>
       </c>
       <c r="X17" s="94" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="Y17" s="94" t="n">
         <v>22.83</v>
-      </c>
-      <c r="Y17" s="94" t="n">
-        <v>62.48</v>
       </c>
       <c r="Z17" s="94" t="n">
         <v>62.48</v>
       </c>
       <c r="AA17" s="94" t="n">
+        <v>62.48</v>
+      </c>
+      <c r="AB17" s="94" t="n">
         <v>60.29</v>
-      </c>
-      <c r="AB17" s="94" t="n">
-        <v>68.20999999999999</v>
       </c>
       <c r="AC17" s="94" t="n">
         <v>68.20999999999999</v>
       </c>
       <c r="AD17" s="94" t="n">
-        <v/>
+        <v>68.20999999999999</v>
       </c>
       <c r="AE17" s="94" t="n">
         <v/>
@@ -8295,143 +8296,145 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="D18" s="91" t="inlineStr">
+      <c r="D18" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E18" s="91" t="inlineStr">
+      <c r="F18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F18" s="91" t="inlineStr">
+      <c r="G18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G18" s="91" t="inlineStr">
+      <c r="H18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H18" s="91" t="inlineStr">
+      <c r="I18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I18" s="91" t="inlineStr">
+      <c r="J18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J18" s="91" t="inlineStr">
+      <c r="K18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K18" s="91" t="inlineStr">
+      <c r="L18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L18" s="91" t="inlineStr">
+      <c r="M18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M18" s="91" t="inlineStr">
+      <c r="N18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N18" s="92" t="inlineStr">
+      <c r="O18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O18" s="93" t="inlineStr">
+      <c r="P18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P18" s="93" t="inlineStr">
+      <c r="Q18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q18" s="93" t="inlineStr">
+      <c r="R18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R18" s="92" t="inlineStr">
+      <c r="S18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S18" s="92" t="inlineStr">
+      <c r="T18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T18" s="93" t="inlineStr">
+      <c r="U18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U18" s="91" t="inlineStr">
+      <c r="V18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V18" s="92" t="inlineStr">
+      <c r="W18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W18" s="92" t="inlineStr">
+      <c r="X18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X18" s="93" t="inlineStr">
+      <c r="Y18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y18" s="93" t="inlineStr">
+      <c r="Z18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z18" s="93" t="inlineStr">
+      <c r="AA18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA18" s="93" t="inlineStr">
+      <c r="AB18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB18" s="93" t="inlineStr">
+      <c r="AC18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC18" s="93" t="inlineStr">
+      <c r="AD18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD18" s="91" t="inlineStr">
+      <c r="AE18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
-      </c>
-      <c r="AE18" s="92" t="n">
-        <v/>
       </c>
     </row>
     <row r="19">
@@ -8441,28 +8444,28 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="C19" s="94" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="D19" s="94" t="n">
         <v>3.24</v>
-      </c>
-      <c r="C19" s="94" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="D19" s="94" t="n">
-        <v>5.05</v>
       </c>
       <c r="E19" s="94" t="n">
         <v>5.05</v>
       </c>
       <c r="F19" s="94" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="G19" s="94" t="n">
         <v>5.32</v>
       </c>
-      <c r="G19" s="94" t="n">
+      <c r="H19" s="94" t="n">
         <v>4.98</v>
       </c>
-      <c r="H19" s="94" t="n">
+      <c r="I19" s="94" t="n">
         <v>3.38</v>
-      </c>
-      <c r="I19" s="94" t="n">
-        <v>2.44</v>
       </c>
       <c r="J19" s="94" t="n">
         <v>2.44</v>
@@ -8471,64 +8474,64 @@
         <v>2.44</v>
       </c>
       <c r="L19" s="94" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M19" s="94" t="n">
         <v>1.24</v>
       </c>
-      <c r="M19" s="94" t="n">
+      <c r="N19" s="94" t="n">
         <v>1.86</v>
       </c>
-      <c r="N19" s="94" t="n">
+      <c r="O19" s="94" t="n">
         <v>0.01</v>
       </c>
-      <c r="O19" s="94" t="n">
+      <c r="P19" s="94" t="n">
         <v>0.36</v>
-      </c>
-      <c r="P19" s="94" t="n">
-        <v>-0.5600000000000001</v>
       </c>
       <c r="Q19" s="94" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="R19" s="94" t="n">
-        <v>1.78</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="S19" s="94" t="n">
         <v>1.78</v>
       </c>
       <c r="T19" s="94" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U19" s="94" t="n">
         <v>2.23</v>
       </c>
-      <c r="U19" s="94" t="n">
+      <c r="V19" s="94" t="n">
         <v>3.17</v>
-      </c>
-      <c r="V19" s="94" t="n">
-        <v>3.33</v>
       </c>
       <c r="W19" s="94" t="n">
         <v>3.33</v>
       </c>
       <c r="X19" s="94" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="Y19" s="94" t="n">
         <v>3.03</v>
-      </c>
-      <c r="Y19" s="94" t="n">
-        <v>2.27</v>
       </c>
       <c r="Z19" s="94" t="n">
         <v>2.27</v>
       </c>
       <c r="AA19" s="94" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB19" s="94" t="n">
         <v>3.63</v>
-      </c>
-      <c r="AB19" s="94" t="n">
-        <v>4.58</v>
       </c>
       <c r="AC19" s="94" t="n">
         <v>4.58</v>
       </c>
       <c r="AD19" s="94" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AE19" s="94" t="n">
         <v>5.76</v>
-      </c>
-      <c r="AE19" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="20">
@@ -8538,28 +8541,28 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="C20" s="94" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="D20" s="94" t="n">
         <v>12.45</v>
-      </c>
-      <c r="C20" s="94" t="n">
-        <v>12.45</v>
-      </c>
-      <c r="D20" s="94" t="n">
-        <v>12.02</v>
       </c>
       <c r="E20" s="94" t="n">
         <v>12.02</v>
       </c>
       <c r="F20" s="94" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="G20" s="94" t="n">
         <v>10.8</v>
       </c>
-      <c r="G20" s="94" t="n">
+      <c r="H20" s="94" t="n">
         <v>11.96</v>
       </c>
-      <c r="H20" s="94" t="n">
+      <c r="I20" s="94" t="n">
         <v>10.72</v>
-      </c>
-      <c r="I20" s="94" t="n">
-        <v>9.85</v>
       </c>
       <c r="J20" s="94" t="n">
         <v>9.85</v>
@@ -8568,95 +8571,95 @@
         <v>9.85</v>
       </c>
       <c r="L20" s="94" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="M20" s="94" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="M20" s="94" t="n">
+      <c r="N20" s="94" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="N20" s="94" t="n">
+      <c r="O20" s="94" t="n">
         <v>5.17</v>
       </c>
-      <c r="O20" s="94" t="n">
+      <c r="P20" s="94" t="n">
         <v>4.88</v>
-      </c>
-      <c r="P20" s="94" t="n">
-        <v>5.85</v>
       </c>
       <c r="Q20" s="94" t="n">
         <v>5.85</v>
       </c>
       <c r="R20" s="94" t="n">
-        <v>6.74</v>
+        <v>5.85</v>
       </c>
       <c r="S20" s="94" t="n">
         <v>6.74</v>
       </c>
       <c r="T20" s="94" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="U20" s="94" t="n">
         <v>5.74</v>
       </c>
-      <c r="U20" s="94" t="n">
+      <c r="V20" s="94" t="n">
         <v>5.44</v>
-      </c>
-      <c r="V20" s="94" t="n">
-        <v>5.53</v>
       </c>
       <c r="W20" s="94" t="n">
         <v>5.53</v>
       </c>
       <c r="X20" s="94" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="Y20" s="94" t="n">
         <v>4.51</v>
-      </c>
-      <c r="Y20" s="94" t="n">
-        <v>5.32</v>
       </c>
       <c r="Z20" s="94" t="n">
         <v>5.32</v>
       </c>
       <c r="AA20" s="94" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="AB20" s="94" t="n">
         <v>4.85</v>
-      </c>
-      <c r="AB20" s="94" t="n">
-        <v>7.06</v>
       </c>
       <c r="AC20" s="94" t="n">
         <v>7.06</v>
       </c>
       <c r="AD20" s="94" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="AE20" s="94" t="n">
         <v>8.34</v>
       </c>
-      <c r="AE20" s="94" t="n">
-        <v/>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="96" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="94" t="n">
+        <v>56.94</v>
+      </c>
+      <c r="C21" s="94" t="n">
+        <v>56.94</v>
+      </c>
+      <c r="D21" s="94" t="n">
         <v>16.07</v>
-      </c>
-      <c r="C21" s="94" t="n">
-        <v>16.07</v>
-      </c>
-      <c r="D21" s="94" t="n">
-        <v>67.48999999999999</v>
       </c>
       <c r="E21" s="94" t="n">
         <v>67.48999999999999</v>
       </c>
       <c r="F21" s="94" t="n">
+        <v>67.48999999999999</v>
+      </c>
+      <c r="G21" s="94" t="n">
         <v>98.41</v>
       </c>
-      <c r="G21" s="94" t="n">
+      <c r="H21" s="94" t="n">
         <v>97.23999999999999</v>
       </c>
-      <c r="H21" s="94" t="n">
+      <c r="I21" s="94" t="n">
         <v>95.22</v>
-      </c>
-      <c r="I21" s="94" t="n">
-        <v>90.06</v>
       </c>
       <c r="J21" s="94" t="n">
         <v>90.06</v>
@@ -8665,64 +8668,64 @@
         <v>90.06</v>
       </c>
       <c r="L21" s="94" t="n">
+        <v>90.06</v>
+      </c>
+      <c r="M21" s="94" t="n">
         <v>74.65000000000001</v>
       </c>
-      <c r="M21" s="94" t="n">
+      <c r="N21" s="94" t="n">
         <v>89.31999999999999</v>
       </c>
-      <c r="N21" s="94" t="n">
+      <c r="O21" s="94" t="n">
         <v>34.87</v>
       </c>
-      <c r="O21" s="94" t="n">
+      <c r="P21" s="94" t="n">
         <v>22.53</v>
-      </c>
-      <c r="P21" s="94" t="n">
-        <v>10.95</v>
       </c>
       <c r="Q21" s="94" t="n">
         <v>10.95</v>
       </c>
       <c r="R21" s="94" t="n">
-        <v>42.53</v>
+        <v>10.95</v>
       </c>
       <c r="S21" s="94" t="n">
         <v>42.53</v>
       </c>
       <c r="T21" s="94" t="n">
+        <v>42.53</v>
+      </c>
+      <c r="U21" s="94" t="n">
         <v>32.72</v>
       </c>
-      <c r="U21" s="94" t="n">
+      <c r="V21" s="94" t="n">
         <v>84.81999999999999</v>
-      </c>
-      <c r="V21" s="94" t="n">
-        <v>74.91</v>
       </c>
       <c r="W21" s="94" t="n">
         <v>74.91</v>
       </c>
       <c r="X21" s="94" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="Y21" s="94" t="n">
         <v>6.03</v>
-      </c>
-      <c r="Y21" s="94" t="n">
-        <v>7.97</v>
       </c>
       <c r="Z21" s="94" t="n">
         <v>7.97</v>
       </c>
       <c r="AA21" s="94" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="AB21" s="94" t="n">
         <v>11.56</v>
-      </c>
-      <c r="AB21" s="94" t="n">
-        <v>26.76</v>
       </c>
       <c r="AC21" s="94" t="n">
         <v>26.76</v>
       </c>
       <c r="AD21" s="94" t="n">
+        <v>26.76</v>
+      </c>
+      <c r="AE21" s="94" t="n">
         <v>85.53</v>
-      </c>
-      <c r="AE21" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="22">
@@ -8736,148 +8739,150 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="C22" s="91" t="inlineStr">
+      <c r="C22" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D22" s="91" t="inlineStr">
+      <c r="E22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E22" s="91" t="inlineStr">
+      <c r="F22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F22" s="91" t="inlineStr">
+      <c r="G22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G22" s="91" t="inlineStr">
+      <c r="H22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H22" s="91" t="inlineStr">
+      <c r="I22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I22" s="91" t="inlineStr">
+      <c r="J22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J22" s="91" t="inlineStr">
+      <c r="K22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K22" s="91" t="inlineStr">
+      <c r="L22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L22" s="91" t="inlineStr">
+      <c r="M22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M22" s="91" t="inlineStr">
+      <c r="N22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N22" s="92" t="inlineStr">
+      <c r="O22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O22" s="92" t="inlineStr">
+      <c r="P22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P22" s="93" t="inlineStr">
+      <c r="Q22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q22" s="93" t="inlineStr">
+      <c r="R22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R22" s="92" t="inlineStr">
+      <c r="S22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S22" s="92" t="inlineStr">
+      <c r="T22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T22" s="92" t="inlineStr">
+      <c r="U22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U22" s="92" t="inlineStr">
+      <c r="V22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V22" s="92" t="inlineStr">
+      <c r="W22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W22" s="92" t="inlineStr">
+      <c r="X22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X22" s="93" t="inlineStr">
+      <c r="Y22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y22" s="92" t="inlineStr">
+      <c r="Z22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z22" s="92" t="inlineStr">
+      <c r="AA22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA22" s="93" t="inlineStr">
+      <c r="AB22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB22" s="92" t="inlineStr">
+      <c r="AC22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC22" s="92" t="inlineStr">
+      <c r="AD22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD22" s="92" t="inlineStr">
+      <c r="AE22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
-      </c>
-      <c r="AE22" s="92" t="n">
-        <v/>
       </c>
     </row>
     <row r="23">
@@ -8890,25 +8895,25 @@
         <v>6.2</v>
       </c>
       <c r="C23" s="94" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D23" s="94" t="n">
         <v>5.49</v>
-      </c>
-      <c r="D23" s="94" t="n">
-        <v>5.48</v>
       </c>
       <c r="E23" s="94" t="n">
         <v>5.48</v>
       </c>
       <c r="F23" s="94" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="G23" s="94" t="n">
         <v>5.17</v>
       </c>
-      <c r="G23" s="94" t="n">
+      <c r="H23" s="94" t="n">
         <v>3.86</v>
       </c>
-      <c r="H23" s="94" t="n">
+      <c r="I23" s="94" t="n">
         <v>2.56</v>
-      </c>
-      <c r="I23" s="94" t="n">
-        <v>1.3</v>
       </c>
       <c r="J23" s="94" t="n">
         <v>1.3</v>
@@ -8917,64 +8922,64 @@
         <v>1.3</v>
       </c>
       <c r="L23" s="94" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M23" s="94" t="n">
         <v>-0.28</v>
       </c>
-      <c r="M23" s="94" t="n">
+      <c r="N23" s="94" t="n">
         <v>-0.04</v>
       </c>
-      <c r="N23" s="94" t="n">
+      <c r="O23" s="94" t="n">
         <v>-1.3</v>
       </c>
-      <c r="O23" s="94" t="n">
+      <c r="P23" s="94" t="n">
         <v>-1.04</v>
-      </c>
-      <c r="P23" s="94" t="n">
-        <v>-2.62</v>
       </c>
       <c r="Q23" s="94" t="n">
         <v>-2.62</v>
       </c>
       <c r="R23" s="94" t="n">
-        <v>-0.53</v>
+        <v>-2.62</v>
       </c>
       <c r="S23" s="94" t="n">
         <v>-0.53</v>
       </c>
       <c r="T23" s="94" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="U23" s="94" t="n">
         <v>0.17</v>
       </c>
-      <c r="U23" s="94" t="n">
+      <c r="V23" s="94" t="n">
         <v>0.46</v>
-      </c>
-      <c r="V23" s="94" t="n">
-        <v>1.55</v>
       </c>
       <c r="W23" s="94" t="n">
         <v>1.55</v>
       </c>
       <c r="X23" s="94" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Y23" s="94" t="n">
         <v>1.04</v>
-      </c>
-      <c r="Y23" s="94" t="n">
-        <v>0.45</v>
       </c>
       <c r="Z23" s="94" t="n">
         <v>0.45</v>
       </c>
       <c r="AA23" s="94" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB23" s="94" t="n">
         <v>1.34</v>
-      </c>
-      <c r="AB23" s="94" t="n">
-        <v>1.89</v>
       </c>
       <c r="AC23" s="94" t="n">
         <v>1.89</v>
       </c>
       <c r="AD23" s="94" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AE23" s="94" t="n">
         <v>2.77</v>
-      </c>
-      <c r="AE23" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="24">
@@ -8987,25 +8992,25 @@
         <v>15.88</v>
       </c>
       <c r="C24" s="94" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="D24" s="94" t="n">
         <v>12.52</v>
-      </c>
-      <c r="D24" s="94" t="n">
-        <v>10.1</v>
       </c>
       <c r="E24" s="94" t="n">
         <v>10.1</v>
       </c>
       <c r="F24" s="94" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G24" s="94" t="n">
         <v>9.109999999999999</v>
       </c>
-      <c r="G24" s="94" t="n">
+      <c r="H24" s="94" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="H24" s="94" t="n">
+      <c r="I24" s="94" t="n">
         <v>8.6</v>
-      </c>
-      <c r="I24" s="94" t="n">
-        <v>7.14</v>
       </c>
       <c r="J24" s="94" t="n">
         <v>7.14</v>
@@ -9014,64 +9019,64 @@
         <v>7.14</v>
       </c>
       <c r="L24" s="94" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="M24" s="94" t="n">
         <v>8.06</v>
       </c>
-      <c r="M24" s="94" t="n">
+      <c r="N24" s="94" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="N24" s="94" t="n">
+      <c r="O24" s="94" t="n">
         <v>5.35</v>
       </c>
-      <c r="O24" s="94" t="n">
+      <c r="P24" s="94" t="n">
         <v>4.66</v>
-      </c>
-      <c r="P24" s="94" t="n">
-        <v>4.1</v>
       </c>
       <c r="Q24" s="94" t="n">
         <v>4.1</v>
       </c>
       <c r="R24" s="94" t="n">
-        <v>4.84</v>
+        <v>4.1</v>
       </c>
       <c r="S24" s="94" t="n">
         <v>4.84</v>
       </c>
       <c r="T24" s="94" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="U24" s="94" t="n">
         <v>3.23</v>
       </c>
-      <c r="U24" s="94" t="n">
+      <c r="V24" s="94" t="n">
         <v>4.28</v>
-      </c>
-      <c r="V24" s="94" t="n">
-        <v>6.27</v>
       </c>
       <c r="W24" s="94" t="n">
         <v>6.27</v>
       </c>
       <c r="X24" s="94" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="Y24" s="94" t="n">
         <v>5.98</v>
-      </c>
-      <c r="Y24" s="94" t="n">
-        <v>7.02</v>
       </c>
       <c r="Z24" s="94" t="n">
         <v>7.02</v>
       </c>
       <c r="AA24" s="94" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="AB24" s="94" t="n">
         <v>7.18</v>
-      </c>
-      <c r="AB24" s="94" t="n">
-        <v>9.42</v>
       </c>
       <c r="AC24" s="94" t="n">
         <v>9.42</v>
       </c>
       <c r="AD24" s="94" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="AE24" s="94" t="n">
         <v>10.12</v>
-      </c>
-      <c r="AE24" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="25">
@@ -9084,25 +9089,25 @@
         <v>89</v>
       </c>
       <c r="C25" s="94" t="n">
+        <v>89</v>
+      </c>
+      <c r="D25" s="94" t="n">
         <v>86.3</v>
-      </c>
-      <c r="D25" s="94" t="n">
-        <v>79.05</v>
       </c>
       <c r="E25" s="94" t="n">
         <v>79.05</v>
       </c>
       <c r="F25" s="94" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="G25" s="94" t="n">
         <v>95.43000000000001</v>
       </c>
-      <c r="G25" s="94" t="n">
+      <c r="H25" s="94" t="n">
         <v>92.37</v>
       </c>
-      <c r="H25" s="94" t="n">
+      <c r="I25" s="94" t="n">
         <v>91.09999999999999</v>
-      </c>
-      <c r="I25" s="94" t="n">
-        <v>83.62</v>
       </c>
       <c r="J25" s="94" t="n">
         <v>83.62</v>
@@ -9111,64 +9116,64 @@
         <v>83.62</v>
       </c>
       <c r="L25" s="94" t="n">
+        <v>83.62</v>
+      </c>
+      <c r="M25" s="94" t="n">
         <v>74.87</v>
       </c>
-      <c r="M25" s="94" t="n">
+      <c r="N25" s="94" t="n">
         <v>80.75</v>
       </c>
-      <c r="N25" s="94" t="n">
+      <c r="O25" s="94" t="n">
         <v>58.29</v>
       </c>
-      <c r="O25" s="94" t="n">
+      <c r="P25" s="94" t="n">
         <v>44.79</v>
-      </c>
-      <c r="P25" s="94" t="n">
-        <v>15.07</v>
       </c>
       <c r="Q25" s="94" t="n">
         <v>15.07</v>
       </c>
       <c r="R25" s="94" t="n">
-        <v>49.78</v>
+        <v>15.07</v>
       </c>
       <c r="S25" s="94" t="n">
         <v>49.78</v>
       </c>
       <c r="T25" s="94" t="n">
+        <v>49.78</v>
+      </c>
+      <c r="U25" s="94" t="n">
         <v>34.31</v>
       </c>
-      <c r="U25" s="94" t="n">
+      <c r="V25" s="94" t="n">
         <v>52.18</v>
-      </c>
-      <c r="V25" s="94" t="n">
-        <v>54.91</v>
       </c>
       <c r="W25" s="94" t="n">
         <v>54.91</v>
       </c>
       <c r="X25" s="94" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="Y25" s="94" t="n">
         <v>15.8</v>
-      </c>
-      <c r="Y25" s="94" t="n">
-        <v>21.31</v>
       </c>
       <c r="Z25" s="94" t="n">
         <v>21.31</v>
       </c>
       <c r="AA25" s="94" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="AB25" s="94" t="n">
         <v>22.32</v>
-      </c>
-      <c r="AB25" s="94" t="n">
-        <v>40.35</v>
       </c>
       <c r="AC25" s="94" t="n">
         <v>40.35</v>
       </c>
       <c r="AD25" s="94" t="n">
+        <v>40.35</v>
+      </c>
+      <c r="AE25" s="94" t="n">
         <v>70.73999999999999</v>
-      </c>
-      <c r="AE25" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="26">
@@ -9182,148 +9187,150 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="C26" s="93" t="inlineStr">
+      <c r="C26" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D26" s="91" t="inlineStr">
+      <c r="E26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E26" s="91" t="inlineStr">
+      <c r="F26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F26" s="91" t="inlineStr">
+      <c r="G26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G26" s="91" t="inlineStr">
+      <c r="H26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H26" s="91" t="inlineStr">
+      <c r="I26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I26" s="91" t="inlineStr">
+      <c r="J26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J26" s="91" t="inlineStr">
+      <c r="K26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K26" s="91" t="inlineStr">
+      <c r="L26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L26" s="92" t="inlineStr">
+      <c r="M26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M26" s="91" t="inlineStr">
+      <c r="N26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N26" s="93" t="inlineStr">
+      <c r="O26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O26" s="93" t="inlineStr">
+      <c r="P26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P26" s="93" t="inlineStr">
+      <c r="Q26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q26" s="93" t="inlineStr">
+      <c r="R26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R26" s="93" t="inlineStr">
+      <c r="S26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S26" s="93" t="inlineStr">
+      <c r="T26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T26" s="93" t="inlineStr">
+      <c r="U26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U26" s="91" t="inlineStr">
+      <c r="V26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V26" s="91" t="inlineStr">
+      <c r="W26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W26" s="91" t="inlineStr">
+      <c r="X26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X26" s="93" t="inlineStr">
+      <c r="Y26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y26" s="93" t="inlineStr">
+      <c r="Z26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z26" s="93" t="inlineStr">
+      <c r="AA26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA26" s="93" t="inlineStr">
+      <c r="AB26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB26" s="93" t="inlineStr">
+      <c r="AC26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC26" s="93" t="inlineStr">
+      <c r="AD26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD26" s="91" t="inlineStr">
+      <c r="AE26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
-      </c>
-      <c r="AE26" s="92" t="n">
-        <v/>
       </c>
     </row>
     <row r="27">
@@ -9336,25 +9343,25 @@
         <v>5.46</v>
       </c>
       <c r="C27" s="94" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="D27" s="94" t="n">
         <v>4.17</v>
-      </c>
-      <c r="D27" s="94" t="n">
-        <v>7.75</v>
       </c>
       <c r="E27" s="94" t="n">
         <v>7.75</v>
       </c>
       <c r="F27" s="94" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="G27" s="94" t="n">
         <v>8.9</v>
       </c>
-      <c r="G27" s="94" t="n">
+      <c r="H27" s="94" t="n">
         <v>9.48</v>
       </c>
-      <c r="H27" s="94" t="n">
+      <c r="I27" s="94" t="n">
         <v>6.37</v>
-      </c>
-      <c r="I27" s="94" t="n">
-        <v>5.88</v>
       </c>
       <c r="J27" s="94" t="n">
         <v>5.88</v>
@@ -9363,64 +9370,64 @@
         <v>5.88</v>
       </c>
       <c r="L27" s="94" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="M27" s="94" t="n">
         <v>4.59</v>
       </c>
-      <c r="M27" s="94" t="n">
+      <c r="N27" s="94" t="n">
         <v>6.19</v>
       </c>
-      <c r="N27" s="94" t="n">
+      <c r="O27" s="94" t="n">
         <v>3.69</v>
       </c>
-      <c r="O27" s="94" t="n">
+      <c r="P27" s="94" t="n">
         <v>4.22</v>
-      </c>
-      <c r="P27" s="94" t="n">
-        <v>3.56</v>
       </c>
       <c r="Q27" s="94" t="n">
         <v>3.56</v>
       </c>
       <c r="R27" s="94" t="n">
-        <v>6.19</v>
+        <v>3.56</v>
       </c>
       <c r="S27" s="94" t="n">
         <v>6.19</v>
       </c>
       <c r="T27" s="94" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="U27" s="94" t="n">
         <v>6.61</v>
       </c>
-      <c r="U27" s="94" t="n">
+      <c r="V27" s="94" t="n">
         <v>8.6</v>
-      </c>
-      <c r="V27" s="94" t="n">
-        <v>7.91</v>
       </c>
       <c r="W27" s="94" t="n">
         <v>7.91</v>
       </c>
       <c r="X27" s="94" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="Y27" s="94" t="n">
         <v>7.57</v>
-      </c>
-      <c r="Y27" s="94" t="n">
-        <v>6.47</v>
       </c>
       <c r="Z27" s="94" t="n">
         <v>6.47</v>
       </c>
       <c r="AA27" s="94" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="AB27" s="94" t="n">
         <v>8.75</v>
-      </c>
-      <c r="AB27" s="94" t="n">
-        <v>10.02</v>
       </c>
       <c r="AC27" s="94" t="n">
         <v>10.02</v>
       </c>
       <c r="AD27" s="94" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="AE27" s="94" t="n">
         <v>11.78</v>
-      </c>
-      <c r="AE27" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="28">
@@ -9433,25 +9440,25 @@
         <v>21.81</v>
       </c>
       <c r="C28" s="94" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="D28" s="94" t="n">
         <v>15.29</v>
-      </c>
-      <c r="D28" s="94" t="n">
-        <v>16.05</v>
       </c>
       <c r="E28" s="94" t="n">
         <v>16.05</v>
       </c>
       <c r="F28" s="94" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="G28" s="94" t="n">
         <v>13.95</v>
       </c>
-      <c r="G28" s="94" t="n">
+      <c r="H28" s="94" t="n">
         <v>16.69</v>
       </c>
-      <c r="H28" s="94" t="n">
+      <c r="I28" s="94" t="n">
         <v>13.74</v>
-      </c>
-      <c r="I28" s="94" t="n">
-        <v>13.09</v>
       </c>
       <c r="J28" s="94" t="n">
         <v>13.09</v>
@@ -9460,64 +9467,64 @@
         <v>13.09</v>
       </c>
       <c r="L28" s="94" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="M28" s="94" t="n">
         <v>12.55</v>
       </c>
-      <c r="M28" s="94" t="n">
+      <c r="N28" s="94" t="n">
         <v>12.51</v>
       </c>
-      <c r="N28" s="94" t="n">
+      <c r="O28" s="94" t="n">
         <v>5.82</v>
       </c>
-      <c r="O28" s="94" t="n">
+      <c r="P28" s="94" t="n">
         <v>6</v>
-      </c>
-      <c r="P28" s="94" t="n">
-        <v>8.09</v>
       </c>
       <c r="Q28" s="94" t="n">
         <v>8.09</v>
       </c>
       <c r="R28" s="94" t="n">
-        <v>9</v>
+        <v>8.09</v>
       </c>
       <c r="S28" s="94" t="n">
         <v>9</v>
       </c>
       <c r="T28" s="94" t="n">
+        <v>9</v>
+      </c>
+      <c r="U28" s="94" t="n">
         <v>8.289999999999999</v>
       </c>
-      <c r="U28" s="94" t="n">
+      <c r="V28" s="94" t="n">
         <v>7.32</v>
-      </c>
-      <c r="V28" s="94" t="n">
-        <v>6.22</v>
       </c>
       <c r="W28" s="94" t="n">
         <v>6.22</v>
       </c>
       <c r="X28" s="94" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="Y28" s="94" t="n">
         <v>4.8</v>
-      </c>
-      <c r="Y28" s="94" t="n">
-        <v>5.62</v>
       </c>
       <c r="Z28" s="94" t="n">
         <v>5.62</v>
       </c>
       <c r="AA28" s="94" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="AB28" s="94" t="n">
         <v>4.5</v>
-      </c>
-      <c r="AB28" s="94" t="n">
-        <v>7.01</v>
       </c>
       <c r="AC28" s="94" t="n">
         <v>7.01</v>
       </c>
       <c r="AD28" s="94" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="AE28" s="94" t="n">
         <v>8.779999999999999</v>
-      </c>
-      <c r="AE28" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="29">
@@ -9530,25 +9537,25 @@
         <v>55.99</v>
       </c>
       <c r="C29" s="94" t="n">
+        <v>55.99</v>
+      </c>
+      <c r="D29" s="94" t="n">
         <v>8.699999999999999</v>
-      </c>
-      <c r="D29" s="94" t="n">
-        <v>54.41</v>
       </c>
       <c r="E29" s="94" t="n">
         <v>54.41</v>
       </c>
       <c r="F29" s="94" t="n">
+        <v>54.41</v>
+      </c>
+      <c r="G29" s="94" t="n">
         <v>94.87</v>
       </c>
-      <c r="G29" s="94" t="n">
+      <c r="H29" s="94" t="n">
         <v>93.84999999999999</v>
       </c>
-      <c r="H29" s="94" t="n">
+      <c r="I29" s="94" t="n">
         <v>85.8</v>
-      </c>
-      <c r="I29" s="94" t="n">
-        <v>78.89</v>
       </c>
       <c r="J29" s="94" t="n">
         <v>78.89</v>
@@ -9557,64 +9564,64 @@
         <v>78.89</v>
       </c>
       <c r="L29" s="94" t="n">
+        <v>78.89</v>
+      </c>
+      <c r="M29" s="94" t="n">
         <v>51.88</v>
       </c>
-      <c r="M29" s="94" t="n">
+      <c r="N29" s="94" t="n">
         <v>83.56</v>
       </c>
-      <c r="N29" s="94" t="n">
+      <c r="O29" s="94" t="n">
         <v>6.54</v>
       </c>
-      <c r="O29" s="94" t="n">
+      <c r="P29" s="94" t="n">
         <v>8.380000000000001</v>
-      </c>
-      <c r="P29" s="94" t="n">
-        <v>10.96</v>
       </c>
       <c r="Q29" s="94" t="n">
         <v>10.96</v>
       </c>
       <c r="R29" s="94" t="n">
-        <v>32.97</v>
+        <v>10.96</v>
       </c>
       <c r="S29" s="94" t="n">
         <v>32.97</v>
       </c>
       <c r="T29" s="94" t="n">
+        <v>32.97</v>
+      </c>
+      <c r="U29" s="94" t="n">
         <v>34.13</v>
       </c>
-      <c r="U29" s="94" t="n">
+      <c r="V29" s="94" t="n">
         <v>88.52</v>
-      </c>
-      <c r="V29" s="94" t="n">
-        <v>76.26000000000001</v>
       </c>
       <c r="W29" s="94" t="n">
         <v>76.26000000000001</v>
       </c>
       <c r="X29" s="94" t="n">
+        <v>76.26000000000001</v>
+      </c>
+      <c r="Y29" s="94" t="n">
         <v>5.68</v>
-      </c>
-      <c r="Y29" s="94" t="n">
-        <v>6.54</v>
       </c>
       <c r="Z29" s="94" t="n">
         <v>6.54</v>
       </c>
       <c r="AA29" s="94" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="AB29" s="94" t="n">
         <v>11.7</v>
-      </c>
-      <c r="AB29" s="94" t="n">
-        <v>24.8</v>
       </c>
       <c r="AC29" s="94" t="n">
         <v>24.8</v>
       </c>
       <c r="AD29" s="94" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AE29" s="94" t="n">
         <v>85.38</v>
-      </c>
-      <c r="AE29" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="30">
@@ -9623,109 +9630,109 @@
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B30" s="93" t="inlineStr">
+      <c r="B30" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C30" s="92" t="inlineStr">
+      <c r="D30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D30" s="91" t="inlineStr">
+      <c r="E30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E30" s="91" t="inlineStr">
+      <c r="F30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F30" s="91" t="inlineStr">
+      <c r="G30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G30" s="91" t="inlineStr">
+      <c r="H30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H30" s="91" t="inlineStr">
+      <c r="I30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I30" s="92" t="inlineStr">
+      <c r="J30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J30" s="93" t="inlineStr">
+      <c r="K30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K30" s="93" t="inlineStr">
+      <c r="L30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L30" s="93" t="inlineStr">
+      <c r="M30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M30" s="93" t="inlineStr">
+      <c r="N30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N30" s="93" t="inlineStr">
+      <c r="O30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O30" s="93" t="inlineStr">
+      <c r="P30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P30" s="93" t="inlineStr">
+      <c r="Q30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q30" s="93" t="inlineStr">
+      <c r="R30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R30" s="92" t="inlineStr">
+      <c r="S30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S30" s="91" t="inlineStr">
+      <c r="T30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T30" s="91" t="inlineStr">
+      <c r="U30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U30" s="93" t="inlineStr">
+      <c r="V30" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="V30" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="W30" s="91" t="inlineStr">
@@ -9781,46 +9788,46 @@
         </is>
       </c>
       <c r="B31" s="94" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C31" s="94" t="n">
         <v>0.29</v>
       </c>
-      <c r="C31" s="94" t="n">
+      <c r="D31" s="94" t="n">
         <v>2.49</v>
-      </c>
-      <c r="D31" s="94" t="n">
-        <v>5.32</v>
       </c>
       <c r="E31" s="94" t="n">
         <v>5.32</v>
       </c>
       <c r="F31" s="94" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="G31" s="94" t="n">
         <v>4.76</v>
       </c>
-      <c r="G31" s="94" t="n">
+      <c r="H31" s="94" t="n">
         <v>4.05</v>
       </c>
-      <c r="H31" s="94" t="n">
+      <c r="I31" s="94" t="n">
         <v>1.6</v>
       </c>
-      <c r="I31" s="94" t="n">
+      <c r="J31" s="94" t="n">
         <v>-0.13</v>
-      </c>
-      <c r="J31" s="94" t="n">
-        <v>-1.36</v>
       </c>
       <c r="K31" s="94" t="n">
         <v>-1.36</v>
       </c>
       <c r="L31" s="94" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="M31" s="94" t="n">
         <v>-0.87</v>
       </c>
-      <c r="M31" s="94" t="n">
+      <c r="N31" s="94" t="n">
         <v>-1.88</v>
       </c>
-      <c r="N31" s="94" t="n">
+      <c r="O31" s="94" t="n">
         <v>-3.6</v>
-      </c>
-      <c r="O31" s="94" t="n">
-        <v>-1.05</v>
       </c>
       <c r="P31" s="94" t="n">
         <v>-1.05</v>
@@ -9829,19 +9836,19 @@
         <v>-1.05</v>
       </c>
       <c r="R31" s="94" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="S31" s="94" t="n">
         <v>0.57</v>
       </c>
-      <c r="S31" s="94" t="n">
+      <c r="T31" s="94" t="n">
         <v>1.79</v>
       </c>
-      <c r="T31" s="94" t="n">
+      <c r="U31" s="94" t="n">
         <v>2.94</v>
       </c>
-      <c r="U31" s="94" t="n">
+      <c r="V31" s="94" t="n">
         <v>-0.07000000000000001</v>
-      </c>
-      <c r="V31" s="94" t="n">
-        <v>3.26</v>
       </c>
       <c r="W31" s="94" t="n">
         <v>3.26</v>
@@ -9859,65 +9866,65 @@
         <v>3.26</v>
       </c>
       <c r="AB31" s="94" t="n">
-        <v>4.49</v>
+        <v>3.26</v>
       </c>
       <c r="AC31" s="94" t="n">
         <v>4.49</v>
       </c>
       <c r="AD31" s="94" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="AE31" s="94" t="n">
         <v>4.65</v>
       </c>
-      <c r="AE31" s="94" t="n">
-        <v>1.24</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32" s="76" t="inlineStr">
+      <c r="A32" s="95" t="inlineStr">
         <is>
           <t>jp225:RNG120</t>
         </is>
       </c>
       <c r="B32" s="94" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="C32" s="94" t="n">
         <v>8.65</v>
       </c>
-      <c r="C32" s="94" t="n">
+      <c r="D32" s="94" t="n">
         <v>3.78</v>
-      </c>
-      <c r="D32" s="94" t="n">
-        <v>2.12</v>
       </c>
       <c r="E32" s="94" t="n">
         <v>2.12</v>
       </c>
       <c r="F32" s="94" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G32" s="94" t="n">
         <v>3.72</v>
       </c>
-      <c r="G32" s="94" t="n">
+      <c r="H32" s="94" t="n">
         <v>3.06</v>
       </c>
-      <c r="H32" s="94" t="n">
+      <c r="I32" s="94" t="n">
         <v>3.61</v>
       </c>
-      <c r="I32" s="94" t="n">
+      <c r="J32" s="94" t="n">
         <v>2.73</v>
-      </c>
-      <c r="J32" s="94" t="n">
-        <v>-1.8</v>
       </c>
       <c r="K32" s="94" t="n">
         <v>-1.8</v>
       </c>
       <c r="L32" s="94" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="M32" s="94" t="n">
         <v>-2.58</v>
       </c>
-      <c r="M32" s="94" t="n">
+      <c r="N32" s="94" t="n">
         <v>-2.92</v>
       </c>
-      <c r="N32" s="94" t="n">
+      <c r="O32" s="94" t="n">
         <v>-3.97</v>
-      </c>
-      <c r="O32" s="94" t="n">
-        <v>-2.33</v>
       </c>
       <c r="P32" s="94" t="n">
         <v>-2.33</v>
@@ -9926,19 +9933,19 @@
         <v>-2.33</v>
       </c>
       <c r="R32" s="94" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="S32" s="94" t="n">
         <v>-3.63</v>
       </c>
-      <c r="S32" s="94" t="n">
+      <c r="T32" s="94" t="n">
         <v>-3.14</v>
       </c>
-      <c r="T32" s="94" t="n">
+      <c r="U32" s="94" t="n">
         <v>-2.69</v>
       </c>
-      <c r="U32" s="94" t="n">
+      <c r="V32" s="94" t="n">
         <v>-6.91</v>
-      </c>
-      <c r="V32" s="94" t="n">
-        <v>-4.63</v>
       </c>
       <c r="W32" s="94" t="n">
         <v>-4.63</v>
@@ -9956,16 +9963,16 @@
         <v>-4.63</v>
       </c>
       <c r="AB32" s="94" t="n">
-        <v>-3.12</v>
+        <v>-4.63</v>
       </c>
       <c r="AC32" s="94" t="n">
         <v>-3.12</v>
       </c>
       <c r="AD32" s="94" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="AE32" s="94" t="n">
         <v>-2.97</v>
-      </c>
-      <c r="AE32" s="94" t="n">
-        <v>-4.36</v>
       </c>
     </row>
     <row r="33">
@@ -9975,46 +9982,46 @@
         </is>
       </c>
       <c r="B33" s="94" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="C33" s="94" t="n">
         <v>44.81</v>
       </c>
-      <c r="C33" s="94" t="n">
+      <c r="D33" s="94" t="n">
         <v>54.76</v>
-      </c>
-      <c r="D33" s="94" t="n">
-        <v>63.06</v>
       </c>
       <c r="E33" s="94" t="n">
         <v>63.06</v>
       </c>
       <c r="F33" s="94" t="n">
+        <v>63.06</v>
+      </c>
+      <c r="G33" s="94" t="n">
         <v>63.69</v>
       </c>
-      <c r="G33" s="94" t="n">
+      <c r="H33" s="94" t="n">
         <v>59.51</v>
       </c>
-      <c r="H33" s="94" t="n">
+      <c r="I33" s="94" t="n">
         <v>49.22</v>
       </c>
-      <c r="I33" s="94" t="n">
+      <c r="J33" s="94" t="n">
         <v>46.79</v>
-      </c>
-      <c r="J33" s="94" t="n">
-        <v>37.14</v>
       </c>
       <c r="K33" s="94" t="n">
         <v>37.14</v>
       </c>
       <c r="L33" s="94" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="M33" s="94" t="n">
         <v>38.82</v>
       </c>
-      <c r="M33" s="94" t="n">
+      <c r="N33" s="94" t="n">
         <v>36.1</v>
       </c>
-      <c r="N33" s="94" t="n">
+      <c r="O33" s="94" t="n">
         <v>36.44</v>
-      </c>
-      <c r="O33" s="94" t="n">
-        <v>45.43</v>
       </c>
       <c r="P33" s="94" t="n">
         <v>45.43</v>
@@ -10023,19 +10030,19 @@
         <v>45.43</v>
       </c>
       <c r="R33" s="94" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="S33" s="94" t="n">
         <v>52.04</v>
       </c>
-      <c r="S33" s="94" t="n">
+      <c r="T33" s="94" t="n">
         <v>58.96</v>
       </c>
-      <c r="T33" s="94" t="n">
+      <c r="U33" s="94" t="n">
         <v>60.92</v>
       </c>
-      <c r="U33" s="94" t="n">
+      <c r="V33" s="94" t="n">
         <v>49.64</v>
-      </c>
-      <c r="V33" s="94" t="n">
-        <v>61.59</v>
       </c>
       <c r="W33" s="94" t="n">
         <v>61.59</v>
@@ -10053,16 +10060,16 @@
         <v>61.59</v>
       </c>
       <c r="AB33" s="94" t="n">
-        <v>71.7</v>
+        <v>61.59</v>
       </c>
       <c r="AC33" s="94" t="n">
         <v>71.7</v>
       </c>
       <c r="AD33" s="94" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="AE33" s="94" t="n">
         <v>61.28</v>
-      </c>
-      <c r="AE33" s="94" t="n">
-        <v>51.56</v>
       </c>
     </row>
     <row r="34">
@@ -10096,114 +10103,114 @@
           <t>red</t>
         </is>
       </c>
-      <c r="G34" s="92" t="inlineStr">
+      <c r="G34" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H34" s="92" t="inlineStr">
+      <c r="I34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I34" s="91" t="inlineStr">
+      <c r="J34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J34" s="91" t="inlineStr">
+      <c r="K34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K34" s="91" t="inlineStr">
+      <c r="L34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L34" s="92" t="inlineStr">
+      <c r="M34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M34" s="92" t="inlineStr">
+      <c r="N34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N34" s="93" t="inlineStr">
+      <c r="O34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O34" s="93" t="inlineStr">
+      <c r="P34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P34" s="93" t="inlineStr">
+      <c r="Q34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q34" s="93" t="inlineStr">
+      <c r="R34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R34" s="93" t="inlineStr">
+      <c r="S34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S34" s="93" t="inlineStr">
+      <c r="T34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T34" s="93" t="inlineStr">
+      <c r="U34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U34" s="93" t="inlineStr">
+      <c r="V34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V34" s="93" t="inlineStr">
+      <c r="W34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W34" s="93" t="inlineStr">
+      <c r="X34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X34" s="92" t="inlineStr">
+      <c r="Y34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y34" s="92" t="inlineStr">
+      <c r="Z34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z34" s="92" t="inlineStr">
+      <c r="AA34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA34" s="92" t="inlineStr">
+      <c r="AB34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AB34" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AC34" s="91" t="inlineStr">
@@ -10241,82 +10248,82 @@
         <v>0.05</v>
       </c>
       <c r="F35" s="94" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G35" s="94" t="n">
         <v>0.08</v>
       </c>
-      <c r="G35" s="94" t="n">
+      <c r="H35" s="94" t="n">
         <v>-1.53</v>
       </c>
-      <c r="H35" s="94" t="n">
+      <c r="I35" s="94" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="I35" s="94" t="n">
+      <c r="J35" s="94" t="n">
         <v>-0.25</v>
-      </c>
-      <c r="J35" s="94" t="n">
-        <v>-0.66</v>
       </c>
       <c r="K35" s="94" t="n">
         <v>-0.66</v>
       </c>
       <c r="L35" s="94" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="M35" s="94" t="n">
         <v>-2.25</v>
       </c>
-      <c r="M35" s="94" t="n">
+      <c r="N35" s="94" t="n">
         <v>-2.65</v>
       </c>
-      <c r="N35" s="94" t="n">
+      <c r="O35" s="94" t="n">
         <v>-3.96</v>
       </c>
-      <c r="O35" s="94" t="n">
+      <c r="P35" s="94" t="n">
         <v>-3.87</v>
-      </c>
-      <c r="P35" s="94" t="n">
-        <v>-4.36</v>
       </c>
       <c r="Q35" s="94" t="n">
         <v>-4.36</v>
       </c>
       <c r="R35" s="94" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="S35" s="94" t="n">
         <v>-2.63</v>
       </c>
-      <c r="S35" s="94" t="n">
+      <c r="T35" s="94" t="n">
         <v>-2.35</v>
       </c>
-      <c r="T35" s="94" t="n">
+      <c r="U35" s="94" t="n">
         <v>-3.06</v>
       </c>
-      <c r="U35" s="94" t="n">
+      <c r="V35" s="94" t="n">
         <v>-3.26</v>
-      </c>
-      <c r="V35" s="94" t="n">
-        <v>-2.47</v>
       </c>
       <c r="W35" s="94" t="n">
         <v>-2.47</v>
       </c>
       <c r="X35" s="94" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="Y35" s="94" t="n">
         <v>-0.95</v>
-      </c>
-      <c r="Y35" s="94" t="n">
-        <v>-0.41</v>
       </c>
       <c r="Z35" s="94" t="n">
         <v>-0.41</v>
       </c>
       <c r="AA35" s="94" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="AB35" s="94" t="n">
         <v>0.16</v>
-      </c>
-      <c r="AB35" s="94" t="n">
-        <v>0.36</v>
       </c>
       <c r="AC35" s="94" t="n">
         <v>0.36</v>
       </c>
       <c r="AD35" s="94" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AE35" s="94" t="n">
         <v>-0.41</v>
-      </c>
-      <c r="AE35" s="94" t="n">
-        <v>-1.07</v>
       </c>
     </row>
     <row r="36">
@@ -10338,82 +10345,82 @@
         <v>4.53</v>
       </c>
       <c r="F36" s="94" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="G36" s="94" t="n">
         <v>6.02</v>
       </c>
-      <c r="G36" s="94" t="n">
+      <c r="H36" s="94" t="n">
         <v>0.48</v>
       </c>
-      <c r="H36" s="94" t="n">
+      <c r="I36" s="94" t="n">
         <v>1.56</v>
       </c>
-      <c r="I36" s="94" t="n">
+      <c r="J36" s="94" t="n">
         <v>-0.16</v>
-      </c>
-      <c r="J36" s="94" t="n">
-        <v>0.33</v>
       </c>
       <c r="K36" s="94" t="n">
         <v>0.33</v>
       </c>
       <c r="L36" s="94" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M36" s="94" t="n">
         <v>-0.34</v>
       </c>
-      <c r="M36" s="94" t="n">
+      <c r="N36" s="94" t="n">
         <v>-0.48</v>
       </c>
-      <c r="N36" s="94" t="n">
+      <c r="O36" s="94" t="n">
         <v>-0.33</v>
       </c>
-      <c r="O36" s="94" t="n">
+      <c r="P36" s="94" t="n">
         <v>-0.23</v>
-      </c>
-      <c r="P36" s="94" t="n">
-        <v>-0.11</v>
       </c>
       <c r="Q36" s="94" t="n">
         <v>-0.11</v>
       </c>
       <c r="R36" s="94" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="S36" s="94" t="n">
         <v>-0.71</v>
       </c>
-      <c r="S36" s="94" t="n">
+      <c r="T36" s="94" t="n">
         <v>-1.09</v>
       </c>
-      <c r="T36" s="94" t="n">
+      <c r="U36" s="94" t="n">
         <v>-2.16</v>
       </c>
-      <c r="U36" s="94" t="n">
+      <c r="V36" s="94" t="n">
         <v>-1.76</v>
-      </c>
-      <c r="V36" s="94" t="n">
-        <v>-2.08</v>
       </c>
       <c r="W36" s="94" t="n">
         <v>-2.08</v>
       </c>
       <c r="X36" s="94" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="Y36" s="94" t="n">
         <v>-0.79</v>
-      </c>
-      <c r="Y36" s="94" t="n">
-        <v>-1.09</v>
       </c>
       <c r="Z36" s="94" t="n">
         <v>-1.09</v>
       </c>
       <c r="AA36" s="94" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="AB36" s="94" t="n">
         <v>-0.92</v>
-      </c>
-      <c r="AB36" s="94" t="n">
-        <v>-0.84</v>
       </c>
       <c r="AC36" s="94" t="n">
         <v>-0.84</v>
       </c>
       <c r="AD36" s="94" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="AE36" s="94" t="n">
         <v>-1.61</v>
-      </c>
-      <c r="AE36" s="94" t="n">
-        <v>-0.74</v>
       </c>
     </row>
     <row r="37">
@@ -10435,82 +10442,82 @@
         <v>85.3</v>
       </c>
       <c r="F37" s="94" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="G37" s="94" t="n">
         <v>80.56</v>
       </c>
-      <c r="G37" s="94" t="n">
+      <c r="H37" s="94" t="n">
         <v>39.31</v>
       </c>
-      <c r="H37" s="94" t="n">
+      <c r="I37" s="94" t="n">
         <v>55.71</v>
       </c>
-      <c r="I37" s="94" t="n">
+      <c r="J37" s="94" t="n">
         <v>76.36</v>
-      </c>
-      <c r="J37" s="94" t="n">
-        <v>75.59</v>
       </c>
       <c r="K37" s="94" t="n">
         <v>75.59</v>
       </c>
       <c r="L37" s="94" t="n">
+        <v>75.59</v>
+      </c>
+      <c r="M37" s="94" t="n">
         <v>63.48</v>
       </c>
-      <c r="M37" s="94" t="n">
+      <c r="N37" s="94" t="n">
         <v>47.6</v>
       </c>
-      <c r="N37" s="94" t="n">
+      <c r="O37" s="94" t="n">
         <v>21.39</v>
       </c>
-      <c r="O37" s="94" t="n">
+      <c r="P37" s="94" t="n">
         <v>30.94</v>
-      </c>
-      <c r="P37" s="94" t="n">
-        <v>9.859999999999999</v>
       </c>
       <c r="Q37" s="94" t="n">
         <v>9.859999999999999</v>
       </c>
       <c r="R37" s="94" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="S37" s="94" t="n">
         <v>24.76</v>
       </c>
-      <c r="S37" s="94" t="n">
+      <c r="T37" s="94" t="n">
         <v>37.84</v>
       </c>
-      <c r="T37" s="94" t="n">
+      <c r="U37" s="94" t="n">
         <v>14.49</v>
       </c>
-      <c r="U37" s="94" t="n">
+      <c r="V37" s="94" t="n">
         <v>11.22</v>
-      </c>
-      <c r="V37" s="94" t="n">
-        <v>17.28</v>
       </c>
       <c r="W37" s="94" t="n">
         <v>17.28</v>
       </c>
       <c r="X37" s="94" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="Y37" s="94" t="n">
         <v>51.04</v>
-      </c>
-      <c r="Y37" s="94" t="n">
-        <v>34.51</v>
       </c>
       <c r="Z37" s="94" t="n">
         <v>34.51</v>
       </c>
       <c r="AA37" s="94" t="n">
+        <v>34.51</v>
+      </c>
+      <c r="AB37" s="94" t="n">
         <v>57.76</v>
-      </c>
-      <c r="AB37" s="94" t="n">
-        <v>78.84999999999999</v>
       </c>
       <c r="AC37" s="94" t="n">
         <v>78.84999999999999</v>
       </c>
       <c r="AD37" s="94" t="n">
+        <v>78.84999999999999</v>
+      </c>
+      <c r="AE37" s="94" t="n">
         <v>74.3</v>
-      </c>
-      <c r="AE37" s="94" t="n">
-        <v>80.23</v>
       </c>
     </row>
     <row r="38">
@@ -10524,148 +10531,150 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="C38" s="93" t="inlineStr">
+      <c r="C38" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D38" s="92" t="inlineStr">
+      <c r="E38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E38" s="92" t="inlineStr">
+      <c r="F38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F38" s="92" t="inlineStr">
+      <c r="G38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G38" s="92" t="inlineStr">
+      <c r="H38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H38" s="93" t="inlineStr">
+      <c r="I38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I38" s="92" t="inlineStr">
+      <c r="J38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J38" s="92" t="inlineStr">
+      <c r="K38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K38" s="92" t="inlineStr">
+      <c r="L38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L38" s="92" t="inlineStr">
+      <c r="M38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M38" s="92" t="inlineStr">
+      <c r="N38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N38" s="93" t="inlineStr">
+      <c r="O38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O38" s="93" t="inlineStr">
+      <c r="P38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P38" s="93" t="inlineStr">
+      <c r="Q38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q38" s="93" t="inlineStr">
+      <c r="R38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R38" s="93" t="inlineStr">
+      <c r="S38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S38" s="92" t="inlineStr">
+      <c r="T38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T38" s="93" t="inlineStr">
+      <c r="U38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U38" s="93" t="inlineStr">
+      <c r="V38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V38" s="91" t="inlineStr">
+      <c r="W38" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W38" s="91" t="inlineStr">
+      <c r="X38" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X38" s="91" t="inlineStr">
+      <c r="Y38" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y38" s="92" t="inlineStr">
+      <c r="Z38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z38" s="92" t="inlineStr">
+      <c r="AA38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA38" s="92" t="inlineStr">
+      <c r="AB38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB38" s="92" t="inlineStr">
+      <c r="AC38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC38" s="92" t="inlineStr">
+      <c r="AD38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD38" s="92" t="inlineStr">
+      <c r="AE38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
-      </c>
-      <c r="AE38" s="92" t="n">
-        <v/>
       </c>
     </row>
     <row r="39">
@@ -10675,94 +10684,94 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
+        <v>-4.17</v>
+      </c>
+      <c r="C39" s="94" t="n">
         <v>-4.39</v>
       </c>
-      <c r="C39" s="94" t="n">
+      <c r="D39" s="94" t="n">
         <v>-5.72</v>
-      </c>
-      <c r="D39" s="94" t="n">
-        <v>-5.2</v>
       </c>
       <c r="E39" s="94" t="n">
         <v>-5.2</v>
       </c>
       <c r="F39" s="94" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="G39" s="94" t="n">
         <v>-4.36</v>
       </c>
-      <c r="G39" s="94" t="n">
+      <c r="H39" s="94" t="n">
         <v>-3.77</v>
       </c>
-      <c r="H39" s="94" t="n">
+      <c r="I39" s="94" t="n">
         <v>-5.28</v>
       </c>
-      <c r="I39" s="94" t="n">
+      <c r="J39" s="94" t="n">
         <v>-3.76</v>
-      </c>
-      <c r="J39" s="94" t="n">
-        <v>-4.49</v>
       </c>
       <c r="K39" s="94" t="n">
         <v>-4.49</v>
       </c>
       <c r="L39" s="94" t="n">
+        <v>-4.49</v>
+      </c>
+      <c r="M39" s="94" t="n">
         <v>-5.06</v>
       </c>
-      <c r="M39" s="94" t="n">
+      <c r="N39" s="94" t="n">
         <v>-5.54</v>
       </c>
-      <c r="N39" s="94" t="n">
+      <c r="O39" s="94" t="n">
         <v>-5.56</v>
       </c>
-      <c r="O39" s="94" t="n">
+      <c r="P39" s="94" t="n">
         <v>-6.35</v>
-      </c>
-      <c r="P39" s="94" t="n">
-        <v>-5.43</v>
       </c>
       <c r="Q39" s="94" t="n">
         <v>-5.43</v>
       </c>
       <c r="R39" s="94" t="n">
+        <v>-5.43</v>
+      </c>
+      <c r="S39" s="94" t="n">
         <v>-5.31</v>
       </c>
-      <c r="S39" s="94" t="n">
+      <c r="T39" s="94" t="n">
         <v>-3.97</v>
       </c>
-      <c r="T39" s="94" t="n">
+      <c r="U39" s="94" t="n">
         <v>-4.18</v>
       </c>
-      <c r="U39" s="94" t="n">
+      <c r="V39" s="94" t="n">
         <v>-4.3</v>
-      </c>
-      <c r="V39" s="94" t="n">
-        <v>-2.95</v>
       </c>
       <c r="W39" s="94" t="n">
         <v>-2.95</v>
       </c>
       <c r="X39" s="94" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="Y39" s="94" t="n">
         <v>-1.36</v>
       </c>
-      <c r="Y39" s="94" t="n">
+      <c r="Z39" s="94" t="n">
         <v>-3.89</v>
       </c>
-      <c r="Z39" s="94" t="n">
+      <c r="AA39" s="94" t="n">
         <v>-5.28</v>
       </c>
-      <c r="AA39" s="94" t="n">
+      <c r="AB39" s="94" t="n">
         <v>-7.14</v>
-      </c>
-      <c r="AB39" s="94" t="n">
-        <v>-6.64</v>
       </c>
       <c r="AC39" s="94" t="n">
         <v>-6.64</v>
       </c>
       <c r="AD39" s="94" t="n">
+        <v>-6.64</v>
+      </c>
+      <c r="AE39" s="94" t="n">
         <v>-8.300000000000001</v>
-      </c>
-      <c r="AE39" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="40">
@@ -10772,191 +10781,191 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="C40" s="94" t="n">
         <v>-4.49</v>
       </c>
-      <c r="C40" s="94" t="n">
+      <c r="D40" s="94" t="n">
         <v>-4.11</v>
-      </c>
-      <c r="D40" s="94" t="n">
-        <v>-3.26</v>
       </c>
       <c r="E40" s="94" t="n">
         <v>-3.26</v>
       </c>
       <c r="F40" s="94" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="G40" s="94" t="n">
         <v>-5.51</v>
       </c>
-      <c r="G40" s="94" t="n">
+      <c r="H40" s="94" t="n">
         <v>-6.67</v>
       </c>
-      <c r="H40" s="94" t="n">
+      <c r="I40" s="94" t="n">
         <v>-7.22</v>
       </c>
-      <c r="I40" s="94" t="n">
+      <c r="J40" s="94" t="n">
         <v>-5.38</v>
-      </c>
-      <c r="J40" s="94" t="n">
-        <v>-5.82</v>
       </c>
       <c r="K40" s="94" t="n">
         <v>-5.82</v>
       </c>
       <c r="L40" s="94" t="n">
+        <v>-5.82</v>
+      </c>
+      <c r="M40" s="94" t="n">
         <v>-5.27</v>
       </c>
-      <c r="M40" s="94" t="n">
+      <c r="N40" s="94" t="n">
         <v>-4.14</v>
       </c>
-      <c r="N40" s="94" t="n">
+      <c r="O40" s="94" t="n">
         <v>-4.55</v>
       </c>
-      <c r="O40" s="94" t="n">
+      <c r="P40" s="94" t="n">
         <v>-5.1</v>
-      </c>
-      <c r="P40" s="94" t="n">
-        <v>-3.88</v>
       </c>
       <c r="Q40" s="94" t="n">
         <v>-3.88</v>
       </c>
       <c r="R40" s="94" t="n">
+        <v>-3.88</v>
+      </c>
+      <c r="S40" s="94" t="n">
         <v>-3.7</v>
       </c>
-      <c r="S40" s="94" t="n">
+      <c r="T40" s="94" t="n">
         <v>-3.93</v>
       </c>
-      <c r="T40" s="94" t="n">
+      <c r="U40" s="94" t="n">
         <v>-3.12</v>
       </c>
-      <c r="U40" s="94" t="n">
+      <c r="V40" s="94" t="n">
         <v>-3.35</v>
-      </c>
-      <c r="V40" s="94" t="n">
-        <v>-1.61</v>
       </c>
       <c r="W40" s="94" t="n">
         <v>-1.61</v>
       </c>
       <c r="X40" s="94" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="Y40" s="94" t="n">
         <v>0.06</v>
       </c>
-      <c r="Y40" s="94" t="n">
+      <c r="Z40" s="94" t="n">
         <v>-1.77</v>
       </c>
-      <c r="Z40" s="94" t="n">
+      <c r="AA40" s="94" t="n">
         <v>-2.75</v>
       </c>
-      <c r="AA40" s="94" t="n">
+      <c r="AB40" s="94" t="n">
         <v>-2.14</v>
-      </c>
-      <c r="AB40" s="94" t="n">
-        <v>-1.62</v>
       </c>
       <c r="AC40" s="94" t="n">
         <v>-1.62</v>
       </c>
       <c r="AD40" s="94" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="AE40" s="94" t="n">
         <v>-1.97</v>
       </c>
-      <c r="AE40" s="94" t="n">
-        <v/>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" s="96" t="inlineStr">
+      <c r="A41" s="76" t="inlineStr">
         <is>
           <t>sensex:RS10</t>
         </is>
       </c>
       <c r="B41" s="94" t="n">
+        <v>44.55</v>
+      </c>
+      <c r="C41" s="94" t="n">
         <v>38.59</v>
       </c>
-      <c r="C41" s="94" t="n">
+      <c r="D41" s="94" t="n">
         <v>31.52</v>
-      </c>
-      <c r="D41" s="94" t="n">
-        <v>37.51</v>
       </c>
       <c r="E41" s="94" t="n">
         <v>37.51</v>
       </c>
       <c r="F41" s="94" t="n">
+        <v>37.51</v>
+      </c>
+      <c r="G41" s="94" t="n">
         <v>40.26</v>
       </c>
-      <c r="G41" s="94" t="n">
+      <c r="H41" s="94" t="n">
         <v>38.85</v>
       </c>
-      <c r="H41" s="94" t="n">
+      <c r="I41" s="94" t="n">
         <v>31.71</v>
       </c>
-      <c r="I41" s="94" t="n">
+      <c r="J41" s="94" t="n">
         <v>41.13</v>
-      </c>
-      <c r="J41" s="94" t="n">
-        <v>34.71</v>
       </c>
       <c r="K41" s="94" t="n">
         <v>34.71</v>
       </c>
       <c r="L41" s="94" t="n">
+        <v>34.71</v>
+      </c>
+      <c r="M41" s="94" t="n">
         <v>38.21</v>
       </c>
-      <c r="M41" s="94" t="n">
+      <c r="N41" s="94" t="n">
         <v>33.68</v>
       </c>
-      <c r="N41" s="94" t="n">
+      <c r="O41" s="94" t="n">
         <v>30.45</v>
       </c>
-      <c r="O41" s="94" t="n">
+      <c r="P41" s="94" t="n">
         <v>28.07</v>
-      </c>
-      <c r="P41" s="94" t="n">
-        <v>34.68</v>
       </c>
       <c r="Q41" s="94" t="n">
         <v>34.68</v>
       </c>
       <c r="R41" s="94" t="n">
+        <v>34.68</v>
+      </c>
+      <c r="S41" s="94" t="n">
         <v>36.46</v>
       </c>
-      <c r="S41" s="94" t="n">
+      <c r="T41" s="94" t="n">
         <v>40.56</v>
       </c>
-      <c r="T41" s="94" t="n">
+      <c r="U41" s="94" t="n">
         <v>40.95</v>
       </c>
-      <c r="U41" s="94" t="n">
+      <c r="V41" s="94" t="n">
         <v>38.45</v>
-      </c>
-      <c r="V41" s="94" t="n">
-        <v>48.38</v>
       </c>
       <c r="W41" s="94" t="n">
         <v>48.38</v>
       </c>
       <c r="X41" s="94" t="n">
+        <v>48.38</v>
+      </c>
+      <c r="Y41" s="94" t="n">
         <v>55.82</v>
       </c>
-      <c r="Y41" s="94" t="n">
+      <c r="Z41" s="94" t="n">
         <v>39</v>
       </c>
-      <c r="Z41" s="94" t="n">
+      <c r="AA41" s="94" t="n">
         <v>33.12</v>
       </c>
-      <c r="AA41" s="94" t="n">
+      <c r="AB41" s="94" t="n">
         <v>34</v>
-      </c>
-      <c r="AB41" s="94" t="n">
-        <v>37.69</v>
       </c>
       <c r="AC41" s="94" t="n">
         <v>37.69</v>
       </c>
       <c r="AD41" s="94" t="n">
+        <v>37.69</v>
+      </c>
+      <c r="AE41" s="94" t="n">
         <v>34.47</v>
-      </c>
-      <c r="AE41" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="42">
@@ -10975,138 +10984,140 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="D42" s="91" t="inlineStr">
+      <c r="D42" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E42" s="91" t="inlineStr">
+      <c r="F42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F42" s="91" t="inlineStr">
+      <c r="G42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G42" s="91" t="inlineStr">
+      <c r="H42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H42" s="91" t="inlineStr">
+      <c r="I42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I42" s="91" t="inlineStr">
+      <c r="J42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J42" s="91" t="inlineStr">
+      <c r="K42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K42" s="91" t="inlineStr">
+      <c r="L42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L42" s="91" t="inlineStr">
+      <c r="M42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M42" s="91" t="inlineStr">
+      <c r="N42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N42" s="92" t="inlineStr">
+      <c r="O42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O42" s="92" t="inlineStr">
+      <c r="P42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P42" s="92" t="inlineStr">
+      <c r="Q42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q42" s="92" t="inlineStr">
+      <c r="R42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R42" s="91" t="inlineStr">
+      <c r="S42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S42" s="91" t="inlineStr">
+      <c r="T42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T42" s="91" t="inlineStr">
+      <c r="U42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U42" s="91" t="inlineStr">
+      <c r="V42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V42" s="93" t="inlineStr">
+      <c r="W42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W42" s="93" t="inlineStr">
+      <c r="X42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X42" s="91" t="inlineStr">
+      <c r="Y42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y42" s="91" t="inlineStr">
+      <c r="Z42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z42" s="91" t="inlineStr">
+      <c r="AA42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA42" s="92" t="inlineStr">
+      <c r="AB42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB42" s="91" t="inlineStr">
+      <c r="AC42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC42" s="91" t="inlineStr">
+      <c r="AD42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
-      </c>
-      <c r="AD42" s="92" t="n">
-        <v/>
       </c>
       <c r="AE42" s="92" t="n">
         <v/>
@@ -11119,91 +11130,91 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="C43" s="94" t="n">
         <v>7.44</v>
       </c>
-      <c r="C43" s="94" t="n">
+      <c r="D43" s="94" t="n">
         <v>6.44</v>
-      </c>
-      <c r="D43" s="94" t="n">
-        <v>5.55</v>
       </c>
       <c r="E43" s="94" t="n">
         <v>5.55</v>
       </c>
       <c r="F43" s="94" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="G43" s="94" t="n">
         <v>4.44</v>
       </c>
-      <c r="G43" s="94" t="n">
+      <c r="H43" s="94" t="n">
         <v>4.53</v>
       </c>
-      <c r="H43" s="94" t="n">
+      <c r="I43" s="94" t="n">
         <v>3.57</v>
       </c>
-      <c r="I43" s="94" t="n">
+      <c r="J43" s="94" t="n">
         <v>3.15</v>
-      </c>
-      <c r="J43" s="94" t="n">
-        <v>2.32</v>
       </c>
       <c r="K43" s="94" t="n">
         <v>2.32</v>
       </c>
       <c r="L43" s="94" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M43" s="94" t="n">
         <v>1.31</v>
       </c>
-      <c r="M43" s="94" t="n">
+      <c r="N43" s="94" t="n">
         <v>-1.82</v>
       </c>
-      <c r="N43" s="94" t="n">
+      <c r="O43" s="94" t="n">
         <v>-2.11</v>
       </c>
-      <c r="O43" s="94" t="n">
+      <c r="P43" s="94" t="n">
         <v>-1.11</v>
-      </c>
-      <c r="P43" s="94" t="n">
-        <v>-1.21</v>
       </c>
       <c r="Q43" s="94" t="n">
         <v>-1.21</v>
       </c>
       <c r="R43" s="94" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="S43" s="94" t="n">
         <v>-1.47</v>
       </c>
-      <c r="S43" s="94" t="n">
+      <c r="T43" s="94" t="n">
         <v>-1.66</v>
       </c>
-      <c r="T43" s="94" t="n">
+      <c r="U43" s="94" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="U43" s="94" t="n">
+      <c r="V43" s="94" t="n">
         <v>-1.51</v>
-      </c>
-      <c r="V43" s="94" t="n">
-        <v>-3.18</v>
       </c>
       <c r="W43" s="94" t="n">
         <v>-3.18</v>
       </c>
       <c r="X43" s="94" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="Y43" s="94" t="n">
         <v>-2.41</v>
-      </c>
-      <c r="Y43" s="94" t="n">
-        <v>-2.13</v>
       </c>
       <c r="Z43" s="94" t="n">
         <v>-2.13</v>
       </c>
       <c r="AA43" s="94" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="AB43" s="94" t="n">
         <v>-2.2</v>
-      </c>
-      <c r="AB43" s="94" t="n">
-        <v>-2.93</v>
       </c>
       <c r="AC43" s="94" t="n">
         <v>-2.93</v>
       </c>
       <c r="AD43" s="94" t="n">
-        <v/>
+        <v>-2.93</v>
       </c>
       <c r="AE43" s="94" t="n">
         <v/>
@@ -11216,91 +11227,91 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="C44" s="94" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="C44" s="94" t="n">
+      <c r="D44" s="94" t="n">
         <v>8.82</v>
-      </c>
-      <c r="D44" s="94" t="n">
-        <v>11.19</v>
       </c>
       <c r="E44" s="94" t="n">
         <v>11.19</v>
       </c>
       <c r="F44" s="94" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="G44" s="94" t="n">
         <v>10.4</v>
       </c>
-      <c r="G44" s="94" t="n">
+      <c r="H44" s="94" t="n">
         <v>8.08</v>
       </c>
-      <c r="H44" s="94" t="n">
+      <c r="I44" s="94" t="n">
         <v>5.43</v>
       </c>
-      <c r="I44" s="94" t="n">
+      <c r="J44" s="94" t="n">
         <v>2.68</v>
-      </c>
-      <c r="J44" s="94" t="n">
-        <v>3.14</v>
       </c>
       <c r="K44" s="94" t="n">
         <v>3.14</v>
       </c>
       <c r="L44" s="94" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="M44" s="94" t="n">
         <v>2.56</v>
       </c>
-      <c r="M44" s="94" t="n">
+      <c r="N44" s="94" t="n">
         <v>-0.57</v>
       </c>
-      <c r="N44" s="94" t="n">
+      <c r="O44" s="94" t="n">
         <v>-0.05</v>
       </c>
-      <c r="O44" s="94" t="n">
+      <c r="P44" s="94" t="n">
         <v>-1.4</v>
-      </c>
-      <c r="P44" s="94" t="n">
-        <v>-2.21</v>
       </c>
       <c r="Q44" s="94" t="n">
         <v>-2.21</v>
       </c>
       <c r="R44" s="94" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="S44" s="94" t="n">
         <v>-1.73</v>
       </c>
-      <c r="S44" s="94" t="n">
+      <c r="T44" s="94" t="n">
         <v>-1.09</v>
       </c>
-      <c r="T44" s="94" t="n">
+      <c r="U44" s="94" t="n">
         <v>-1.28</v>
       </c>
-      <c r="U44" s="94" t="n">
+      <c r="V44" s="94" t="n">
         <v>-1.65</v>
-      </c>
-      <c r="V44" s="94" t="n">
-        <v>-3.93</v>
       </c>
       <c r="W44" s="94" t="n">
         <v>-3.93</v>
       </c>
       <c r="X44" s="94" t="n">
+        <v>-3.93</v>
+      </c>
+      <c r="Y44" s="94" t="n">
         <v>-3.13</v>
-      </c>
-      <c r="Y44" s="94" t="n">
-        <v>-4.45</v>
       </c>
       <c r="Z44" s="94" t="n">
         <v>-4.45</v>
       </c>
       <c r="AA44" s="94" t="n">
+        <v>-4.45</v>
+      </c>
+      <c r="AB44" s="94" t="n">
         <v>-4.11</v>
-      </c>
-      <c r="AB44" s="94" t="n">
-        <v>-2.88</v>
       </c>
       <c r="AC44" s="94" t="n">
         <v>-2.88</v>
       </c>
       <c r="AD44" s="94" t="n">
-        <v/>
+        <v>-2.88</v>
       </c>
       <c r="AE44" s="94" t="n">
         <v/>
@@ -11313,91 +11324,91 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
+        <v>62.13</v>
+      </c>
+      <c r="C45" s="94" t="n">
         <v>80.88</v>
       </c>
-      <c r="C45" s="94" t="n">
+      <c r="D45" s="94" t="n">
         <v>84.89</v>
-      </c>
-      <c r="D45" s="94" t="n">
-        <v>93.34</v>
       </c>
       <c r="E45" s="94" t="n">
         <v>93.34</v>
       </c>
       <c r="F45" s="94" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="G45" s="94" t="n">
         <v>92.31999999999999</v>
       </c>
-      <c r="G45" s="94" t="n">
+      <c r="H45" s="94" t="n">
         <v>90.48999999999999</v>
       </c>
-      <c r="H45" s="94" t="n">
+      <c r="I45" s="94" t="n">
         <v>87.65000000000001</v>
       </c>
-      <c r="I45" s="94" t="n">
+      <c r="J45" s="94" t="n">
         <v>85.73</v>
-      </c>
-      <c r="J45" s="94" t="n">
-        <v>84.51000000000001</v>
       </c>
       <c r="K45" s="94" t="n">
         <v>84.51000000000001</v>
       </c>
       <c r="L45" s="94" t="n">
+        <v>84.51000000000001</v>
+      </c>
+      <c r="M45" s="94" t="n">
         <v>80.23</v>
       </c>
-      <c r="M45" s="94" t="n">
+      <c r="N45" s="94" t="n">
         <v>62.6</v>
       </c>
-      <c r="N45" s="94" t="n">
+      <c r="O45" s="94" t="n">
         <v>51.62</v>
       </c>
-      <c r="O45" s="94" t="n">
+      <c r="P45" s="94" t="n">
         <v>48.02</v>
-      </c>
-      <c r="P45" s="94" t="n">
-        <v>52.7</v>
       </c>
       <c r="Q45" s="94" t="n">
         <v>52.7</v>
       </c>
       <c r="R45" s="94" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="S45" s="94" t="n">
         <v>66.38</v>
       </c>
-      <c r="S45" s="94" t="n">
+      <c r="T45" s="94" t="n">
         <v>61.23</v>
       </c>
-      <c r="T45" s="94" t="n">
+      <c r="U45" s="94" t="n">
         <v>69.54000000000001</v>
       </c>
-      <c r="U45" s="94" t="n">
+      <c r="V45" s="94" t="n">
         <v>65.06</v>
-      </c>
-      <c r="V45" s="94" t="n">
-        <v>37.52</v>
       </c>
       <c r="W45" s="94" t="n">
         <v>37.52</v>
       </c>
       <c r="X45" s="94" t="n">
+        <v>37.52</v>
+      </c>
+      <c r="Y45" s="94" t="n">
         <v>65.84</v>
-      </c>
-      <c r="Y45" s="94" t="n">
-        <v>63.25</v>
       </c>
       <c r="Z45" s="94" t="n">
         <v>63.25</v>
       </c>
       <c r="AA45" s="94" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="AB45" s="94" t="n">
         <v>46.49</v>
-      </c>
-      <c r="AB45" s="94" t="n">
-        <v>60.14</v>
       </c>
       <c r="AC45" s="94" t="n">
         <v>60.14</v>
       </c>
       <c r="AD45" s="94" t="n">
-        <v/>
+        <v>60.14</v>
       </c>
       <c r="AE45" s="94" t="n">
         <v/>
@@ -11429,128 +11440,130 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="F46" s="91" t="inlineStr">
+      <c r="F46" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G46" s="91" t="inlineStr">
+      <c r="H46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H46" s="91" t="inlineStr">
+      <c r="I46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I46" s="91" t="inlineStr">
+      <c r="J46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J46" s="91" t="inlineStr">
+      <c r="K46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K46" s="91" t="inlineStr">
+      <c r="L46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L46" s="91" t="inlineStr">
+      <c r="M46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M46" s="91" t="inlineStr">
+      <c r="N46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N46" s="91" t="inlineStr">
+      <c r="O46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O46" s="93" t="inlineStr">
+      <c r="P46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P46" s="92" t="inlineStr">
+      <c r="Q46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q46" s="92" t="inlineStr">
+      <c r="R46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R46" s="91" t="inlineStr">
+      <c r="S46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S46" s="91" t="inlineStr">
+      <c r="T46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T46" s="91" t="inlineStr">
+      <c r="U46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U46" s="91" t="inlineStr">
+      <c r="V46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V46" s="93" t="inlineStr">
+      <c r="W46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W46" s="93" t="inlineStr">
+      <c r="X46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X46" s="92" t="inlineStr">
+      <c r="Y46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y46" s="93" t="inlineStr">
+      <c r="Z46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z46" s="93" t="inlineStr">
+      <c r="AA46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA46" s="93" t="inlineStr">
+      <c r="AB46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB46" s="93" t="inlineStr">
+      <c r="AC46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC46" s="93" t="inlineStr">
+      <c r="AD46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
-      </c>
-      <c r="AD46" s="92" t="n">
-        <v/>
       </c>
       <c r="AE46" s="92" t="n">
         <v/>
@@ -11563,76 +11576,76 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="C47" s="94" t="n">
         <v>10.02</v>
       </c>
-      <c r="C47" s="94" t="n">
+      <c r="D47" s="94" t="n">
         <v>8.960000000000001</v>
-      </c>
-      <c r="D47" s="94" t="n">
-        <v>9.92</v>
       </c>
       <c r="E47" s="94" t="n">
         <v>9.92</v>
       </c>
       <c r="F47" s="94" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="G47" s="94" t="n">
         <v>10.12</v>
       </c>
-      <c r="G47" s="94" t="n">
+      <c r="H47" s="94" t="n">
         <v>9.68</v>
       </c>
-      <c r="H47" s="94" t="n">
+      <c r="I47" s="94" t="n">
         <v>8.34</v>
       </c>
-      <c r="I47" s="94" t="n">
+      <c r="J47" s="94" t="n">
         <v>7.86</v>
-      </c>
-      <c r="J47" s="94" t="n">
-        <v>6.34</v>
       </c>
       <c r="K47" s="94" t="n">
         <v>6.34</v>
       </c>
       <c r="L47" s="94" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="M47" s="94" t="n">
         <v>5.47</v>
       </c>
-      <c r="M47" s="94" t="n">
+      <c r="N47" s="94" t="n">
         <v>5.88</v>
       </c>
-      <c r="N47" s="94" t="n">
+      <c r="O47" s="94" t="n">
         <v>4.03</v>
       </c>
-      <c r="O47" s="94" t="n">
+      <c r="P47" s="94" t="n">
         <v>3.2</v>
-      </c>
-      <c r="P47" s="94" t="n">
-        <v>4.34</v>
       </c>
       <c r="Q47" s="94" t="n">
         <v>4.34</v>
       </c>
       <c r="R47" s="94" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="S47" s="94" t="n">
         <v>5.76</v>
       </c>
-      <c r="S47" s="94" t="n">
+      <c r="T47" s="94" t="n">
         <v>5.58</v>
       </c>
-      <c r="T47" s="94" t="n">
+      <c r="U47" s="94" t="n">
         <v>6.68</v>
       </c>
-      <c r="U47" s="94" t="n">
+      <c r="V47" s="94" t="n">
         <v>5.82</v>
-      </c>
-      <c r="V47" s="94" t="n">
-        <v>4.11</v>
       </c>
       <c r="W47" s="94" t="n">
         <v>4.11</v>
       </c>
       <c r="X47" s="94" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="Y47" s="94" t="n">
         <v>5.31</v>
-      </c>
-      <c r="Y47" s="94" t="n">
-        <v>3.88</v>
       </c>
       <c r="Z47" s="94" t="n">
         <v>3.88</v>
@@ -11641,13 +11654,13 @@
         <v>3.88</v>
       </c>
       <c r="AB47" s="94" t="n">
-        <v>4.01</v>
+        <v>3.88</v>
       </c>
       <c r="AC47" s="94" t="n">
         <v>4.01</v>
       </c>
       <c r="AD47" s="94" t="n">
-        <v/>
+        <v>4.01</v>
       </c>
       <c r="AE47" s="94" t="n">
         <v/>
@@ -11660,76 +11673,76 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="C48" s="94" t="n">
         <v>23.49</v>
       </c>
-      <c r="C48" s="94" t="n">
+      <c r="D48" s="94" t="n">
         <v>22.74</v>
-      </c>
-      <c r="D48" s="94" t="n">
-        <v>21.14</v>
       </c>
       <c r="E48" s="94" t="n">
         <v>21.14</v>
       </c>
       <c r="F48" s="94" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="G48" s="94" t="n">
         <v>18.41</v>
       </c>
-      <c r="G48" s="94" t="n">
+      <c r="H48" s="94" t="n">
         <v>14.83</v>
       </c>
-      <c r="H48" s="94" t="n">
+      <c r="I48" s="94" t="n">
         <v>14.29</v>
       </c>
-      <c r="I48" s="94" t="n">
+      <c r="J48" s="94" t="n">
         <v>14.57</v>
-      </c>
-      <c r="J48" s="94" t="n">
-        <v>13.5</v>
       </c>
       <c r="K48" s="94" t="n">
         <v>13.5</v>
       </c>
       <c r="L48" s="94" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M48" s="94" t="n">
         <v>12.88</v>
       </c>
-      <c r="M48" s="94" t="n">
+      <c r="N48" s="94" t="n">
         <v>11.9</v>
       </c>
-      <c r="N48" s="94" t="n">
+      <c r="O48" s="94" t="n">
         <v>9.23</v>
       </c>
-      <c r="O48" s="94" t="n">
+      <c r="P48" s="94" t="n">
         <v>9.380000000000001</v>
-      </c>
-      <c r="P48" s="94" t="n">
-        <v>11.24</v>
       </c>
       <c r="Q48" s="94" t="n">
         <v>11.24</v>
       </c>
       <c r="R48" s="94" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="S48" s="94" t="n">
         <v>10.69</v>
       </c>
-      <c r="S48" s="94" t="n">
+      <c r="T48" s="94" t="n">
         <v>10.27</v>
       </c>
-      <c r="T48" s="94" t="n">
+      <c r="U48" s="94" t="n">
         <v>9.84</v>
       </c>
-      <c r="U48" s="94" t="n">
+      <c r="V48" s="94" t="n">
         <v>8.74</v>
-      </c>
-      <c r="V48" s="94" t="n">
-        <v>6.18</v>
       </c>
       <c r="W48" s="94" t="n">
         <v>6.18</v>
       </c>
       <c r="X48" s="94" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="Y48" s="94" t="n">
         <v>8.039999999999999</v>
-      </c>
-      <c r="Y48" s="94" t="n">
-        <v>8.16</v>
       </c>
       <c r="Z48" s="94" t="n">
         <v>8.16</v>
@@ -11738,13 +11751,13 @@
         <v>8.16</v>
       </c>
       <c r="AB48" s="94" t="n">
-        <v>9.59</v>
+        <v>8.16</v>
       </c>
       <c r="AC48" s="94" t="n">
         <v>9.59</v>
       </c>
       <c r="AD48" s="94" t="n">
-        <v/>
+        <v>9.59</v>
       </c>
       <c r="AE48" s="94" t="n">
         <v/>
@@ -11757,76 +11770,76 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
+        <v>82.22</v>
+      </c>
+      <c r="C49" s="94" t="n">
         <v>80.29000000000001</v>
       </c>
-      <c r="C49" s="94" t="n">
+      <c r="D49" s="94" t="n">
         <v>75.37</v>
-      </c>
-      <c r="D49" s="94" t="n">
-        <v>89.53</v>
       </c>
       <c r="E49" s="94" t="n">
         <v>89.53</v>
       </c>
       <c r="F49" s="94" t="n">
+        <v>89.53</v>
+      </c>
+      <c r="G49" s="94" t="n">
         <v>91.64</v>
       </c>
-      <c r="G49" s="94" t="n">
+      <c r="H49" s="94" t="n">
         <v>89.73</v>
       </c>
-      <c r="H49" s="94" t="n">
+      <c r="I49" s="94" t="n">
         <v>86.16</v>
       </c>
-      <c r="I49" s="94" t="n">
+      <c r="J49" s="94" t="n">
         <v>85.12</v>
-      </c>
-      <c r="J49" s="94" t="n">
-        <v>83.34999999999999</v>
       </c>
       <c r="K49" s="94" t="n">
         <v>83.34999999999999</v>
       </c>
       <c r="L49" s="94" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="M49" s="94" t="n">
         <v>76.81</v>
       </c>
-      <c r="M49" s="94" t="n">
+      <c r="N49" s="94" t="n">
         <v>74.04000000000001</v>
       </c>
-      <c r="N49" s="94" t="n">
+      <c r="O49" s="94" t="n">
         <v>58.54</v>
       </c>
-      <c r="O49" s="94" t="n">
+      <c r="P49" s="94" t="n">
         <v>46.37</v>
-      </c>
-      <c r="P49" s="94" t="n">
-        <v>54.22</v>
       </c>
       <c r="Q49" s="94" t="n">
         <v>54.22</v>
       </c>
       <c r="R49" s="94" t="n">
+        <v>54.22</v>
+      </c>
+      <c r="S49" s="94" t="n">
         <v>65.81999999999999</v>
       </c>
-      <c r="S49" s="94" t="n">
+      <c r="T49" s="94" t="n">
         <v>67.31999999999999</v>
       </c>
-      <c r="T49" s="94" t="n">
+      <c r="U49" s="94" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="U49" s="94" t="n">
+      <c r="V49" s="94" t="n">
         <v>62.55</v>
-      </c>
-      <c r="V49" s="94" t="n">
-        <v>39.09</v>
       </c>
       <c r="W49" s="94" t="n">
         <v>39.09</v>
       </c>
       <c r="X49" s="94" t="n">
+        <v>39.09</v>
+      </c>
+      <c r="Y49" s="94" t="n">
         <v>48.84</v>
-      </c>
-      <c r="Y49" s="94" t="n">
-        <v>35.85</v>
       </c>
       <c r="Z49" s="94" t="n">
         <v>35.85</v>
@@ -11835,13 +11848,13 @@
         <v>35.85</v>
       </c>
       <c r="AB49" s="94" t="n">
-        <v>41.58</v>
+        <v>35.85</v>
       </c>
       <c r="AC49" s="94" t="n">
         <v>41.58</v>
       </c>
       <c r="AD49" s="94" t="n">
-        <v/>
+        <v>41.58</v>
       </c>
       <c r="AE49" s="94" t="n">
         <v/>
@@ -11850,14 +11863,14 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：us500:RS2:16.07&lt;=22;sensex:RS10:38.59&lt;=39</t>
+          <t>今日买报：</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:75.39&gt;=73;us30:RS3:89.0&gt;=85;vn:RS3:85.3&gt;=85;dax30:RNG60:10.02&gt;=10;dax30:RNG120:23.49&gt;=20</t>
+          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:75.39&gt;=73;us30:RS3:89.0&gt;=85;jp225:RNG120:25.29&gt;=20;vn:RS3:85.3&gt;=85;dax30:RNG60:11.63&gt;=10;dax30:RNG120:22.04&gt;=20</t>
         </is>
       </c>
     </row>
@@ -15458,13 +15471,13 @@
       <c r="G2" s="36" t="n">
         <v>66</v>
       </c>
-      <c r="H2" s="97" t="n">
+      <c r="H2" s="96" t="n">
         <v>22.3514585</v>
       </c>
       <c r="I2" s="36" t="n">
         <v>7.06</v>
       </c>
-      <c r="J2" s="98">
+      <c r="J2" s="97">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -15496,13 +15509,13 @@
       <c r="G3" s="39" t="n">
         <v>73</v>
       </c>
-      <c r="H3" s="99" t="n">
+      <c r="H3" s="98" t="n">
         <v>35.0298984</v>
       </c>
       <c r="I3" s="39" t="n">
         <v>11.41</v>
       </c>
-      <c r="J3" s="98">
+      <c r="J3" s="97">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -15534,13 +15547,13 @@
       <c r="G4" s="39" t="n">
         <v>85</v>
       </c>
-      <c r="H4" s="99" t="n">
+      <c r="H4" s="98" t="n">
         <v>122.4911655</v>
       </c>
       <c r="I4" s="39" t="n">
         <v>76.98</v>
       </c>
-      <c r="J4" s="100">
+      <c r="J4" s="99">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -15572,13 +15585,13 @@
       <c r="G5" s="39" t="n">
         <v>96</v>
       </c>
-      <c r="H5" s="99" t="n">
+      <c r="H5" s="98" t="n">
         <v>136.13543</v>
       </c>
       <c r="I5" s="39" t="n">
         <v>100.05</v>
       </c>
-      <c r="J5" s="100">
+      <c r="J5" s="99">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -15610,13 +15623,13 @@
       <c r="G6" s="39" t="n">
         <v>95</v>
       </c>
-      <c r="H6" s="99" t="n">
+      <c r="H6" s="98" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I6" s="39" t="n">
         <v>44.37</v>
       </c>
-      <c r="J6" s="100">
+      <c r="J6" s="99">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -15648,13 +15661,13 @@
       <c r="G7" s="39" t="n">
         <v>86</v>
       </c>
-      <c r="H7" s="99" t="n">
+      <c r="H7" s="98" t="n">
         <v>123.8525927</v>
       </c>
       <c r="I7" s="39" t="n">
         <v>63.41</v>
       </c>
-      <c r="J7" s="100">
+      <c r="J7" s="99">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -15686,13 +15699,13 @@
       <c r="G8" s="39" t="n">
         <v>87</v>
       </c>
-      <c r="H8" s="99" t="n">
+      <c r="H8" s="98" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I8" s="39" t="n">
         <v>26.39</v>
       </c>
-      <c r="J8" s="100">
+      <c r="J8" s="99">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -15724,13 +15737,13 @@
       <c r="G9" s="39" t="n">
         <v>83</v>
       </c>
-      <c r="H9" s="99" t="n">
+      <c r="H9" s="98" t="n">
         <v>47.02060524</v>
       </c>
       <c r="I9" s="39" t="n">
         <v>37.82</v>
       </c>
-      <c r="J9" s="100">
+      <c r="J9" s="99">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -15761,13 +15774,13 @@
       <c r="G10" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="H10" s="101" t="n">
+      <c r="H10" s="100" t="n">
         <v>27.8860732</v>
       </c>
       <c r="I10" s="24" t="n">
         <v>-10.97</v>
       </c>
-      <c r="J10" s="102" t="n">
+      <c r="J10" s="101" t="n">
         <v>0.278860732</v>
       </c>
     </row>
@@ -15798,13 +15811,13 @@
       <c r="G11" s="24" t="n">
         <v>93</v>
       </c>
-      <c r="H11" s="101" t="n">
+      <c r="H11" s="100" t="n">
         <v>17.4948656</v>
       </c>
       <c r="I11" s="24" t="n">
         <v>-7.7</v>
       </c>
-      <c r="J11" s="102">
+      <c r="J11" s="101">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -8892,7 +8892,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>6.2</v>
@@ -8989,7 +8989,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>15.88</v>
+        <v>14.66</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>15.88</v>
@@ -9080,13 +9080,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="95" t="inlineStr">
+      <c r="A25" s="76" t="inlineStr">
         <is>
           <t>us30:RS3</t>
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>89</v>
+        <v>68.69</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>89</v>
@@ -10684,7 +10684,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-4.17</v>
+        <v>-4</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>-4.39</v>
@@ -10781,7 +10781,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>-3.15</v>
+        <v>-2.98</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>-4.49</v>
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>44.55</v>
+        <v>45.92</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>38.59</v>
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>5.95</v>
+        <v>6.25</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>7.44</v>
@@ -11227,7 +11227,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>7.99</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>8.970000000000001</v>
@@ -11324,7 +11324,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>62.13</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>80.88</v>
@@ -11420,9 +11420,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B46" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C46" s="92" t="inlineStr">
@@ -11576,7 +11576,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>11.63</v>
+        <v>12.36</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>10.02</v>
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>22.04</v>
+        <v>22.83</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>23.49</v>
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>82.22</v>
+        <v>85.23</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>80.29000000000001</v>
@@ -11870,7 +11870,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:75.39&gt;=73;us30:RS3:89.0&gt;=85;jp225:RNG120:25.29&gt;=20;vn:RS3:85.3&gt;=85;dax30:RNG60:11.63&gt;=10;dax30:RNG120:22.04&gt;=20</t>
+          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:75.39&gt;=73;jp225:RNG120:25.29&gt;=20;vn:RS3:85.3&gt;=85;dax30:RNG60:12.36&gt;=10;dax30:RNG120:22.83&gt;=20</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -6341,152 +6341,152 @@
       </c>
       <c r="B1" s="77" t="inlineStr">
         <is>
+          <t>250130</t>
+        </is>
+      </c>
+      <c r="C1" s="77" t="inlineStr">
+        <is>
           <t>250129</t>
         </is>
       </c>
-      <c r="C1" s="77" t="inlineStr">
+      <c r="D1" s="77" t="inlineStr">
         <is>
           <t>250128</t>
         </is>
       </c>
-      <c r="D1" s="77" t="inlineStr">
+      <c r="E1" s="77" t="inlineStr">
         <is>
           <t>250127</t>
         </is>
       </c>
-      <c r="E1" s="77" t="inlineStr">
+      <c r="F1" s="77" t="inlineStr">
         <is>
           <t>250126</t>
         </is>
       </c>
-      <c r="F1" s="77" t="inlineStr">
+      <c r="G1" s="77" t="inlineStr">
         <is>
           <t>250124</t>
         </is>
       </c>
-      <c r="G1" s="77" t="inlineStr">
+      <c r="H1" s="77" t="inlineStr">
         <is>
           <t>250123</t>
         </is>
       </c>
-      <c r="H1" s="77" t="inlineStr">
+      <c r="I1" s="77" t="inlineStr">
         <is>
           <t>250122</t>
         </is>
       </c>
-      <c r="I1" s="77" t="inlineStr">
+      <c r="J1" s="77" t="inlineStr">
         <is>
           <t>250121</t>
         </is>
       </c>
-      <c r="J1" s="77" t="inlineStr">
+      <c r="K1" s="77" t="inlineStr">
         <is>
           <t>250120</t>
         </is>
       </c>
-      <c r="K1" s="77" t="inlineStr">
+      <c r="L1" s="77" t="inlineStr">
         <is>
           <t>250119</t>
         </is>
       </c>
-      <c r="L1" s="77" t="inlineStr">
+      <c r="M1" s="77" t="inlineStr">
         <is>
           <t>250117</t>
         </is>
       </c>
-      <c r="M1" s="77" t="inlineStr">
+      <c r="N1" s="77" t="inlineStr">
         <is>
           <t>250116</t>
         </is>
       </c>
-      <c r="N1" s="77" t="inlineStr">
+      <c r="O1" s="77" t="inlineStr">
         <is>
           <t>250115</t>
         </is>
       </c>
-      <c r="O1" s="77" t="inlineStr">
+      <c r="P1" s="77" t="inlineStr">
         <is>
           <t>250114</t>
         </is>
       </c>
-      <c r="P1" s="77" t="inlineStr">
+      <c r="Q1" s="77" t="inlineStr">
         <is>
           <t>250113</t>
         </is>
       </c>
-      <c r="Q1" s="77" t="inlineStr">
+      <c r="R1" s="77" t="inlineStr">
         <is>
           <t>250112</t>
         </is>
       </c>
-      <c r="R1" s="77" t="inlineStr">
+      <c r="S1" s="77" t="inlineStr">
         <is>
           <t>250110</t>
         </is>
       </c>
-      <c r="S1" s="77" t="inlineStr">
+      <c r="T1" s="77" t="inlineStr">
         <is>
           <t>250109</t>
         </is>
       </c>
-      <c r="T1" s="77" t="inlineStr">
+      <c r="U1" s="77" t="inlineStr">
         <is>
           <t>250108</t>
         </is>
       </c>
-      <c r="U1" s="77" t="inlineStr">
+      <c r="V1" s="77" t="inlineStr">
         <is>
           <t>250107</t>
         </is>
       </c>
-      <c r="V1" s="77" t="inlineStr">
+      <c r="W1" s="77" t="inlineStr">
         <is>
           <t>250106</t>
         </is>
       </c>
-      <c r="W1" s="77" t="inlineStr">
+      <c r="X1" s="77" t="inlineStr">
         <is>
           <t>250105</t>
         </is>
       </c>
-      <c r="X1" s="77" t="inlineStr">
+      <c r="Y1" s="77" t="inlineStr">
         <is>
           <t>250103</t>
         </is>
       </c>
-      <c r="Y1" s="77" t="inlineStr">
+      <c r="Z1" s="77" t="inlineStr">
         <is>
           <t>250102</t>
         </is>
       </c>
-      <c r="Z1" s="77" t="inlineStr">
+      <c r="AA1" s="77" t="inlineStr">
         <is>
           <t>250101</t>
         </is>
       </c>
-      <c r="AA1" s="77" t="inlineStr">
+      <c r="AB1" s="77" t="inlineStr">
         <is>
           <t>241231</t>
         </is>
       </c>
-      <c r="AB1" s="77" t="inlineStr">
+      <c r="AC1" s="77" t="inlineStr">
         <is>
           <t>241230</t>
         </is>
       </c>
-      <c r="AC1" s="77" t="inlineStr">
+      <c r="AD1" s="77" t="inlineStr">
         <is>
           <t>241229</t>
         </is>
       </c>
-      <c r="AD1" s="77" t="inlineStr">
+      <c r="AE1" s="77" t="inlineStr">
         <is>
           <t>241227</t>
-        </is>
-      </c>
-      <c r="AE1" s="77" t="inlineStr">
-        <is>
-          <t>241226</t>
         </is>
       </c>
     </row>
@@ -6521,114 +6521,114 @@
           <t>red</t>
         </is>
       </c>
-      <c r="G2" s="92" t="inlineStr">
+      <c r="G2" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H2" s="93" t="inlineStr">
+      <c r="I2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I2" s="92" t="inlineStr">
+      <c r="J2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J2" s="92" t="inlineStr">
+      <c r="K2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K2" s="92" t="inlineStr">
+      <c r="L2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L2" s="92" t="inlineStr">
+      <c r="M2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M2" s="92" t="inlineStr">
+      <c r="N2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N2" s="92" t="inlineStr">
+      <c r="O2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O2" s="92" t="inlineStr">
+      <c r="P2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P2" s="92" t="inlineStr">
+      <c r="Q2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q2" s="93" t="inlineStr">
+      <c r="R2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R2" s="93" t="inlineStr">
+      <c r="S2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S2" s="92" t="inlineStr">
+      <c r="T2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T2" s="92" t="inlineStr">
+      <c r="U2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U2" s="92" t="inlineStr">
+      <c r="V2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V2" s="93" t="inlineStr">
+      <c r="W2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W2" s="93" t="inlineStr">
+      <c r="X2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X2" s="93" t="inlineStr">
+      <c r="Y2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y2" s="93" t="inlineStr">
+      <c r="Z2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z2" s="93" t="inlineStr">
+      <c r="AA2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA2" s="93" t="inlineStr">
+      <c r="AB2" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AB2" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AC2" s="91" t="inlineStr">
@@ -6663,85 +6663,85 @@
         <v>-0.65</v>
       </c>
       <c r="E3" s="94" t="n">
-        <v>-0.83</v>
+        <v>-0.65</v>
       </c>
       <c r="F3" s="94" t="n">
         <v>-0.83</v>
       </c>
       <c r="G3" s="94" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="H3" s="94" t="n">
         <v>-1.1</v>
       </c>
-      <c r="H3" s="94" t="n">
+      <c r="I3" s="94" t="n">
         <v>-2.21</v>
       </c>
-      <c r="I3" s="94" t="n">
+      <c r="J3" s="94" t="n">
         <v>-2.4</v>
       </c>
-      <c r="J3" s="94" t="n">
+      <c r="K3" s="94" t="n">
         <v>-1.68</v>
-      </c>
-      <c r="K3" s="94" t="n">
-        <v>-1.17</v>
       </c>
       <c r="L3" s="94" t="n">
         <v>-1.17</v>
       </c>
       <c r="M3" s="94" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="N3" s="94" t="n">
         <v>-2.02</v>
       </c>
-      <c r="N3" s="94" t="n">
+      <c r="O3" s="94" t="n">
         <v>-1.79</v>
       </c>
-      <c r="O3" s="94" t="n">
+      <c r="P3" s="94" t="n">
         <v>-0.83</v>
       </c>
-      <c r="P3" s="94" t="n">
+      <c r="Q3" s="94" t="n">
         <v>-3.09</v>
-      </c>
-      <c r="Q3" s="94" t="n">
-        <v>-0.03</v>
       </c>
       <c r="R3" s="94" t="n">
         <v>-0.03</v>
       </c>
       <c r="S3" s="94" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="T3" s="94" t="n">
         <v>0.26</v>
       </c>
-      <c r="T3" s="94" t="n">
+      <c r="U3" s="94" t="n">
         <v>0.9</v>
       </c>
-      <c r="U3" s="94" t="n">
+      <c r="V3" s="94" t="n">
         <v>-1.66</v>
       </c>
-      <c r="V3" s="94" t="n">
+      <c r="W3" s="94" t="n">
         <v>-0.34</v>
-      </c>
-      <c r="W3" s="94" t="n">
-        <v>-2.74</v>
       </c>
       <c r="X3" s="94" t="n">
         <v>-2.74</v>
       </c>
       <c r="Y3" s="94" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="Z3" s="94" t="n">
         <v>0.11</v>
-      </c>
-      <c r="Z3" s="94" t="n">
-        <v>-3.95</v>
       </c>
       <c r="AA3" s="94" t="n">
         <v>-3.95</v>
       </c>
       <c r="AB3" s="94" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="AC3" s="94" t="n">
         <v>2.12</v>
-      </c>
-      <c r="AC3" s="94" t="n">
-        <v>10.12</v>
       </c>
       <c r="AD3" s="94" t="n">
         <v>10.12</v>
       </c>
       <c r="AE3" s="94" t="n">
-        <v>13.23</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="4">
@@ -6760,85 +6760,85 @@
         <v>10.61</v>
       </c>
       <c r="E4" s="94" t="n">
-        <v>12.97</v>
+        <v>10.61</v>
       </c>
       <c r="F4" s="94" t="n">
         <v>12.97</v>
       </c>
       <c r="G4" s="94" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="H4" s="94" t="n">
         <v>11.7</v>
       </c>
-      <c r="H4" s="94" t="n">
+      <c r="I4" s="94" t="n">
         <v>11.16</v>
       </c>
-      <c r="I4" s="94" t="n">
+      <c r="J4" s="94" t="n">
         <v>12.33</v>
       </c>
-      <c r="J4" s="94" t="n">
+      <c r="K4" s="94" t="n">
         <v>11.8</v>
-      </c>
-      <c r="K4" s="94" t="n">
-        <v>11.2</v>
       </c>
       <c r="L4" s="94" t="n">
         <v>11.2</v>
       </c>
       <c r="M4" s="94" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="N4" s="94" t="n">
         <v>9.17</v>
       </c>
-      <c r="N4" s="94" t="n">
+      <c r="O4" s="94" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="O4" s="94" t="n">
+      <c r="P4" s="94" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="P4" s="94" t="n">
+      <c r="Q4" s="94" t="n">
         <v>6.68</v>
-      </c>
-      <c r="Q4" s="94" t="n">
-        <v>6.46</v>
       </c>
       <c r="R4" s="94" t="n">
         <v>6.46</v>
       </c>
       <c r="S4" s="94" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="T4" s="94" t="n">
         <v>7.98</v>
       </c>
-      <c r="T4" s="94" t="n">
+      <c r="U4" s="94" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="U4" s="94" t="n">
+      <c r="V4" s="94" t="n">
         <v>8.73</v>
       </c>
-      <c r="V4" s="94" t="n">
+      <c r="W4" s="94" t="n">
         <v>9.1</v>
-      </c>
-      <c r="W4" s="94" t="n">
-        <v>8.52</v>
       </c>
       <c r="X4" s="94" t="n">
         <v>8.52</v>
       </c>
       <c r="Y4" s="94" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="Z4" s="94" t="n">
         <v>11.64</v>
-      </c>
-      <c r="Z4" s="94" t="n">
-        <v>13.62</v>
       </c>
       <c r="AA4" s="94" t="n">
         <v>13.62</v>
       </c>
       <c r="AB4" s="94" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="AC4" s="94" t="n">
         <v>15.21</v>
-      </c>
-      <c r="AC4" s="94" t="n">
-        <v>14.01</v>
       </c>
       <c r="AD4" s="94" t="n">
         <v>14.01</v>
       </c>
       <c r="AE4" s="94" t="n">
-        <v>13.38</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="5">
@@ -6857,85 +6857,85 @@
         <v>67.42</v>
       </c>
       <c r="E5" s="94" t="n">
-        <v>71.19</v>
+        <v>67.42</v>
       </c>
       <c r="F5" s="94" t="n">
         <v>71.19</v>
       </c>
       <c r="G5" s="94" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="H5" s="94" t="n">
         <v>50.98</v>
       </c>
-      <c r="H5" s="94" t="n">
+      <c r="I5" s="94" t="n">
         <v>25.28</v>
       </c>
-      <c r="I5" s="94" t="n">
+      <c r="J5" s="94" t="n">
         <v>65.31999999999999</v>
       </c>
-      <c r="J5" s="94" t="n">
+      <c r="K5" s="94" t="n">
         <v>69.8</v>
-      </c>
-      <c r="K5" s="94" t="n">
-        <v>67.65000000000001</v>
       </c>
       <c r="L5" s="94" t="n">
         <v>67.65000000000001</v>
       </c>
       <c r="M5" s="94" t="n">
+        <v>67.65000000000001</v>
+      </c>
+      <c r="N5" s="94" t="n">
         <v>63.76</v>
       </c>
-      <c r="N5" s="94" t="n">
+      <c r="O5" s="94" t="n">
         <v>58.67</v>
       </c>
-      <c r="O5" s="94" t="n">
+      <c r="P5" s="94" t="n">
         <v>68.65000000000001</v>
       </c>
-      <c r="P5" s="94" t="n">
+      <c r="Q5" s="94" t="n">
         <v>8.279999999999999</v>
-      </c>
-      <c r="Q5" s="94" t="n">
-        <v>9.460000000000001</v>
       </c>
       <c r="R5" s="94" t="n">
         <v>9.460000000000001</v>
       </c>
       <c r="S5" s="94" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="T5" s="94" t="n">
         <v>19.81</v>
       </c>
-      <c r="T5" s="94" t="n">
+      <c r="U5" s="94" t="n">
         <v>29.11</v>
       </c>
-      <c r="U5" s="94" t="n">
+      <c r="V5" s="94" t="n">
         <v>28.48</v>
       </c>
-      <c r="V5" s="94" t="n">
+      <c r="W5" s="94" t="n">
         <v>4.01</v>
-      </c>
-      <c r="W5" s="94" t="n">
-        <v>4.21</v>
       </c>
       <c r="X5" s="94" t="n">
         <v>4.21</v>
       </c>
       <c r="Y5" s="94" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="Z5" s="94" t="n">
         <v>6.55</v>
-      </c>
-      <c r="Z5" s="94" t="n">
-        <v>18.7</v>
       </c>
       <c r="AA5" s="94" t="n">
         <v>18.7</v>
       </c>
       <c r="AB5" s="94" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AC5" s="94" t="n">
         <v>81.11</v>
-      </c>
-      <c r="AC5" s="94" t="n">
-        <v>73.47</v>
       </c>
       <c r="AD5" s="94" t="n">
         <v>73.47</v>
       </c>
       <c r="AE5" s="94" t="n">
-        <v>71.25</v>
+        <v>73.47</v>
       </c>
     </row>
     <row r="6">
@@ -6959,124 +6959,124 @@
           <t>green</t>
         </is>
       </c>
-      <c r="E6" s="91" t="inlineStr">
+      <c r="E6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F6" s="91" t="inlineStr">
+      <c r="G6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G6" s="93" t="inlineStr">
+      <c r="H6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H6" s="91" t="inlineStr">
+      <c r="I6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I6" s="91" t="inlineStr">
+      <c r="J6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J6" s="92" t="inlineStr">
+      <c r="K6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K6" s="92" t="inlineStr">
+      <c r="L6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L6" s="92" t="inlineStr">
+      <c r="M6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M6" s="93" t="inlineStr">
+      <c r="N6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N6" s="91" t="inlineStr">
+      <c r="O6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O6" s="91" t="inlineStr">
+      <c r="P6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P6" s="92" t="inlineStr">
+      <c r="Q6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q6" s="92" t="inlineStr">
+      <c r="R6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R6" s="92" t="inlineStr">
+      <c r="S6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S6" s="92" t="inlineStr">
+      <c r="T6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T6" s="92" t="inlineStr">
+      <c r="U6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U6" s="92" t="inlineStr">
+      <c r="V6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V6" s="93" t="inlineStr">
+      <c r="W6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W6" s="93" t="inlineStr">
+      <c r="X6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X6" s="93" t="inlineStr">
+      <c r="Y6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y6" s="93" t="inlineStr">
+      <c r="Z6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z6" s="93" t="inlineStr">
+      <c r="AA6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA6" s="93" t="inlineStr">
+      <c r="AB6" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AB6" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AC6" s="91" t="inlineStr">
@@ -7111,85 +7111,85 @@
         <v>1.63</v>
       </c>
       <c r="E7" s="94" t="n">
-        <v>0.55</v>
+        <v>1.63</v>
       </c>
       <c r="F7" s="94" t="n">
         <v>0.55</v>
       </c>
       <c r="G7" s="94" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H7" s="94" t="n">
         <v>0.76</v>
       </c>
-      <c r="H7" s="94" t="n">
+      <c r="I7" s="94" t="n">
         <v>-0</v>
       </c>
-      <c r="I7" s="94" t="n">
+      <c r="J7" s="94" t="n">
         <v>-1.04</v>
       </c>
-      <c r="J7" s="94" t="n">
+      <c r="K7" s="94" t="n">
         <v>-2.32</v>
-      </c>
-      <c r="K7" s="94" t="n">
-        <v>-1.2</v>
       </c>
       <c r="L7" s="94" t="n">
         <v>-1.2</v>
       </c>
       <c r="M7" s="94" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="N7" s="94" t="n">
         <v>-2.32</v>
       </c>
-      <c r="N7" s="94" t="n">
+      <c r="O7" s="94" t="n">
         <v>-0.83</v>
       </c>
-      <c r="O7" s="94" t="n">
+      <c r="P7" s="94" t="n">
         <v>-1.86</v>
       </c>
-      <c r="P7" s="94" t="n">
+      <c r="Q7" s="94" t="n">
         <v>-2.7</v>
-      </c>
-      <c r="Q7" s="94" t="n">
-        <v>8.130000000000001</v>
       </c>
       <c r="R7" s="94" t="n">
         <v>8.130000000000001</v>
       </c>
       <c r="S7" s="94" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="T7" s="94" t="n">
         <v>9.789999999999999</v>
       </c>
-      <c r="T7" s="94" t="n">
+      <c r="U7" s="94" t="n">
         <v>7.38</v>
       </c>
-      <c r="U7" s="94" t="n">
+      <c r="V7" s="94" t="n">
         <v>4.27</v>
       </c>
-      <c r="V7" s="94" t="n">
+      <c r="W7" s="94" t="n">
         <v>4.43</v>
-      </c>
-      <c r="W7" s="94" t="n">
-        <v>-1.29</v>
       </c>
       <c r="X7" s="94" t="n">
         <v>-1.29</v>
       </c>
       <c r="Y7" s="94" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="Z7" s="94" t="n">
         <v>-4.26</v>
-      </c>
-      <c r="Z7" s="94" t="n">
-        <v>-3.42</v>
       </c>
       <c r="AA7" s="94" t="n">
         <v>-3.42</v>
       </c>
       <c r="AB7" s="94" t="n">
+        <v>-3.42</v>
+      </c>
+      <c r="AC7" s="94" t="n">
         <v>17</v>
-      </c>
-      <c r="AC7" s="94" t="n">
-        <v>37.64</v>
       </c>
       <c r="AD7" s="94" t="n">
         <v>37.64</v>
       </c>
       <c r="AE7" s="94" t="n">
-        <v>48.17</v>
+        <v>37.64</v>
       </c>
     </row>
     <row r="8">
@@ -7208,85 +7208,85 @@
         <v>28.48</v>
       </c>
       <c r="E8" s="94" t="n">
-        <v>37.3</v>
+        <v>28.48</v>
       </c>
       <c r="F8" s="94" t="n">
         <v>37.3</v>
       </c>
       <c r="G8" s="94" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="H8" s="94" t="n">
         <v>36.53</v>
       </c>
-      <c r="H8" s="94" t="n">
+      <c r="I8" s="94" t="n">
         <v>35.49</v>
       </c>
-      <c r="I8" s="94" t="n">
+      <c r="J8" s="94" t="n">
         <v>36.76</v>
       </c>
-      <c r="J8" s="94" t="n">
+      <c r="K8" s="94" t="n">
         <v>35.74</v>
-      </c>
-      <c r="K8" s="94" t="n">
-        <v>33.95</v>
       </c>
       <c r="L8" s="94" t="n">
         <v>33.95</v>
       </c>
       <c r="M8" s="94" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="N8" s="94" t="n">
         <v>27.18</v>
       </c>
-      <c r="N8" s="94" t="n">
+      <c r="O8" s="94" t="n">
         <v>30.45</v>
       </c>
-      <c r="O8" s="94" t="n">
+      <c r="P8" s="94" t="n">
         <v>33.5</v>
       </c>
-      <c r="P8" s="94" t="n">
+      <c r="Q8" s="94" t="n">
         <v>30.62</v>
-      </c>
-      <c r="Q8" s="94" t="n">
-        <v>29.85</v>
       </c>
       <c r="R8" s="94" t="n">
         <v>29.85</v>
       </c>
       <c r="S8" s="94" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="T8" s="94" t="n">
         <v>34.31</v>
       </c>
-      <c r="T8" s="94" t="n">
+      <c r="U8" s="94" t="n">
         <v>34.35</v>
       </c>
-      <c r="U8" s="94" t="n">
+      <c r="V8" s="94" t="n">
         <v>34.47</v>
       </c>
-      <c r="V8" s="94" t="n">
+      <c r="W8" s="94" t="n">
         <v>32.14</v>
-      </c>
-      <c r="W8" s="94" t="n">
-        <v>32.67</v>
       </c>
       <c r="X8" s="94" t="n">
         <v>32.67</v>
       </c>
       <c r="Y8" s="94" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="Z8" s="94" t="n">
         <v>37.96</v>
-      </c>
-      <c r="Z8" s="94" t="n">
-        <v>41.51</v>
       </c>
       <c r="AA8" s="94" t="n">
         <v>41.51</v>
       </c>
       <c r="AB8" s="94" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="AC8" s="94" t="n">
         <v>47.84</v>
-      </c>
-      <c r="AC8" s="94" t="n">
-        <v>45.14</v>
       </c>
       <c r="AD8" s="94" t="n">
         <v>45.14</v>
       </c>
       <c r="AE8" s="94" t="n">
-        <v>46.9</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="9">
@@ -7305,85 +7305,85 @@
         <v>35.78</v>
       </c>
       <c r="E9" s="94" t="n">
-        <v>56.52</v>
+        <v>35.78</v>
       </c>
       <c r="F9" s="94" t="n">
         <v>56.52</v>
       </c>
       <c r="G9" s="94" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="H9" s="94" t="n">
         <v>45.32</v>
       </c>
-      <c r="H9" s="94" t="n">
+      <c r="I9" s="94" t="n">
         <v>57.96</v>
       </c>
-      <c r="I9" s="94" t="n">
+      <c r="J9" s="94" t="n">
         <v>59.34</v>
       </c>
-      <c r="J9" s="94" t="n">
+      <c r="K9" s="94" t="n">
         <v>51.65</v>
-      </c>
-      <c r="K9" s="94" t="n">
-        <v>49.39</v>
       </c>
       <c r="L9" s="94" t="n">
         <v>49.39</v>
       </c>
       <c r="M9" s="94" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="N9" s="94" t="n">
         <v>40.47</v>
       </c>
-      <c r="N9" s="94" t="n">
+      <c r="O9" s="94" t="n">
         <v>59.12</v>
       </c>
-      <c r="O9" s="94" t="n">
+      <c r="P9" s="94" t="n">
         <v>63.67</v>
       </c>
-      <c r="P9" s="94" t="n">
+      <c r="Q9" s="94" t="n">
         <v>34.88</v>
-      </c>
-      <c r="Q9" s="94" t="n">
-        <v>32.56</v>
       </c>
       <c r="R9" s="94" t="n">
         <v>32.56</v>
       </c>
       <c r="S9" s="94" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="T9" s="94" t="n">
         <v>40.33</v>
       </c>
-      <c r="T9" s="94" t="n">
+      <c r="U9" s="94" t="n">
         <v>43.12</v>
       </c>
-      <c r="U9" s="94" t="n">
+      <c r="V9" s="94" t="n">
         <v>43.39</v>
       </c>
-      <c r="V9" s="94" t="n">
+      <c r="W9" s="94" t="n">
         <v>16.15</v>
-      </c>
-      <c r="W9" s="94" t="n">
-        <v>16.9</v>
       </c>
       <c r="X9" s="94" t="n">
         <v>16.9</v>
       </c>
       <c r="Y9" s="94" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="Z9" s="94" t="n">
         <v>20.18</v>
-      </c>
-      <c r="Z9" s="94" t="n">
-        <v>32.85</v>
       </c>
       <c r="AA9" s="94" t="n">
         <v>32.85</v>
       </c>
       <c r="AB9" s="94" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="AC9" s="94" t="n">
         <v>62.46</v>
-      </c>
-      <c r="AC9" s="94" t="n">
-        <v>60.63</v>
       </c>
       <c r="AD9" s="94" t="n">
         <v>60.63</v>
       </c>
       <c r="AE9" s="94" t="n">
-        <v>72.27</v>
+        <v>60.63</v>
       </c>
     </row>
     <row r="10">
@@ -7407,124 +7407,124 @@
           <t>green</t>
         </is>
       </c>
-      <c r="E10" s="91" t="inlineStr">
+      <c r="E10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F10" s="91" t="inlineStr">
+      <c r="G10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G10" s="91" t="inlineStr">
+      <c r="H10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H10" s="91" t="inlineStr">
+      <c r="I10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I10" s="91" t="inlineStr">
+      <c r="J10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J10" s="91" t="inlineStr">
+      <c r="K10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K10" s="91" t="inlineStr">
+      <c r="L10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L10" s="91" t="inlineStr">
+      <c r="M10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M10" s="92" t="inlineStr">
+      <c r="N10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N10" s="92" t="inlineStr">
+      <c r="O10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O10" s="91" t="inlineStr">
+      <c r="P10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P10" s="92" t="inlineStr">
+      <c r="Q10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q10" s="92" t="inlineStr">
+      <c r="R10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R10" s="92" t="inlineStr">
+      <c r="S10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S10" s="92" t="inlineStr">
+      <c r="T10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T10" s="92" t="inlineStr">
+      <c r="U10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U10" s="92" t="inlineStr">
+      <c r="V10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V10" s="93" t="inlineStr">
+      <c r="W10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W10" s="93" t="inlineStr">
+      <c r="X10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X10" s="93" t="inlineStr">
+      <c r="Y10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y10" s="93" t="inlineStr">
+      <c r="Z10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z10" s="93" t="inlineStr">
+      <c r="AA10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA10" s="93" t="inlineStr">
+      <c r="AB10" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AB10" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AC10" s="92" t="inlineStr">
@@ -7559,85 +7559,85 @@
         <v>-2.82</v>
       </c>
       <c r="E11" s="94" t="n">
-        <v>-1.97</v>
+        <v>-2.82</v>
       </c>
       <c r="F11" s="94" t="n">
         <v>-1.97</v>
       </c>
       <c r="G11" s="94" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="H11" s="94" t="n">
         <v>-2.71</v>
       </c>
-      <c r="H11" s="94" t="n">
+      <c r="I11" s="94" t="n">
         <v>-3.5</v>
       </c>
-      <c r="I11" s="94" t="n">
+      <c r="J11" s="94" t="n">
         <v>-5.24</v>
       </c>
-      <c r="J11" s="94" t="n">
+      <c r="K11" s="94" t="n">
         <v>-5.99</v>
-      </c>
-      <c r="K11" s="94" t="n">
-        <v>-4.96</v>
       </c>
       <c r="L11" s="94" t="n">
         <v>-4.96</v>
       </c>
       <c r="M11" s="94" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="N11" s="94" t="n">
         <v>-6.98</v>
       </c>
-      <c r="N11" s="94" t="n">
+      <c r="O11" s="94" t="n">
         <v>-8.08</v>
       </c>
-      <c r="O11" s="94" t="n">
+      <c r="P11" s="94" t="n">
         <v>-6.09</v>
       </c>
-      <c r="P11" s="94" t="n">
+      <c r="Q11" s="94" t="n">
         <v>-9.69</v>
-      </c>
-      <c r="Q11" s="94" t="n">
-        <v>-2.86</v>
       </c>
       <c r="R11" s="94" t="n">
         <v>-2.86</v>
       </c>
       <c r="S11" s="94" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="T11" s="94" t="n">
         <v>-1.44</v>
       </c>
-      <c r="T11" s="94" t="n">
+      <c r="U11" s="94" t="n">
         <v>-3.72</v>
       </c>
-      <c r="U11" s="94" t="n">
+      <c r="V11" s="94" t="n">
         <v>-5.89</v>
       </c>
-      <c r="V11" s="94" t="n">
+      <c r="W11" s="94" t="n">
         <v>-4.13</v>
-      </c>
-      <c r="W11" s="94" t="n">
-        <v>-8.9</v>
       </c>
       <c r="X11" s="94" t="n">
         <v>-8.9</v>
       </c>
       <c r="Y11" s="94" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="Z11" s="94" t="n">
         <v>-9.630000000000001</v>
-      </c>
-      <c r="Z11" s="94" t="n">
-        <v>-16.02</v>
       </c>
       <c r="AA11" s="94" t="n">
         <v>-16.02</v>
       </c>
       <c r="AB11" s="94" t="n">
+        <v>-16.02</v>
+      </c>
+      <c r="AC11" s="94" t="n">
         <v>1.43</v>
-      </c>
-      <c r="AC11" s="94" t="n">
-        <v>16.94</v>
       </c>
       <c r="AD11" s="94" t="n">
         <v>16.94</v>
       </c>
       <c r="AE11" s="94" t="n">
-        <v>28.92</v>
+        <v>16.94</v>
       </c>
     </row>
     <row r="12">
@@ -7656,85 +7656,85 @@
         <v>22.25</v>
       </c>
       <c r="E12" s="94" t="n">
-        <v>30.1</v>
+        <v>22.25</v>
       </c>
       <c r="F12" s="94" t="n">
         <v>30.1</v>
       </c>
       <c r="G12" s="94" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="H12" s="94" t="n">
         <v>27.98</v>
       </c>
-      <c r="H12" s="94" t="n">
+      <c r="I12" s="94" t="n">
         <v>26.6</v>
       </c>
-      <c r="I12" s="94" t="n">
+      <c r="J12" s="94" t="n">
         <v>28.46</v>
       </c>
-      <c r="J12" s="94" t="n">
+      <c r="K12" s="94" t="n">
         <v>27.49</v>
-      </c>
-      <c r="K12" s="94" t="n">
-        <v>23.68</v>
       </c>
       <c r="L12" s="94" t="n">
         <v>23.68</v>
       </c>
       <c r="M12" s="94" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="N12" s="94" t="n">
         <v>18.99</v>
       </c>
-      <c r="N12" s="94" t="n">
+      <c r="O12" s="94" t="n">
         <v>18.11</v>
       </c>
-      <c r="O12" s="94" t="n">
+      <c r="P12" s="94" t="n">
         <v>20.84</v>
       </c>
-      <c r="P12" s="94" t="n">
+      <c r="Q12" s="94" t="n">
         <v>16.86</v>
-      </c>
-      <c r="Q12" s="94" t="n">
-        <v>16.44</v>
       </c>
       <c r="R12" s="94" t="n">
         <v>16.44</v>
       </c>
       <c r="S12" s="94" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="T12" s="94" t="n">
         <v>20.18</v>
       </c>
-      <c r="T12" s="94" t="n">
+      <c r="U12" s="94" t="n">
         <v>19.29</v>
       </c>
-      <c r="U12" s="94" t="n">
+      <c r="V12" s="94" t="n">
         <v>20.37</v>
       </c>
-      <c r="V12" s="94" t="n">
+      <c r="W12" s="94" t="n">
         <v>21.99</v>
-      </c>
-      <c r="W12" s="94" t="n">
-        <v>22.02</v>
       </c>
       <c r="X12" s="94" t="n">
         <v>22.02</v>
       </c>
       <c r="Y12" s="94" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="Z12" s="94" t="n">
         <v>26.5</v>
-      </c>
-      <c r="Z12" s="94" t="n">
-        <v>29.36</v>
       </c>
       <c r="AA12" s="94" t="n">
         <v>29.36</v>
       </c>
       <c r="AB12" s="94" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="AC12" s="94" t="n">
         <v>33.94</v>
-      </c>
-      <c r="AC12" s="94" t="n">
-        <v>32.82</v>
       </c>
       <c r="AD12" s="94" t="n">
         <v>32.82</v>
       </c>
       <c r="AE12" s="94" t="n">
-        <v>32.72</v>
+        <v>32.82</v>
       </c>
     </row>
     <row r="13">
@@ -7753,85 +7753,85 @@
         <v>31.12</v>
       </c>
       <c r="E13" s="94" t="n">
-        <v>77.11</v>
+        <v>31.12</v>
       </c>
       <c r="F13" s="94" t="n">
         <v>77.11</v>
       </c>
       <c r="G13" s="94" t="n">
+        <v>77.11</v>
+      </c>
+      <c r="H13" s="94" t="n">
         <v>55.59</v>
       </c>
-      <c r="H13" s="94" t="n">
+      <c r="I13" s="94" t="n">
         <v>66.94</v>
       </c>
-      <c r="I13" s="94" t="n">
+      <c r="J13" s="94" t="n">
         <v>83.7</v>
       </c>
-      <c r="J13" s="94" t="n">
+      <c r="K13" s="94" t="n">
         <v>81.64</v>
-      </c>
-      <c r="K13" s="94" t="n">
-        <v>68.69</v>
       </c>
       <c r="L13" s="94" t="n">
         <v>68.69</v>
       </c>
       <c r="M13" s="94" t="n">
+        <v>68.69</v>
+      </c>
+      <c r="N13" s="94" t="n">
         <v>60.87</v>
       </c>
-      <c r="N13" s="94" t="n">
+      <c r="O13" s="94" t="n">
         <v>54.48</v>
       </c>
-      <c r="O13" s="94" t="n">
+      <c r="P13" s="94" t="n">
         <v>78.59</v>
       </c>
-      <c r="P13" s="94" t="n">
+      <c r="Q13" s="94" t="n">
         <v>21.44</v>
-      </c>
-      <c r="Q13" s="94" t="n">
-        <v>9.02</v>
       </c>
       <c r="R13" s="94" t="n">
         <v>9.02</v>
       </c>
       <c r="S13" s="94" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="T13" s="94" t="n">
         <v>18.81</v>
       </c>
-      <c r="T13" s="94" t="n">
+      <c r="U13" s="94" t="n">
         <v>14.94</v>
       </c>
-      <c r="U13" s="94" t="n">
+      <c r="V13" s="94" t="n">
         <v>20.9</v>
       </c>
-      <c r="V13" s="94" t="n">
+      <c r="W13" s="94" t="n">
         <v>2.46</v>
-      </c>
-      <c r="W13" s="94" t="n">
-        <v>2.51</v>
       </c>
       <c r="X13" s="94" t="n">
         <v>2.51</v>
       </c>
       <c r="Y13" s="94" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Z13" s="94" t="n">
         <v>3.75</v>
-      </c>
-      <c r="Z13" s="94" t="n">
-        <v>9.470000000000001</v>
       </c>
       <c r="AA13" s="94" t="n">
         <v>9.470000000000001</v>
       </c>
       <c r="AB13" s="94" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="AC13" s="94" t="n">
         <v>49.72</v>
-      </c>
-      <c r="AC13" s="94" t="n">
-        <v>46.46</v>
       </c>
       <c r="AD13" s="94" t="n">
         <v>46.46</v>
       </c>
       <c r="AE13" s="94" t="n">
-        <v>54.92</v>
+        <v>46.46</v>
       </c>
     </row>
     <row r="14">
@@ -7865,128 +7865,130 @@
           <t>red</t>
         </is>
       </c>
-      <c r="G14" s="92" t="inlineStr">
+      <c r="G14" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H14" s="92" t="inlineStr">
+      <c r="I14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I14" s="91" t="inlineStr">
+      <c r="J14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J14" s="91" t="inlineStr">
+      <c r="K14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K14" s="91" t="inlineStr">
+      <c r="L14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L14" s="91" t="inlineStr">
+      <c r="M14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M14" s="91" t="inlineStr">
+      <c r="N14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N14" s="92" t="inlineStr">
+      <c r="O14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O14" s="92" t="inlineStr">
+      <c r="P14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P14" s="93" t="inlineStr">
+      <c r="Q14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q14" s="93" t="inlineStr">
+      <c r="R14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R14" s="93" t="inlineStr">
+      <c r="S14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S14" s="93" t="inlineStr">
+      <c r="T14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T14" s="93" t="inlineStr">
+      <c r="U14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U14" s="93" t="inlineStr">
+      <c r="V14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V14" s="93" t="inlineStr">
+      <c r="W14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W14" s="93" t="inlineStr">
+      <c r="X14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X14" s="93" t="inlineStr">
+      <c r="Y14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y14" s="93" t="inlineStr">
+      <c r="Z14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z14" s="91" t="inlineStr">
+      <c r="AA14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA14" s="91" t="inlineStr">
+      <c r="AB14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB14" s="91" t="inlineStr">
+      <c r="AC14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC14" s="91" t="inlineStr">
+      <c r="AD14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD14" s="91" t="inlineStr">
+      <c r="AE14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
-      </c>
-      <c r="AE14" s="92" t="n">
-        <v/>
       </c>
     </row>
     <row r="15">
@@ -8002,88 +8004,88 @@
         <v>-0.45</v>
       </c>
       <c r="D15" s="94" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E15" s="94" t="n">
         <v>-0.9</v>
-      </c>
-      <c r="E15" s="94" t="n">
-        <v>-3.07</v>
       </c>
       <c r="F15" s="94" t="n">
         <v>-3.07</v>
       </c>
       <c r="G15" s="94" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="H15" s="94" t="n">
         <v>-4.36</v>
       </c>
-      <c r="H15" s="94" t="n">
+      <c r="I15" s="94" t="n">
         <v>-3.94</v>
       </c>
-      <c r="I15" s="94" t="n">
+      <c r="J15" s="94" t="n">
         <v>-1.87</v>
       </c>
-      <c r="J15" s="94" t="n">
+      <c r="K15" s="94" t="n">
         <v>-4.02</v>
-      </c>
-      <c r="K15" s="94" t="n">
-        <v>-4.46</v>
       </c>
       <c r="L15" s="94" t="n">
         <v>-4.46</v>
       </c>
       <c r="M15" s="94" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="N15" s="94" t="n">
         <v>-4.67</v>
       </c>
-      <c r="N15" s="94" t="n">
+      <c r="O15" s="94" t="n">
         <v>-7.3</v>
       </c>
-      <c r="O15" s="94" t="n">
+      <c r="P15" s="94" t="n">
         <v>-4.28</v>
       </c>
-      <c r="P15" s="94" t="n">
+      <c r="Q15" s="94" t="n">
         <v>-6.96</v>
-      </c>
-      <c r="Q15" s="94" t="n">
-        <v>-6.17</v>
       </c>
       <c r="R15" s="94" t="n">
         <v>-6.17</v>
       </c>
       <c r="S15" s="94" t="n">
+        <v>-6.17</v>
+      </c>
+      <c r="T15" s="94" t="n">
         <v>-8.779999999999999</v>
       </c>
-      <c r="T15" s="94" t="n">
+      <c r="U15" s="94" t="n">
         <v>-9.279999999999999</v>
       </c>
-      <c r="U15" s="94" t="n">
+      <c r="V15" s="94" t="n">
         <v>-5.76</v>
       </c>
-      <c r="V15" s="94" t="n">
+      <c r="W15" s="94" t="n">
         <v>-5.92</v>
-      </c>
-      <c r="W15" s="94" t="n">
-        <v>-14.46</v>
       </c>
       <c r="X15" s="94" t="n">
         <v>-14.46</v>
       </c>
       <c r="Y15" s="94" t="n">
+        <v>-14.46</v>
+      </c>
+      <c r="Z15" s="94" t="n">
         <v>-13.69</v>
-      </c>
-      <c r="Z15" s="94" t="n">
-        <v>-9.289999999999999</v>
       </c>
       <c r="AA15" s="94" t="n">
         <v>-9.289999999999999</v>
       </c>
       <c r="AB15" s="94" t="n">
+        <v>-9.289999999999999</v>
+      </c>
+      <c r="AC15" s="94" t="n">
         <v>-10.7</v>
-      </c>
-      <c r="AC15" s="94" t="n">
-        <v>-4.94</v>
       </c>
       <c r="AD15" s="94" t="n">
         <v>-4.94</v>
       </c>
       <c r="AE15" s="94" t="n">
-        <v/>
+        <v>-4.94</v>
       </c>
     </row>
     <row r="16">
@@ -8099,88 +8101,88 @@
         <v>19.35</v>
       </c>
       <c r="D16" s="94" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="E16" s="94" t="n">
         <v>16.72</v>
-      </c>
-      <c r="E16" s="94" t="n">
-        <v>15.69</v>
       </c>
       <c r="F16" s="94" t="n">
         <v>15.69</v>
       </c>
       <c r="G16" s="94" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="H16" s="94" t="n">
         <v>15.87</v>
       </c>
-      <c r="H16" s="94" t="n">
+      <c r="I16" s="94" t="n">
         <v>14.74</v>
       </c>
-      <c r="I16" s="94" t="n">
+      <c r="J16" s="94" t="n">
         <v>18.13</v>
       </c>
-      <c r="J16" s="94" t="n">
+      <c r="K16" s="94" t="n">
         <v>17.18</v>
-      </c>
-      <c r="K16" s="94" t="n">
-        <v>13.13</v>
       </c>
       <c r="L16" s="94" t="n">
         <v>13.13</v>
       </c>
       <c r="M16" s="94" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="N16" s="94" t="n">
         <v>11.76</v>
       </c>
-      <c r="N16" s="94" t="n">
+      <c r="O16" s="94" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="O16" s="94" t="n">
+      <c r="P16" s="94" t="n">
         <v>10.35</v>
       </c>
-      <c r="P16" s="94" t="n">
+      <c r="Q16" s="94" t="n">
         <v>6.16</v>
-      </c>
-      <c r="Q16" s="94" t="n">
-        <v>7.47</v>
       </c>
       <c r="R16" s="94" t="n">
         <v>7.47</v>
       </c>
       <c r="S16" s="94" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="T16" s="94" t="n">
         <v>8.529999999999999</v>
       </c>
-      <c r="T16" s="94" t="n">
+      <c r="U16" s="94" t="n">
         <v>7.02</v>
       </c>
-      <c r="U16" s="94" t="n">
+      <c r="V16" s="94" t="n">
         <v>6.31</v>
       </c>
-      <c r="V16" s="94" t="n">
+      <c r="W16" s="94" t="n">
         <v>10.41</v>
-      </c>
-      <c r="W16" s="94" t="n">
-        <v>13.1</v>
       </c>
       <c r="X16" s="94" t="n">
         <v>13.1</v>
       </c>
       <c r="Y16" s="94" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="Z16" s="94" t="n">
         <v>11.98</v>
-      </c>
-      <c r="Z16" s="94" t="n">
-        <v>14.47</v>
       </c>
       <c r="AA16" s="94" t="n">
         <v>14.47</v>
       </c>
       <c r="AB16" s="94" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="AC16" s="94" t="n">
         <v>12.59</v>
-      </c>
-      <c r="AC16" s="94" t="n">
-        <v>11.44</v>
       </c>
       <c r="AD16" s="94" t="n">
         <v>11.44</v>
       </c>
       <c r="AE16" s="94" t="n">
-        <v/>
+        <v>11.44</v>
       </c>
     </row>
     <row r="17">
@@ -8196,88 +8198,88 @@
         <v>75.39</v>
       </c>
       <c r="D17" s="94" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="E17" s="94" t="n">
         <v>74.31</v>
-      </c>
-      <c r="E17" s="94" t="n">
-        <v>69.52</v>
       </c>
       <c r="F17" s="94" t="n">
         <v>69.52</v>
       </c>
       <c r="G17" s="94" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="H17" s="94" t="n">
         <v>50.12</v>
       </c>
-      <c r="H17" s="94" t="n">
+      <c r="I17" s="94" t="n">
         <v>55.82</v>
       </c>
-      <c r="I17" s="94" t="n">
+      <c r="J17" s="94" t="n">
         <v>86.87</v>
       </c>
-      <c r="J17" s="94" t="n">
+      <c r="K17" s="94" t="n">
         <v>82.95</v>
-      </c>
-      <c r="K17" s="94" t="n">
-        <v>70.41</v>
       </c>
       <c r="L17" s="94" t="n">
         <v>70.41</v>
       </c>
       <c r="M17" s="94" t="n">
+        <v>70.41</v>
+      </c>
+      <c r="N17" s="94" t="n">
         <v>67.17</v>
       </c>
-      <c r="N17" s="94" t="n">
+      <c r="O17" s="94" t="n">
         <v>51.86</v>
       </c>
-      <c r="O17" s="94" t="n">
+      <c r="P17" s="94" t="n">
         <v>46.63</v>
       </c>
-      <c r="P17" s="94" t="n">
+      <c r="Q17" s="94" t="n">
         <v>7.26</v>
-      </c>
-      <c r="Q17" s="94" t="n">
-        <v>10.43</v>
       </c>
       <c r="R17" s="94" t="n">
         <v>10.43</v>
       </c>
       <c r="S17" s="94" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="T17" s="94" t="n">
         <v>15.01</v>
       </c>
-      <c r="T17" s="94" t="n">
+      <c r="U17" s="94" t="n">
         <v>16.18</v>
       </c>
-      <c r="U17" s="94" t="n">
+      <c r="V17" s="94" t="n">
         <v>21.65</v>
       </c>
-      <c r="V17" s="94" t="n">
+      <c r="W17" s="94" t="n">
         <v>34.02</v>
-      </c>
-      <c r="W17" s="94" t="n">
-        <v>39.01</v>
       </c>
       <c r="X17" s="94" t="n">
         <v>39.01</v>
       </c>
       <c r="Y17" s="94" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="Z17" s="94" t="n">
         <v>22.83</v>
-      </c>
-      <c r="Z17" s="94" t="n">
-        <v>62.48</v>
       </c>
       <c r="AA17" s="94" t="n">
         <v>62.48</v>
       </c>
       <c r="AB17" s="94" t="n">
+        <v>62.48</v>
+      </c>
+      <c r="AC17" s="94" t="n">
         <v>60.29</v>
-      </c>
-      <c r="AC17" s="94" t="n">
-        <v>68.20999999999999</v>
       </c>
       <c r="AD17" s="94" t="n">
         <v>68.20999999999999</v>
       </c>
       <c r="AE17" s="94" t="n">
-        <v/>
+        <v>68.20999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -8301,139 +8303,139 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="E18" s="91" t="inlineStr">
+      <c r="E18" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F18" s="91" t="inlineStr">
+      <c r="G18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G18" s="91" t="inlineStr">
+      <c r="H18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H18" s="91" t="inlineStr">
+      <c r="I18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I18" s="91" t="inlineStr">
+      <c r="J18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J18" s="91" t="inlineStr">
+      <c r="K18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K18" s="91" t="inlineStr">
+      <c r="L18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L18" s="91" t="inlineStr">
+      <c r="M18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M18" s="91" t="inlineStr">
+      <c r="N18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N18" s="91" t="inlineStr">
+      <c r="O18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O18" s="92" t="inlineStr">
+      <c r="P18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P18" s="93" t="inlineStr">
+      <c r="Q18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q18" s="93" t="inlineStr">
+      <c r="R18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R18" s="93" t="inlineStr">
+      <c r="S18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S18" s="92" t="inlineStr">
+      <c r="T18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T18" s="92" t="inlineStr">
+      <c r="U18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U18" s="93" t="inlineStr">
+      <c r="V18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V18" s="91" t="inlineStr">
+      <c r="W18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W18" s="92" t="inlineStr">
+      <c r="X18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X18" s="92" t="inlineStr">
+      <c r="Y18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y18" s="93" t="inlineStr">
+      <c r="Z18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z18" s="93" t="inlineStr">
+      <c r="AA18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA18" s="93" t="inlineStr">
+      <c r="AB18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB18" s="93" t="inlineStr">
+      <c r="AC18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC18" s="93" t="inlineStr">
+      <c r="AD18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD18" s="93" t="inlineStr">
+      <c r="AE18" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AE18" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -8444,31 +8446,31 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="C19" s="94" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="D19" s="94" t="n">
         <v>4.03</v>
       </c>
-      <c r="C19" s="94" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="D19" s="94" t="n">
+      <c r="E19" s="94" t="n">
         <v>3.24</v>
-      </c>
-      <c r="E19" s="94" t="n">
-        <v>5.05</v>
       </c>
       <c r="F19" s="94" t="n">
         <v>5.05</v>
       </c>
       <c r="G19" s="94" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="H19" s="94" t="n">
         <v>5.32</v>
       </c>
-      <c r="H19" s="94" t="n">
+      <c r="I19" s="94" t="n">
         <v>4.98</v>
       </c>
-      <c r="I19" s="94" t="n">
+      <c r="J19" s="94" t="n">
         <v>3.38</v>
-      </c>
-      <c r="J19" s="94" t="n">
-        <v>2.44</v>
       </c>
       <c r="K19" s="94" t="n">
         <v>2.44</v>
@@ -8477,61 +8479,61 @@
         <v>2.44</v>
       </c>
       <c r="M19" s="94" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N19" s="94" t="n">
         <v>1.24</v>
       </c>
-      <c r="N19" s="94" t="n">
+      <c r="O19" s="94" t="n">
         <v>1.86</v>
       </c>
-      <c r="O19" s="94" t="n">
+      <c r="P19" s="94" t="n">
         <v>0.01</v>
       </c>
-      <c r="P19" s="94" t="n">
+      <c r="Q19" s="94" t="n">
         <v>0.36</v>
-      </c>
-      <c r="Q19" s="94" t="n">
-        <v>-0.5600000000000001</v>
       </c>
       <c r="R19" s="94" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="S19" s="94" t="n">
-        <v>1.78</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="T19" s="94" t="n">
         <v>1.78</v>
       </c>
       <c r="U19" s="94" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V19" s="94" t="n">
         <v>2.23</v>
       </c>
-      <c r="V19" s="94" t="n">
+      <c r="W19" s="94" t="n">
         <v>3.17</v>
-      </c>
-      <c r="W19" s="94" t="n">
-        <v>3.33</v>
       </c>
       <c r="X19" s="94" t="n">
         <v>3.33</v>
       </c>
       <c r="Y19" s="94" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="Z19" s="94" t="n">
         <v>3.03</v>
-      </c>
-      <c r="Z19" s="94" t="n">
-        <v>2.27</v>
       </c>
       <c r="AA19" s="94" t="n">
         <v>2.27</v>
       </c>
       <c r="AB19" s="94" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC19" s="94" t="n">
         <v>3.63</v>
-      </c>
-      <c r="AC19" s="94" t="n">
-        <v>4.58</v>
       </c>
       <c r="AD19" s="94" t="n">
         <v>4.58</v>
       </c>
       <c r="AE19" s="94" t="n">
-        <v>5.76</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="20">
@@ -8541,31 +8543,31 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="C20" s="94" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="D20" s="94" t="n">
         <v>16.99</v>
       </c>
-      <c r="C20" s="94" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="D20" s="94" t="n">
+      <c r="E20" s="94" t="n">
         <v>12.45</v>
-      </c>
-      <c r="E20" s="94" t="n">
-        <v>12.02</v>
       </c>
       <c r="F20" s="94" t="n">
         <v>12.02</v>
       </c>
       <c r="G20" s="94" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="H20" s="94" t="n">
         <v>10.8</v>
       </c>
-      <c r="H20" s="94" t="n">
+      <c r="I20" s="94" t="n">
         <v>11.96</v>
       </c>
-      <c r="I20" s="94" t="n">
+      <c r="J20" s="94" t="n">
         <v>10.72</v>
-      </c>
-      <c r="J20" s="94" t="n">
-        <v>9.85</v>
       </c>
       <c r="K20" s="94" t="n">
         <v>9.85</v>
@@ -8574,61 +8576,61 @@
         <v>9.85</v>
       </c>
       <c r="M20" s="94" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="N20" s="94" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="N20" s="94" t="n">
+      <c r="O20" s="94" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="O20" s="94" t="n">
+      <c r="P20" s="94" t="n">
         <v>5.17</v>
       </c>
-      <c r="P20" s="94" t="n">
+      <c r="Q20" s="94" t="n">
         <v>4.88</v>
-      </c>
-      <c r="Q20" s="94" t="n">
-        <v>5.85</v>
       </c>
       <c r="R20" s="94" t="n">
         <v>5.85</v>
       </c>
       <c r="S20" s="94" t="n">
-        <v>6.74</v>
+        <v>5.85</v>
       </c>
       <c r="T20" s="94" t="n">
         <v>6.74</v>
       </c>
       <c r="U20" s="94" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="V20" s="94" t="n">
         <v>5.74</v>
       </c>
-      <c r="V20" s="94" t="n">
+      <c r="W20" s="94" t="n">
         <v>5.44</v>
-      </c>
-      <c r="W20" s="94" t="n">
-        <v>5.53</v>
       </c>
       <c r="X20" s="94" t="n">
         <v>5.53</v>
       </c>
       <c r="Y20" s="94" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="Z20" s="94" t="n">
         <v>4.51</v>
-      </c>
-      <c r="Z20" s="94" t="n">
-        <v>5.32</v>
       </c>
       <c r="AA20" s="94" t="n">
         <v>5.32</v>
       </c>
       <c r="AB20" s="94" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="AC20" s="94" t="n">
         <v>4.85</v>
-      </c>
-      <c r="AC20" s="94" t="n">
-        <v>7.06</v>
       </c>
       <c r="AD20" s="94" t="n">
         <v>7.06</v>
       </c>
       <c r="AE20" s="94" t="n">
-        <v>8.34</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="21">
@@ -8638,31 +8640,31 @@
         </is>
       </c>
       <c r="B21" s="94" t="n">
+        <v>37.99</v>
+      </c>
+      <c r="C21" s="94" t="n">
+        <v>37.99</v>
+      </c>
+      <c r="D21" s="94" t="n">
         <v>56.94</v>
       </c>
-      <c r="C21" s="94" t="n">
-        <v>56.94</v>
-      </c>
-      <c r="D21" s="94" t="n">
+      <c r="E21" s="94" t="n">
         <v>16.07</v>
-      </c>
-      <c r="E21" s="94" t="n">
-        <v>67.48999999999999</v>
       </c>
       <c r="F21" s="94" t="n">
         <v>67.48999999999999</v>
       </c>
       <c r="G21" s="94" t="n">
+        <v>67.48999999999999</v>
+      </c>
+      <c r="H21" s="94" t="n">
         <v>98.41</v>
       </c>
-      <c r="H21" s="94" t="n">
+      <c r="I21" s="94" t="n">
         <v>97.23999999999999</v>
       </c>
-      <c r="I21" s="94" t="n">
+      <c r="J21" s="94" t="n">
         <v>95.22</v>
-      </c>
-      <c r="J21" s="94" t="n">
-        <v>90.06</v>
       </c>
       <c r="K21" s="94" t="n">
         <v>90.06</v>
@@ -8671,61 +8673,61 @@
         <v>90.06</v>
       </c>
       <c r="M21" s="94" t="n">
+        <v>90.06</v>
+      </c>
+      <c r="N21" s="94" t="n">
         <v>74.65000000000001</v>
       </c>
-      <c r="N21" s="94" t="n">
+      <c r="O21" s="94" t="n">
         <v>89.31999999999999</v>
       </c>
-      <c r="O21" s="94" t="n">
+      <c r="P21" s="94" t="n">
         <v>34.87</v>
       </c>
-      <c r="P21" s="94" t="n">
+      <c r="Q21" s="94" t="n">
         <v>22.53</v>
-      </c>
-      <c r="Q21" s="94" t="n">
-        <v>10.95</v>
       </c>
       <c r="R21" s="94" t="n">
         <v>10.95</v>
       </c>
       <c r="S21" s="94" t="n">
-        <v>42.53</v>
+        <v>10.95</v>
       </c>
       <c r="T21" s="94" t="n">
         <v>42.53</v>
       </c>
       <c r="U21" s="94" t="n">
+        <v>42.53</v>
+      </c>
+      <c r="V21" s="94" t="n">
         <v>32.72</v>
       </c>
-      <c r="V21" s="94" t="n">
+      <c r="W21" s="94" t="n">
         <v>84.81999999999999</v>
-      </c>
-      <c r="W21" s="94" t="n">
-        <v>74.91</v>
       </c>
       <c r="X21" s="94" t="n">
         <v>74.91</v>
       </c>
       <c r="Y21" s="94" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="Z21" s="94" t="n">
         <v>6.03</v>
-      </c>
-      <c r="Z21" s="94" t="n">
-        <v>7.97</v>
       </c>
       <c r="AA21" s="94" t="n">
         <v>7.97</v>
       </c>
       <c r="AB21" s="94" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="AC21" s="94" t="n">
         <v>11.56</v>
-      </c>
-      <c r="AC21" s="94" t="n">
-        <v>26.76</v>
       </c>
       <c r="AD21" s="94" t="n">
         <v>26.76</v>
       </c>
       <c r="AE21" s="94" t="n">
-        <v>85.53</v>
+        <v>26.76</v>
       </c>
     </row>
     <row r="22">
@@ -8744,134 +8746,134 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="D22" s="91" t="inlineStr">
+      <c r="D22" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E22" s="91" t="inlineStr">
+      <c r="F22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F22" s="91" t="inlineStr">
+      <c r="G22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G22" s="91" t="inlineStr">
+      <c r="H22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H22" s="91" t="inlineStr">
+      <c r="I22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I22" s="91" t="inlineStr">
+      <c r="J22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J22" s="91" t="inlineStr">
+      <c r="K22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K22" s="91" t="inlineStr">
+      <c r="L22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L22" s="91" t="inlineStr">
+      <c r="M22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M22" s="91" t="inlineStr">
+      <c r="N22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N22" s="91" t="inlineStr">
+      <c r="O22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O22" s="92" t="inlineStr">
+      <c r="P22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P22" s="92" t="inlineStr">
+      <c r="Q22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q22" s="93" t="inlineStr">
+      <c r="R22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R22" s="93" t="inlineStr">
+      <c r="S22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S22" s="92" t="inlineStr">
+      <c r="T22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T22" s="92" t="inlineStr">
+      <c r="U22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U22" s="92" t="inlineStr">
+      <c r="V22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V22" s="92" t="inlineStr">
+      <c r="W22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W22" s="92" t="inlineStr">
+      <c r="X22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X22" s="92" t="inlineStr">
+      <c r="Y22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y22" s="93" t="inlineStr">
+      <c r="Z22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z22" s="92" t="inlineStr">
+      <c r="AA22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA22" s="92" t="inlineStr">
+      <c r="AB22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB22" s="93" t="inlineStr">
+      <c r="AC22" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AC22" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AD22" s="92" t="inlineStr">
@@ -8895,28 +8897,28 @@
         <v>6.1</v>
       </c>
       <c r="C23" s="94" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="D23" s="94" t="n">
         <v>6.2</v>
       </c>
-      <c r="D23" s="94" t="n">
+      <c r="E23" s="94" t="n">
         <v>5.49</v>
-      </c>
-      <c r="E23" s="94" t="n">
-        <v>5.48</v>
       </c>
       <c r="F23" s="94" t="n">
         <v>5.48</v>
       </c>
       <c r="G23" s="94" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="H23" s="94" t="n">
         <v>5.17</v>
       </c>
-      <c r="H23" s="94" t="n">
+      <c r="I23" s="94" t="n">
         <v>3.86</v>
       </c>
-      <c r="I23" s="94" t="n">
+      <c r="J23" s="94" t="n">
         <v>2.56</v>
-      </c>
-      <c r="J23" s="94" t="n">
-        <v>1.3</v>
       </c>
       <c r="K23" s="94" t="n">
         <v>1.3</v>
@@ -8925,61 +8927,61 @@
         <v>1.3</v>
       </c>
       <c r="M23" s="94" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N23" s="94" t="n">
         <v>-0.28</v>
       </c>
-      <c r="N23" s="94" t="n">
+      <c r="O23" s="94" t="n">
         <v>-0.04</v>
       </c>
-      <c r="O23" s="94" t="n">
+      <c r="P23" s="94" t="n">
         <v>-1.3</v>
       </c>
-      <c r="P23" s="94" t="n">
+      <c r="Q23" s="94" t="n">
         <v>-1.04</v>
-      </c>
-      <c r="Q23" s="94" t="n">
-        <v>-2.62</v>
       </c>
       <c r="R23" s="94" t="n">
         <v>-2.62</v>
       </c>
       <c r="S23" s="94" t="n">
-        <v>-0.53</v>
+        <v>-2.62</v>
       </c>
       <c r="T23" s="94" t="n">
         <v>-0.53</v>
       </c>
       <c r="U23" s="94" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="V23" s="94" t="n">
         <v>0.17</v>
       </c>
-      <c r="V23" s="94" t="n">
+      <c r="W23" s="94" t="n">
         <v>0.46</v>
-      </c>
-      <c r="W23" s="94" t="n">
-        <v>1.55</v>
       </c>
       <c r="X23" s="94" t="n">
         <v>1.55</v>
       </c>
       <c r="Y23" s="94" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z23" s="94" t="n">
         <v>1.04</v>
-      </c>
-      <c r="Z23" s="94" t="n">
-        <v>0.45</v>
       </c>
       <c r="AA23" s="94" t="n">
         <v>0.45</v>
       </c>
       <c r="AB23" s="94" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC23" s="94" t="n">
         <v>1.34</v>
-      </c>
-      <c r="AC23" s="94" t="n">
-        <v>1.89</v>
       </c>
       <c r="AD23" s="94" t="n">
         <v>1.89</v>
       </c>
       <c r="AE23" s="94" t="n">
-        <v>2.77</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="24">
@@ -8992,28 +8994,28 @@
         <v>14.66</v>
       </c>
       <c r="C24" s="94" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="D24" s="94" t="n">
         <v>15.88</v>
       </c>
-      <c r="D24" s="94" t="n">
+      <c r="E24" s="94" t="n">
         <v>12.52</v>
-      </c>
-      <c r="E24" s="94" t="n">
-        <v>10.1</v>
       </c>
       <c r="F24" s="94" t="n">
         <v>10.1</v>
       </c>
       <c r="G24" s="94" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H24" s="94" t="n">
         <v>9.109999999999999</v>
       </c>
-      <c r="H24" s="94" t="n">
+      <c r="I24" s="94" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="I24" s="94" t="n">
+      <c r="J24" s="94" t="n">
         <v>8.6</v>
-      </c>
-      <c r="J24" s="94" t="n">
-        <v>7.14</v>
       </c>
       <c r="K24" s="94" t="n">
         <v>7.14</v>
@@ -9022,61 +9024,61 @@
         <v>7.14</v>
       </c>
       <c r="M24" s="94" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="N24" s="94" t="n">
         <v>8.06</v>
       </c>
-      <c r="N24" s="94" t="n">
+      <c r="O24" s="94" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="O24" s="94" t="n">
+      <c r="P24" s="94" t="n">
         <v>5.35</v>
       </c>
-      <c r="P24" s="94" t="n">
+      <c r="Q24" s="94" t="n">
         <v>4.66</v>
-      </c>
-      <c r="Q24" s="94" t="n">
-        <v>4.1</v>
       </c>
       <c r="R24" s="94" t="n">
         <v>4.1</v>
       </c>
       <c r="S24" s="94" t="n">
-        <v>4.84</v>
+        <v>4.1</v>
       </c>
       <c r="T24" s="94" t="n">
         <v>4.84</v>
       </c>
       <c r="U24" s="94" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="V24" s="94" t="n">
         <v>3.23</v>
       </c>
-      <c r="V24" s="94" t="n">
+      <c r="W24" s="94" t="n">
         <v>4.28</v>
-      </c>
-      <c r="W24" s="94" t="n">
-        <v>6.27</v>
       </c>
       <c r="X24" s="94" t="n">
         <v>6.27</v>
       </c>
       <c r="Y24" s="94" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="Z24" s="94" t="n">
         <v>5.98</v>
-      </c>
-      <c r="Z24" s="94" t="n">
-        <v>7.02</v>
       </c>
       <c r="AA24" s="94" t="n">
         <v>7.02</v>
       </c>
       <c r="AB24" s="94" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="AC24" s="94" t="n">
         <v>7.18</v>
-      </c>
-      <c r="AC24" s="94" t="n">
-        <v>9.42</v>
       </c>
       <c r="AD24" s="94" t="n">
         <v>9.42</v>
       </c>
       <c r="AE24" s="94" t="n">
-        <v>10.12</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="25">
@@ -9089,28 +9091,28 @@
         <v>68.69</v>
       </c>
       <c r="C25" s="94" t="n">
+        <v>68.69</v>
+      </c>
+      <c r="D25" s="94" t="n">
         <v>89</v>
       </c>
-      <c r="D25" s="94" t="n">
+      <c r="E25" s="94" t="n">
         <v>86.3</v>
-      </c>
-      <c r="E25" s="94" t="n">
-        <v>79.05</v>
       </c>
       <c r="F25" s="94" t="n">
         <v>79.05</v>
       </c>
       <c r="G25" s="94" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="H25" s="94" t="n">
         <v>95.43000000000001</v>
       </c>
-      <c r="H25" s="94" t="n">
+      <c r="I25" s="94" t="n">
         <v>92.37</v>
       </c>
-      <c r="I25" s="94" t="n">
+      <c r="J25" s="94" t="n">
         <v>91.09999999999999</v>
-      </c>
-      <c r="J25" s="94" t="n">
-        <v>83.62</v>
       </c>
       <c r="K25" s="94" t="n">
         <v>83.62</v>
@@ -9119,61 +9121,61 @@
         <v>83.62</v>
       </c>
       <c r="M25" s="94" t="n">
+        <v>83.62</v>
+      </c>
+      <c r="N25" s="94" t="n">
         <v>74.87</v>
       </c>
-      <c r="N25" s="94" t="n">
+      <c r="O25" s="94" t="n">
         <v>80.75</v>
       </c>
-      <c r="O25" s="94" t="n">
+      <c r="P25" s="94" t="n">
         <v>58.29</v>
       </c>
-      <c r="P25" s="94" t="n">
+      <c r="Q25" s="94" t="n">
         <v>44.79</v>
-      </c>
-      <c r="Q25" s="94" t="n">
-        <v>15.07</v>
       </c>
       <c r="R25" s="94" t="n">
         <v>15.07</v>
       </c>
       <c r="S25" s="94" t="n">
-        <v>49.78</v>
+        <v>15.07</v>
       </c>
       <c r="T25" s="94" t="n">
         <v>49.78</v>
       </c>
       <c r="U25" s="94" t="n">
+        <v>49.78</v>
+      </c>
+      <c r="V25" s="94" t="n">
         <v>34.31</v>
       </c>
-      <c r="V25" s="94" t="n">
+      <c r="W25" s="94" t="n">
         <v>52.18</v>
-      </c>
-      <c r="W25" s="94" t="n">
-        <v>54.91</v>
       </c>
       <c r="X25" s="94" t="n">
         <v>54.91</v>
       </c>
       <c r="Y25" s="94" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="Z25" s="94" t="n">
         <v>15.8</v>
-      </c>
-      <c r="Z25" s="94" t="n">
-        <v>21.31</v>
       </c>
       <c r="AA25" s="94" t="n">
         <v>21.31</v>
       </c>
       <c r="AB25" s="94" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="AC25" s="94" t="n">
         <v>22.32</v>
-      </c>
-      <c r="AC25" s="94" t="n">
-        <v>40.35</v>
       </c>
       <c r="AD25" s="94" t="n">
         <v>40.35</v>
       </c>
       <c r="AE25" s="94" t="n">
-        <v>70.73999999999999</v>
+        <v>40.35</v>
       </c>
     </row>
     <row r="26">
@@ -9182,154 +9184,154 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="92" t="inlineStr">
+      <c r="B26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C26" s="92" t="inlineStr">
+      <c r="E26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F26" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G26" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H26" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I26" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J26" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K26" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L26" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M26" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D26" s="93" t="inlineStr">
+      <c r="O26" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E26" s="91" t="inlineStr">
+      <c r="Q26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="S26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="T26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="U26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="V26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="W26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F26" s="91" t="inlineStr">
+      <c r="X26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G26" s="91" t="inlineStr">
+      <c r="Y26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H26" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="I26" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J26" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K26" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L26" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M26" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N26" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O26" s="93" t="inlineStr">
+      <c r="Z26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P26" s="93" t="inlineStr">
+      <c r="AA26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q26" s="93" t="inlineStr">
+      <c r="AB26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R26" s="93" t="inlineStr">
+      <c r="AC26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S26" s="93" t="inlineStr">
+      <c r="AD26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T26" s="93" t="inlineStr">
+      <c r="AE26" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="U26" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="V26" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W26" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X26" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y26" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z26" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA26" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB26" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC26" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD26" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE26" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -9340,31 +9342,31 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="C27" s="94" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="D27" s="94" t="n">
         <v>5.46</v>
       </c>
-      <c r="C27" s="94" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="D27" s="94" t="n">
+      <c r="E27" s="94" t="n">
         <v>4.17</v>
-      </c>
-      <c r="E27" s="94" t="n">
-        <v>7.75</v>
       </c>
       <c r="F27" s="94" t="n">
         <v>7.75</v>
       </c>
       <c r="G27" s="94" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="H27" s="94" t="n">
         <v>8.9</v>
       </c>
-      <c r="H27" s="94" t="n">
+      <c r="I27" s="94" t="n">
         <v>9.48</v>
       </c>
-      <c r="I27" s="94" t="n">
+      <c r="J27" s="94" t="n">
         <v>6.37</v>
-      </c>
-      <c r="J27" s="94" t="n">
-        <v>5.88</v>
       </c>
       <c r="K27" s="94" t="n">
         <v>5.88</v>
@@ -9373,61 +9375,61 @@
         <v>5.88</v>
       </c>
       <c r="M27" s="94" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="N27" s="94" t="n">
         <v>4.59</v>
       </c>
-      <c r="N27" s="94" t="n">
+      <c r="O27" s="94" t="n">
         <v>6.19</v>
       </c>
-      <c r="O27" s="94" t="n">
+      <c r="P27" s="94" t="n">
         <v>3.69</v>
       </c>
-      <c r="P27" s="94" t="n">
+      <c r="Q27" s="94" t="n">
         <v>4.22</v>
-      </c>
-      <c r="Q27" s="94" t="n">
-        <v>3.56</v>
       </c>
       <c r="R27" s="94" t="n">
         <v>3.56</v>
       </c>
       <c r="S27" s="94" t="n">
-        <v>6.19</v>
+        <v>3.56</v>
       </c>
       <c r="T27" s="94" t="n">
         <v>6.19</v>
       </c>
       <c r="U27" s="94" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="V27" s="94" t="n">
         <v>6.61</v>
       </c>
-      <c r="V27" s="94" t="n">
+      <c r="W27" s="94" t="n">
         <v>8.6</v>
-      </c>
-      <c r="W27" s="94" t="n">
-        <v>7.91</v>
       </c>
       <c r="X27" s="94" t="n">
         <v>7.91</v>
       </c>
       <c r="Y27" s="94" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="Z27" s="94" t="n">
         <v>7.57</v>
-      </c>
-      <c r="Z27" s="94" t="n">
-        <v>6.47</v>
       </c>
       <c r="AA27" s="94" t="n">
         <v>6.47</v>
       </c>
       <c r="AB27" s="94" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="AC27" s="94" t="n">
         <v>8.75</v>
-      </c>
-      <c r="AC27" s="94" t="n">
-        <v>10.02</v>
       </c>
       <c r="AD27" s="94" t="n">
         <v>10.02</v>
       </c>
       <c r="AE27" s="94" t="n">
-        <v>11.78</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="28">
@@ -9437,31 +9439,31 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="C28" s="94" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="D28" s="94" t="n">
         <v>21.81</v>
       </c>
-      <c r="C28" s="94" t="n">
-        <v>21.81</v>
-      </c>
-      <c r="D28" s="94" t="n">
+      <c r="E28" s="94" t="n">
         <v>15.29</v>
-      </c>
-      <c r="E28" s="94" t="n">
-        <v>16.05</v>
       </c>
       <c r="F28" s="94" t="n">
         <v>16.05</v>
       </c>
       <c r="G28" s="94" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="H28" s="94" t="n">
         <v>13.95</v>
       </c>
-      <c r="H28" s="94" t="n">
+      <c r="I28" s="94" t="n">
         <v>16.69</v>
       </c>
-      <c r="I28" s="94" t="n">
+      <c r="J28" s="94" t="n">
         <v>13.74</v>
-      </c>
-      <c r="J28" s="94" t="n">
-        <v>13.09</v>
       </c>
       <c r="K28" s="94" t="n">
         <v>13.09</v>
@@ -9470,61 +9472,61 @@
         <v>13.09</v>
       </c>
       <c r="M28" s="94" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="N28" s="94" t="n">
         <v>12.55</v>
       </c>
-      <c r="N28" s="94" t="n">
+      <c r="O28" s="94" t="n">
         <v>12.51</v>
       </c>
-      <c r="O28" s="94" t="n">
+      <c r="P28" s="94" t="n">
         <v>5.82</v>
       </c>
-      <c r="P28" s="94" t="n">
+      <c r="Q28" s="94" t="n">
         <v>6</v>
-      </c>
-      <c r="Q28" s="94" t="n">
-        <v>8.09</v>
       </c>
       <c r="R28" s="94" t="n">
         <v>8.09</v>
       </c>
       <c r="S28" s="94" t="n">
-        <v>9</v>
+        <v>8.09</v>
       </c>
       <c r="T28" s="94" t="n">
         <v>9</v>
       </c>
       <c r="U28" s="94" t="n">
+        <v>9</v>
+      </c>
+      <c r="V28" s="94" t="n">
         <v>8.289999999999999</v>
       </c>
-      <c r="V28" s="94" t="n">
+      <c r="W28" s="94" t="n">
         <v>7.32</v>
-      </c>
-      <c r="W28" s="94" t="n">
-        <v>6.22</v>
       </c>
       <c r="X28" s="94" t="n">
         <v>6.22</v>
       </c>
       <c r="Y28" s="94" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="Z28" s="94" t="n">
         <v>4.8</v>
-      </c>
-      <c r="Z28" s="94" t="n">
-        <v>5.62</v>
       </c>
       <c r="AA28" s="94" t="n">
         <v>5.62</v>
       </c>
       <c r="AB28" s="94" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="AC28" s="94" t="n">
         <v>4.5</v>
-      </c>
-      <c r="AC28" s="94" t="n">
-        <v>7.01</v>
       </c>
       <c r="AD28" s="94" t="n">
         <v>7.01</v>
       </c>
       <c r="AE28" s="94" t="n">
-        <v>8.779999999999999</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="29">
@@ -9534,31 +9536,31 @@
         </is>
       </c>
       <c r="B29" s="94" t="n">
+        <v>44.16</v>
+      </c>
+      <c r="C29" s="94" t="n">
+        <v>44.16</v>
+      </c>
+      <c r="D29" s="94" t="n">
         <v>55.99</v>
       </c>
-      <c r="C29" s="94" t="n">
-        <v>55.99</v>
-      </c>
-      <c r="D29" s="94" t="n">
+      <c r="E29" s="94" t="n">
         <v>8.699999999999999</v>
-      </c>
-      <c r="E29" s="94" t="n">
-        <v>54.41</v>
       </c>
       <c r="F29" s="94" t="n">
         <v>54.41</v>
       </c>
       <c r="G29" s="94" t="n">
+        <v>54.41</v>
+      </c>
+      <c r="H29" s="94" t="n">
         <v>94.87</v>
       </c>
-      <c r="H29" s="94" t="n">
+      <c r="I29" s="94" t="n">
         <v>93.84999999999999</v>
       </c>
-      <c r="I29" s="94" t="n">
+      <c r="J29" s="94" t="n">
         <v>85.8</v>
-      </c>
-      <c r="J29" s="94" t="n">
-        <v>78.89</v>
       </c>
       <c r="K29" s="94" t="n">
         <v>78.89</v>
@@ -9567,61 +9569,61 @@
         <v>78.89</v>
       </c>
       <c r="M29" s="94" t="n">
+        <v>78.89</v>
+      </c>
+      <c r="N29" s="94" t="n">
         <v>51.88</v>
       </c>
-      <c r="N29" s="94" t="n">
+      <c r="O29" s="94" t="n">
         <v>83.56</v>
       </c>
-      <c r="O29" s="94" t="n">
+      <c r="P29" s="94" t="n">
         <v>6.54</v>
       </c>
-      <c r="P29" s="94" t="n">
+      <c r="Q29" s="94" t="n">
         <v>8.380000000000001</v>
-      </c>
-      <c r="Q29" s="94" t="n">
-        <v>10.96</v>
       </c>
       <c r="R29" s="94" t="n">
         <v>10.96</v>
       </c>
       <c r="S29" s="94" t="n">
-        <v>32.97</v>
+        <v>10.96</v>
       </c>
       <c r="T29" s="94" t="n">
         <v>32.97</v>
       </c>
       <c r="U29" s="94" t="n">
+        <v>32.97</v>
+      </c>
+      <c r="V29" s="94" t="n">
         <v>34.13</v>
       </c>
-      <c r="V29" s="94" t="n">
+      <c r="W29" s="94" t="n">
         <v>88.52</v>
-      </c>
-      <c r="W29" s="94" t="n">
-        <v>76.26000000000001</v>
       </c>
       <c r="X29" s="94" t="n">
         <v>76.26000000000001</v>
       </c>
       <c r="Y29" s="94" t="n">
+        <v>76.26000000000001</v>
+      </c>
+      <c r="Z29" s="94" t="n">
         <v>5.68</v>
-      </c>
-      <c r="Z29" s="94" t="n">
-        <v>6.54</v>
       </c>
       <c r="AA29" s="94" t="n">
         <v>6.54</v>
       </c>
       <c r="AB29" s="94" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="AC29" s="94" t="n">
         <v>11.7</v>
-      </c>
-      <c r="AC29" s="94" t="n">
-        <v>24.8</v>
       </c>
       <c r="AD29" s="94" t="n">
         <v>24.8</v>
       </c>
       <c r="AE29" s="94" t="n">
-        <v>85.38</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="30">
@@ -9630,114 +9632,114 @@
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B30" s="92" t="inlineStr">
+      <c r="B30" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C30" s="93" t="inlineStr">
+      <c r="D30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D30" s="92" t="inlineStr">
+      <c r="E30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E30" s="91" t="inlineStr">
+      <c r="F30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F30" s="91" t="inlineStr">
+      <c r="G30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G30" s="91" t="inlineStr">
+      <c r="H30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H30" s="91" t="inlineStr">
+      <c r="I30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I30" s="91" t="inlineStr">
+      <c r="J30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J30" s="92" t="inlineStr">
+      <c r="K30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K30" s="93" t="inlineStr">
+      <c r="L30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L30" s="93" t="inlineStr">
+      <c r="M30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M30" s="93" t="inlineStr">
+      <c r="N30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N30" s="93" t="inlineStr">
+      <c r="O30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O30" s="93" t="inlineStr">
+      <c r="P30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P30" s="93" t="inlineStr">
+      <c r="Q30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q30" s="93" t="inlineStr">
+      <c r="R30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R30" s="93" t="inlineStr">
+      <c r="S30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S30" s="92" t="inlineStr">
+      <c r="T30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T30" s="91" t="inlineStr">
+      <c r="U30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U30" s="91" t="inlineStr">
+      <c r="V30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V30" s="93" t="inlineStr">
+      <c r="W30" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="W30" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="X30" s="91" t="inlineStr">
@@ -9788,49 +9790,49 @@
         </is>
       </c>
       <c r="B31" s="94" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C31" s="94" t="n">
         <v>0.35</v>
       </c>
-      <c r="C31" s="94" t="n">
+      <c r="D31" s="94" t="n">
         <v>0.29</v>
       </c>
-      <c r="D31" s="94" t="n">
+      <c r="E31" s="94" t="n">
         <v>2.49</v>
-      </c>
-      <c r="E31" s="94" t="n">
-        <v>5.32</v>
       </c>
       <c r="F31" s="94" t="n">
         <v>5.32</v>
       </c>
       <c r="G31" s="94" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="H31" s="94" t="n">
         <v>4.76</v>
       </c>
-      <c r="H31" s="94" t="n">
+      <c r="I31" s="94" t="n">
         <v>4.05</v>
       </c>
-      <c r="I31" s="94" t="n">
+      <c r="J31" s="94" t="n">
         <v>1.6</v>
       </c>
-      <c r="J31" s="94" t="n">
+      <c r="K31" s="94" t="n">
         <v>-0.13</v>
-      </c>
-      <c r="K31" s="94" t="n">
-        <v>-1.36</v>
       </c>
       <c r="L31" s="94" t="n">
         <v>-1.36</v>
       </c>
       <c r="M31" s="94" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="N31" s="94" t="n">
         <v>-0.87</v>
       </c>
-      <c r="N31" s="94" t="n">
+      <c r="O31" s="94" t="n">
         <v>-1.88</v>
       </c>
-      <c r="O31" s="94" t="n">
+      <c r="P31" s="94" t="n">
         <v>-3.6</v>
-      </c>
-      <c r="P31" s="94" t="n">
-        <v>-1.05</v>
       </c>
       <c r="Q31" s="94" t="n">
         <v>-1.05</v>
@@ -9839,19 +9841,19 @@
         <v>-1.05</v>
       </c>
       <c r="S31" s="94" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="T31" s="94" t="n">
         <v>0.57</v>
       </c>
-      <c r="T31" s="94" t="n">
+      <c r="U31" s="94" t="n">
         <v>1.79</v>
       </c>
-      <c r="U31" s="94" t="n">
+      <c r="V31" s="94" t="n">
         <v>2.94</v>
       </c>
-      <c r="V31" s="94" t="n">
+      <c r="W31" s="94" t="n">
         <v>-0.07000000000000001</v>
-      </c>
-      <c r="W31" s="94" t="n">
-        <v>3.26</v>
       </c>
       <c r="X31" s="94" t="n">
         <v>3.26</v>
@@ -9869,65 +9871,65 @@
         <v>3.26</v>
       </c>
       <c r="AC31" s="94" t="n">
-        <v>4.49</v>
+        <v>3.26</v>
       </c>
       <c r="AD31" s="94" t="n">
         <v>4.49</v>
       </c>
       <c r="AE31" s="94" t="n">
-        <v>4.65</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="95" t="inlineStr">
+      <c r="A32" s="76" t="inlineStr">
         <is>
           <t>jp225:RNG120</t>
         </is>
       </c>
       <c r="B32" s="94" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="C32" s="94" t="n">
         <v>25.29</v>
       </c>
-      <c r="C32" s="94" t="n">
+      <c r="D32" s="94" t="n">
         <v>8.65</v>
       </c>
-      <c r="D32" s="94" t="n">
+      <c r="E32" s="94" t="n">
         <v>3.78</v>
-      </c>
-      <c r="E32" s="94" t="n">
-        <v>2.12</v>
       </c>
       <c r="F32" s="94" t="n">
         <v>2.12</v>
       </c>
       <c r="G32" s="94" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H32" s="94" t="n">
         <v>3.72</v>
       </c>
-      <c r="H32" s="94" t="n">
+      <c r="I32" s="94" t="n">
         <v>3.06</v>
       </c>
-      <c r="I32" s="94" t="n">
+      <c r="J32" s="94" t="n">
         <v>3.61</v>
       </c>
-      <c r="J32" s="94" t="n">
+      <c r="K32" s="94" t="n">
         <v>2.73</v>
-      </c>
-      <c r="K32" s="94" t="n">
-        <v>-1.8</v>
       </c>
       <c r="L32" s="94" t="n">
         <v>-1.8</v>
       </c>
       <c r="M32" s="94" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="N32" s="94" t="n">
         <v>-2.58</v>
       </c>
-      <c r="N32" s="94" t="n">
+      <c r="O32" s="94" t="n">
         <v>-2.92</v>
       </c>
-      <c r="O32" s="94" t="n">
+      <c r="P32" s="94" t="n">
         <v>-3.97</v>
-      </c>
-      <c r="P32" s="94" t="n">
-        <v>-2.33</v>
       </c>
       <c r="Q32" s="94" t="n">
         <v>-2.33</v>
@@ -9936,19 +9938,19 @@
         <v>-2.33</v>
       </c>
       <c r="S32" s="94" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="T32" s="94" t="n">
         <v>-3.63</v>
       </c>
-      <c r="T32" s="94" t="n">
+      <c r="U32" s="94" t="n">
         <v>-3.14</v>
       </c>
-      <c r="U32" s="94" t="n">
+      <c r="V32" s="94" t="n">
         <v>-2.69</v>
       </c>
-      <c r="V32" s="94" t="n">
+      <c r="W32" s="94" t="n">
         <v>-6.91</v>
-      </c>
-      <c r="W32" s="94" t="n">
-        <v>-4.63</v>
       </c>
       <c r="X32" s="94" t="n">
         <v>-4.63</v>
@@ -9966,13 +9968,13 @@
         <v>-4.63</v>
       </c>
       <c r="AC32" s="94" t="n">
-        <v>-3.12</v>
+        <v>-4.63</v>
       </c>
       <c r="AD32" s="94" t="n">
         <v>-3.12</v>
       </c>
       <c r="AE32" s="94" t="n">
-        <v>-2.97</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="33">
@@ -9982,49 +9984,49 @@
         </is>
       </c>
       <c r="B33" s="94" t="n">
+        <v>53.61</v>
+      </c>
+      <c r="C33" s="94" t="n">
         <v>51.93</v>
       </c>
-      <c r="C33" s="94" t="n">
+      <c r="D33" s="94" t="n">
         <v>44.81</v>
       </c>
-      <c r="D33" s="94" t="n">
+      <c r="E33" s="94" t="n">
         <v>54.76</v>
-      </c>
-      <c r="E33" s="94" t="n">
-        <v>63.06</v>
       </c>
       <c r="F33" s="94" t="n">
         <v>63.06</v>
       </c>
       <c r="G33" s="94" t="n">
+        <v>63.06</v>
+      </c>
+      <c r="H33" s="94" t="n">
         <v>63.69</v>
       </c>
-      <c r="H33" s="94" t="n">
+      <c r="I33" s="94" t="n">
         <v>59.51</v>
       </c>
-      <c r="I33" s="94" t="n">
+      <c r="J33" s="94" t="n">
         <v>49.22</v>
       </c>
-      <c r="J33" s="94" t="n">
+      <c r="K33" s="94" t="n">
         <v>46.79</v>
-      </c>
-      <c r="K33" s="94" t="n">
-        <v>37.14</v>
       </c>
       <c r="L33" s="94" t="n">
         <v>37.14</v>
       </c>
       <c r="M33" s="94" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="N33" s="94" t="n">
         <v>38.82</v>
       </c>
-      <c r="N33" s="94" t="n">
+      <c r="O33" s="94" t="n">
         <v>36.1</v>
       </c>
-      <c r="O33" s="94" t="n">
+      <c r="P33" s="94" t="n">
         <v>36.44</v>
-      </c>
-      <c r="P33" s="94" t="n">
-        <v>45.43</v>
       </c>
       <c r="Q33" s="94" t="n">
         <v>45.43</v>
@@ -10033,19 +10035,19 @@
         <v>45.43</v>
       </c>
       <c r="S33" s="94" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="T33" s="94" t="n">
         <v>52.04</v>
       </c>
-      <c r="T33" s="94" t="n">
+      <c r="U33" s="94" t="n">
         <v>58.96</v>
       </c>
-      <c r="U33" s="94" t="n">
+      <c r="V33" s="94" t="n">
         <v>60.92</v>
       </c>
-      <c r="V33" s="94" t="n">
+      <c r="W33" s="94" t="n">
         <v>49.64</v>
-      </c>
-      <c r="W33" s="94" t="n">
-        <v>61.59</v>
       </c>
       <c r="X33" s="94" t="n">
         <v>61.59</v>
@@ -10063,13 +10065,13 @@
         <v>61.59</v>
       </c>
       <c r="AC33" s="94" t="n">
-        <v>71.7</v>
+        <v>61.59</v>
       </c>
       <c r="AD33" s="94" t="n">
         <v>71.7</v>
       </c>
       <c r="AE33" s="94" t="n">
-        <v>61.28</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="34">
@@ -10108,114 +10110,114 @@
           <t>red</t>
         </is>
       </c>
-      <c r="H34" s="92" t="inlineStr">
+      <c r="H34" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I34" s="92" t="inlineStr">
+      <c r="J34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J34" s="91" t="inlineStr">
+      <c r="K34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K34" s="91" t="inlineStr">
+      <c r="L34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L34" s="91" t="inlineStr">
+      <c r="M34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M34" s="92" t="inlineStr">
+      <c r="N34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N34" s="92" t="inlineStr">
+      <c r="O34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O34" s="93" t="inlineStr">
+      <c r="P34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P34" s="93" t="inlineStr">
+      <c r="Q34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q34" s="93" t="inlineStr">
+      <c r="R34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R34" s="93" t="inlineStr">
+      <c r="S34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S34" s="93" t="inlineStr">
+      <c r="T34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T34" s="93" t="inlineStr">
+      <c r="U34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U34" s="93" t="inlineStr">
+      <c r="V34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V34" s="93" t="inlineStr">
+      <c r="W34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W34" s="93" t="inlineStr">
+      <c r="X34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X34" s="93" t="inlineStr">
+      <c r="Y34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y34" s="92" t="inlineStr">
+      <c r="Z34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z34" s="92" t="inlineStr">
+      <c r="AA34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA34" s="92" t="inlineStr">
+      <c r="AB34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB34" s="92" t="inlineStr">
+      <c r="AC34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AC34" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AD34" s="91" t="inlineStr">
@@ -10251,79 +10253,79 @@
         <v>0.05</v>
       </c>
       <c r="G35" s="94" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H35" s="94" t="n">
         <v>0.08</v>
       </c>
-      <c r="H35" s="94" t="n">
+      <c r="I35" s="94" t="n">
         <v>-1.53</v>
       </c>
-      <c r="I35" s="94" t="n">
+      <c r="J35" s="94" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="J35" s="94" t="n">
+      <c r="K35" s="94" t="n">
         <v>-0.25</v>
-      </c>
-      <c r="K35" s="94" t="n">
-        <v>-0.66</v>
       </c>
       <c r="L35" s="94" t="n">
         <v>-0.66</v>
       </c>
       <c r="M35" s="94" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="N35" s="94" t="n">
         <v>-2.25</v>
       </c>
-      <c r="N35" s="94" t="n">
+      <c r="O35" s="94" t="n">
         <v>-2.65</v>
       </c>
-      <c r="O35" s="94" t="n">
+      <c r="P35" s="94" t="n">
         <v>-3.96</v>
       </c>
-      <c r="P35" s="94" t="n">
+      <c r="Q35" s="94" t="n">
         <v>-3.87</v>
-      </c>
-      <c r="Q35" s="94" t="n">
-        <v>-4.36</v>
       </c>
       <c r="R35" s="94" t="n">
         <v>-4.36</v>
       </c>
       <c r="S35" s="94" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="T35" s="94" t="n">
         <v>-2.63</v>
       </c>
-      <c r="T35" s="94" t="n">
+      <c r="U35" s="94" t="n">
         <v>-2.35</v>
       </c>
-      <c r="U35" s="94" t="n">
+      <c r="V35" s="94" t="n">
         <v>-3.06</v>
       </c>
-      <c r="V35" s="94" t="n">
+      <c r="W35" s="94" t="n">
         <v>-3.26</v>
-      </c>
-      <c r="W35" s="94" t="n">
-        <v>-2.47</v>
       </c>
       <c r="X35" s="94" t="n">
         <v>-2.47</v>
       </c>
       <c r="Y35" s="94" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="Z35" s="94" t="n">
         <v>-0.95</v>
-      </c>
-      <c r="Z35" s="94" t="n">
-        <v>-0.41</v>
       </c>
       <c r="AA35" s="94" t="n">
         <v>-0.41</v>
       </c>
       <c r="AB35" s="94" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="AC35" s="94" t="n">
         <v>0.16</v>
-      </c>
-      <c r="AC35" s="94" t="n">
-        <v>0.36</v>
       </c>
       <c r="AD35" s="94" t="n">
         <v>0.36</v>
       </c>
       <c r="AE35" s="94" t="n">
-        <v>-0.41</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="36">
@@ -10348,79 +10350,79 @@
         <v>4.53</v>
       </c>
       <c r="G36" s="94" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="H36" s="94" t="n">
         <v>6.02</v>
       </c>
-      <c r="H36" s="94" t="n">
+      <c r="I36" s="94" t="n">
         <v>0.48</v>
       </c>
-      <c r="I36" s="94" t="n">
+      <c r="J36" s="94" t="n">
         <v>1.56</v>
       </c>
-      <c r="J36" s="94" t="n">
+      <c r="K36" s="94" t="n">
         <v>-0.16</v>
-      </c>
-      <c r="K36" s="94" t="n">
-        <v>0.33</v>
       </c>
       <c r="L36" s="94" t="n">
         <v>0.33</v>
       </c>
       <c r="M36" s="94" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N36" s="94" t="n">
         <v>-0.34</v>
       </c>
-      <c r="N36" s="94" t="n">
+      <c r="O36" s="94" t="n">
         <v>-0.48</v>
       </c>
-      <c r="O36" s="94" t="n">
+      <c r="P36" s="94" t="n">
         <v>-0.33</v>
       </c>
-      <c r="P36" s="94" t="n">
+      <c r="Q36" s="94" t="n">
         <v>-0.23</v>
-      </c>
-      <c r="Q36" s="94" t="n">
-        <v>-0.11</v>
       </c>
       <c r="R36" s="94" t="n">
         <v>-0.11</v>
       </c>
       <c r="S36" s="94" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="T36" s="94" t="n">
         <v>-0.71</v>
       </c>
-      <c r="T36" s="94" t="n">
+      <c r="U36" s="94" t="n">
         <v>-1.09</v>
       </c>
-      <c r="U36" s="94" t="n">
+      <c r="V36" s="94" t="n">
         <v>-2.16</v>
       </c>
-      <c r="V36" s="94" t="n">
+      <c r="W36" s="94" t="n">
         <v>-1.76</v>
-      </c>
-      <c r="W36" s="94" t="n">
-        <v>-2.08</v>
       </c>
       <c r="X36" s="94" t="n">
         <v>-2.08</v>
       </c>
       <c r="Y36" s="94" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="Z36" s="94" t="n">
         <v>-0.79</v>
-      </c>
-      <c r="Z36" s="94" t="n">
-        <v>-1.09</v>
       </c>
       <c r="AA36" s="94" t="n">
         <v>-1.09</v>
       </c>
       <c r="AB36" s="94" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="AC36" s="94" t="n">
         <v>-0.92</v>
-      </c>
-      <c r="AC36" s="94" t="n">
-        <v>-0.84</v>
       </c>
       <c r="AD36" s="94" t="n">
         <v>-0.84</v>
       </c>
       <c r="AE36" s="94" t="n">
-        <v>-1.61</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="37">
@@ -10445,79 +10447,79 @@
         <v>85.3</v>
       </c>
       <c r="G37" s="94" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="H37" s="94" t="n">
         <v>80.56</v>
       </c>
-      <c r="H37" s="94" t="n">
+      <c r="I37" s="94" t="n">
         <v>39.31</v>
       </c>
-      <c r="I37" s="94" t="n">
+      <c r="J37" s="94" t="n">
         <v>55.71</v>
       </c>
-      <c r="J37" s="94" t="n">
+      <c r="K37" s="94" t="n">
         <v>76.36</v>
-      </c>
-      <c r="K37" s="94" t="n">
-        <v>75.59</v>
       </c>
       <c r="L37" s="94" t="n">
         <v>75.59</v>
       </c>
       <c r="M37" s="94" t="n">
+        <v>75.59</v>
+      </c>
+      <c r="N37" s="94" t="n">
         <v>63.48</v>
       </c>
-      <c r="N37" s="94" t="n">
+      <c r="O37" s="94" t="n">
         <v>47.6</v>
       </c>
-      <c r="O37" s="94" t="n">
+      <c r="P37" s="94" t="n">
         <v>21.39</v>
       </c>
-      <c r="P37" s="94" t="n">
+      <c r="Q37" s="94" t="n">
         <v>30.94</v>
-      </c>
-      <c r="Q37" s="94" t="n">
-        <v>9.859999999999999</v>
       </c>
       <c r="R37" s="94" t="n">
         <v>9.859999999999999</v>
       </c>
       <c r="S37" s="94" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="T37" s="94" t="n">
         <v>24.76</v>
       </c>
-      <c r="T37" s="94" t="n">
+      <c r="U37" s="94" t="n">
         <v>37.84</v>
       </c>
-      <c r="U37" s="94" t="n">
+      <c r="V37" s="94" t="n">
         <v>14.49</v>
       </c>
-      <c r="V37" s="94" t="n">
+      <c r="W37" s="94" t="n">
         <v>11.22</v>
-      </c>
-      <c r="W37" s="94" t="n">
-        <v>17.28</v>
       </c>
       <c r="X37" s="94" t="n">
         <v>17.28</v>
       </c>
       <c r="Y37" s="94" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="Z37" s="94" t="n">
         <v>51.04</v>
-      </c>
-      <c r="Z37" s="94" t="n">
-        <v>34.51</v>
       </c>
       <c r="AA37" s="94" t="n">
         <v>34.51</v>
       </c>
       <c r="AB37" s="94" t="n">
+        <v>34.51</v>
+      </c>
+      <c r="AC37" s="94" t="n">
         <v>57.76</v>
-      </c>
-      <c r="AC37" s="94" t="n">
-        <v>78.84999999999999</v>
       </c>
       <c r="AD37" s="94" t="n">
         <v>78.84999999999999</v>
       </c>
       <c r="AE37" s="94" t="n">
-        <v>74.3</v>
+        <v>78.84999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -10526,129 +10528,129 @@
           <t>sensex:EIDE</t>
         </is>
       </c>
-      <c r="B38" s="92" t="inlineStr">
+      <c r="B38" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C38" s="92" t="inlineStr">
+      <c r="D38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D38" s="93" t="inlineStr">
+      <c r="E38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E38" s="92" t="inlineStr">
+      <c r="F38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F38" s="92" t="inlineStr">
+      <c r="G38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G38" s="92" t="inlineStr">
+      <c r="H38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H38" s="92" t="inlineStr">
+      <c r="I38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I38" s="93" t="inlineStr">
+      <c r="J38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J38" s="92" t="inlineStr">
+      <c r="K38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K38" s="92" t="inlineStr">
+      <c r="L38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L38" s="92" t="inlineStr">
+      <c r="M38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M38" s="92" t="inlineStr">
+      <c r="N38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N38" s="92" t="inlineStr">
+      <c r="O38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O38" s="93" t="inlineStr">
+      <c r="P38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P38" s="93" t="inlineStr">
+      <c r="Q38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q38" s="93" t="inlineStr">
+      <c r="R38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R38" s="93" t="inlineStr">
+      <c r="S38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S38" s="93" t="inlineStr">
+      <c r="T38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T38" s="92" t="inlineStr">
+      <c r="U38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U38" s="93" t="inlineStr">
+      <c r="V38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V38" s="93" t="inlineStr">
+      <c r="W38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W38" s="91" t="inlineStr">
+      <c r="X38" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X38" s="91" t="inlineStr">
+      <c r="Y38" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y38" s="91" t="inlineStr">
+      <c r="Z38" s="91" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="Z38" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AA38" s="92" t="inlineStr">
@@ -10684,94 +10686,94 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="C39" s="94" t="n">
         <v>-4</v>
       </c>
-      <c r="C39" s="94" t="n">
+      <c r="D39" s="94" t="n">
         <v>-4.39</v>
       </c>
-      <c r="D39" s="94" t="n">
+      <c r="E39" s="94" t="n">
         <v>-5.72</v>
-      </c>
-      <c r="E39" s="94" t="n">
-        <v>-5.2</v>
       </c>
       <c r="F39" s="94" t="n">
         <v>-5.2</v>
       </c>
       <c r="G39" s="94" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="H39" s="94" t="n">
         <v>-4.36</v>
       </c>
-      <c r="H39" s="94" t="n">
+      <c r="I39" s="94" t="n">
         <v>-3.77</v>
       </c>
-      <c r="I39" s="94" t="n">
+      <c r="J39" s="94" t="n">
         <v>-5.28</v>
       </c>
-      <c r="J39" s="94" t="n">
+      <c r="K39" s="94" t="n">
         <v>-3.76</v>
-      </c>
-      <c r="K39" s="94" t="n">
-        <v>-4.49</v>
       </c>
       <c r="L39" s="94" t="n">
         <v>-4.49</v>
       </c>
       <c r="M39" s="94" t="n">
+        <v>-4.49</v>
+      </c>
+      <c r="N39" s="94" t="n">
         <v>-5.06</v>
       </c>
-      <c r="N39" s="94" t="n">
+      <c r="O39" s="94" t="n">
         <v>-5.54</v>
       </c>
-      <c r="O39" s="94" t="n">
+      <c r="P39" s="94" t="n">
         <v>-5.56</v>
       </c>
-      <c r="P39" s="94" t="n">
+      <c r="Q39" s="94" t="n">
         <v>-6.35</v>
-      </c>
-      <c r="Q39" s="94" t="n">
-        <v>-5.43</v>
       </c>
       <c r="R39" s="94" t="n">
         <v>-5.43</v>
       </c>
       <c r="S39" s="94" t="n">
+        <v>-5.43</v>
+      </c>
+      <c r="T39" s="94" t="n">
         <v>-5.31</v>
       </c>
-      <c r="T39" s="94" t="n">
+      <c r="U39" s="94" t="n">
         <v>-3.97</v>
       </c>
-      <c r="U39" s="94" t="n">
+      <c r="V39" s="94" t="n">
         <v>-4.18</v>
       </c>
-      <c r="V39" s="94" t="n">
+      <c r="W39" s="94" t="n">
         <v>-4.3</v>
-      </c>
-      <c r="W39" s="94" t="n">
-        <v>-2.95</v>
       </c>
       <c r="X39" s="94" t="n">
         <v>-2.95</v>
       </c>
       <c r="Y39" s="94" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="Z39" s="94" t="n">
         <v>-1.36</v>
       </c>
-      <c r="Z39" s="94" t="n">
+      <c r="AA39" s="94" t="n">
         <v>-3.89</v>
       </c>
-      <c r="AA39" s="94" t="n">
+      <c r="AB39" s="94" t="n">
         <v>-5.28</v>
       </c>
-      <c r="AB39" s="94" t="n">
+      <c r="AC39" s="94" t="n">
         <v>-7.14</v>
-      </c>
-      <c r="AC39" s="94" t="n">
-        <v>-6.64</v>
       </c>
       <c r="AD39" s="94" t="n">
         <v>-6.64</v>
       </c>
       <c r="AE39" s="94" t="n">
-        <v>-8.300000000000001</v>
+        <v>-6.64</v>
       </c>
     </row>
     <row r="40">
@@ -10781,94 +10783,94 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
+        <v>-3.67</v>
+      </c>
+      <c r="C40" s="94" t="n">
         <v>-2.98</v>
       </c>
-      <c r="C40" s="94" t="n">
+      <c r="D40" s="94" t="n">
         <v>-4.49</v>
       </c>
-      <c r="D40" s="94" t="n">
+      <c r="E40" s="94" t="n">
         <v>-4.11</v>
-      </c>
-      <c r="E40" s="94" t="n">
-        <v>-3.26</v>
       </c>
       <c r="F40" s="94" t="n">
         <v>-3.26</v>
       </c>
       <c r="G40" s="94" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="H40" s="94" t="n">
         <v>-5.51</v>
       </c>
-      <c r="H40" s="94" t="n">
+      <c r="I40" s="94" t="n">
         <v>-6.67</v>
       </c>
-      <c r="I40" s="94" t="n">
+      <c r="J40" s="94" t="n">
         <v>-7.22</v>
       </c>
-      <c r="J40" s="94" t="n">
+      <c r="K40" s="94" t="n">
         <v>-5.38</v>
-      </c>
-      <c r="K40" s="94" t="n">
-        <v>-5.82</v>
       </c>
       <c r="L40" s="94" t="n">
         <v>-5.82</v>
       </c>
       <c r="M40" s="94" t="n">
+        <v>-5.82</v>
+      </c>
+      <c r="N40" s="94" t="n">
         <v>-5.27</v>
       </c>
-      <c r="N40" s="94" t="n">
+      <c r="O40" s="94" t="n">
         <v>-4.14</v>
       </c>
-      <c r="O40" s="94" t="n">
+      <c r="P40" s="94" t="n">
         <v>-4.55</v>
       </c>
-      <c r="P40" s="94" t="n">
+      <c r="Q40" s="94" t="n">
         <v>-5.1</v>
-      </c>
-      <c r="Q40" s="94" t="n">
-        <v>-3.88</v>
       </c>
       <c r="R40" s="94" t="n">
         <v>-3.88</v>
       </c>
       <c r="S40" s="94" t="n">
+        <v>-3.88</v>
+      </c>
+      <c r="T40" s="94" t="n">
         <v>-3.7</v>
       </c>
-      <c r="T40" s="94" t="n">
+      <c r="U40" s="94" t="n">
         <v>-3.93</v>
       </c>
-      <c r="U40" s="94" t="n">
+      <c r="V40" s="94" t="n">
         <v>-3.12</v>
       </c>
-      <c r="V40" s="94" t="n">
+      <c r="W40" s="94" t="n">
         <v>-3.35</v>
-      </c>
-      <c r="W40" s="94" t="n">
-        <v>-1.61</v>
       </c>
       <c r="X40" s="94" t="n">
         <v>-1.61</v>
       </c>
       <c r="Y40" s="94" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="Z40" s="94" t="n">
         <v>0.06</v>
       </c>
-      <c r="Z40" s="94" t="n">
+      <c r="AA40" s="94" t="n">
         <v>-1.77</v>
       </c>
-      <c r="AA40" s="94" t="n">
+      <c r="AB40" s="94" t="n">
         <v>-2.75</v>
       </c>
-      <c r="AB40" s="94" t="n">
+      <c r="AC40" s="94" t="n">
         <v>-2.14</v>
-      </c>
-      <c r="AC40" s="94" t="n">
-        <v>-1.62</v>
       </c>
       <c r="AD40" s="94" t="n">
         <v>-1.62</v>
       </c>
       <c r="AE40" s="94" t="n">
-        <v>-1.97</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="41">
@@ -10878,94 +10880,94 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="C41" s="94" t="n">
         <v>45.92</v>
       </c>
-      <c r="C41" s="94" t="n">
+      <c r="D41" s="94" t="n">
         <v>38.59</v>
       </c>
-      <c r="D41" s="94" t="n">
+      <c r="E41" s="94" t="n">
         <v>31.52</v>
-      </c>
-      <c r="E41" s="94" t="n">
-        <v>37.51</v>
       </c>
       <c r="F41" s="94" t="n">
         <v>37.51</v>
       </c>
       <c r="G41" s="94" t="n">
+        <v>37.51</v>
+      </c>
+      <c r="H41" s="94" t="n">
         <v>40.26</v>
       </c>
-      <c r="H41" s="94" t="n">
+      <c r="I41" s="94" t="n">
         <v>38.85</v>
       </c>
-      <c r="I41" s="94" t="n">
+      <c r="J41" s="94" t="n">
         <v>31.71</v>
       </c>
-      <c r="J41" s="94" t="n">
+      <c r="K41" s="94" t="n">
         <v>41.13</v>
-      </c>
-      <c r="K41" s="94" t="n">
-        <v>34.71</v>
       </c>
       <c r="L41" s="94" t="n">
         <v>34.71</v>
       </c>
       <c r="M41" s="94" t="n">
+        <v>34.71</v>
+      </c>
+      <c r="N41" s="94" t="n">
         <v>38.21</v>
       </c>
-      <c r="N41" s="94" t="n">
+      <c r="O41" s="94" t="n">
         <v>33.68</v>
       </c>
-      <c r="O41" s="94" t="n">
+      <c r="P41" s="94" t="n">
         <v>30.45</v>
       </c>
-      <c r="P41" s="94" t="n">
+      <c r="Q41" s="94" t="n">
         <v>28.07</v>
-      </c>
-      <c r="Q41" s="94" t="n">
-        <v>34.68</v>
       </c>
       <c r="R41" s="94" t="n">
         <v>34.68</v>
       </c>
       <c r="S41" s="94" t="n">
+        <v>34.68</v>
+      </c>
+      <c r="T41" s="94" t="n">
         <v>36.46</v>
       </c>
-      <c r="T41" s="94" t="n">
+      <c r="U41" s="94" t="n">
         <v>40.56</v>
       </c>
-      <c r="U41" s="94" t="n">
+      <c r="V41" s="94" t="n">
         <v>40.95</v>
       </c>
-      <c r="V41" s="94" t="n">
+      <c r="W41" s="94" t="n">
         <v>38.45</v>
-      </c>
-      <c r="W41" s="94" t="n">
-        <v>48.38</v>
       </c>
       <c r="X41" s="94" t="n">
         <v>48.38</v>
       </c>
       <c r="Y41" s="94" t="n">
+        <v>48.38</v>
+      </c>
+      <c r="Z41" s="94" t="n">
         <v>55.82</v>
       </c>
-      <c r="Z41" s="94" t="n">
+      <c r="AA41" s="94" t="n">
         <v>39</v>
       </c>
-      <c r="AA41" s="94" t="n">
+      <c r="AB41" s="94" t="n">
         <v>33.12</v>
       </c>
-      <c r="AB41" s="94" t="n">
+      <c r="AC41" s="94" t="n">
         <v>34</v>
-      </c>
-      <c r="AC41" s="94" t="n">
-        <v>37.69</v>
       </c>
       <c r="AD41" s="94" t="n">
         <v>37.69</v>
       </c>
       <c r="AE41" s="94" t="n">
-        <v>34.47</v>
+        <v>37.69</v>
       </c>
     </row>
     <row r="42">
@@ -10989,138 +10991,140 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="E42" s="91" t="inlineStr">
+      <c r="E42" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F42" s="91" t="inlineStr">
+      <c r="G42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G42" s="91" t="inlineStr">
+      <c r="H42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H42" s="91" t="inlineStr">
+      <c r="I42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I42" s="91" t="inlineStr">
+      <c r="J42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J42" s="91" t="inlineStr">
+      <c r="K42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K42" s="91" t="inlineStr">
+      <c r="L42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L42" s="91" t="inlineStr">
+      <c r="M42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M42" s="91" t="inlineStr">
+      <c r="N42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N42" s="91" t="inlineStr">
+      <c r="O42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O42" s="92" t="inlineStr">
+      <c r="P42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P42" s="92" t="inlineStr">
+      <c r="Q42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q42" s="92" t="inlineStr">
+      <c r="R42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R42" s="92" t="inlineStr">
+      <c r="S42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S42" s="91" t="inlineStr">
+      <c r="T42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T42" s="91" t="inlineStr">
+      <c r="U42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U42" s="91" t="inlineStr">
+      <c r="V42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V42" s="91" t="inlineStr">
+      <c r="W42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W42" s="93" t="inlineStr">
+      <c r="X42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X42" s="93" t="inlineStr">
+      <c r="Y42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y42" s="91" t="inlineStr">
+      <c r="Z42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z42" s="91" t="inlineStr">
+      <c r="AA42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA42" s="91" t="inlineStr">
+      <c r="AB42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB42" s="92" t="inlineStr">
+      <c r="AC42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC42" s="91" t="inlineStr">
+      <c r="AD42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD42" s="91" t="inlineStr">
+      <c r="AE42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
-      </c>
-      <c r="AE42" s="92" t="n">
-        <v/>
       </c>
     </row>
     <row r="43">
@@ -11133,91 +11137,91 @@
         <v>6.25</v>
       </c>
       <c r="C43" s="94" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D43" s="94" t="n">
         <v>7.44</v>
       </c>
-      <c r="D43" s="94" t="n">
+      <c r="E43" s="94" t="n">
         <v>6.44</v>
-      </c>
-      <c r="E43" s="94" t="n">
-        <v>5.55</v>
       </c>
       <c r="F43" s="94" t="n">
         <v>5.55</v>
       </c>
       <c r="G43" s="94" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="H43" s="94" t="n">
         <v>4.44</v>
       </c>
-      <c r="H43" s="94" t="n">
+      <c r="I43" s="94" t="n">
         <v>4.53</v>
       </c>
-      <c r="I43" s="94" t="n">
+      <c r="J43" s="94" t="n">
         <v>3.57</v>
       </c>
-      <c r="J43" s="94" t="n">
+      <c r="K43" s="94" t="n">
         <v>3.15</v>
-      </c>
-      <c r="K43" s="94" t="n">
-        <v>2.32</v>
       </c>
       <c r="L43" s="94" t="n">
         <v>2.32</v>
       </c>
       <c r="M43" s="94" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="N43" s="94" t="n">
         <v>1.31</v>
       </c>
-      <c r="N43" s="94" t="n">
+      <c r="O43" s="94" t="n">
         <v>-1.82</v>
       </c>
-      <c r="O43" s="94" t="n">
+      <c r="P43" s="94" t="n">
         <v>-2.11</v>
       </c>
-      <c r="P43" s="94" t="n">
+      <c r="Q43" s="94" t="n">
         <v>-1.11</v>
-      </c>
-      <c r="Q43" s="94" t="n">
-        <v>-1.21</v>
       </c>
       <c r="R43" s="94" t="n">
         <v>-1.21</v>
       </c>
       <c r="S43" s="94" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="T43" s="94" t="n">
         <v>-1.47</v>
       </c>
-      <c r="T43" s="94" t="n">
+      <c r="U43" s="94" t="n">
         <v>-1.66</v>
       </c>
-      <c r="U43" s="94" t="n">
+      <c r="V43" s="94" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="V43" s="94" t="n">
+      <c r="W43" s="94" t="n">
         <v>-1.51</v>
-      </c>
-      <c r="W43" s="94" t="n">
-        <v>-3.18</v>
       </c>
       <c r="X43" s="94" t="n">
         <v>-3.18</v>
       </c>
       <c r="Y43" s="94" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="Z43" s="94" t="n">
         <v>-2.41</v>
-      </c>
-      <c r="Z43" s="94" t="n">
-        <v>-2.13</v>
       </c>
       <c r="AA43" s="94" t="n">
         <v>-2.13</v>
       </c>
       <c r="AB43" s="94" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="AC43" s="94" t="n">
         <v>-2.2</v>
-      </c>
-      <c r="AC43" s="94" t="n">
-        <v>-2.93</v>
       </c>
       <c r="AD43" s="94" t="n">
         <v>-2.93</v>
       </c>
       <c r="AE43" s="94" t="n">
-        <v/>
+        <v>-2.93</v>
       </c>
     </row>
     <row r="44">
@@ -11230,91 +11234,91 @@
         <v>8.289999999999999</v>
       </c>
       <c r="C44" s="94" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="D44" s="94" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="D44" s="94" t="n">
+      <c r="E44" s="94" t="n">
         <v>8.82</v>
-      </c>
-      <c r="E44" s="94" t="n">
-        <v>11.19</v>
       </c>
       <c r="F44" s="94" t="n">
         <v>11.19</v>
       </c>
       <c r="G44" s="94" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="H44" s="94" t="n">
         <v>10.4</v>
       </c>
-      <c r="H44" s="94" t="n">
+      <c r="I44" s="94" t="n">
         <v>8.08</v>
       </c>
-      <c r="I44" s="94" t="n">
+      <c r="J44" s="94" t="n">
         <v>5.43</v>
       </c>
-      <c r="J44" s="94" t="n">
+      <c r="K44" s="94" t="n">
         <v>2.68</v>
-      </c>
-      <c r="K44" s="94" t="n">
-        <v>3.14</v>
       </c>
       <c r="L44" s="94" t="n">
         <v>3.14</v>
       </c>
       <c r="M44" s="94" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N44" s="94" t="n">
         <v>2.56</v>
       </c>
-      <c r="N44" s="94" t="n">
+      <c r="O44" s="94" t="n">
         <v>-0.57</v>
       </c>
-      <c r="O44" s="94" t="n">
+      <c r="P44" s="94" t="n">
         <v>-0.05</v>
       </c>
-      <c r="P44" s="94" t="n">
+      <c r="Q44" s="94" t="n">
         <v>-1.4</v>
-      </c>
-      <c r="Q44" s="94" t="n">
-        <v>-2.21</v>
       </c>
       <c r="R44" s="94" t="n">
         <v>-2.21</v>
       </c>
       <c r="S44" s="94" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="T44" s="94" t="n">
         <v>-1.73</v>
       </c>
-      <c r="T44" s="94" t="n">
+      <c r="U44" s="94" t="n">
         <v>-1.09</v>
       </c>
-      <c r="U44" s="94" t="n">
+      <c r="V44" s="94" t="n">
         <v>-1.28</v>
       </c>
-      <c r="V44" s="94" t="n">
+      <c r="W44" s="94" t="n">
         <v>-1.65</v>
-      </c>
-      <c r="W44" s="94" t="n">
-        <v>-3.93</v>
       </c>
       <c r="X44" s="94" t="n">
         <v>-3.93</v>
       </c>
       <c r="Y44" s="94" t="n">
+        <v>-3.93</v>
+      </c>
+      <c r="Z44" s="94" t="n">
         <v>-3.13</v>
-      </c>
-      <c r="Z44" s="94" t="n">
-        <v>-4.45</v>
       </c>
       <c r="AA44" s="94" t="n">
         <v>-4.45</v>
       </c>
       <c r="AB44" s="94" t="n">
+        <v>-4.45</v>
+      </c>
+      <c r="AC44" s="94" t="n">
         <v>-4.11</v>
-      </c>
-      <c r="AC44" s="94" t="n">
-        <v>-2.88</v>
       </c>
       <c r="AD44" s="94" t="n">
         <v>-2.88</v>
       </c>
       <c r="AE44" s="94" t="n">
-        <v/>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="45">
@@ -11327,91 +11331,91 @@
         <v>69.76000000000001</v>
       </c>
       <c r="C45" s="94" t="n">
+        <v>69.76000000000001</v>
+      </c>
+      <c r="D45" s="94" t="n">
         <v>80.88</v>
       </c>
-      <c r="D45" s="94" t="n">
+      <c r="E45" s="94" t="n">
         <v>84.89</v>
-      </c>
-      <c r="E45" s="94" t="n">
-        <v>93.34</v>
       </c>
       <c r="F45" s="94" t="n">
         <v>93.34</v>
       </c>
       <c r="G45" s="94" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="H45" s="94" t="n">
         <v>92.31999999999999</v>
       </c>
-      <c r="H45" s="94" t="n">
+      <c r="I45" s="94" t="n">
         <v>90.48999999999999</v>
       </c>
-      <c r="I45" s="94" t="n">
+      <c r="J45" s="94" t="n">
         <v>87.65000000000001</v>
       </c>
-      <c r="J45" s="94" t="n">
+      <c r="K45" s="94" t="n">
         <v>85.73</v>
-      </c>
-      <c r="K45" s="94" t="n">
-        <v>84.51000000000001</v>
       </c>
       <c r="L45" s="94" t="n">
         <v>84.51000000000001</v>
       </c>
       <c r="M45" s="94" t="n">
+        <v>84.51000000000001</v>
+      </c>
+      <c r="N45" s="94" t="n">
         <v>80.23</v>
       </c>
-      <c r="N45" s="94" t="n">
+      <c r="O45" s="94" t="n">
         <v>62.6</v>
       </c>
-      <c r="O45" s="94" t="n">
+      <c r="P45" s="94" t="n">
         <v>51.62</v>
       </c>
-      <c r="P45" s="94" t="n">
+      <c r="Q45" s="94" t="n">
         <v>48.02</v>
-      </c>
-      <c r="Q45" s="94" t="n">
-        <v>52.7</v>
       </c>
       <c r="R45" s="94" t="n">
         <v>52.7</v>
       </c>
       <c r="S45" s="94" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="T45" s="94" t="n">
         <v>66.38</v>
       </c>
-      <c r="T45" s="94" t="n">
+      <c r="U45" s="94" t="n">
         <v>61.23</v>
       </c>
-      <c r="U45" s="94" t="n">
+      <c r="V45" s="94" t="n">
         <v>69.54000000000001</v>
       </c>
-      <c r="V45" s="94" t="n">
+      <c r="W45" s="94" t="n">
         <v>65.06</v>
-      </c>
-      <c r="W45" s="94" t="n">
-        <v>37.52</v>
       </c>
       <c r="X45" s="94" t="n">
         <v>37.52</v>
       </c>
       <c r="Y45" s="94" t="n">
+        <v>37.52</v>
+      </c>
+      <c r="Z45" s="94" t="n">
         <v>65.84</v>
-      </c>
-      <c r="Z45" s="94" t="n">
-        <v>63.25</v>
       </c>
       <c r="AA45" s="94" t="n">
         <v>63.25</v>
       </c>
       <c r="AB45" s="94" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="AC45" s="94" t="n">
         <v>46.49</v>
-      </c>
-      <c r="AC45" s="94" t="n">
-        <v>60.14</v>
       </c>
       <c r="AD45" s="94" t="n">
         <v>60.14</v>
       </c>
       <c r="AE45" s="94" t="n">
-        <v/>
+        <v>60.14</v>
       </c>
     </row>
     <row r="46">
@@ -11425,148 +11429,150 @@
           <t>red</t>
         </is>
       </c>
-      <c r="C46" s="92" t="inlineStr">
+      <c r="C46" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D46" s="92" t="inlineStr">
+      <c r="E46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E46" s="92" t="inlineStr">
+      <c r="F46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F46" s="92" t="inlineStr">
+      <c r="G46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G46" s="91" t="inlineStr">
+      <c r="H46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H46" s="91" t="inlineStr">
+      <c r="I46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I46" s="91" t="inlineStr">
+      <c r="J46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J46" s="91" t="inlineStr">
+      <c r="K46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K46" s="91" t="inlineStr">
+      <c r="L46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L46" s="91" t="inlineStr">
+      <c r="M46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M46" s="91" t="inlineStr">
+      <c r="N46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N46" s="91" t="inlineStr">
+      <c r="O46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O46" s="91" t="inlineStr">
+      <c r="P46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P46" s="93" t="inlineStr">
+      <c r="Q46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q46" s="92" t="inlineStr">
+      <c r="R46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R46" s="92" t="inlineStr">
+      <c r="S46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S46" s="91" t="inlineStr">
+      <c r="T46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T46" s="91" t="inlineStr">
+      <c r="U46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U46" s="91" t="inlineStr">
+      <c r="V46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V46" s="91" t="inlineStr">
+      <c r="W46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W46" s="93" t="inlineStr">
+      <c r="X46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X46" s="93" t="inlineStr">
+      <c r="Y46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y46" s="92" t="inlineStr">
+      <c r="Z46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z46" s="93" t="inlineStr">
+      <c r="AA46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA46" s="93" t="inlineStr">
+      <c r="AB46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB46" s="93" t="inlineStr">
+      <c r="AC46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC46" s="93" t="inlineStr">
+      <c r="AD46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD46" s="93" t="inlineStr">
+      <c r="AE46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
-      </c>
-      <c r="AE46" s="92" t="n">
-        <v/>
       </c>
     </row>
     <row r="47">
@@ -11579,76 +11585,76 @@
         <v>12.36</v>
       </c>
       <c r="C47" s="94" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="D47" s="94" t="n">
         <v>10.02</v>
       </c>
-      <c r="D47" s="94" t="n">
+      <c r="E47" s="94" t="n">
         <v>8.960000000000001</v>
-      </c>
-      <c r="E47" s="94" t="n">
-        <v>9.92</v>
       </c>
       <c r="F47" s="94" t="n">
         <v>9.92</v>
       </c>
       <c r="G47" s="94" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="H47" s="94" t="n">
         <v>10.12</v>
       </c>
-      <c r="H47" s="94" t="n">
+      <c r="I47" s="94" t="n">
         <v>9.68</v>
       </c>
-      <c r="I47" s="94" t="n">
+      <c r="J47" s="94" t="n">
         <v>8.34</v>
       </c>
-      <c r="J47" s="94" t="n">
+      <c r="K47" s="94" t="n">
         <v>7.86</v>
-      </c>
-      <c r="K47" s="94" t="n">
-        <v>6.34</v>
       </c>
       <c r="L47" s="94" t="n">
         <v>6.34</v>
       </c>
       <c r="M47" s="94" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="N47" s="94" t="n">
         <v>5.47</v>
       </c>
-      <c r="N47" s="94" t="n">
+      <c r="O47" s="94" t="n">
         <v>5.88</v>
       </c>
-      <c r="O47" s="94" t="n">
+      <c r="P47" s="94" t="n">
         <v>4.03</v>
       </c>
-      <c r="P47" s="94" t="n">
+      <c r="Q47" s="94" t="n">
         <v>3.2</v>
-      </c>
-      <c r="Q47" s="94" t="n">
-        <v>4.34</v>
       </c>
       <c r="R47" s="94" t="n">
         <v>4.34</v>
       </c>
       <c r="S47" s="94" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="T47" s="94" t="n">
         <v>5.76</v>
       </c>
-      <c r="T47" s="94" t="n">
+      <c r="U47" s="94" t="n">
         <v>5.58</v>
       </c>
-      <c r="U47" s="94" t="n">
+      <c r="V47" s="94" t="n">
         <v>6.68</v>
       </c>
-      <c r="V47" s="94" t="n">
+      <c r="W47" s="94" t="n">
         <v>5.82</v>
-      </c>
-      <c r="W47" s="94" t="n">
-        <v>4.11</v>
       </c>
       <c r="X47" s="94" t="n">
         <v>4.11</v>
       </c>
       <c r="Y47" s="94" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="Z47" s="94" t="n">
         <v>5.31</v>
-      </c>
-      <c r="Z47" s="94" t="n">
-        <v>3.88</v>
       </c>
       <c r="AA47" s="94" t="n">
         <v>3.88</v>
@@ -11657,13 +11663,13 @@
         <v>3.88</v>
       </c>
       <c r="AC47" s="94" t="n">
-        <v>4.01</v>
+        <v>3.88</v>
       </c>
       <c r="AD47" s="94" t="n">
         <v>4.01</v>
       </c>
       <c r="AE47" s="94" t="n">
-        <v/>
+        <v>4.01</v>
       </c>
     </row>
     <row r="48">
@@ -11676,76 +11682,76 @@
         <v>22.83</v>
       </c>
       <c r="C48" s="94" t="n">
+        <v>22.83</v>
+      </c>
+      <c r="D48" s="94" t="n">
         <v>23.49</v>
       </c>
-      <c r="D48" s="94" t="n">
+      <c r="E48" s="94" t="n">
         <v>22.74</v>
-      </c>
-      <c r="E48" s="94" t="n">
-        <v>21.14</v>
       </c>
       <c r="F48" s="94" t="n">
         <v>21.14</v>
       </c>
       <c r="G48" s="94" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="H48" s="94" t="n">
         <v>18.41</v>
       </c>
-      <c r="H48" s="94" t="n">
+      <c r="I48" s="94" t="n">
         <v>14.83</v>
       </c>
-      <c r="I48" s="94" t="n">
+      <c r="J48" s="94" t="n">
         <v>14.29</v>
       </c>
-      <c r="J48" s="94" t="n">
+      <c r="K48" s="94" t="n">
         <v>14.57</v>
-      </c>
-      <c r="K48" s="94" t="n">
-        <v>13.5</v>
       </c>
       <c r="L48" s="94" t="n">
         <v>13.5</v>
       </c>
       <c r="M48" s="94" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="N48" s="94" t="n">
         <v>12.88</v>
       </c>
-      <c r="N48" s="94" t="n">
+      <c r="O48" s="94" t="n">
         <v>11.9</v>
       </c>
-      <c r="O48" s="94" t="n">
+      <c r="P48" s="94" t="n">
         <v>9.23</v>
       </c>
-      <c r="P48" s="94" t="n">
+      <c r="Q48" s="94" t="n">
         <v>9.380000000000001</v>
-      </c>
-      <c r="Q48" s="94" t="n">
-        <v>11.24</v>
       </c>
       <c r="R48" s="94" t="n">
         <v>11.24</v>
       </c>
       <c r="S48" s="94" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="T48" s="94" t="n">
         <v>10.69</v>
       </c>
-      <c r="T48" s="94" t="n">
+      <c r="U48" s="94" t="n">
         <v>10.27</v>
       </c>
-      <c r="U48" s="94" t="n">
+      <c r="V48" s="94" t="n">
         <v>9.84</v>
       </c>
-      <c r="V48" s="94" t="n">
+      <c r="W48" s="94" t="n">
         <v>8.74</v>
-      </c>
-      <c r="W48" s="94" t="n">
-        <v>6.18</v>
       </c>
       <c r="X48" s="94" t="n">
         <v>6.18</v>
       </c>
       <c r="Y48" s="94" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="Z48" s="94" t="n">
         <v>8.039999999999999</v>
-      </c>
-      <c r="Z48" s="94" t="n">
-        <v>8.16</v>
       </c>
       <c r="AA48" s="94" t="n">
         <v>8.16</v>
@@ -11754,13 +11760,13 @@
         <v>8.16</v>
       </c>
       <c r="AC48" s="94" t="n">
-        <v>9.59</v>
+        <v>8.16</v>
       </c>
       <c r="AD48" s="94" t="n">
         <v>9.59</v>
       </c>
       <c r="AE48" s="94" t="n">
-        <v/>
+        <v>9.59</v>
       </c>
     </row>
     <row r="49">
@@ -11773,76 +11779,76 @@
         <v>85.23</v>
       </c>
       <c r="C49" s="94" t="n">
+        <v>85.23</v>
+      </c>
+      <c r="D49" s="94" t="n">
         <v>80.29000000000001</v>
       </c>
-      <c r="D49" s="94" t="n">
+      <c r="E49" s="94" t="n">
         <v>75.37</v>
-      </c>
-      <c r="E49" s="94" t="n">
-        <v>89.53</v>
       </c>
       <c r="F49" s="94" t="n">
         <v>89.53</v>
       </c>
       <c r="G49" s="94" t="n">
+        <v>89.53</v>
+      </c>
+      <c r="H49" s="94" t="n">
         <v>91.64</v>
       </c>
-      <c r="H49" s="94" t="n">
+      <c r="I49" s="94" t="n">
         <v>89.73</v>
       </c>
-      <c r="I49" s="94" t="n">
+      <c r="J49" s="94" t="n">
         <v>86.16</v>
       </c>
-      <c r="J49" s="94" t="n">
+      <c r="K49" s="94" t="n">
         <v>85.12</v>
-      </c>
-      <c r="K49" s="94" t="n">
-        <v>83.34999999999999</v>
       </c>
       <c r="L49" s="94" t="n">
         <v>83.34999999999999</v>
       </c>
       <c r="M49" s="94" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="N49" s="94" t="n">
         <v>76.81</v>
       </c>
-      <c r="N49" s="94" t="n">
+      <c r="O49" s="94" t="n">
         <v>74.04000000000001</v>
       </c>
-      <c r="O49" s="94" t="n">
+      <c r="P49" s="94" t="n">
         <v>58.54</v>
       </c>
-      <c r="P49" s="94" t="n">
+      <c r="Q49" s="94" t="n">
         <v>46.37</v>
-      </c>
-      <c r="Q49" s="94" t="n">
-        <v>54.22</v>
       </c>
       <c r="R49" s="94" t="n">
         <v>54.22</v>
       </c>
       <c r="S49" s="94" t="n">
+        <v>54.22</v>
+      </c>
+      <c r="T49" s="94" t="n">
         <v>65.81999999999999</v>
       </c>
-      <c r="T49" s="94" t="n">
+      <c r="U49" s="94" t="n">
         <v>67.31999999999999</v>
       </c>
-      <c r="U49" s="94" t="n">
+      <c r="V49" s="94" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="V49" s="94" t="n">
+      <c r="W49" s="94" t="n">
         <v>62.55</v>
-      </c>
-      <c r="W49" s="94" t="n">
-        <v>39.09</v>
       </c>
       <c r="X49" s="94" t="n">
         <v>39.09</v>
       </c>
       <c r="Y49" s="94" t="n">
+        <v>39.09</v>
+      </c>
+      <c r="Z49" s="94" t="n">
         <v>48.84</v>
-      </c>
-      <c r="Z49" s="94" t="n">
-        <v>35.85</v>
       </c>
       <c r="AA49" s="94" t="n">
         <v>35.85</v>
@@ -11851,13 +11857,13 @@
         <v>35.85</v>
       </c>
       <c r="AC49" s="94" t="n">
-        <v>41.58</v>
+        <v>35.85</v>
       </c>
       <c r="AD49" s="94" t="n">
         <v>41.58</v>
       </c>
       <c r="AE49" s="94" t="n">
-        <v/>
+        <v>41.58</v>
       </c>
     </row>
     <row r="51">
@@ -11870,7 +11876,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:75.39&gt;=73;jp225:RNG120:25.29&gt;=20;vn:RS3:85.3&gt;=85;dax30:RNG60:12.36&gt;=10;dax30:RNG120:22.83&gt;=20</t>
+          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:75.39&gt;=73;vn:RS3:85.3&gt;=85;dax30:RNG60:12.36&gt;=10;dax30:RNG120:22.83&gt;=20</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>6.1</v>
+        <v>7.47</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>6.1</v>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>14.66</v>
+        <v>15.78</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>14.66</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>68.69</v>
+        <v>77.98</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>68.69</v>
@@ -9184,9 +9184,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B26" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C26" s="93" t="inlineStr">
@@ -9342,7 +9342,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>5.51</v>
+        <v>8.77</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>5.51</v>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>19.95</v>
+        <v>21.52</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>19.95</v>
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>44.16</v>
+        <v>53.71</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>44.16</v>
@@ -10686,7 +10686,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-2.54</v>
+        <v>-2.57</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>-4</v>
@@ -10783,7 +10783,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>-3.67</v>
+        <v>-3.7</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>-2.98</v>
@@ -10880,7 +10880,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>48.6</v>
+        <v>48.37</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>45.92</v>
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>6.25</v>
+        <v>7.73</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>6.25</v>
@@ -11231,7 +11231,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>8.289999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>8.289999999999999</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>69.76000000000001</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>69.76000000000001</v>
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>12.36</v>
+        <v>13.89</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>12.36</v>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>22.83</v>
+        <v>22.89</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>22.83</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>85.23</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>85.23</v>
@@ -11876,7 +11876,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:75.39&gt;=73;vn:RS3:85.3&gt;=85;dax30:RNG60:12.36&gt;=10;dax30:RNG120:22.83&gt;=20</t>
+          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:75.39&gt;=73;vn:RS3:85.3&gt;=85;dax30:RNG60:13.89&gt;=10;dax30:RNG120:22.89&gt;=20</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -800,7 +800,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1063,6 +1063,7 @@
     <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6341,152 +6342,152 @@
       </c>
       <c r="B1" s="77" t="inlineStr">
         <is>
+          <t>250203</t>
+        </is>
+      </c>
+      <c r="C1" s="77" t="inlineStr">
+        <is>
+          <t>250202</t>
+        </is>
+      </c>
+      <c r="D1" s="77" t="inlineStr">
+        <is>
+          <t>250201</t>
+        </is>
+      </c>
+      <c r="E1" s="77" t="inlineStr">
+        <is>
+          <t>250131</t>
+        </is>
+      </c>
+      <c r="F1" s="77" t="inlineStr">
+        <is>
           <t>250130</t>
         </is>
       </c>
-      <c r="C1" s="77" t="inlineStr">
+      <c r="G1" s="77" t="inlineStr">
         <is>
           <t>250129</t>
         </is>
       </c>
-      <c r="D1" s="77" t="inlineStr">
+      <c r="H1" s="77" t="inlineStr">
         <is>
           <t>250128</t>
         </is>
       </c>
-      <c r="E1" s="77" t="inlineStr">
+      <c r="I1" s="77" t="inlineStr">
         <is>
           <t>250127</t>
         </is>
       </c>
-      <c r="F1" s="77" t="inlineStr">
+      <c r="J1" s="77" t="inlineStr">
         <is>
           <t>250126</t>
         </is>
       </c>
-      <c r="G1" s="77" t="inlineStr">
+      <c r="K1" s="77" t="inlineStr">
         <is>
           <t>250124</t>
         </is>
       </c>
-      <c r="H1" s="77" t="inlineStr">
+      <c r="L1" s="77" t="inlineStr">
         <is>
           <t>250123</t>
         </is>
       </c>
-      <c r="I1" s="77" t="inlineStr">
+      <c r="M1" s="77" t="inlineStr">
         <is>
           <t>250122</t>
         </is>
       </c>
-      <c r="J1" s="77" t="inlineStr">
+      <c r="N1" s="77" t="inlineStr">
         <is>
           <t>250121</t>
         </is>
       </c>
-      <c r="K1" s="77" t="inlineStr">
+      <c r="O1" s="77" t="inlineStr">
         <is>
           <t>250120</t>
         </is>
       </c>
-      <c r="L1" s="77" t="inlineStr">
+      <c r="P1" s="77" t="inlineStr">
         <is>
           <t>250119</t>
         </is>
       </c>
-      <c r="M1" s="77" t="inlineStr">
+      <c r="Q1" s="77" t="inlineStr">
         <is>
           <t>250117</t>
         </is>
       </c>
-      <c r="N1" s="77" t="inlineStr">
+      <c r="R1" s="77" t="inlineStr">
         <is>
           <t>250116</t>
         </is>
       </c>
-      <c r="O1" s="77" t="inlineStr">
+      <c r="S1" s="77" t="inlineStr">
         <is>
           <t>250115</t>
         </is>
       </c>
-      <c r="P1" s="77" t="inlineStr">
+      <c r="T1" s="77" t="inlineStr">
         <is>
           <t>250114</t>
         </is>
       </c>
-      <c r="Q1" s="77" t="inlineStr">
+      <c r="U1" s="77" t="inlineStr">
         <is>
           <t>250113</t>
         </is>
       </c>
-      <c r="R1" s="77" t="inlineStr">
+      <c r="V1" s="77" t="inlineStr">
         <is>
           <t>250112</t>
         </is>
       </c>
-      <c r="S1" s="77" t="inlineStr">
+      <c r="W1" s="77" t="inlineStr">
         <is>
           <t>250110</t>
         </is>
       </c>
-      <c r="T1" s="77" t="inlineStr">
+      <c r="X1" s="77" t="inlineStr">
         <is>
           <t>250109</t>
         </is>
       </c>
-      <c r="U1" s="77" t="inlineStr">
+      <c r="Y1" s="77" t="inlineStr">
         <is>
           <t>250108</t>
         </is>
       </c>
-      <c r="V1" s="77" t="inlineStr">
+      <c r="Z1" s="77" t="inlineStr">
         <is>
           <t>250107</t>
         </is>
       </c>
-      <c r="W1" s="77" t="inlineStr">
+      <c r="AA1" s="77" t="inlineStr">
         <is>
           <t>250106</t>
         </is>
       </c>
-      <c r="X1" s="77" t="inlineStr">
+      <c r="AB1" s="77" t="inlineStr">
         <is>
           <t>250105</t>
         </is>
       </c>
-      <c r="Y1" s="77" t="inlineStr">
+      <c r="AC1" s="77" t="inlineStr">
         <is>
           <t>250103</t>
         </is>
       </c>
-      <c r="Z1" s="77" t="inlineStr">
+      <c r="AD1" s="77" t="inlineStr">
         <is>
           <t>250102</t>
         </is>
       </c>
-      <c r="AA1" s="77" t="inlineStr">
+      <c r="AE1" s="77" t="inlineStr">
         <is>
           <t>250101</t>
-        </is>
-      </c>
-      <c r="AB1" s="77" t="inlineStr">
-        <is>
-          <t>241231</t>
-        </is>
-      </c>
-      <c r="AC1" s="77" t="inlineStr">
-        <is>
-          <t>241230</t>
-        </is>
-      </c>
-      <c r="AD1" s="77" t="inlineStr">
-        <is>
-          <t>241229</t>
-        </is>
-      </c>
-      <c r="AE1" s="77" t="inlineStr">
-        <is>
-          <t>241227</t>
         </is>
       </c>
     </row>
@@ -6526,125 +6527,123 @@
           <t>red</t>
         </is>
       </c>
-      <c r="H2" s="92" t="inlineStr">
+      <c r="H2" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I2" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J2" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K2" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I2" s="93" t="inlineStr">
+      <c r="M2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J2" s="92" t="inlineStr">
+      <c r="N2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K2" s="92" t="inlineStr">
+      <c r="O2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L2" s="92" t="inlineStr">
+      <c r="P2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M2" s="92" t="inlineStr">
+      <c r="Q2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N2" s="92" t="inlineStr">
+      <c r="R2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O2" s="92" t="inlineStr">
+      <c r="S2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P2" s="92" t="inlineStr">
+      <c r="T2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q2" s="92" t="inlineStr">
+      <c r="U2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R2" s="93" t="inlineStr">
+      <c r="V2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S2" s="93" t="inlineStr">
+      <c r="W2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T2" s="92" t="inlineStr">
+      <c r="X2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U2" s="92" t="inlineStr">
+      <c r="Y2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V2" s="92" t="inlineStr">
+      <c r="Z2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W2" s="93" t="inlineStr">
+      <c r="AA2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X2" s="93" t="inlineStr">
+      <c r="AB2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y2" s="93" t="inlineStr">
+      <c r="AC2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z2" s="93" t="inlineStr">
+      <c r="AD2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC2" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD2" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE2" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
+      <c r="AE2" s="92" t="n">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -6666,82 +6665,82 @@
         <v>-0.65</v>
       </c>
       <c r="F3" s="94" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G3" s="94" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="H3" s="94" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="I3" s="94" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="J3" s="94" t="n">
         <v>-0.83</v>
       </c>
-      <c r="G3" s="94" t="n">
+      <c r="K3" s="94" t="n">
         <v>-0.83</v>
       </c>
-      <c r="H3" s="94" t="n">
+      <c r="L3" s="94" t="n">
         <v>-1.1</v>
       </c>
-      <c r="I3" s="94" t="n">
+      <c r="M3" s="94" t="n">
         <v>-2.21</v>
       </c>
-      <c r="J3" s="94" t="n">
+      <c r="N3" s="94" t="n">
         <v>-2.4</v>
       </c>
-      <c r="K3" s="94" t="n">
+      <c r="O3" s="94" t="n">
         <v>-1.68</v>
       </c>
-      <c r="L3" s="94" t="n">
+      <c r="P3" s="94" t="n">
         <v>-1.17</v>
       </c>
-      <c r="M3" s="94" t="n">
+      <c r="Q3" s="94" t="n">
         <v>-1.17</v>
       </c>
-      <c r="N3" s="94" t="n">
+      <c r="R3" s="94" t="n">
         <v>-2.02</v>
       </c>
-      <c r="O3" s="94" t="n">
+      <c r="S3" s="94" t="n">
         <v>-1.79</v>
       </c>
-      <c r="P3" s="94" t="n">
+      <c r="T3" s="94" t="n">
         <v>-0.83</v>
       </c>
-      <c r="Q3" s="94" t="n">
+      <c r="U3" s="94" t="n">
         <v>-3.09</v>
       </c>
-      <c r="R3" s="94" t="n">
+      <c r="V3" s="94" t="n">
         <v>-0.03</v>
       </c>
-      <c r="S3" s="94" t="n">
+      <c r="W3" s="94" t="n">
         <v>-0.03</v>
       </c>
-      <c r="T3" s="94" t="n">
+      <c r="X3" s="94" t="n">
         <v>0.26</v>
       </c>
-      <c r="U3" s="94" t="n">
+      <c r="Y3" s="94" t="n">
         <v>0.9</v>
       </c>
-      <c r="V3" s="94" t="n">
+      <c r="Z3" s="94" t="n">
         <v>-1.66</v>
       </c>
-      <c r="W3" s="94" t="n">
+      <c r="AA3" s="94" t="n">
         <v>-0.34</v>
       </c>
-      <c r="X3" s="94" t="n">
+      <c r="AB3" s="94" t="n">
         <v>-2.74</v>
       </c>
-      <c r="Y3" s="94" t="n">
+      <c r="AC3" s="94" t="n">
         <v>-2.74</v>
       </c>
-      <c r="Z3" s="94" t="n">
+      <c r="AD3" s="94" t="n">
         <v>0.11</v>
       </c>
-      <c r="AA3" s="94" t="n">
-        <v>-3.95</v>
-      </c>
-      <c r="AB3" s="94" t="n">
-        <v>-3.95</v>
-      </c>
-      <c r="AC3" s="94" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD3" s="94" t="n">
-        <v>10.12</v>
-      </c>
       <c r="AE3" s="94" t="n">
-        <v>10.12</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -6763,82 +6762,82 @@
         <v>10.61</v>
       </c>
       <c r="F4" s="94" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="G4" s="94" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="H4" s="94" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="I4" s="94" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="J4" s="94" t="n">
         <v>12.97</v>
       </c>
-      <c r="G4" s="94" t="n">
+      <c r="K4" s="94" t="n">
         <v>12.97</v>
       </c>
-      <c r="H4" s="94" t="n">
+      <c r="L4" s="94" t="n">
         <v>11.7</v>
       </c>
-      <c r="I4" s="94" t="n">
+      <c r="M4" s="94" t="n">
         <v>11.16</v>
       </c>
-      <c r="J4" s="94" t="n">
+      <c r="N4" s="94" t="n">
         <v>12.33</v>
       </c>
-      <c r="K4" s="94" t="n">
+      <c r="O4" s="94" t="n">
         <v>11.8</v>
       </c>
-      <c r="L4" s="94" t="n">
+      <c r="P4" s="94" t="n">
         <v>11.2</v>
       </c>
-      <c r="M4" s="94" t="n">
+      <c r="Q4" s="94" t="n">
         <v>11.2</v>
       </c>
-      <c r="N4" s="94" t="n">
+      <c r="R4" s="94" t="n">
         <v>9.17</v>
       </c>
-      <c r="O4" s="94" t="n">
+      <c r="S4" s="94" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="P4" s="94" t="n">
+      <c r="T4" s="94" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="Q4" s="94" t="n">
+      <c r="U4" s="94" t="n">
         <v>6.68</v>
       </c>
-      <c r="R4" s="94" t="n">
+      <c r="V4" s="94" t="n">
         <v>6.46</v>
       </c>
-      <c r="S4" s="94" t="n">
+      <c r="W4" s="94" t="n">
         <v>6.46</v>
       </c>
-      <c r="T4" s="94" t="n">
+      <c r="X4" s="94" t="n">
         <v>7.98</v>
       </c>
-      <c r="U4" s="94" t="n">
+      <c r="Y4" s="94" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="V4" s="94" t="n">
+      <c r="Z4" s="94" t="n">
         <v>8.73</v>
       </c>
-      <c r="W4" s="94" t="n">
+      <c r="AA4" s="94" t="n">
         <v>9.1</v>
       </c>
-      <c r="X4" s="94" t="n">
+      <c r="AB4" s="94" t="n">
         <v>8.52</v>
       </c>
-      <c r="Y4" s="94" t="n">
+      <c r="AC4" s="94" t="n">
         <v>8.52</v>
       </c>
-      <c r="Z4" s="94" t="n">
+      <c r="AD4" s="94" t="n">
         <v>11.64</v>
       </c>
-      <c r="AA4" s="94" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="AB4" s="94" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="AC4" s="94" t="n">
-        <v>15.21</v>
-      </c>
-      <c r="AD4" s="94" t="n">
-        <v>14.01</v>
-      </c>
       <c r="AE4" s="94" t="n">
-        <v>14.01</v>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -6860,82 +6859,82 @@
         <v>67.42</v>
       </c>
       <c r="F5" s="94" t="n">
+        <v>67.42</v>
+      </c>
+      <c r="G5" s="94" t="n">
+        <v>67.42</v>
+      </c>
+      <c r="H5" s="94" t="n">
+        <v>67.42</v>
+      </c>
+      <c r="I5" s="94" t="n">
+        <v>67.42</v>
+      </c>
+      <c r="J5" s="94" t="n">
         <v>71.19</v>
       </c>
-      <c r="G5" s="94" t="n">
+      <c r="K5" s="94" t="n">
         <v>71.19</v>
       </c>
-      <c r="H5" s="94" t="n">
+      <c r="L5" s="94" t="n">
         <v>50.98</v>
       </c>
-      <c r="I5" s="94" t="n">
+      <c r="M5" s="94" t="n">
         <v>25.28</v>
       </c>
-      <c r="J5" s="94" t="n">
+      <c r="N5" s="94" t="n">
         <v>65.31999999999999</v>
       </c>
-      <c r="K5" s="94" t="n">
+      <c r="O5" s="94" t="n">
         <v>69.8</v>
       </c>
-      <c r="L5" s="94" t="n">
+      <c r="P5" s="94" t="n">
         <v>67.65000000000001</v>
       </c>
-      <c r="M5" s="94" t="n">
+      <c r="Q5" s="94" t="n">
         <v>67.65000000000001</v>
       </c>
-      <c r="N5" s="94" t="n">
+      <c r="R5" s="94" t="n">
         <v>63.76</v>
       </c>
-      <c r="O5" s="94" t="n">
+      <c r="S5" s="94" t="n">
         <v>58.67</v>
       </c>
-      <c r="P5" s="94" t="n">
+      <c r="T5" s="94" t="n">
         <v>68.65000000000001</v>
       </c>
-      <c r="Q5" s="94" t="n">
+      <c r="U5" s="94" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="R5" s="94" t="n">
+      <c r="V5" s="94" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="S5" s="94" t="n">
+      <c r="W5" s="94" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="T5" s="94" t="n">
+      <c r="X5" s="94" t="n">
         <v>19.81</v>
       </c>
-      <c r="U5" s="94" t="n">
+      <c r="Y5" s="94" t="n">
         <v>29.11</v>
       </c>
-      <c r="V5" s="94" t="n">
+      <c r="Z5" s="94" t="n">
         <v>28.48</v>
       </c>
-      <c r="W5" s="94" t="n">
+      <c r="AA5" s="94" t="n">
         <v>4.01</v>
       </c>
-      <c r="X5" s="94" t="n">
+      <c r="AB5" s="94" t="n">
         <v>4.21</v>
       </c>
-      <c r="Y5" s="94" t="n">
+      <c r="AC5" s="94" t="n">
         <v>4.21</v>
       </c>
-      <c r="Z5" s="94" t="n">
+      <c r="AD5" s="94" t="n">
         <v>6.55</v>
       </c>
-      <c r="AA5" s="94" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="AB5" s="94" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="AC5" s="94" t="n">
-        <v>81.11</v>
-      </c>
-      <c r="AD5" s="94" t="n">
-        <v>73.47</v>
-      </c>
       <c r="AE5" s="94" t="n">
-        <v>73.47</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -6964,135 +6963,133 @@
           <t>green</t>
         </is>
       </c>
-      <c r="F6" s="91" t="inlineStr">
+      <c r="F6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G6" s="91" t="inlineStr">
+      <c r="K6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H6" s="93" t="inlineStr">
+      <c r="L6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I6" s="91" t="inlineStr">
+      <c r="M6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J6" s="91" t="inlineStr">
+      <c r="N6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K6" s="92" t="inlineStr">
+      <c r="O6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L6" s="92" t="inlineStr">
+      <c r="P6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M6" s="92" t="inlineStr">
+      <c r="Q6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N6" s="93" t="inlineStr">
+      <c r="R6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O6" s="91" t="inlineStr">
+      <c r="S6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P6" s="91" t="inlineStr">
+      <c r="T6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q6" s="92" t="inlineStr">
+      <c r="U6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R6" s="92" t="inlineStr">
+      <c r="V6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S6" s="92" t="inlineStr">
+      <c r="W6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T6" s="92" t="inlineStr">
+      <c r="X6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U6" s="92" t="inlineStr">
+      <c r="Y6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V6" s="92" t="inlineStr">
+      <c r="Z6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W6" s="93" t="inlineStr">
+      <c r="AA6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X6" s="93" t="inlineStr">
+      <c r="AB6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y6" s="93" t="inlineStr">
+      <c r="AC6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z6" s="93" t="inlineStr">
+      <c r="AD6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA6" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB6" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC6" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD6" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE6" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
+      <c r="AE6" s="92" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -7114,82 +7111,82 @@
         <v>1.63</v>
       </c>
       <c r="F7" s="94" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G7" s="94" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H7" s="94" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I7" s="94" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J7" s="94" t="n">
         <v>0.55</v>
       </c>
-      <c r="G7" s="94" t="n">
+      <c r="K7" s="94" t="n">
         <v>0.55</v>
       </c>
-      <c r="H7" s="94" t="n">
+      <c r="L7" s="94" t="n">
         <v>0.76</v>
       </c>
-      <c r="I7" s="94" t="n">
+      <c r="M7" s="94" t="n">
         <v>-0</v>
       </c>
-      <c r="J7" s="94" t="n">
+      <c r="N7" s="94" t="n">
         <v>-1.04</v>
       </c>
-      <c r="K7" s="94" t="n">
+      <c r="O7" s="94" t="n">
         <v>-2.32</v>
       </c>
-      <c r="L7" s="94" t="n">
+      <c r="P7" s="94" t="n">
         <v>-1.2</v>
       </c>
-      <c r="M7" s="94" t="n">
+      <c r="Q7" s="94" t="n">
         <v>-1.2</v>
       </c>
-      <c r="N7" s="94" t="n">
+      <c r="R7" s="94" t="n">
         <v>-2.32</v>
       </c>
-      <c r="O7" s="94" t="n">
+      <c r="S7" s="94" t="n">
         <v>-0.83</v>
       </c>
-      <c r="P7" s="94" t="n">
+      <c r="T7" s="94" t="n">
         <v>-1.86</v>
       </c>
-      <c r="Q7" s="94" t="n">
+      <c r="U7" s="94" t="n">
         <v>-2.7</v>
       </c>
-      <c r="R7" s="94" t="n">
+      <c r="V7" s="94" t="n">
         <v>8.130000000000001</v>
       </c>
-      <c r="S7" s="94" t="n">
+      <c r="W7" s="94" t="n">
         <v>8.130000000000001</v>
       </c>
-      <c r="T7" s="94" t="n">
+      <c r="X7" s="94" t="n">
         <v>9.789999999999999</v>
       </c>
-      <c r="U7" s="94" t="n">
+      <c r="Y7" s="94" t="n">
         <v>7.38</v>
       </c>
-      <c r="V7" s="94" t="n">
+      <c r="Z7" s="94" t="n">
         <v>4.27</v>
       </c>
-      <c r="W7" s="94" t="n">
+      <c r="AA7" s="94" t="n">
         <v>4.43</v>
       </c>
-      <c r="X7" s="94" t="n">
+      <c r="AB7" s="94" t="n">
         <v>-1.29</v>
       </c>
-      <c r="Y7" s="94" t="n">
+      <c r="AC7" s="94" t="n">
         <v>-1.29</v>
       </c>
-      <c r="Z7" s="94" t="n">
+      <c r="AD7" s="94" t="n">
         <v>-4.26</v>
       </c>
-      <c r="AA7" s="94" t="n">
-        <v>-3.42</v>
-      </c>
-      <c r="AB7" s="94" t="n">
-        <v>-3.42</v>
-      </c>
-      <c r="AC7" s="94" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD7" s="94" t="n">
-        <v>37.64</v>
-      </c>
       <c r="AE7" s="94" t="n">
-        <v>37.64</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -7211,82 +7208,82 @@
         <v>28.48</v>
       </c>
       <c r="F8" s="94" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="G8" s="94" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="H8" s="94" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="I8" s="94" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="J8" s="94" t="n">
         <v>37.3</v>
       </c>
-      <c r="G8" s="94" t="n">
+      <c r="K8" s="94" t="n">
         <v>37.3</v>
       </c>
-      <c r="H8" s="94" t="n">
+      <c r="L8" s="94" t="n">
         <v>36.53</v>
       </c>
-      <c r="I8" s="94" t="n">
+      <c r="M8" s="94" t="n">
         <v>35.49</v>
       </c>
-      <c r="J8" s="94" t="n">
+      <c r="N8" s="94" t="n">
         <v>36.76</v>
       </c>
-      <c r="K8" s="94" t="n">
+      <c r="O8" s="94" t="n">
         <v>35.74</v>
       </c>
-      <c r="L8" s="94" t="n">
+      <c r="P8" s="94" t="n">
         <v>33.95</v>
       </c>
-      <c r="M8" s="94" t="n">
+      <c r="Q8" s="94" t="n">
         <v>33.95</v>
       </c>
-      <c r="N8" s="94" t="n">
+      <c r="R8" s="94" t="n">
         <v>27.18</v>
       </c>
-      <c r="O8" s="94" t="n">
+      <c r="S8" s="94" t="n">
         <v>30.45</v>
       </c>
-      <c r="P8" s="94" t="n">
+      <c r="T8" s="94" t="n">
         <v>33.5</v>
       </c>
-      <c r="Q8" s="94" t="n">
+      <c r="U8" s="94" t="n">
         <v>30.62</v>
       </c>
-      <c r="R8" s="94" t="n">
+      <c r="V8" s="94" t="n">
         <v>29.85</v>
       </c>
-      <c r="S8" s="94" t="n">
+      <c r="W8" s="94" t="n">
         <v>29.85</v>
       </c>
-      <c r="T8" s="94" t="n">
+      <c r="X8" s="94" t="n">
         <v>34.31</v>
       </c>
-      <c r="U8" s="94" t="n">
+      <c r="Y8" s="94" t="n">
         <v>34.35</v>
       </c>
-      <c r="V8" s="94" t="n">
+      <c r="Z8" s="94" t="n">
         <v>34.47</v>
       </c>
-      <c r="W8" s="94" t="n">
+      <c r="AA8" s="94" t="n">
         <v>32.14</v>
       </c>
-      <c r="X8" s="94" t="n">
+      <c r="AB8" s="94" t="n">
         <v>32.67</v>
       </c>
-      <c r="Y8" s="94" t="n">
+      <c r="AC8" s="94" t="n">
         <v>32.67</v>
       </c>
-      <c r="Z8" s="94" t="n">
+      <c r="AD8" s="94" t="n">
         <v>37.96</v>
       </c>
-      <c r="AA8" s="94" t="n">
-        <v>41.51</v>
-      </c>
-      <c r="AB8" s="94" t="n">
-        <v>41.51</v>
-      </c>
-      <c r="AC8" s="94" t="n">
-        <v>47.84</v>
-      </c>
-      <c r="AD8" s="94" t="n">
-        <v>45.14</v>
-      </c>
       <c r="AE8" s="94" t="n">
-        <v>45.14</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -7308,82 +7305,82 @@
         <v>35.78</v>
       </c>
       <c r="F9" s="94" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="G9" s="94" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="H9" s="94" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="I9" s="94" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="J9" s="94" t="n">
         <v>56.52</v>
       </c>
-      <c r="G9" s="94" t="n">
+      <c r="K9" s="94" t="n">
         <v>56.52</v>
       </c>
-      <c r="H9" s="94" t="n">
+      <c r="L9" s="94" t="n">
         <v>45.32</v>
       </c>
-      <c r="I9" s="94" t="n">
+      <c r="M9" s="94" t="n">
         <v>57.96</v>
       </c>
-      <c r="J9" s="94" t="n">
+      <c r="N9" s="94" t="n">
         <v>59.34</v>
       </c>
-      <c r="K9" s="94" t="n">
+      <c r="O9" s="94" t="n">
         <v>51.65</v>
       </c>
-      <c r="L9" s="94" t="n">
+      <c r="P9" s="94" t="n">
         <v>49.39</v>
       </c>
-      <c r="M9" s="94" t="n">
+      <c r="Q9" s="94" t="n">
         <v>49.39</v>
       </c>
-      <c r="N9" s="94" t="n">
+      <c r="R9" s="94" t="n">
         <v>40.47</v>
       </c>
-      <c r="O9" s="94" t="n">
+      <c r="S9" s="94" t="n">
         <v>59.12</v>
       </c>
-      <c r="P9" s="94" t="n">
+      <c r="T9" s="94" t="n">
         <v>63.67</v>
       </c>
-      <c r="Q9" s="94" t="n">
+      <c r="U9" s="94" t="n">
         <v>34.88</v>
       </c>
-      <c r="R9" s="94" t="n">
+      <c r="V9" s="94" t="n">
         <v>32.56</v>
       </c>
-      <c r="S9" s="94" t="n">
+      <c r="W9" s="94" t="n">
         <v>32.56</v>
       </c>
-      <c r="T9" s="94" t="n">
+      <c r="X9" s="94" t="n">
         <v>40.33</v>
       </c>
-      <c r="U9" s="94" t="n">
+      <c r="Y9" s="94" t="n">
         <v>43.12</v>
       </c>
-      <c r="V9" s="94" t="n">
+      <c r="Z9" s="94" t="n">
         <v>43.39</v>
       </c>
-      <c r="W9" s="94" t="n">
+      <c r="AA9" s="94" t="n">
         <v>16.15</v>
       </c>
-      <c r="X9" s="94" t="n">
+      <c r="AB9" s="94" t="n">
         <v>16.9</v>
       </c>
-      <c r="Y9" s="94" t="n">
+      <c r="AC9" s="94" t="n">
         <v>16.9</v>
       </c>
-      <c r="Z9" s="94" t="n">
+      <c r="AD9" s="94" t="n">
         <v>20.18</v>
       </c>
-      <c r="AA9" s="94" t="n">
-        <v>32.85</v>
-      </c>
-      <c r="AB9" s="94" t="n">
-        <v>32.85</v>
-      </c>
-      <c r="AC9" s="94" t="n">
-        <v>62.46</v>
-      </c>
-      <c r="AD9" s="94" t="n">
-        <v>60.63</v>
-      </c>
       <c r="AE9" s="94" t="n">
-        <v>60.63</v>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -7412,135 +7409,133 @@
           <t>green</t>
         </is>
       </c>
-      <c r="F10" s="91" t="inlineStr">
+      <c r="F10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G10" s="91" t="inlineStr">
+      <c r="K10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H10" s="91" t="inlineStr">
+      <c r="L10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I10" s="91" t="inlineStr">
+      <c r="M10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J10" s="91" t="inlineStr">
+      <c r="N10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K10" s="91" t="inlineStr">
+      <c r="O10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L10" s="91" t="inlineStr">
+      <c r="P10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M10" s="91" t="inlineStr">
+      <c r="Q10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N10" s="92" t="inlineStr">
+      <c r="R10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O10" s="92" t="inlineStr">
+      <c r="S10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P10" s="91" t="inlineStr">
+      <c r="T10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q10" s="92" t="inlineStr">
+      <c r="U10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R10" s="92" t="inlineStr">
+      <c r="V10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S10" s="92" t="inlineStr">
+      <c r="W10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T10" s="92" t="inlineStr">
+      <c r="X10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U10" s="92" t="inlineStr">
+      <c r="Y10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V10" s="92" t="inlineStr">
+      <c r="Z10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W10" s="93" t="inlineStr">
+      <c r="AA10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X10" s="93" t="inlineStr">
+      <c r="AB10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y10" s="93" t="inlineStr">
+      <c r="AC10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z10" s="93" t="inlineStr">
+      <c r="AD10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC10" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD10" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE10" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
+      <c r="AE10" s="92" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -7562,82 +7557,82 @@
         <v>-2.82</v>
       </c>
       <c r="F11" s="94" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="G11" s="94" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="H11" s="94" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="I11" s="94" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="J11" s="94" t="n">
         <v>-1.97</v>
       </c>
-      <c r="G11" s="94" t="n">
+      <c r="K11" s="94" t="n">
         <v>-1.97</v>
       </c>
-      <c r="H11" s="94" t="n">
+      <c r="L11" s="94" t="n">
         <v>-2.71</v>
       </c>
-      <c r="I11" s="94" t="n">
+      <c r="M11" s="94" t="n">
         <v>-3.5</v>
       </c>
-      <c r="J11" s="94" t="n">
+      <c r="N11" s="94" t="n">
         <v>-5.24</v>
       </c>
-      <c r="K11" s="94" t="n">
+      <c r="O11" s="94" t="n">
         <v>-5.99</v>
       </c>
-      <c r="L11" s="94" t="n">
+      <c r="P11" s="94" t="n">
         <v>-4.96</v>
       </c>
-      <c r="M11" s="94" t="n">
+      <c r="Q11" s="94" t="n">
         <v>-4.96</v>
       </c>
-      <c r="N11" s="94" t="n">
+      <c r="R11" s="94" t="n">
         <v>-6.98</v>
       </c>
-      <c r="O11" s="94" t="n">
+      <c r="S11" s="94" t="n">
         <v>-8.08</v>
       </c>
-      <c r="P11" s="94" t="n">
+      <c r="T11" s="94" t="n">
         <v>-6.09</v>
       </c>
-      <c r="Q11" s="94" t="n">
+      <c r="U11" s="94" t="n">
         <v>-9.69</v>
       </c>
-      <c r="R11" s="94" t="n">
+      <c r="V11" s="94" t="n">
         <v>-2.86</v>
       </c>
-      <c r="S11" s="94" t="n">
+      <c r="W11" s="94" t="n">
         <v>-2.86</v>
       </c>
-      <c r="T11" s="94" t="n">
+      <c r="X11" s="94" t="n">
         <v>-1.44</v>
       </c>
-      <c r="U11" s="94" t="n">
+      <c r="Y11" s="94" t="n">
         <v>-3.72</v>
       </c>
-      <c r="V11" s="94" t="n">
+      <c r="Z11" s="94" t="n">
         <v>-5.89</v>
       </c>
-      <c r="W11" s="94" t="n">
+      <c r="AA11" s="94" t="n">
         <v>-4.13</v>
       </c>
-      <c r="X11" s="94" t="n">
+      <c r="AB11" s="94" t="n">
         <v>-8.9</v>
       </c>
-      <c r="Y11" s="94" t="n">
+      <c r="AC11" s="94" t="n">
         <v>-8.9</v>
       </c>
-      <c r="Z11" s="94" t="n">
+      <c r="AD11" s="94" t="n">
         <v>-9.630000000000001</v>
       </c>
-      <c r="AA11" s="94" t="n">
-        <v>-16.02</v>
-      </c>
-      <c r="AB11" s="94" t="n">
-        <v>-16.02</v>
-      </c>
-      <c r="AC11" s="94" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD11" s="94" t="n">
-        <v>16.94</v>
-      </c>
       <c r="AE11" s="94" t="n">
-        <v>16.94</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -7659,82 +7654,82 @@
         <v>22.25</v>
       </c>
       <c r="F12" s="94" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="G12" s="94" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="H12" s="94" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="I12" s="94" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="J12" s="94" t="n">
         <v>30.1</v>
       </c>
-      <c r="G12" s="94" t="n">
+      <c r="K12" s="94" t="n">
         <v>30.1</v>
       </c>
-      <c r="H12" s="94" t="n">
+      <c r="L12" s="94" t="n">
         <v>27.98</v>
       </c>
-      <c r="I12" s="94" t="n">
+      <c r="M12" s="94" t="n">
         <v>26.6</v>
       </c>
-      <c r="J12" s="94" t="n">
+      <c r="N12" s="94" t="n">
         <v>28.46</v>
       </c>
-      <c r="K12" s="94" t="n">
+      <c r="O12" s="94" t="n">
         <v>27.49</v>
       </c>
-      <c r="L12" s="94" t="n">
+      <c r="P12" s="94" t="n">
         <v>23.68</v>
       </c>
-      <c r="M12" s="94" t="n">
+      <c r="Q12" s="94" t="n">
         <v>23.68</v>
       </c>
-      <c r="N12" s="94" t="n">
+      <c r="R12" s="94" t="n">
         <v>18.99</v>
       </c>
-      <c r="O12" s="94" t="n">
+      <c r="S12" s="94" t="n">
         <v>18.11</v>
       </c>
-      <c r="P12" s="94" t="n">
+      <c r="T12" s="94" t="n">
         <v>20.84</v>
       </c>
-      <c r="Q12" s="94" t="n">
+      <c r="U12" s="94" t="n">
         <v>16.86</v>
       </c>
-      <c r="R12" s="94" t="n">
+      <c r="V12" s="94" t="n">
         <v>16.44</v>
       </c>
-      <c r="S12" s="94" t="n">
+      <c r="W12" s="94" t="n">
         <v>16.44</v>
       </c>
-      <c r="T12" s="94" t="n">
+      <c r="X12" s="94" t="n">
         <v>20.18</v>
       </c>
-      <c r="U12" s="94" t="n">
+      <c r="Y12" s="94" t="n">
         <v>19.29</v>
       </c>
-      <c r="V12" s="94" t="n">
+      <c r="Z12" s="94" t="n">
         <v>20.37</v>
       </c>
-      <c r="W12" s="94" t="n">
+      <c r="AA12" s="94" t="n">
         <v>21.99</v>
       </c>
-      <c r="X12" s="94" t="n">
+      <c r="AB12" s="94" t="n">
         <v>22.02</v>
       </c>
-      <c r="Y12" s="94" t="n">
+      <c r="AC12" s="94" t="n">
         <v>22.02</v>
       </c>
-      <c r="Z12" s="94" t="n">
+      <c r="AD12" s="94" t="n">
         <v>26.5</v>
       </c>
-      <c r="AA12" s="94" t="n">
-        <v>29.36</v>
-      </c>
-      <c r="AB12" s="94" t="n">
-        <v>29.36</v>
-      </c>
-      <c r="AC12" s="94" t="n">
-        <v>33.94</v>
-      </c>
-      <c r="AD12" s="94" t="n">
-        <v>32.82</v>
-      </c>
       <c r="AE12" s="94" t="n">
-        <v>32.82</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -7756,82 +7751,82 @@
         <v>31.12</v>
       </c>
       <c r="F13" s="94" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="G13" s="94" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="H13" s="94" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="I13" s="94" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="J13" s="94" t="n">
         <v>77.11</v>
       </c>
-      <c r="G13" s="94" t="n">
+      <c r="K13" s="94" t="n">
         <v>77.11</v>
       </c>
-      <c r="H13" s="94" t="n">
+      <c r="L13" s="94" t="n">
         <v>55.59</v>
       </c>
-      <c r="I13" s="94" t="n">
+      <c r="M13" s="94" t="n">
         <v>66.94</v>
       </c>
-      <c r="J13" s="94" t="n">
+      <c r="N13" s="94" t="n">
         <v>83.7</v>
       </c>
-      <c r="K13" s="94" t="n">
+      <c r="O13" s="94" t="n">
         <v>81.64</v>
       </c>
-      <c r="L13" s="94" t="n">
+      <c r="P13" s="94" t="n">
         <v>68.69</v>
       </c>
-      <c r="M13" s="94" t="n">
+      <c r="Q13" s="94" t="n">
         <v>68.69</v>
       </c>
-      <c r="N13" s="94" t="n">
+      <c r="R13" s="94" t="n">
         <v>60.87</v>
       </c>
-      <c r="O13" s="94" t="n">
+      <c r="S13" s="94" t="n">
         <v>54.48</v>
       </c>
-      <c r="P13" s="94" t="n">
+      <c r="T13" s="94" t="n">
         <v>78.59</v>
       </c>
-      <c r="Q13" s="94" t="n">
+      <c r="U13" s="94" t="n">
         <v>21.44</v>
       </c>
-      <c r="R13" s="94" t="n">
+      <c r="V13" s="94" t="n">
         <v>9.02</v>
       </c>
-      <c r="S13" s="94" t="n">
+      <c r="W13" s="94" t="n">
         <v>9.02</v>
       </c>
-      <c r="T13" s="94" t="n">
+      <c r="X13" s="94" t="n">
         <v>18.81</v>
       </c>
-      <c r="U13" s="94" t="n">
+      <c r="Y13" s="94" t="n">
         <v>14.94</v>
       </c>
-      <c r="V13" s="94" t="n">
+      <c r="Z13" s="94" t="n">
         <v>20.9</v>
       </c>
-      <c r="W13" s="94" t="n">
+      <c r="AA13" s="94" t="n">
         <v>2.46</v>
       </c>
-      <c r="X13" s="94" t="n">
+      <c r="AB13" s="94" t="n">
         <v>2.51</v>
       </c>
-      <c r="Y13" s="94" t="n">
+      <c r="AC13" s="94" t="n">
         <v>2.51</v>
       </c>
-      <c r="Z13" s="94" t="n">
+      <c r="AD13" s="94" t="n">
         <v>3.75</v>
       </c>
-      <c r="AA13" s="94" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="AB13" s="94" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="AC13" s="94" t="n">
-        <v>49.72</v>
-      </c>
-      <c r="AD13" s="94" t="n">
-        <v>46.46</v>
-      </c>
       <c r="AE13" s="94" t="n">
-        <v>46.46</v>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -7840,155 +7835,153 @@
           <t>hk50:EIDE</t>
         </is>
       </c>
-      <c r="B14" s="91" t="inlineStr">
+      <c r="B14" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="C14" s="91" t="inlineStr">
+      <c r="D14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D14" s="91" t="inlineStr">
+      <c r="E14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E14" s="91" t="inlineStr">
+      <c r="F14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F14" s="91" t="inlineStr">
+      <c r="G14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G14" s="91" t="inlineStr">
+      <c r="H14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H14" s="92" t="inlineStr">
+      <c r="I14" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J14" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K14" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I14" s="92" t="inlineStr">
+      <c r="M14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J14" s="91" t="inlineStr">
+      <c r="N14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K14" s="91" t="inlineStr">
+      <c r="O14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L14" s="91" t="inlineStr">
+      <c r="P14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M14" s="91" t="inlineStr">
+      <c r="Q14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N14" s="91" t="inlineStr">
+      <c r="R14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O14" s="92" t="inlineStr">
+      <c r="S14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P14" s="92" t="inlineStr">
+      <c r="T14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q14" s="93" t="inlineStr">
+      <c r="U14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R14" s="93" t="inlineStr">
+      <c r="V14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S14" s="93" t="inlineStr">
+      <c r="W14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T14" s="93" t="inlineStr">
+      <c r="X14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U14" s="93" t="inlineStr">
+      <c r="Y14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V14" s="93" t="inlineStr">
+      <c r="Z14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W14" s="93" t="inlineStr">
+      <c r="AA14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X14" s="93" t="inlineStr">
+      <c r="AB14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y14" s="93" t="inlineStr">
+      <c r="AC14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z14" s="93" t="inlineStr">
+      <c r="AD14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA14" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB14" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC14" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD14" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE14" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
+      <c r="AE14" s="92" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -7998,7 +7991,7 @@
         </is>
       </c>
       <c r="B15" s="94" t="n">
-        <v>-0.45</v>
+        <v>-1.41</v>
       </c>
       <c r="C15" s="94" t="n">
         <v>-0.45</v>
@@ -8007,85 +8000,85 @@
         <v>-0.45</v>
       </c>
       <c r="E15" s="94" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="F15" s="94" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="G15" s="94" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="H15" s="94" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="I15" s="94" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F15" s="94" t="n">
+      <c r="J15" s="94" t="n">
         <v>-3.07</v>
       </c>
-      <c r="G15" s="94" t="n">
+      <c r="K15" s="94" t="n">
         <v>-3.07</v>
       </c>
-      <c r="H15" s="94" t="n">
+      <c r="L15" s="94" t="n">
         <v>-4.36</v>
       </c>
-      <c r="I15" s="94" t="n">
+      <c r="M15" s="94" t="n">
         <v>-3.94</v>
       </c>
-      <c r="J15" s="94" t="n">
+      <c r="N15" s="94" t="n">
         <v>-1.87</v>
       </c>
-      <c r="K15" s="94" t="n">
+      <c r="O15" s="94" t="n">
         <v>-4.02</v>
       </c>
-      <c r="L15" s="94" t="n">
+      <c r="P15" s="94" t="n">
         <v>-4.46</v>
       </c>
-      <c r="M15" s="94" t="n">
+      <c r="Q15" s="94" t="n">
         <v>-4.46</v>
       </c>
-      <c r="N15" s="94" t="n">
+      <c r="R15" s="94" t="n">
         <v>-4.67</v>
       </c>
-      <c r="O15" s="94" t="n">
+      <c r="S15" s="94" t="n">
         <v>-7.3</v>
       </c>
-      <c r="P15" s="94" t="n">
+      <c r="T15" s="94" t="n">
         <v>-4.28</v>
       </c>
-      <c r="Q15" s="94" t="n">
+      <c r="U15" s="94" t="n">
         <v>-6.96</v>
       </c>
-      <c r="R15" s="94" t="n">
+      <c r="V15" s="94" t="n">
         <v>-6.17</v>
       </c>
-      <c r="S15" s="94" t="n">
+      <c r="W15" s="94" t="n">
         <v>-6.17</v>
       </c>
-      <c r="T15" s="94" t="n">
+      <c r="X15" s="94" t="n">
         <v>-8.779999999999999</v>
       </c>
-      <c r="U15" s="94" t="n">
+      <c r="Y15" s="94" t="n">
         <v>-9.279999999999999</v>
       </c>
-      <c r="V15" s="94" t="n">
+      <c r="Z15" s="94" t="n">
         <v>-5.76</v>
       </c>
-      <c r="W15" s="94" t="n">
+      <c r="AA15" s="94" t="n">
         <v>-5.92</v>
       </c>
-      <c r="X15" s="94" t="n">
+      <c r="AB15" s="94" t="n">
         <v>-14.46</v>
       </c>
-      <c r="Y15" s="94" t="n">
+      <c r="AC15" s="94" t="n">
         <v>-14.46</v>
       </c>
-      <c r="Z15" s="94" t="n">
+      <c r="AD15" s="94" t="n">
         <v>-13.69</v>
       </c>
-      <c r="AA15" s="94" t="n">
-        <v>-9.289999999999999</v>
-      </c>
-      <c r="AB15" s="94" t="n">
-        <v>-9.289999999999999</v>
-      </c>
-      <c r="AC15" s="94" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="AD15" s="94" t="n">
-        <v>-4.94</v>
-      </c>
       <c r="AE15" s="94" t="n">
-        <v>-4.94</v>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -8095,7 +8088,7 @@
         </is>
       </c>
       <c r="B16" s="94" t="n">
-        <v>19.35</v>
+        <v>21.07</v>
       </c>
       <c r="C16" s="94" t="n">
         <v>19.35</v>
@@ -8104,85 +8097,85 @@
         <v>19.35</v>
       </c>
       <c r="E16" s="94" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="F16" s="94" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="G16" s="94" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="H16" s="94" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="I16" s="94" t="n">
         <v>16.72</v>
       </c>
-      <c r="F16" s="94" t="n">
+      <c r="J16" s="94" t="n">
         <v>15.69</v>
       </c>
-      <c r="G16" s="94" t="n">
+      <c r="K16" s="94" t="n">
         <v>15.69</v>
       </c>
-      <c r="H16" s="94" t="n">
+      <c r="L16" s="94" t="n">
         <v>15.87</v>
       </c>
-      <c r="I16" s="94" t="n">
+      <c r="M16" s="94" t="n">
         <v>14.74</v>
       </c>
-      <c r="J16" s="94" t="n">
+      <c r="N16" s="94" t="n">
         <v>18.13</v>
       </c>
-      <c r="K16" s="94" t="n">
+      <c r="O16" s="94" t="n">
         <v>17.18</v>
       </c>
-      <c r="L16" s="94" t="n">
+      <c r="P16" s="94" t="n">
         <v>13.13</v>
       </c>
-      <c r="M16" s="94" t="n">
+      <c r="Q16" s="94" t="n">
         <v>13.13</v>
       </c>
-      <c r="N16" s="94" t="n">
+      <c r="R16" s="94" t="n">
         <v>11.76</v>
       </c>
-      <c r="O16" s="94" t="n">
+      <c r="S16" s="94" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="P16" s="94" t="n">
+      <c r="T16" s="94" t="n">
         <v>10.35</v>
       </c>
-      <c r="Q16" s="94" t="n">
+      <c r="U16" s="94" t="n">
         <v>6.16</v>
       </c>
-      <c r="R16" s="94" t="n">
+      <c r="V16" s="94" t="n">
         <v>7.47</v>
       </c>
-      <c r="S16" s="94" t="n">
+      <c r="W16" s="94" t="n">
         <v>7.47</v>
       </c>
-      <c r="T16" s="94" t="n">
+      <c r="X16" s="94" t="n">
         <v>8.529999999999999</v>
       </c>
-      <c r="U16" s="94" t="n">
+      <c r="Y16" s="94" t="n">
         <v>7.02</v>
       </c>
-      <c r="V16" s="94" t="n">
+      <c r="Z16" s="94" t="n">
         <v>6.31</v>
       </c>
-      <c r="W16" s="94" t="n">
+      <c r="AA16" s="94" t="n">
         <v>10.41</v>
       </c>
-      <c r="X16" s="94" t="n">
+      <c r="AB16" s="94" t="n">
         <v>13.1</v>
       </c>
-      <c r="Y16" s="94" t="n">
+      <c r="AC16" s="94" t="n">
         <v>13.1</v>
       </c>
-      <c r="Z16" s="94" t="n">
+      <c r="AD16" s="94" t="n">
         <v>11.98</v>
       </c>
-      <c r="AA16" s="94" t="n">
-        <v>14.47</v>
-      </c>
-      <c r="AB16" s="94" t="n">
-        <v>14.47</v>
-      </c>
-      <c r="AC16" s="94" t="n">
-        <v>12.59</v>
-      </c>
-      <c r="AD16" s="94" t="n">
-        <v>11.44</v>
-      </c>
       <c r="AE16" s="94" t="n">
-        <v>11.44</v>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -8192,7 +8185,7 @@
         </is>
       </c>
       <c r="B17" s="94" t="n">
-        <v>75.39</v>
+        <v>74.2</v>
       </c>
       <c r="C17" s="94" t="n">
         <v>75.39</v>
@@ -8201,85 +8194,85 @@
         <v>75.39</v>
       </c>
       <c r="E17" s="94" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="F17" s="94" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="G17" s="94" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="H17" s="94" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="I17" s="94" t="n">
         <v>74.31</v>
       </c>
-      <c r="F17" s="94" t="n">
+      <c r="J17" s="94" t="n">
         <v>69.52</v>
       </c>
-      <c r="G17" s="94" t="n">
+      <c r="K17" s="94" t="n">
         <v>69.52</v>
       </c>
-      <c r="H17" s="94" t="n">
+      <c r="L17" s="94" t="n">
         <v>50.12</v>
       </c>
-      <c r="I17" s="94" t="n">
+      <c r="M17" s="94" t="n">
         <v>55.82</v>
       </c>
-      <c r="J17" s="94" t="n">
+      <c r="N17" s="94" t="n">
         <v>86.87</v>
       </c>
-      <c r="K17" s="94" t="n">
+      <c r="O17" s="94" t="n">
         <v>82.95</v>
       </c>
-      <c r="L17" s="94" t="n">
+      <c r="P17" s="94" t="n">
         <v>70.41</v>
       </c>
-      <c r="M17" s="94" t="n">
+      <c r="Q17" s="94" t="n">
         <v>70.41</v>
       </c>
-      <c r="N17" s="94" t="n">
+      <c r="R17" s="94" t="n">
         <v>67.17</v>
       </c>
-      <c r="O17" s="94" t="n">
+      <c r="S17" s="94" t="n">
         <v>51.86</v>
       </c>
-      <c r="P17" s="94" t="n">
+      <c r="T17" s="94" t="n">
         <v>46.63</v>
       </c>
-      <c r="Q17" s="94" t="n">
+      <c r="U17" s="94" t="n">
         <v>7.26</v>
       </c>
-      <c r="R17" s="94" t="n">
+      <c r="V17" s="94" t="n">
         <v>10.43</v>
       </c>
-      <c r="S17" s="94" t="n">
+      <c r="W17" s="94" t="n">
         <v>10.43</v>
       </c>
-      <c r="T17" s="94" t="n">
+      <c r="X17" s="94" t="n">
         <v>15.01</v>
       </c>
-      <c r="U17" s="94" t="n">
+      <c r="Y17" s="94" t="n">
         <v>16.18</v>
       </c>
-      <c r="V17" s="94" t="n">
+      <c r="Z17" s="94" t="n">
         <v>21.65</v>
       </c>
-      <c r="W17" s="94" t="n">
+      <c r="AA17" s="94" t="n">
         <v>34.02</v>
       </c>
-      <c r="X17" s="94" t="n">
+      <c r="AB17" s="94" t="n">
         <v>39.01</v>
       </c>
-      <c r="Y17" s="94" t="n">
+      <c r="AC17" s="94" t="n">
         <v>39.01</v>
       </c>
-      <c r="Z17" s="94" t="n">
+      <c r="AD17" s="94" t="n">
         <v>22.83</v>
       </c>
-      <c r="AA17" s="94" t="n">
-        <v>62.48</v>
-      </c>
-      <c r="AB17" s="94" t="n">
-        <v>62.48</v>
-      </c>
-      <c r="AC17" s="94" t="n">
-        <v>60.29</v>
-      </c>
-      <c r="AD17" s="94" t="n">
-        <v>68.20999999999999</v>
-      </c>
       <c r="AE17" s="94" t="n">
-        <v>68.20999999999999</v>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -8288,155 +8281,153 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="92" t="inlineStr">
+      <c r="B18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C18" s="92" t="inlineStr">
+      <c r="D18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D18" s="92" t="inlineStr">
+      <c r="E18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E18" s="92" t="inlineStr">
+      <c r="F18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F18" s="91" t="inlineStr">
+      <c r="G18" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H18" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I18" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G18" s="91" t="inlineStr">
+      <c r="K18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H18" s="91" t="inlineStr">
+      <c r="L18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I18" s="91" t="inlineStr">
+      <c r="M18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J18" s="91" t="inlineStr">
+      <c r="N18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K18" s="91" t="inlineStr">
+      <c r="O18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L18" s="91" t="inlineStr">
+      <c r="P18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M18" s="91" t="inlineStr">
+      <c r="Q18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N18" s="91" t="inlineStr">
+      <c r="R18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O18" s="91" t="inlineStr">
+      <c r="S18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P18" s="92" t="inlineStr">
+      <c r="T18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q18" s="93" t="inlineStr">
+      <c r="U18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R18" s="93" t="inlineStr">
+      <c r="V18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S18" s="93" t="inlineStr">
+      <c r="W18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T18" s="92" t="inlineStr">
+      <c r="X18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U18" s="92" t="inlineStr">
+      <c r="Y18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V18" s="93" t="inlineStr">
+      <c r="Z18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W18" s="91" t="inlineStr">
+      <c r="AA18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X18" s="92" t="inlineStr">
+      <c r="AB18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y18" s="92" t="inlineStr">
+      <c r="AC18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z18" s="93" t="inlineStr">
+      <c r="AD18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA18" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB18" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC18" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD18" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE18" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
+      <c r="AE18" s="92" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -8446,94 +8437,94 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="C19" s="94" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="D19" s="94" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="E19" s="94" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="F19" s="94" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="G19" s="94" t="n">
         <v>3.88</v>
       </c>
-      <c r="C19" s="94" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="D19" s="94" t="n">
+      <c r="H19" s="94" t="n">
         <v>4.03</v>
       </c>
-      <c r="E19" s="94" t="n">
+      <c r="I19" s="94" t="n">
         <v>3.24</v>
       </c>
-      <c r="F19" s="94" t="n">
+      <c r="J19" s="94" t="n">
         <v>5.05</v>
       </c>
-      <c r="G19" s="94" t="n">
+      <c r="K19" s="94" t="n">
         <v>5.05</v>
       </c>
-      <c r="H19" s="94" t="n">
+      <c r="L19" s="94" t="n">
         <v>5.32</v>
       </c>
-      <c r="I19" s="94" t="n">
+      <c r="M19" s="94" t="n">
         <v>4.98</v>
       </c>
-      <c r="J19" s="94" t="n">
+      <c r="N19" s="94" t="n">
         <v>3.38</v>
       </c>
-      <c r="K19" s="94" t="n">
+      <c r="O19" s="94" t="n">
         <v>2.44</v>
       </c>
-      <c r="L19" s="94" t="n">
+      <c r="P19" s="94" t="n">
         <v>2.44</v>
       </c>
-      <c r="M19" s="94" t="n">
+      <c r="Q19" s="94" t="n">
         <v>2.44</v>
       </c>
-      <c r="N19" s="94" t="n">
+      <c r="R19" s="94" t="n">
         <v>1.24</v>
       </c>
-      <c r="O19" s="94" t="n">
+      <c r="S19" s="94" t="n">
         <v>1.86</v>
       </c>
-      <c r="P19" s="94" t="n">
+      <c r="T19" s="94" t="n">
         <v>0.01</v>
       </c>
-      <c r="Q19" s="94" t="n">
+      <c r="U19" s="94" t="n">
         <v>0.36</v>
       </c>
-      <c r="R19" s="94" t="n">
+      <c r="V19" s="94" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="S19" s="94" t="n">
+      <c r="W19" s="94" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="T19" s="94" t="n">
+      <c r="X19" s="94" t="n">
         <v>1.78</v>
       </c>
-      <c r="U19" s="94" t="n">
+      <c r="Y19" s="94" t="n">
         <v>1.78</v>
       </c>
-      <c r="V19" s="94" t="n">
+      <c r="Z19" s="94" t="n">
         <v>2.23</v>
       </c>
-      <c r="W19" s="94" t="n">
+      <c r="AA19" s="94" t="n">
         <v>3.17</v>
       </c>
-      <c r="X19" s="94" t="n">
+      <c r="AB19" s="94" t="n">
         <v>3.33</v>
       </c>
-      <c r="Y19" s="94" t="n">
+      <c r="AC19" s="94" t="n">
         <v>3.33</v>
       </c>
-      <c r="Z19" s="94" t="n">
+      <c r="AD19" s="94" t="n">
         <v>3.03</v>
       </c>
-      <c r="AA19" s="94" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB19" s="94" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AC19" s="94" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="AD19" s="94" t="n">
-        <v>4.58</v>
-      </c>
       <c r="AE19" s="94" t="n">
-        <v>4.58</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -8543,191 +8534,191 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="C20" s="94" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="D20" s="94" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="E20" s="94" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="F20" s="94" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="G20" s="94" t="n">
         <v>15.25</v>
       </c>
-      <c r="C20" s="94" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="D20" s="94" t="n">
+      <c r="H20" s="94" t="n">
         <v>16.99</v>
       </c>
-      <c r="E20" s="94" t="n">
+      <c r="I20" s="94" t="n">
         <v>12.45</v>
       </c>
-      <c r="F20" s="94" t="n">
+      <c r="J20" s="94" t="n">
         <v>12.02</v>
       </c>
-      <c r="G20" s="94" t="n">
+      <c r="K20" s="94" t="n">
         <v>12.02</v>
       </c>
-      <c r="H20" s="94" t="n">
+      <c r="L20" s="94" t="n">
         <v>10.8</v>
       </c>
-      <c r="I20" s="94" t="n">
+      <c r="M20" s="94" t="n">
         <v>11.96</v>
       </c>
-      <c r="J20" s="94" t="n">
+      <c r="N20" s="94" t="n">
         <v>10.72</v>
       </c>
-      <c r="K20" s="94" t="n">
+      <c r="O20" s="94" t="n">
         <v>9.85</v>
       </c>
-      <c r="L20" s="94" t="n">
+      <c r="P20" s="94" t="n">
         <v>9.85</v>
       </c>
-      <c r="M20" s="94" t="n">
+      <c r="Q20" s="94" t="n">
         <v>9.85</v>
       </c>
-      <c r="N20" s="94" t="n">
+      <c r="R20" s="94" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="O20" s="94" t="n">
+      <c r="S20" s="94" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="P20" s="94" t="n">
+      <c r="T20" s="94" t="n">
         <v>5.17</v>
       </c>
-      <c r="Q20" s="94" t="n">
+      <c r="U20" s="94" t="n">
         <v>4.88</v>
       </c>
-      <c r="R20" s="94" t="n">
+      <c r="V20" s="94" t="n">
         <v>5.85</v>
       </c>
-      <c r="S20" s="94" t="n">
+      <c r="W20" s="94" t="n">
         <v>5.85</v>
       </c>
-      <c r="T20" s="94" t="n">
+      <c r="X20" s="94" t="n">
         <v>6.74</v>
       </c>
-      <c r="U20" s="94" t="n">
+      <c r="Y20" s="94" t="n">
         <v>6.74</v>
       </c>
-      <c r="V20" s="94" t="n">
+      <c r="Z20" s="94" t="n">
         <v>5.74</v>
       </c>
-      <c r="W20" s="94" t="n">
+      <c r="AA20" s="94" t="n">
         <v>5.44</v>
       </c>
-      <c r="X20" s="94" t="n">
+      <c r="AB20" s="94" t="n">
         <v>5.53</v>
       </c>
-      <c r="Y20" s="94" t="n">
+      <c r="AC20" s="94" t="n">
         <v>5.53</v>
       </c>
-      <c r="Z20" s="94" t="n">
+      <c r="AD20" s="94" t="n">
         <v>4.51</v>
       </c>
-      <c r="AA20" s="94" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="AB20" s="94" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="AC20" s="94" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AD20" s="94" t="n">
-        <v>7.06</v>
-      </c>
       <c r="AE20" s="94" t="n">
-        <v>7.06</v>
+        <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="96" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="94" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="C21" s="94" t="n">
+        <v>35.39</v>
+      </c>
+      <c r="D21" s="94" t="n">
+        <v>35.39</v>
+      </c>
+      <c r="E21" s="94" t="n">
+        <v>35.39</v>
+      </c>
+      <c r="F21" s="94" t="n">
+        <v>64.51000000000001</v>
+      </c>
+      <c r="G21" s="94" t="n">
         <v>37.99</v>
       </c>
-      <c r="C21" s="94" t="n">
-        <v>37.99</v>
-      </c>
-      <c r="D21" s="94" t="n">
+      <c r="H21" s="94" t="n">
         <v>56.94</v>
       </c>
-      <c r="E21" s="94" t="n">
+      <c r="I21" s="94" t="n">
         <v>16.07</v>
       </c>
-      <c r="F21" s="94" t="n">
+      <c r="J21" s="94" t="n">
         <v>67.48999999999999</v>
       </c>
-      <c r="G21" s="94" t="n">
+      <c r="K21" s="94" t="n">
         <v>67.48999999999999</v>
       </c>
-      <c r="H21" s="94" t="n">
+      <c r="L21" s="94" t="n">
         <v>98.41</v>
       </c>
-      <c r="I21" s="94" t="n">
+      <c r="M21" s="94" t="n">
         <v>97.23999999999999</v>
       </c>
-      <c r="J21" s="94" t="n">
+      <c r="N21" s="94" t="n">
         <v>95.22</v>
       </c>
-      <c r="K21" s="94" t="n">
+      <c r="O21" s="94" t="n">
         <v>90.06</v>
       </c>
-      <c r="L21" s="94" t="n">
+      <c r="P21" s="94" t="n">
         <v>90.06</v>
       </c>
-      <c r="M21" s="94" t="n">
+      <c r="Q21" s="94" t="n">
         <v>90.06</v>
       </c>
-      <c r="N21" s="94" t="n">
+      <c r="R21" s="94" t="n">
         <v>74.65000000000001</v>
       </c>
-      <c r="O21" s="94" t="n">
+      <c r="S21" s="94" t="n">
         <v>89.31999999999999</v>
       </c>
-      <c r="P21" s="94" t="n">
+      <c r="T21" s="94" t="n">
         <v>34.87</v>
       </c>
-      <c r="Q21" s="94" t="n">
+      <c r="U21" s="94" t="n">
         <v>22.53</v>
       </c>
-      <c r="R21" s="94" t="n">
+      <c r="V21" s="94" t="n">
         <v>10.95</v>
       </c>
-      <c r="S21" s="94" t="n">
+      <c r="W21" s="94" t="n">
         <v>10.95</v>
       </c>
-      <c r="T21" s="94" t="n">
+      <c r="X21" s="94" t="n">
         <v>42.53</v>
       </c>
-      <c r="U21" s="94" t="n">
+      <c r="Y21" s="94" t="n">
         <v>42.53</v>
       </c>
-      <c r="V21" s="94" t="n">
+      <c r="Z21" s="94" t="n">
         <v>32.72</v>
       </c>
-      <c r="W21" s="94" t="n">
+      <c r="AA21" s="94" t="n">
         <v>84.81999999999999</v>
       </c>
-      <c r="X21" s="94" t="n">
+      <c r="AB21" s="94" t="n">
         <v>74.91</v>
       </c>
-      <c r="Y21" s="94" t="n">
+      <c r="AC21" s="94" t="n">
         <v>74.91</v>
       </c>
-      <c r="Z21" s="94" t="n">
+      <c r="AD21" s="94" t="n">
         <v>6.03</v>
       </c>
-      <c r="AA21" s="94" t="n">
-        <v>7.97</v>
-      </c>
-      <c r="AB21" s="94" t="n">
-        <v>7.97</v>
-      </c>
-      <c r="AC21" s="94" t="n">
-        <v>11.56</v>
-      </c>
-      <c r="AD21" s="94" t="n">
-        <v>26.76</v>
-      </c>
       <c r="AE21" s="94" t="n">
-        <v>26.76</v>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -8751,140 +8742,138 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="E22" s="91" t="inlineStr">
+      <c r="E22" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F22" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G22" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H22" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F22" s="91" t="inlineStr">
+      <c r="J22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G22" s="91" t="inlineStr">
+      <c r="K22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H22" s="91" t="inlineStr">
+      <c r="L22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I22" s="91" t="inlineStr">
+      <c r="M22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J22" s="91" t="inlineStr">
+      <c r="N22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K22" s="91" t="inlineStr">
+      <c r="O22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L22" s="91" t="inlineStr">
+      <c r="P22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M22" s="91" t="inlineStr">
+      <c r="Q22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N22" s="91" t="inlineStr">
+      <c r="R22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O22" s="91" t="inlineStr">
+      <c r="S22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P22" s="92" t="inlineStr">
+      <c r="T22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q22" s="92" t="inlineStr">
+      <c r="U22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R22" s="93" t="inlineStr">
+      <c r="V22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S22" s="93" t="inlineStr">
+      <c r="W22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T22" s="92" t="inlineStr">
+      <c r="X22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U22" s="92" t="inlineStr">
+      <c r="Y22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V22" s="92" t="inlineStr">
+      <c r="Z22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W22" s="92" t="inlineStr">
+      <c r="AA22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X22" s="92" t="inlineStr">
+      <c r="AB22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y22" s="92" t="inlineStr">
+      <c r="AC22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z22" s="93" t="inlineStr">
+      <c r="AD22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA22" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB22" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC22" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD22" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE22" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
+      <c r="AE22" s="92" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -8894,94 +8883,94 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="C23" s="94" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="D23" s="94" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="E23" s="94" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="F23" s="94" t="n">
         <v>7.47</v>
       </c>
-      <c r="C23" s="94" t="n">
+      <c r="G23" s="94" t="n">
         <v>6.1</v>
       </c>
-      <c r="D23" s="94" t="n">
+      <c r="H23" s="94" t="n">
         <v>6.2</v>
       </c>
-      <c r="E23" s="94" t="n">
+      <c r="I23" s="94" t="n">
         <v>5.49</v>
       </c>
-      <c r="F23" s="94" t="n">
+      <c r="J23" s="94" t="n">
         <v>5.48</v>
       </c>
-      <c r="G23" s="94" t="n">
+      <c r="K23" s="94" t="n">
         <v>5.48</v>
       </c>
-      <c r="H23" s="94" t="n">
+      <c r="L23" s="94" t="n">
         <v>5.17</v>
       </c>
-      <c r="I23" s="94" t="n">
+      <c r="M23" s="94" t="n">
         <v>3.86</v>
       </c>
-      <c r="J23" s="94" t="n">
+      <c r="N23" s="94" t="n">
         <v>2.56</v>
       </c>
-      <c r="K23" s="94" t="n">
+      <c r="O23" s="94" t="n">
         <v>1.3</v>
       </c>
-      <c r="L23" s="94" t="n">
+      <c r="P23" s="94" t="n">
         <v>1.3</v>
       </c>
-      <c r="M23" s="94" t="n">
+      <c r="Q23" s="94" t="n">
         <v>1.3</v>
       </c>
-      <c r="N23" s="94" t="n">
+      <c r="R23" s="94" t="n">
         <v>-0.28</v>
       </c>
-      <c r="O23" s="94" t="n">
+      <c r="S23" s="94" t="n">
         <v>-0.04</v>
       </c>
-      <c r="P23" s="94" t="n">
+      <c r="T23" s="94" t="n">
         <v>-1.3</v>
       </c>
-      <c r="Q23" s="94" t="n">
+      <c r="U23" s="94" t="n">
         <v>-1.04</v>
       </c>
-      <c r="R23" s="94" t="n">
+      <c r="V23" s="94" t="n">
         <v>-2.62</v>
       </c>
-      <c r="S23" s="94" t="n">
+      <c r="W23" s="94" t="n">
         <v>-2.62</v>
       </c>
-      <c r="T23" s="94" t="n">
+      <c r="X23" s="94" t="n">
         <v>-0.53</v>
       </c>
-      <c r="U23" s="94" t="n">
+      <c r="Y23" s="94" t="n">
         <v>-0.53</v>
       </c>
-      <c r="V23" s="94" t="n">
+      <c r="Z23" s="94" t="n">
         <v>0.17</v>
       </c>
-      <c r="W23" s="94" t="n">
+      <c r="AA23" s="94" t="n">
         <v>0.46</v>
       </c>
-      <c r="X23" s="94" t="n">
+      <c r="AB23" s="94" t="n">
         <v>1.55</v>
       </c>
-      <c r="Y23" s="94" t="n">
+      <c r="AC23" s="94" t="n">
         <v>1.55</v>
       </c>
-      <c r="Z23" s="94" t="n">
+      <c r="AD23" s="94" t="n">
         <v>1.04</v>
       </c>
-      <c r="AA23" s="94" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AB23" s="94" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AC23" s="94" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD23" s="94" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AE23" s="94" t="n">
-        <v>1.89</v>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -8991,94 +8980,94 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="C24" s="94" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="D24" s="94" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="E24" s="94" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="F24" s="94" t="n">
         <v>15.78</v>
       </c>
-      <c r="C24" s="94" t="n">
+      <c r="G24" s="94" t="n">
         <v>14.66</v>
       </c>
-      <c r="D24" s="94" t="n">
+      <c r="H24" s="94" t="n">
         <v>15.88</v>
       </c>
-      <c r="E24" s="94" t="n">
+      <c r="I24" s="94" t="n">
         <v>12.52</v>
       </c>
-      <c r="F24" s="94" t="n">
+      <c r="J24" s="94" t="n">
         <v>10.1</v>
       </c>
-      <c r="G24" s="94" t="n">
+      <c r="K24" s="94" t="n">
         <v>10.1</v>
       </c>
-      <c r="H24" s="94" t="n">
+      <c r="L24" s="94" t="n">
         <v>9.109999999999999</v>
       </c>
-      <c r="I24" s="94" t="n">
+      <c r="M24" s="94" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="J24" s="94" t="n">
+      <c r="N24" s="94" t="n">
         <v>8.6</v>
       </c>
-      <c r="K24" s="94" t="n">
+      <c r="O24" s="94" t="n">
         <v>7.14</v>
       </c>
-      <c r="L24" s="94" t="n">
+      <c r="P24" s="94" t="n">
         <v>7.14</v>
       </c>
-      <c r="M24" s="94" t="n">
+      <c r="Q24" s="94" t="n">
         <v>7.14</v>
       </c>
-      <c r="N24" s="94" t="n">
+      <c r="R24" s="94" t="n">
         <v>8.06</v>
       </c>
-      <c r="O24" s="94" t="n">
+      <c r="S24" s="94" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="P24" s="94" t="n">
+      <c r="T24" s="94" t="n">
         <v>5.35</v>
       </c>
-      <c r="Q24" s="94" t="n">
+      <c r="U24" s="94" t="n">
         <v>4.66</v>
       </c>
-      <c r="R24" s="94" t="n">
+      <c r="V24" s="94" t="n">
         <v>4.1</v>
       </c>
-      <c r="S24" s="94" t="n">
+      <c r="W24" s="94" t="n">
         <v>4.1</v>
       </c>
-      <c r="T24" s="94" t="n">
+      <c r="X24" s="94" t="n">
         <v>4.84</v>
       </c>
-      <c r="U24" s="94" t="n">
+      <c r="Y24" s="94" t="n">
         <v>4.84</v>
       </c>
-      <c r="V24" s="94" t="n">
+      <c r="Z24" s="94" t="n">
         <v>3.23</v>
       </c>
-      <c r="W24" s="94" t="n">
+      <c r="AA24" s="94" t="n">
         <v>4.28</v>
       </c>
-      <c r="X24" s="94" t="n">
+      <c r="AB24" s="94" t="n">
         <v>6.27</v>
       </c>
-      <c r="Y24" s="94" t="n">
+      <c r="AC24" s="94" t="n">
         <v>6.27</v>
       </c>
-      <c r="Z24" s="94" t="n">
+      <c r="AD24" s="94" t="n">
         <v>5.98</v>
       </c>
-      <c r="AA24" s="94" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="AB24" s="94" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="AC24" s="94" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="AD24" s="94" t="n">
-        <v>9.42</v>
-      </c>
       <c r="AE24" s="94" t="n">
-        <v>9.42</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -9088,94 +9077,94 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="C25" s="94" t="n">
+        <v>41.24</v>
+      </c>
+      <c r="D25" s="94" t="n">
+        <v>41.24</v>
+      </c>
+      <c r="E25" s="94" t="n">
+        <v>41.24</v>
+      </c>
+      <c r="F25" s="94" t="n">
         <v>77.98</v>
       </c>
-      <c r="C25" s="94" t="n">
+      <c r="G25" s="94" t="n">
         <v>68.69</v>
       </c>
-      <c r="D25" s="94" t="n">
+      <c r="H25" s="94" t="n">
         <v>89</v>
       </c>
-      <c r="E25" s="94" t="n">
+      <c r="I25" s="94" t="n">
         <v>86.3</v>
       </c>
-      <c r="F25" s="94" t="n">
+      <c r="J25" s="94" t="n">
         <v>79.05</v>
       </c>
-      <c r="G25" s="94" t="n">
+      <c r="K25" s="94" t="n">
         <v>79.05</v>
       </c>
-      <c r="H25" s="94" t="n">
+      <c r="L25" s="94" t="n">
         <v>95.43000000000001</v>
       </c>
-      <c r="I25" s="94" t="n">
+      <c r="M25" s="94" t="n">
         <v>92.37</v>
       </c>
-      <c r="J25" s="94" t="n">
+      <c r="N25" s="94" t="n">
         <v>91.09999999999999</v>
       </c>
-      <c r="K25" s="94" t="n">
+      <c r="O25" s="94" t="n">
         <v>83.62</v>
       </c>
-      <c r="L25" s="94" t="n">
+      <c r="P25" s="94" t="n">
         <v>83.62</v>
       </c>
-      <c r="M25" s="94" t="n">
+      <c r="Q25" s="94" t="n">
         <v>83.62</v>
       </c>
-      <c r="N25" s="94" t="n">
+      <c r="R25" s="94" t="n">
         <v>74.87</v>
       </c>
-      <c r="O25" s="94" t="n">
+      <c r="S25" s="94" t="n">
         <v>80.75</v>
       </c>
-      <c r="P25" s="94" t="n">
+      <c r="T25" s="94" t="n">
         <v>58.29</v>
       </c>
-      <c r="Q25" s="94" t="n">
+      <c r="U25" s="94" t="n">
         <v>44.79</v>
       </c>
-      <c r="R25" s="94" t="n">
+      <c r="V25" s="94" t="n">
         <v>15.07</v>
       </c>
-      <c r="S25" s="94" t="n">
+      <c r="W25" s="94" t="n">
         <v>15.07</v>
       </c>
-      <c r="T25" s="94" t="n">
+      <c r="X25" s="94" t="n">
         <v>49.78</v>
       </c>
-      <c r="U25" s="94" t="n">
+      <c r="Y25" s="94" t="n">
         <v>49.78</v>
       </c>
-      <c r="V25" s="94" t="n">
+      <c r="Z25" s="94" t="n">
         <v>34.31</v>
       </c>
-      <c r="W25" s="94" t="n">
+      <c r="AA25" s="94" t="n">
         <v>52.18</v>
       </c>
-      <c r="X25" s="94" t="n">
+      <c r="AB25" s="94" t="n">
         <v>54.91</v>
       </c>
-      <c r="Y25" s="94" t="n">
+      <c r="AC25" s="94" t="n">
         <v>54.91</v>
       </c>
-      <c r="Z25" s="94" t="n">
+      <c r="AD25" s="94" t="n">
         <v>15.8</v>
       </c>
-      <c r="AA25" s="94" t="n">
-        <v>21.31</v>
-      </c>
-      <c r="AB25" s="94" t="n">
-        <v>21.31</v>
-      </c>
-      <c r="AC25" s="94" t="n">
-        <v>22.32</v>
-      </c>
-      <c r="AD25" s="94" t="n">
-        <v>40.35</v>
-      </c>
       <c r="AE25" s="94" t="n">
-        <v>40.35</v>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -9184,155 +9173,153 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="92" t="inlineStr">
+      <c r="B26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C26" s="93" t="inlineStr">
+      <c r="G26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D26" s="92" t="inlineStr">
+      <c r="H26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E26" s="93" t="inlineStr">
+      <c r="I26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F26" s="91" t="inlineStr">
+      <c r="J26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G26" s="91" t="inlineStr">
+      <c r="K26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H26" s="91" t="inlineStr">
+      <c r="L26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I26" s="91" t="inlineStr">
+      <c r="M26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J26" s="91" t="inlineStr">
+      <c r="N26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K26" s="91" t="inlineStr">
+      <c r="O26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L26" s="91" t="inlineStr">
+      <c r="P26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M26" s="91" t="inlineStr">
+      <c r="Q26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N26" s="92" t="inlineStr">
+      <c r="R26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O26" s="91" t="inlineStr">
+      <c r="S26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P26" s="93" t="inlineStr">
+      <c r="T26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q26" s="93" t="inlineStr">
+      <c r="U26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R26" s="93" t="inlineStr">
+      <c r="V26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S26" s="93" t="inlineStr">
+      <c r="W26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T26" s="93" t="inlineStr">
+      <c r="X26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U26" s="93" t="inlineStr">
+      <c r="Y26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V26" s="93" t="inlineStr">
+      <c r="Z26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W26" s="91" t="inlineStr">
+      <c r="AA26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X26" s="91" t="inlineStr">
+      <c r="AB26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y26" s="91" t="inlineStr">
+      <c r="AC26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z26" s="93" t="inlineStr">
+      <c r="AD26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA26" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB26" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC26" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD26" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE26" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
+      <c r="AE26" s="92" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -9342,94 +9329,94 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="C27" s="94" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="D27" s="94" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="E27" s="94" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="F27" s="94" t="n">
         <v>8.77</v>
       </c>
-      <c r="C27" s="94" t="n">
+      <c r="G27" s="94" t="n">
         <v>5.51</v>
       </c>
-      <c r="D27" s="94" t="n">
+      <c r="H27" s="94" t="n">
         <v>5.46</v>
       </c>
-      <c r="E27" s="94" t="n">
+      <c r="I27" s="94" t="n">
         <v>4.17</v>
       </c>
-      <c r="F27" s="94" t="n">
+      <c r="J27" s="94" t="n">
         <v>7.75</v>
       </c>
-      <c r="G27" s="94" t="n">
+      <c r="K27" s="94" t="n">
         <v>7.75</v>
       </c>
-      <c r="H27" s="94" t="n">
+      <c r="L27" s="94" t="n">
         <v>8.9</v>
       </c>
-      <c r="I27" s="94" t="n">
+      <c r="M27" s="94" t="n">
         <v>9.48</v>
       </c>
-      <c r="J27" s="94" t="n">
+      <c r="N27" s="94" t="n">
         <v>6.37</v>
       </c>
-      <c r="K27" s="94" t="n">
+      <c r="O27" s="94" t="n">
         <v>5.88</v>
       </c>
-      <c r="L27" s="94" t="n">
+      <c r="P27" s="94" t="n">
         <v>5.88</v>
       </c>
-      <c r="M27" s="94" t="n">
+      <c r="Q27" s="94" t="n">
         <v>5.88</v>
       </c>
-      <c r="N27" s="94" t="n">
+      <c r="R27" s="94" t="n">
         <v>4.59</v>
       </c>
-      <c r="O27" s="94" t="n">
+      <c r="S27" s="94" t="n">
         <v>6.19</v>
       </c>
-      <c r="P27" s="94" t="n">
+      <c r="T27" s="94" t="n">
         <v>3.69</v>
       </c>
-      <c r="Q27" s="94" t="n">
+      <c r="U27" s="94" t="n">
         <v>4.22</v>
       </c>
-      <c r="R27" s="94" t="n">
+      <c r="V27" s="94" t="n">
         <v>3.56</v>
       </c>
-      <c r="S27" s="94" t="n">
+      <c r="W27" s="94" t="n">
         <v>3.56</v>
       </c>
-      <c r="T27" s="94" t="n">
+      <c r="X27" s="94" t="n">
         <v>6.19</v>
       </c>
-      <c r="U27" s="94" t="n">
+      <c r="Y27" s="94" t="n">
         <v>6.19</v>
       </c>
-      <c r="V27" s="94" t="n">
+      <c r="Z27" s="94" t="n">
         <v>6.61</v>
       </c>
-      <c r="W27" s="94" t="n">
+      <c r="AA27" s="94" t="n">
         <v>8.6</v>
       </c>
-      <c r="X27" s="94" t="n">
+      <c r="AB27" s="94" t="n">
         <v>7.91</v>
       </c>
-      <c r="Y27" s="94" t="n">
+      <c r="AC27" s="94" t="n">
         <v>7.91</v>
       </c>
-      <c r="Z27" s="94" t="n">
+      <c r="AD27" s="94" t="n">
         <v>7.57</v>
       </c>
-      <c r="AA27" s="94" t="n">
-        <v>6.47</v>
-      </c>
-      <c r="AB27" s="94" t="n">
-        <v>6.47</v>
-      </c>
-      <c r="AC27" s="94" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="AD27" s="94" t="n">
-        <v>10.02</v>
-      </c>
       <c r="AE27" s="94" t="n">
-        <v>10.02</v>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -9439,191 +9426,191 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="C28" s="94" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="D28" s="94" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="E28" s="94" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="F28" s="94" t="n">
         <v>21.52</v>
       </c>
-      <c r="C28" s="94" t="n">
+      <c r="G28" s="94" t="n">
         <v>19.95</v>
       </c>
-      <c r="D28" s="94" t="n">
+      <c r="H28" s="94" t="n">
         <v>21.81</v>
       </c>
-      <c r="E28" s="94" t="n">
+      <c r="I28" s="94" t="n">
         <v>15.29</v>
       </c>
-      <c r="F28" s="94" t="n">
+      <c r="J28" s="94" t="n">
         <v>16.05</v>
       </c>
-      <c r="G28" s="94" t="n">
+      <c r="K28" s="94" t="n">
         <v>16.05</v>
       </c>
-      <c r="H28" s="94" t="n">
+      <c r="L28" s="94" t="n">
         <v>13.95</v>
       </c>
-      <c r="I28" s="94" t="n">
+      <c r="M28" s="94" t="n">
         <v>16.69</v>
       </c>
-      <c r="J28" s="94" t="n">
+      <c r="N28" s="94" t="n">
         <v>13.74</v>
       </c>
-      <c r="K28" s="94" t="n">
+      <c r="O28" s="94" t="n">
         <v>13.09</v>
       </c>
-      <c r="L28" s="94" t="n">
+      <c r="P28" s="94" t="n">
         <v>13.09</v>
       </c>
-      <c r="M28" s="94" t="n">
+      <c r="Q28" s="94" t="n">
         <v>13.09</v>
       </c>
-      <c r="N28" s="94" t="n">
+      <c r="R28" s="94" t="n">
         <v>12.55</v>
       </c>
-      <c r="O28" s="94" t="n">
+      <c r="S28" s="94" t="n">
         <v>12.51</v>
       </c>
-      <c r="P28" s="94" t="n">
+      <c r="T28" s="94" t="n">
         <v>5.82</v>
       </c>
-      <c r="Q28" s="94" t="n">
+      <c r="U28" s="94" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="94" t="n">
+      <c r="V28" s="94" t="n">
         <v>8.09</v>
       </c>
-      <c r="S28" s="94" t="n">
+      <c r="W28" s="94" t="n">
         <v>8.09</v>
       </c>
-      <c r="T28" s="94" t="n">
+      <c r="X28" s="94" t="n">
         <v>9</v>
       </c>
-      <c r="U28" s="94" t="n">
+      <c r="Y28" s="94" t="n">
         <v>9</v>
       </c>
-      <c r="V28" s="94" t="n">
+      <c r="Z28" s="94" t="n">
         <v>8.289999999999999</v>
       </c>
-      <c r="W28" s="94" t="n">
+      <c r="AA28" s="94" t="n">
         <v>7.32</v>
       </c>
-      <c r="X28" s="94" t="n">
+      <c r="AB28" s="94" t="n">
         <v>6.22</v>
       </c>
-      <c r="Y28" s="94" t="n">
+      <c r="AC28" s="94" t="n">
         <v>6.22</v>
       </c>
-      <c r="Z28" s="94" t="n">
+      <c r="AD28" s="94" t="n">
         <v>4.8</v>
       </c>
-      <c r="AA28" s="94" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="AB28" s="94" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="AC28" s="94" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD28" s="94" t="n">
-        <v>7.01</v>
-      </c>
       <c r="AE28" s="94" t="n">
-        <v>7.01</v>
+        <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="76" t="inlineStr">
+      <c r="A29" s="96" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="94" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="C29" s="94" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="D29" s="94" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="E29" s="94" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="F29" s="94" t="n">
         <v>53.71</v>
       </c>
-      <c r="C29" s="94" t="n">
+      <c r="G29" s="94" t="n">
         <v>44.16</v>
       </c>
-      <c r="D29" s="94" t="n">
+      <c r="H29" s="94" t="n">
         <v>55.99</v>
       </c>
-      <c r="E29" s="94" t="n">
+      <c r="I29" s="94" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="F29" s="94" t="n">
+      <c r="J29" s="94" t="n">
         <v>54.41</v>
       </c>
-      <c r="G29" s="94" t="n">
+      <c r="K29" s="94" t="n">
         <v>54.41</v>
       </c>
-      <c r="H29" s="94" t="n">
+      <c r="L29" s="94" t="n">
         <v>94.87</v>
       </c>
-      <c r="I29" s="94" t="n">
+      <c r="M29" s="94" t="n">
         <v>93.84999999999999</v>
       </c>
-      <c r="J29" s="94" t="n">
+      <c r="N29" s="94" t="n">
         <v>85.8</v>
       </c>
-      <c r="K29" s="94" t="n">
+      <c r="O29" s="94" t="n">
         <v>78.89</v>
       </c>
-      <c r="L29" s="94" t="n">
+      <c r="P29" s="94" t="n">
         <v>78.89</v>
       </c>
-      <c r="M29" s="94" t="n">
+      <c r="Q29" s="94" t="n">
         <v>78.89</v>
       </c>
-      <c r="N29" s="94" t="n">
+      <c r="R29" s="94" t="n">
         <v>51.88</v>
       </c>
-      <c r="O29" s="94" t="n">
+      <c r="S29" s="94" t="n">
         <v>83.56</v>
       </c>
-      <c r="P29" s="94" t="n">
+      <c r="T29" s="94" t="n">
         <v>6.54</v>
       </c>
-      <c r="Q29" s="94" t="n">
+      <c r="U29" s="94" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="R29" s="94" t="n">
+      <c r="V29" s="94" t="n">
         <v>10.96</v>
       </c>
-      <c r="S29" s="94" t="n">
+      <c r="W29" s="94" t="n">
         <v>10.96</v>
       </c>
-      <c r="T29" s="94" t="n">
+      <c r="X29" s="94" t="n">
         <v>32.97</v>
       </c>
-      <c r="U29" s="94" t="n">
+      <c r="Y29" s="94" t="n">
         <v>32.97</v>
       </c>
-      <c r="V29" s="94" t="n">
+      <c r="Z29" s="94" t="n">
         <v>34.13</v>
       </c>
-      <c r="W29" s="94" t="n">
+      <c r="AA29" s="94" t="n">
         <v>88.52</v>
       </c>
-      <c r="X29" s="94" t="n">
+      <c r="AB29" s="94" t="n">
         <v>76.26000000000001</v>
       </c>
-      <c r="Y29" s="94" t="n">
+      <c r="AC29" s="94" t="n">
         <v>76.26000000000001</v>
       </c>
-      <c r="Z29" s="94" t="n">
+      <c r="AD29" s="94" t="n">
         <v>5.68</v>
       </c>
-      <c r="AA29" s="94" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="AB29" s="94" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="AC29" s="94" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="AD29" s="94" t="n">
-        <v>24.8</v>
-      </c>
       <c r="AE29" s="94" t="n">
-        <v>24.8</v>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -9632,155 +9619,147 @@
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B30" s="91" t="inlineStr">
+      <c r="B30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="C30" s="92" t="inlineStr">
+      <c r="E30" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F30" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D30" s="93" t="inlineStr">
+      <c r="H30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E30" s="92" t="inlineStr">
+      <c r="I30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F30" s="91" t="inlineStr">
+      <c r="J30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G30" s="91" t="inlineStr">
+      <c r="K30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H30" s="91" t="inlineStr">
+      <c r="L30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I30" s="91" t="inlineStr">
+      <c r="M30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J30" s="91" t="inlineStr">
+      <c r="N30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K30" s="92" t="inlineStr">
+      <c r="O30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L30" s="93" t="inlineStr">
+      <c r="P30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M30" s="93" t="inlineStr">
+      <c r="Q30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N30" s="93" t="inlineStr">
+      <c r="R30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O30" s="93" t="inlineStr">
+      <c r="S30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P30" s="93" t="inlineStr">
+      <c r="T30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q30" s="93" t="inlineStr">
+      <c r="U30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R30" s="93" t="inlineStr">
+      <c r="V30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S30" s="93" t="inlineStr">
+      <c r="W30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T30" s="92" t="inlineStr">
+      <c r="X30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U30" s="91" t="inlineStr">
+      <c r="Y30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V30" s="91" t="inlineStr">
+      <c r="Z30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W30" s="93" t="inlineStr">
+      <c r="AA30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X30" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y30" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z30" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA30" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB30" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC30" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD30" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE30" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
+      <c r="AB30" s="92" t="n">
+        <v/>
+      </c>
+      <c r="AC30" s="92" t="n">
+        <v/>
+      </c>
+      <c r="AD30" s="92" t="n">
+        <v/>
+      </c>
+      <c r="AE30" s="92" t="n">
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -9790,94 +9769,94 @@
         </is>
       </c>
       <c r="B31" s="94" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C31" s="94" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="D31" s="94" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E31" s="94" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F31" s="94" t="n">
         <v>1.11</v>
       </c>
-      <c r="C31" s="94" t="n">
+      <c r="G31" s="94" t="n">
         <v>0.35</v>
       </c>
-      <c r="D31" s="94" t="n">
+      <c r="H31" s="94" t="n">
         <v>0.29</v>
       </c>
-      <c r="E31" s="94" t="n">
+      <c r="I31" s="94" t="n">
         <v>2.49</v>
       </c>
-      <c r="F31" s="94" t="n">
+      <c r="J31" s="94" t="n">
         <v>5.32</v>
       </c>
-      <c r="G31" s="94" t="n">
+      <c r="K31" s="94" t="n">
         <v>5.32</v>
       </c>
-      <c r="H31" s="94" t="n">
+      <c r="L31" s="94" t="n">
         <v>4.76</v>
       </c>
-      <c r="I31" s="94" t="n">
+      <c r="M31" s="94" t="n">
         <v>4.05</v>
       </c>
-      <c r="J31" s="94" t="n">
+      <c r="N31" s="94" t="n">
         <v>1.6</v>
       </c>
-      <c r="K31" s="94" t="n">
+      <c r="O31" s="94" t="n">
         <v>-0.13</v>
       </c>
-      <c r="L31" s="94" t="n">
+      <c r="P31" s="94" t="n">
         <v>-1.36</v>
       </c>
-      <c r="M31" s="94" t="n">
+      <c r="Q31" s="94" t="n">
         <v>-1.36</v>
       </c>
-      <c r="N31" s="94" t="n">
+      <c r="R31" s="94" t="n">
         <v>-0.87</v>
       </c>
-      <c r="O31" s="94" t="n">
+      <c r="S31" s="94" t="n">
         <v>-1.88</v>
       </c>
-      <c r="P31" s="94" t="n">
+      <c r="T31" s="94" t="n">
         <v>-3.6</v>
       </c>
-      <c r="Q31" s="94" t="n">
+      <c r="U31" s="94" t="n">
         <v>-1.05</v>
       </c>
-      <c r="R31" s="94" t="n">
+      <c r="V31" s="94" t="n">
         <v>-1.05</v>
       </c>
-      <c r="S31" s="94" t="n">
+      <c r="W31" s="94" t="n">
         <v>-1.05</v>
       </c>
-      <c r="T31" s="94" t="n">
+      <c r="X31" s="94" t="n">
         <v>0.57</v>
       </c>
-      <c r="U31" s="94" t="n">
+      <c r="Y31" s="94" t="n">
         <v>1.79</v>
       </c>
-      <c r="V31" s="94" t="n">
+      <c r="Z31" s="94" t="n">
         <v>2.94</v>
       </c>
-      <c r="W31" s="94" t="n">
+      <c r="AA31" s="94" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="X31" s="94" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="Y31" s="94" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="Z31" s="94" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="AA31" s="94" t="n">
-        <v>3.26</v>
-      </c>
       <c r="AB31" s="94" t="n">
-        <v>3.26</v>
+        <v/>
       </c>
       <c r="AC31" s="94" t="n">
-        <v>3.26</v>
+        <v/>
       </c>
       <c r="AD31" s="94" t="n">
-        <v>4.49</v>
+        <v/>
       </c>
       <c r="AE31" s="94" t="n">
-        <v>4.49</v>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -9887,94 +9866,94 @@
         </is>
       </c>
       <c r="B32" s="94" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="C32" s="94" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="D32" s="94" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="E32" s="94" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="F32" s="94" t="n">
         <v>13.95</v>
       </c>
-      <c r="C32" s="94" t="n">
+      <c r="G32" s="94" t="n">
         <v>25.29</v>
       </c>
-      <c r="D32" s="94" t="n">
+      <c r="H32" s="94" t="n">
         <v>8.65</v>
       </c>
-      <c r="E32" s="94" t="n">
+      <c r="I32" s="94" t="n">
         <v>3.78</v>
       </c>
-      <c r="F32" s="94" t="n">
+      <c r="J32" s="94" t="n">
         <v>2.12</v>
       </c>
-      <c r="G32" s="94" t="n">
+      <c r="K32" s="94" t="n">
         <v>2.12</v>
       </c>
-      <c r="H32" s="94" t="n">
+      <c r="L32" s="94" t="n">
         <v>3.72</v>
       </c>
-      <c r="I32" s="94" t="n">
+      <c r="M32" s="94" t="n">
         <v>3.06</v>
       </c>
-      <c r="J32" s="94" t="n">
+      <c r="N32" s="94" t="n">
         <v>3.61</v>
       </c>
-      <c r="K32" s="94" t="n">
+      <c r="O32" s="94" t="n">
         <v>2.73</v>
       </c>
-      <c r="L32" s="94" t="n">
+      <c r="P32" s="94" t="n">
         <v>-1.8</v>
       </c>
-      <c r="M32" s="94" t="n">
+      <c r="Q32" s="94" t="n">
         <v>-1.8</v>
       </c>
-      <c r="N32" s="94" t="n">
+      <c r="R32" s="94" t="n">
         <v>-2.58</v>
       </c>
-      <c r="O32" s="94" t="n">
+      <c r="S32" s="94" t="n">
         <v>-2.92</v>
       </c>
-      <c r="P32" s="94" t="n">
+      <c r="T32" s="94" t="n">
         <v>-3.97</v>
       </c>
-      <c r="Q32" s="94" t="n">
+      <c r="U32" s="94" t="n">
         <v>-2.33</v>
       </c>
-      <c r="R32" s="94" t="n">
+      <c r="V32" s="94" t="n">
         <v>-2.33</v>
       </c>
-      <c r="S32" s="94" t="n">
+      <c r="W32" s="94" t="n">
         <v>-2.33</v>
       </c>
-      <c r="T32" s="94" t="n">
+      <c r="X32" s="94" t="n">
         <v>-3.63</v>
       </c>
-      <c r="U32" s="94" t="n">
+      <c r="Y32" s="94" t="n">
         <v>-3.14</v>
       </c>
-      <c r="V32" s="94" t="n">
+      <c r="Z32" s="94" t="n">
         <v>-2.69</v>
       </c>
-      <c r="W32" s="94" t="n">
+      <c r="AA32" s="94" t="n">
         <v>-6.91</v>
       </c>
-      <c r="X32" s="94" t="n">
-        <v>-4.63</v>
-      </c>
-      <c r="Y32" s="94" t="n">
-        <v>-4.63</v>
-      </c>
-      <c r="Z32" s="94" t="n">
-        <v>-4.63</v>
-      </c>
-      <c r="AA32" s="94" t="n">
-        <v>-4.63</v>
-      </c>
       <c r="AB32" s="94" t="n">
-        <v>-4.63</v>
+        <v/>
       </c>
       <c r="AC32" s="94" t="n">
-        <v>-4.63</v>
+        <v/>
       </c>
       <c r="AD32" s="94" t="n">
-        <v>-3.12</v>
+        <v/>
       </c>
       <c r="AE32" s="94" t="n">
-        <v>-3.12</v>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -9984,94 +9963,94 @@
         </is>
       </c>
       <c r="B33" s="94" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="C33" s="94" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="D33" s="94" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="E33" s="94" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="F33" s="94" t="n">
         <v>53.61</v>
       </c>
-      <c r="C33" s="94" t="n">
+      <c r="G33" s="94" t="n">
         <v>51.93</v>
       </c>
-      <c r="D33" s="94" t="n">
+      <c r="H33" s="94" t="n">
         <v>44.81</v>
       </c>
-      <c r="E33" s="94" t="n">
+      <c r="I33" s="94" t="n">
         <v>54.76</v>
       </c>
-      <c r="F33" s="94" t="n">
+      <c r="J33" s="94" t="n">
         <v>63.06</v>
       </c>
-      <c r="G33" s="94" t="n">
+      <c r="K33" s="94" t="n">
         <v>63.06</v>
       </c>
-      <c r="H33" s="94" t="n">
+      <c r="L33" s="94" t="n">
         <v>63.69</v>
       </c>
-      <c r="I33" s="94" t="n">
+      <c r="M33" s="94" t="n">
         <v>59.51</v>
       </c>
-      <c r="J33" s="94" t="n">
+      <c r="N33" s="94" t="n">
         <v>49.22</v>
       </c>
-      <c r="K33" s="94" t="n">
+      <c r="O33" s="94" t="n">
         <v>46.79</v>
       </c>
-      <c r="L33" s="94" t="n">
+      <c r="P33" s="94" t="n">
         <v>37.14</v>
       </c>
-      <c r="M33" s="94" t="n">
+      <c r="Q33" s="94" t="n">
         <v>37.14</v>
       </c>
-      <c r="N33" s="94" t="n">
+      <c r="R33" s="94" t="n">
         <v>38.82</v>
       </c>
-      <c r="O33" s="94" t="n">
+      <c r="S33" s="94" t="n">
         <v>36.1</v>
       </c>
-      <c r="P33" s="94" t="n">
+      <c r="T33" s="94" t="n">
         <v>36.44</v>
       </c>
-      <c r="Q33" s="94" t="n">
+      <c r="U33" s="94" t="n">
         <v>45.43</v>
       </c>
-      <c r="R33" s="94" t="n">
+      <c r="V33" s="94" t="n">
         <v>45.43</v>
       </c>
-      <c r="S33" s="94" t="n">
+      <c r="W33" s="94" t="n">
         <v>45.43</v>
       </c>
-      <c r="T33" s="94" t="n">
+      <c r="X33" s="94" t="n">
         <v>52.04</v>
       </c>
-      <c r="U33" s="94" t="n">
+      <c r="Y33" s="94" t="n">
         <v>58.96</v>
       </c>
-      <c r="V33" s="94" t="n">
+      <c r="Z33" s="94" t="n">
         <v>60.92</v>
       </c>
-      <c r="W33" s="94" t="n">
+      <c r="AA33" s="94" t="n">
         <v>49.64</v>
       </c>
-      <c r="X33" s="94" t="n">
-        <v>61.59</v>
-      </c>
-      <c r="Y33" s="94" t="n">
-        <v>61.59</v>
-      </c>
-      <c r="Z33" s="94" t="n">
-        <v>61.59</v>
-      </c>
-      <c r="AA33" s="94" t="n">
-        <v>61.59</v>
-      </c>
       <c r="AB33" s="94" t="n">
-        <v>61.59</v>
+        <v/>
       </c>
       <c r="AC33" s="94" t="n">
-        <v>61.59</v>
+        <v/>
       </c>
       <c r="AD33" s="94" t="n">
-        <v>71.7</v>
+        <v/>
       </c>
       <c r="AE33" s="94" t="n">
-        <v>71.7</v>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -10080,155 +10059,153 @@
           <t>vn:EIDE</t>
         </is>
       </c>
-      <c r="B34" s="91" t="inlineStr">
+      <c r="B34" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="C34" s="91" t="inlineStr">
+      <c r="D34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D34" s="91" t="inlineStr">
+      <c r="E34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E34" s="91" t="inlineStr">
+      <c r="F34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F34" s="91" t="inlineStr">
+      <c r="G34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G34" s="91" t="inlineStr">
+      <c r="H34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H34" s="91" t="inlineStr">
+      <c r="I34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I34" s="92" t="inlineStr">
+      <c r="J34" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K34" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L34" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J34" s="92" t="inlineStr">
+      <c r="N34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K34" s="91" t="inlineStr">
+      <c r="O34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L34" s="91" t="inlineStr">
+      <c r="P34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M34" s="91" t="inlineStr">
+      <c r="Q34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N34" s="92" t="inlineStr">
+      <c r="R34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O34" s="92" t="inlineStr">
+      <c r="S34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P34" s="93" t="inlineStr">
+      <c r="T34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q34" s="93" t="inlineStr">
+      <c r="U34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R34" s="93" t="inlineStr">
+      <c r="V34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S34" s="93" t="inlineStr">
+      <c r="W34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T34" s="93" t="inlineStr">
+      <c r="X34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U34" s="93" t="inlineStr">
+      <c r="Y34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V34" s="93" t="inlineStr">
+      <c r="Z34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W34" s="93" t="inlineStr">
+      <c r="AA34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X34" s="93" t="inlineStr">
+      <c r="AB34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y34" s="93" t="inlineStr">
+      <c r="AC34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z34" s="92" t="inlineStr">
+      <c r="AD34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA34" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB34" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC34" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD34" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE34" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
+      <c r="AE34" s="92" t="n">
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -10238,7 +10215,7 @@
         </is>
       </c>
       <c r="B35" s="94" t="n">
-        <v>0.05</v>
+        <v>-0.15</v>
       </c>
       <c r="C35" s="94" t="n">
         <v>0.05</v>
@@ -10256,76 +10233,76 @@
         <v>0.05</v>
       </c>
       <c r="H35" s="94" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I35" s="94" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J35" s="94" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K35" s="94" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L35" s="94" t="n">
         <v>0.08</v>
       </c>
-      <c r="I35" s="94" t="n">
+      <c r="M35" s="94" t="n">
         <v>-1.53</v>
       </c>
-      <c r="J35" s="94" t="n">
+      <c r="N35" s="94" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="K35" s="94" t="n">
+      <c r="O35" s="94" t="n">
         <v>-0.25</v>
       </c>
-      <c r="L35" s="94" t="n">
+      <c r="P35" s="94" t="n">
         <v>-0.66</v>
       </c>
-      <c r="M35" s="94" t="n">
+      <c r="Q35" s="94" t="n">
         <v>-0.66</v>
       </c>
-      <c r="N35" s="94" t="n">
+      <c r="R35" s="94" t="n">
         <v>-2.25</v>
       </c>
-      <c r="O35" s="94" t="n">
+      <c r="S35" s="94" t="n">
         <v>-2.65</v>
       </c>
-      <c r="P35" s="94" t="n">
+      <c r="T35" s="94" t="n">
         <v>-3.96</v>
       </c>
-      <c r="Q35" s="94" t="n">
+      <c r="U35" s="94" t="n">
         <v>-3.87</v>
       </c>
-      <c r="R35" s="94" t="n">
+      <c r="V35" s="94" t="n">
         <v>-4.36</v>
       </c>
-      <c r="S35" s="94" t="n">
+      <c r="W35" s="94" t="n">
         <v>-4.36</v>
       </c>
-      <c r="T35" s="94" t="n">
+      <c r="X35" s="94" t="n">
         <v>-2.63</v>
       </c>
-      <c r="U35" s="94" t="n">
+      <c r="Y35" s="94" t="n">
         <v>-2.35</v>
       </c>
-      <c r="V35" s="94" t="n">
+      <c r="Z35" s="94" t="n">
         <v>-3.06</v>
       </c>
-      <c r="W35" s="94" t="n">
+      <c r="AA35" s="94" t="n">
         <v>-3.26</v>
       </c>
-      <c r="X35" s="94" t="n">
+      <c r="AB35" s="94" t="n">
         <v>-2.47</v>
       </c>
-      <c r="Y35" s="94" t="n">
+      <c r="AC35" s="94" t="n">
         <v>-2.47</v>
       </c>
-      <c r="Z35" s="94" t="n">
+      <c r="AD35" s="94" t="n">
         <v>-0.95</v>
       </c>
-      <c r="AA35" s="94" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="AB35" s="94" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="AC35" s="94" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AD35" s="94" t="n">
-        <v>0.36</v>
-      </c>
       <c r="AE35" s="94" t="n">
-        <v>0.36</v>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -10335,7 +10312,7 @@
         </is>
       </c>
       <c r="B36" s="94" t="n">
-        <v>4.53</v>
+        <v>3.06</v>
       </c>
       <c r="C36" s="94" t="n">
         <v>4.53</v>
@@ -10353,86 +10330,86 @@
         <v>4.53</v>
       </c>
       <c r="H36" s="94" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="I36" s="94" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="J36" s="94" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="K36" s="94" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="L36" s="94" t="n">
         <v>6.02</v>
       </c>
-      <c r="I36" s="94" t="n">
+      <c r="M36" s="94" t="n">
         <v>0.48</v>
       </c>
-      <c r="J36" s="94" t="n">
+      <c r="N36" s="94" t="n">
         <v>1.56</v>
       </c>
-      <c r="K36" s="94" t="n">
+      <c r="O36" s="94" t="n">
         <v>-0.16</v>
       </c>
-      <c r="L36" s="94" t="n">
+      <c r="P36" s="94" t="n">
         <v>0.33</v>
       </c>
-      <c r="M36" s="94" t="n">
+      <c r="Q36" s="94" t="n">
         <v>0.33</v>
       </c>
-      <c r="N36" s="94" t="n">
+      <c r="R36" s="94" t="n">
         <v>-0.34</v>
       </c>
-      <c r="O36" s="94" t="n">
+      <c r="S36" s="94" t="n">
         <v>-0.48</v>
       </c>
-      <c r="P36" s="94" t="n">
+      <c r="T36" s="94" t="n">
         <v>-0.33</v>
       </c>
-      <c r="Q36" s="94" t="n">
+      <c r="U36" s="94" t="n">
         <v>-0.23</v>
       </c>
-      <c r="R36" s="94" t="n">
+      <c r="V36" s="94" t="n">
         <v>-0.11</v>
       </c>
-      <c r="S36" s="94" t="n">
+      <c r="W36" s="94" t="n">
         <v>-0.11</v>
       </c>
-      <c r="T36" s="94" t="n">
+      <c r="X36" s="94" t="n">
         <v>-0.71</v>
       </c>
-      <c r="U36" s="94" t="n">
+      <c r="Y36" s="94" t="n">
         <v>-1.09</v>
       </c>
-      <c r="V36" s="94" t="n">
+      <c r="Z36" s="94" t="n">
         <v>-2.16</v>
       </c>
-      <c r="W36" s="94" t="n">
+      <c r="AA36" s="94" t="n">
         <v>-1.76</v>
       </c>
-      <c r="X36" s="94" t="n">
+      <c r="AB36" s="94" t="n">
         <v>-2.08</v>
       </c>
-      <c r="Y36" s="94" t="n">
+      <c r="AC36" s="94" t="n">
         <v>-2.08</v>
       </c>
-      <c r="Z36" s="94" t="n">
+      <c r="AD36" s="94" t="n">
         <v>-0.79</v>
       </c>
-      <c r="AA36" s="94" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="AB36" s="94" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="AC36" s="94" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="AD36" s="94" t="n">
-        <v>-0.84</v>
-      </c>
       <c r="AE36" s="94" t="n">
-        <v>-0.84</v>
+        <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="95" t="inlineStr">
+      <c r="A37" s="76" t="inlineStr">
         <is>
           <t>vn:RS3</t>
         </is>
       </c>
       <c r="B37" s="94" t="n">
-        <v>85.3</v>
+        <v>47.07</v>
       </c>
       <c r="C37" s="94" t="n">
         <v>85.3</v>
@@ -10450,76 +10427,76 @@
         <v>85.3</v>
       </c>
       <c r="H37" s="94" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="I37" s="94" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="J37" s="94" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="K37" s="94" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="L37" s="94" t="n">
         <v>80.56</v>
       </c>
-      <c r="I37" s="94" t="n">
+      <c r="M37" s="94" t="n">
         <v>39.31</v>
       </c>
-      <c r="J37" s="94" t="n">
+      <c r="N37" s="94" t="n">
         <v>55.71</v>
       </c>
-      <c r="K37" s="94" t="n">
+      <c r="O37" s="94" t="n">
         <v>76.36</v>
       </c>
-      <c r="L37" s="94" t="n">
+      <c r="P37" s="94" t="n">
         <v>75.59</v>
       </c>
-      <c r="M37" s="94" t="n">
+      <c r="Q37" s="94" t="n">
         <v>75.59</v>
       </c>
-      <c r="N37" s="94" t="n">
+      <c r="R37" s="94" t="n">
         <v>63.48</v>
       </c>
-      <c r="O37" s="94" t="n">
+      <c r="S37" s="94" t="n">
         <v>47.6</v>
       </c>
-      <c r="P37" s="94" t="n">
+      <c r="T37" s="94" t="n">
         <v>21.39</v>
       </c>
-      <c r="Q37" s="94" t="n">
+      <c r="U37" s="94" t="n">
         <v>30.94</v>
       </c>
-      <c r="R37" s="94" t="n">
+      <c r="V37" s="94" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="S37" s="94" t="n">
+      <c r="W37" s="94" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="T37" s="94" t="n">
+      <c r="X37" s="94" t="n">
         <v>24.76</v>
       </c>
-      <c r="U37" s="94" t="n">
+      <c r="Y37" s="94" t="n">
         <v>37.84</v>
       </c>
-      <c r="V37" s="94" t="n">
+      <c r="Z37" s="94" t="n">
         <v>14.49</v>
       </c>
-      <c r="W37" s="94" t="n">
+      <c r="AA37" s="94" t="n">
         <v>11.22</v>
       </c>
-      <c r="X37" s="94" t="n">
+      <c r="AB37" s="94" t="n">
         <v>17.28</v>
       </c>
-      <c r="Y37" s="94" t="n">
+      <c r="AC37" s="94" t="n">
         <v>17.28</v>
       </c>
-      <c r="Z37" s="94" t="n">
+      <c r="AD37" s="94" t="n">
         <v>51.04</v>
       </c>
-      <c r="AA37" s="94" t="n">
-        <v>34.51</v>
-      </c>
-      <c r="AB37" s="94" t="n">
-        <v>34.51</v>
-      </c>
-      <c r="AC37" s="94" t="n">
-        <v>57.76</v>
-      </c>
-      <c r="AD37" s="94" t="n">
-        <v>78.84999999999999</v>
-      </c>
       <c r="AE37" s="94" t="n">
-        <v>78.84999999999999</v>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -10533,144 +10510,144 @@
           <t>red</t>
         </is>
       </c>
-      <c r="C38" s="92" t="inlineStr">
+      <c r="C38" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D38" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="E38" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F38" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D38" s="92" t="inlineStr">
+      <c r="H38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E38" s="93" t="inlineStr">
+      <c r="I38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F38" s="92" t="inlineStr">
+      <c r="J38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G38" s="92" t="inlineStr">
+      <c r="K38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H38" s="92" t="inlineStr">
+      <c r="L38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I38" s="92" t="inlineStr">
+      <c r="M38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J38" s="93" t="inlineStr">
+      <c r="N38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K38" s="92" t="inlineStr">
+      <c r="O38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L38" s="92" t="inlineStr">
+      <c r="P38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M38" s="92" t="inlineStr">
+      <c r="Q38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N38" s="92" t="inlineStr">
+      <c r="R38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O38" s="92" t="inlineStr">
+      <c r="S38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P38" s="93" t="inlineStr">
+      <c r="T38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q38" s="93" t="inlineStr">
+      <c r="U38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R38" s="93" t="inlineStr">
+      <c r="V38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S38" s="93" t="inlineStr">
+      <c r="W38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T38" s="93" t="inlineStr">
+      <c r="X38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U38" s="92" t="inlineStr">
+      <c r="Y38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V38" s="93" t="inlineStr">
+      <c r="Z38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W38" s="93" t="inlineStr">
+      <c r="AA38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X38" s="91" t="inlineStr">
+      <c r="AB38" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y38" s="91" t="inlineStr">
+      <c r="AC38" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z38" s="91" t="inlineStr">
+      <c r="AD38" s="91" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AA38" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB38" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC38" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD38" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AE38" s="92" t="inlineStr">
@@ -10686,94 +10663,94 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="C39" s="94" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="D39" s="94" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="E39" s="94" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="F39" s="94" t="n">
         <v>-2.57</v>
       </c>
-      <c r="C39" s="94" t="n">
+      <c r="G39" s="94" t="n">
         <v>-4</v>
       </c>
-      <c r="D39" s="94" t="n">
+      <c r="H39" s="94" t="n">
         <v>-4.39</v>
       </c>
-      <c r="E39" s="94" t="n">
+      <c r="I39" s="94" t="n">
         <v>-5.72</v>
       </c>
-      <c r="F39" s="94" t="n">
+      <c r="J39" s="94" t="n">
         <v>-5.2</v>
       </c>
-      <c r="G39" s="94" t="n">
+      <c r="K39" s="94" t="n">
         <v>-5.2</v>
       </c>
-      <c r="H39" s="94" t="n">
+      <c r="L39" s="94" t="n">
         <v>-4.36</v>
       </c>
-      <c r="I39" s="94" t="n">
+      <c r="M39" s="94" t="n">
         <v>-3.77</v>
       </c>
-      <c r="J39" s="94" t="n">
+      <c r="N39" s="94" t="n">
         <v>-5.28</v>
       </c>
-      <c r="K39" s="94" t="n">
+      <c r="O39" s="94" t="n">
         <v>-3.76</v>
       </c>
-      <c r="L39" s="94" t="n">
+      <c r="P39" s="94" t="n">
         <v>-4.49</v>
       </c>
-      <c r="M39" s="94" t="n">
+      <c r="Q39" s="94" t="n">
         <v>-4.49</v>
       </c>
-      <c r="N39" s="94" t="n">
+      <c r="R39" s="94" t="n">
         <v>-5.06</v>
       </c>
-      <c r="O39" s="94" t="n">
+      <c r="S39" s="94" t="n">
         <v>-5.54</v>
       </c>
-      <c r="P39" s="94" t="n">
+      <c r="T39" s="94" t="n">
         <v>-5.56</v>
       </c>
-      <c r="Q39" s="94" t="n">
+      <c r="U39" s="94" t="n">
         <v>-6.35</v>
       </c>
-      <c r="R39" s="94" t="n">
+      <c r="V39" s="94" t="n">
         <v>-5.43</v>
       </c>
-      <c r="S39" s="94" t="n">
+      <c r="W39" s="94" t="n">
         <v>-5.43</v>
       </c>
-      <c r="T39" s="94" t="n">
+      <c r="X39" s="94" t="n">
         <v>-5.31</v>
       </c>
-      <c r="U39" s="94" t="n">
+      <c r="Y39" s="94" t="n">
         <v>-3.97</v>
       </c>
-      <c r="V39" s="94" t="n">
+      <c r="Z39" s="94" t="n">
         <v>-4.18</v>
       </c>
-      <c r="W39" s="94" t="n">
+      <c r="AA39" s="94" t="n">
         <v>-4.3</v>
       </c>
-      <c r="X39" s="94" t="n">
+      <c r="AB39" s="94" t="n">
         <v>-2.95</v>
       </c>
-      <c r="Y39" s="94" t="n">
+      <c r="AC39" s="94" t="n">
         <v>-2.95</v>
       </c>
-      <c r="Z39" s="94" t="n">
+      <c r="AD39" s="94" t="n">
         <v>-1.36</v>
       </c>
-      <c r="AA39" s="94" t="n">
+      <c r="AE39" s="94" t="n">
         <v>-3.89</v>
-      </c>
-      <c r="AB39" s="94" t="n">
-        <v>-5.28</v>
-      </c>
-      <c r="AC39" s="94" t="n">
-        <v>-7.14</v>
-      </c>
-      <c r="AD39" s="94" t="n">
-        <v>-6.64</v>
-      </c>
-      <c r="AE39" s="94" t="n">
-        <v>-6.64</v>
       </c>
     </row>
     <row r="40">
@@ -10783,94 +10760,94 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="C40" s="94" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="D40" s="94" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="E40" s="94" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="F40" s="94" t="n">
         <v>-3.7</v>
       </c>
-      <c r="C40" s="94" t="n">
+      <c r="G40" s="94" t="n">
         <v>-2.98</v>
       </c>
-      <c r="D40" s="94" t="n">
+      <c r="H40" s="94" t="n">
         <v>-4.49</v>
       </c>
-      <c r="E40" s="94" t="n">
+      <c r="I40" s="94" t="n">
         <v>-4.11</v>
       </c>
-      <c r="F40" s="94" t="n">
+      <c r="J40" s="94" t="n">
         <v>-3.26</v>
       </c>
-      <c r="G40" s="94" t="n">
+      <c r="K40" s="94" t="n">
         <v>-3.26</v>
       </c>
-      <c r="H40" s="94" t="n">
+      <c r="L40" s="94" t="n">
         <v>-5.51</v>
       </c>
-      <c r="I40" s="94" t="n">
+      <c r="M40" s="94" t="n">
         <v>-6.67</v>
       </c>
-      <c r="J40" s="94" t="n">
+      <c r="N40" s="94" t="n">
         <v>-7.22</v>
       </c>
-      <c r="K40" s="94" t="n">
+      <c r="O40" s="94" t="n">
         <v>-5.38</v>
       </c>
-      <c r="L40" s="94" t="n">
+      <c r="P40" s="94" t="n">
         <v>-5.82</v>
       </c>
-      <c r="M40" s="94" t="n">
+      <c r="Q40" s="94" t="n">
         <v>-5.82</v>
       </c>
-      <c r="N40" s="94" t="n">
+      <c r="R40" s="94" t="n">
         <v>-5.27</v>
       </c>
-      <c r="O40" s="94" t="n">
+      <c r="S40" s="94" t="n">
         <v>-4.14</v>
       </c>
-      <c r="P40" s="94" t="n">
+      <c r="T40" s="94" t="n">
         <v>-4.55</v>
       </c>
-      <c r="Q40" s="94" t="n">
+      <c r="U40" s="94" t="n">
         <v>-5.1</v>
       </c>
-      <c r="R40" s="94" t="n">
+      <c r="V40" s="94" t="n">
         <v>-3.88</v>
       </c>
-      <c r="S40" s="94" t="n">
+      <c r="W40" s="94" t="n">
         <v>-3.88</v>
       </c>
-      <c r="T40" s="94" t="n">
+      <c r="X40" s="94" t="n">
         <v>-3.7</v>
       </c>
-      <c r="U40" s="94" t="n">
+      <c r="Y40" s="94" t="n">
         <v>-3.93</v>
       </c>
-      <c r="V40" s="94" t="n">
+      <c r="Z40" s="94" t="n">
         <v>-3.12</v>
       </c>
-      <c r="W40" s="94" t="n">
+      <c r="AA40" s="94" t="n">
         <v>-3.35</v>
       </c>
-      <c r="X40" s="94" t="n">
+      <c r="AB40" s="94" t="n">
         <v>-1.61</v>
       </c>
-      <c r="Y40" s="94" t="n">
+      <c r="AC40" s="94" t="n">
         <v>-1.61</v>
       </c>
-      <c r="Z40" s="94" t="n">
+      <c r="AD40" s="94" t="n">
         <v>0.06</v>
       </c>
-      <c r="AA40" s="94" t="n">
+      <c r="AE40" s="94" t="n">
         <v>-1.77</v>
-      </c>
-      <c r="AB40" s="94" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="AC40" s="94" t="n">
-        <v>-2.14</v>
-      </c>
-      <c r="AD40" s="94" t="n">
-        <v>-1.62</v>
-      </c>
-      <c r="AE40" s="94" t="n">
-        <v>-1.62</v>
       </c>
     </row>
     <row r="41">
@@ -10880,94 +10857,94 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
+        <v>51.83</v>
+      </c>
+      <c r="C41" s="94" t="n">
+        <v>55.73</v>
+      </c>
+      <c r="D41" s="94" t="n">
+        <v>55.73</v>
+      </c>
+      <c r="E41" s="94" t="n">
+        <v>55.68</v>
+      </c>
+      <c r="F41" s="94" t="n">
         <v>48.37</v>
       </c>
-      <c r="C41" s="94" t="n">
+      <c r="G41" s="94" t="n">
         <v>45.92</v>
       </c>
-      <c r="D41" s="94" t="n">
+      <c r="H41" s="94" t="n">
         <v>38.59</v>
       </c>
-      <c r="E41" s="94" t="n">
+      <c r="I41" s="94" t="n">
         <v>31.52</v>
       </c>
-      <c r="F41" s="94" t="n">
+      <c r="J41" s="94" t="n">
         <v>37.51</v>
       </c>
-      <c r="G41" s="94" t="n">
+      <c r="K41" s="94" t="n">
         <v>37.51</v>
       </c>
-      <c r="H41" s="94" t="n">
+      <c r="L41" s="94" t="n">
         <v>40.26</v>
       </c>
-      <c r="I41" s="94" t="n">
+      <c r="M41" s="94" t="n">
         <v>38.85</v>
       </c>
-      <c r="J41" s="94" t="n">
+      <c r="N41" s="94" t="n">
         <v>31.71</v>
       </c>
-      <c r="K41" s="94" t="n">
+      <c r="O41" s="94" t="n">
         <v>41.13</v>
       </c>
-      <c r="L41" s="94" t="n">
+      <c r="P41" s="94" t="n">
         <v>34.71</v>
       </c>
-      <c r="M41" s="94" t="n">
+      <c r="Q41" s="94" t="n">
         <v>34.71</v>
       </c>
-      <c r="N41" s="94" t="n">
+      <c r="R41" s="94" t="n">
         <v>38.21</v>
       </c>
-      <c r="O41" s="94" t="n">
+      <c r="S41" s="94" t="n">
         <v>33.68</v>
       </c>
-      <c r="P41" s="94" t="n">
+      <c r="T41" s="94" t="n">
         <v>30.45</v>
       </c>
-      <c r="Q41" s="94" t="n">
+      <c r="U41" s="94" t="n">
         <v>28.07</v>
       </c>
-      <c r="R41" s="94" t="n">
+      <c r="V41" s="94" t="n">
         <v>34.68</v>
       </c>
-      <c r="S41" s="94" t="n">
+      <c r="W41" s="94" t="n">
         <v>34.68</v>
       </c>
-      <c r="T41" s="94" t="n">
+      <c r="X41" s="94" t="n">
         <v>36.46</v>
       </c>
-      <c r="U41" s="94" t="n">
+      <c r="Y41" s="94" t="n">
         <v>40.56</v>
       </c>
-      <c r="V41" s="94" t="n">
+      <c r="Z41" s="94" t="n">
         <v>40.95</v>
       </c>
-      <c r="W41" s="94" t="n">
+      <c r="AA41" s="94" t="n">
         <v>38.45</v>
       </c>
-      <c r="X41" s="94" t="n">
+      <c r="AB41" s="94" t="n">
         <v>48.38</v>
       </c>
-      <c r="Y41" s="94" t="n">
+      <c r="AC41" s="94" t="n">
         <v>48.38</v>
       </c>
-      <c r="Z41" s="94" t="n">
+      <c r="AD41" s="94" t="n">
         <v>55.82</v>
       </c>
-      <c r="AA41" s="94" t="n">
+      <c r="AE41" s="94" t="n">
         <v>39</v>
-      </c>
-      <c r="AB41" s="94" t="n">
-        <v>33.12</v>
-      </c>
-      <c r="AC41" s="94" t="n">
-        <v>34</v>
-      </c>
-      <c r="AD41" s="94" t="n">
-        <v>37.69</v>
-      </c>
-      <c r="AE41" s="94" t="n">
-        <v>37.69</v>
       </c>
     </row>
     <row r="42">
@@ -10996,135 +10973,133 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="F42" s="91" t="inlineStr">
+      <c r="F42" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G42" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H42" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I42" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G42" s="91" t="inlineStr">
+      <c r="K42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H42" s="91" t="inlineStr">
+      <c r="L42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I42" s="91" t="inlineStr">
+      <c r="M42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J42" s="91" t="inlineStr">
+      <c r="N42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K42" s="91" t="inlineStr">
+      <c r="O42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L42" s="91" t="inlineStr">
+      <c r="P42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M42" s="91" t="inlineStr">
+      <c r="Q42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N42" s="91" t="inlineStr">
+      <c r="R42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O42" s="91" t="inlineStr">
+      <c r="S42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P42" s="92" t="inlineStr">
+      <c r="T42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q42" s="92" t="inlineStr">
+      <c r="U42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R42" s="92" t="inlineStr">
+      <c r="V42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S42" s="92" t="inlineStr">
+      <c r="W42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T42" s="91" t="inlineStr">
+      <c r="X42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U42" s="91" t="inlineStr">
+      <c r="Y42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V42" s="91" t="inlineStr">
+      <c r="Z42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W42" s="91" t="inlineStr">
+      <c r="AA42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X42" s="93" t="inlineStr">
+      <c r="AB42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y42" s="93" t="inlineStr">
+      <c r="AC42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z42" s="91" t="inlineStr">
+      <c r="AD42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA42" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB42" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC42" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD42" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE42" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
+      <c r="AE42" s="92" t="n">
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -11134,94 +11109,94 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="C43" s="94" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="D43" s="94" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="E43" s="94" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="F43" s="94" t="n">
         <v>7.73</v>
       </c>
-      <c r="C43" s="94" t="n">
+      <c r="G43" s="94" t="n">
         <v>6.25</v>
       </c>
-      <c r="D43" s="94" t="n">
+      <c r="H43" s="94" t="n">
         <v>7.44</v>
       </c>
-      <c r="E43" s="94" t="n">
+      <c r="I43" s="94" t="n">
         <v>6.44</v>
       </c>
-      <c r="F43" s="94" t="n">
+      <c r="J43" s="94" t="n">
         <v>5.55</v>
       </c>
-      <c r="G43" s="94" t="n">
+      <c r="K43" s="94" t="n">
         <v>5.55</v>
       </c>
-      <c r="H43" s="94" t="n">
+      <c r="L43" s="94" t="n">
         <v>4.44</v>
       </c>
-      <c r="I43" s="94" t="n">
+      <c r="M43" s="94" t="n">
         <v>4.53</v>
       </c>
-      <c r="J43" s="94" t="n">
+      <c r="N43" s="94" t="n">
         <v>3.57</v>
       </c>
-      <c r="K43" s="94" t="n">
+      <c r="O43" s="94" t="n">
         <v>3.15</v>
       </c>
-      <c r="L43" s="94" t="n">
+      <c r="P43" s="94" t="n">
         <v>2.32</v>
       </c>
-      <c r="M43" s="94" t="n">
+      <c r="Q43" s="94" t="n">
         <v>2.32</v>
       </c>
-      <c r="N43" s="94" t="n">
+      <c r="R43" s="94" t="n">
         <v>1.31</v>
       </c>
-      <c r="O43" s="94" t="n">
+      <c r="S43" s="94" t="n">
         <v>-1.82</v>
       </c>
-      <c r="P43" s="94" t="n">
+      <c r="T43" s="94" t="n">
         <v>-2.11</v>
       </c>
-      <c r="Q43" s="94" t="n">
+      <c r="U43" s="94" t="n">
         <v>-1.11</v>
       </c>
-      <c r="R43" s="94" t="n">
+      <c r="V43" s="94" t="n">
         <v>-1.21</v>
       </c>
-      <c r="S43" s="94" t="n">
+      <c r="W43" s="94" t="n">
         <v>-1.21</v>
       </c>
-      <c r="T43" s="94" t="n">
+      <c r="X43" s="94" t="n">
         <v>-1.47</v>
       </c>
-      <c r="U43" s="94" t="n">
+      <c r="Y43" s="94" t="n">
         <v>-1.66</v>
       </c>
-      <c r="V43" s="94" t="n">
+      <c r="Z43" s="94" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="W43" s="94" t="n">
+      <c r="AA43" s="94" t="n">
         <v>-1.51</v>
       </c>
-      <c r="X43" s="94" t="n">
+      <c r="AB43" s="94" t="n">
         <v>-3.18</v>
       </c>
-      <c r="Y43" s="94" t="n">
+      <c r="AC43" s="94" t="n">
         <v>-3.18</v>
       </c>
-      <c r="Z43" s="94" t="n">
+      <c r="AD43" s="94" t="n">
         <v>-2.41</v>
       </c>
-      <c r="AA43" s="94" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="AB43" s="94" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="AC43" s="94" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="AD43" s="94" t="n">
-        <v>-2.93</v>
-      </c>
       <c r="AE43" s="94" t="n">
-        <v>-2.93</v>
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -11231,94 +11206,94 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="C44" s="94" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="D44" s="94" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="E44" s="94" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="F44" s="94" t="n">
         <v>9.529999999999999</v>
       </c>
-      <c r="C44" s="94" t="n">
+      <c r="G44" s="94" t="n">
         <v>8.289999999999999</v>
       </c>
-      <c r="D44" s="94" t="n">
+      <c r="H44" s="94" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="E44" s="94" t="n">
+      <c r="I44" s="94" t="n">
         <v>8.82</v>
       </c>
-      <c r="F44" s="94" t="n">
+      <c r="J44" s="94" t="n">
         <v>11.19</v>
       </c>
-      <c r="G44" s="94" t="n">
+      <c r="K44" s="94" t="n">
         <v>11.19</v>
       </c>
-      <c r="H44" s="94" t="n">
+      <c r="L44" s="94" t="n">
         <v>10.4</v>
       </c>
-      <c r="I44" s="94" t="n">
+      <c r="M44" s="94" t="n">
         <v>8.08</v>
       </c>
-      <c r="J44" s="94" t="n">
+      <c r="N44" s="94" t="n">
         <v>5.43</v>
       </c>
-      <c r="K44" s="94" t="n">
+      <c r="O44" s="94" t="n">
         <v>2.68</v>
       </c>
-      <c r="L44" s="94" t="n">
+      <c r="P44" s="94" t="n">
         <v>3.14</v>
       </c>
-      <c r="M44" s="94" t="n">
+      <c r="Q44" s="94" t="n">
         <v>3.14</v>
       </c>
-      <c r="N44" s="94" t="n">
+      <c r="R44" s="94" t="n">
         <v>2.56</v>
       </c>
-      <c r="O44" s="94" t="n">
+      <c r="S44" s="94" t="n">
         <v>-0.57</v>
       </c>
-      <c r="P44" s="94" t="n">
+      <c r="T44" s="94" t="n">
         <v>-0.05</v>
       </c>
-      <c r="Q44" s="94" t="n">
+      <c r="U44" s="94" t="n">
         <v>-1.4</v>
       </c>
-      <c r="R44" s="94" t="n">
+      <c r="V44" s="94" t="n">
         <v>-2.21</v>
       </c>
-      <c r="S44" s="94" t="n">
+      <c r="W44" s="94" t="n">
         <v>-2.21</v>
       </c>
-      <c r="T44" s="94" t="n">
+      <c r="X44" s="94" t="n">
         <v>-1.73</v>
       </c>
-      <c r="U44" s="94" t="n">
+      <c r="Y44" s="94" t="n">
         <v>-1.09</v>
       </c>
-      <c r="V44" s="94" t="n">
+      <c r="Z44" s="94" t="n">
         <v>-1.28</v>
       </c>
-      <c r="W44" s="94" t="n">
+      <c r="AA44" s="94" t="n">
         <v>-1.65</v>
       </c>
-      <c r="X44" s="94" t="n">
+      <c r="AB44" s="94" t="n">
         <v>-3.93</v>
       </c>
-      <c r="Y44" s="94" t="n">
+      <c r="AC44" s="94" t="n">
         <v>-3.93</v>
       </c>
-      <c r="Z44" s="94" t="n">
+      <c r="AD44" s="94" t="n">
         <v>-3.13</v>
       </c>
-      <c r="AA44" s="94" t="n">
-        <v>-4.45</v>
-      </c>
-      <c r="AB44" s="94" t="n">
-        <v>-4.45</v>
-      </c>
-      <c r="AC44" s="94" t="n">
-        <v>-4.11</v>
-      </c>
-      <c r="AD44" s="94" t="n">
-        <v>-2.88</v>
-      </c>
       <c r="AE44" s="94" t="n">
-        <v>-2.88</v>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -11328,94 +11303,94 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
+        <v>48.42</v>
+      </c>
+      <c r="C45" s="94" t="n">
+        <v>80.51000000000001</v>
+      </c>
+      <c r="D45" s="94" t="n">
+        <v>80.51000000000001</v>
+      </c>
+      <c r="E45" s="94" t="n">
+        <v>80.51000000000001</v>
+      </c>
+      <c r="F45" s="94" t="n">
         <v>79.54000000000001</v>
       </c>
-      <c r="C45" s="94" t="n">
+      <c r="G45" s="94" t="n">
         <v>69.76000000000001</v>
       </c>
-      <c r="D45" s="94" t="n">
+      <c r="H45" s="94" t="n">
         <v>80.88</v>
       </c>
-      <c r="E45" s="94" t="n">
+      <c r="I45" s="94" t="n">
         <v>84.89</v>
       </c>
-      <c r="F45" s="94" t="n">
+      <c r="J45" s="94" t="n">
         <v>93.34</v>
       </c>
-      <c r="G45" s="94" t="n">
+      <c r="K45" s="94" t="n">
         <v>93.34</v>
       </c>
-      <c r="H45" s="94" t="n">
+      <c r="L45" s="94" t="n">
         <v>92.31999999999999</v>
       </c>
-      <c r="I45" s="94" t="n">
+      <c r="M45" s="94" t="n">
         <v>90.48999999999999</v>
       </c>
-      <c r="J45" s="94" t="n">
+      <c r="N45" s="94" t="n">
         <v>87.65000000000001</v>
       </c>
-      <c r="K45" s="94" t="n">
+      <c r="O45" s="94" t="n">
         <v>85.73</v>
       </c>
-      <c r="L45" s="94" t="n">
+      <c r="P45" s="94" t="n">
         <v>84.51000000000001</v>
       </c>
-      <c r="M45" s="94" t="n">
+      <c r="Q45" s="94" t="n">
         <v>84.51000000000001</v>
       </c>
-      <c r="N45" s="94" t="n">
+      <c r="R45" s="94" t="n">
         <v>80.23</v>
       </c>
-      <c r="O45" s="94" t="n">
+      <c r="S45" s="94" t="n">
         <v>62.6</v>
       </c>
-      <c r="P45" s="94" t="n">
+      <c r="T45" s="94" t="n">
         <v>51.62</v>
       </c>
-      <c r="Q45" s="94" t="n">
+      <c r="U45" s="94" t="n">
         <v>48.02</v>
       </c>
-      <c r="R45" s="94" t="n">
+      <c r="V45" s="94" t="n">
         <v>52.7</v>
       </c>
-      <c r="S45" s="94" t="n">
+      <c r="W45" s="94" t="n">
         <v>52.7</v>
       </c>
-      <c r="T45" s="94" t="n">
+      <c r="X45" s="94" t="n">
         <v>66.38</v>
       </c>
-      <c r="U45" s="94" t="n">
+      <c r="Y45" s="94" t="n">
         <v>61.23</v>
       </c>
-      <c r="V45" s="94" t="n">
+      <c r="Z45" s="94" t="n">
         <v>69.54000000000001</v>
       </c>
-      <c r="W45" s="94" t="n">
+      <c r="AA45" s="94" t="n">
         <v>65.06</v>
       </c>
-      <c r="X45" s="94" t="n">
+      <c r="AB45" s="94" t="n">
         <v>37.52</v>
       </c>
-      <c r="Y45" s="94" t="n">
+      <c r="AC45" s="94" t="n">
         <v>37.52</v>
       </c>
-      <c r="Z45" s="94" t="n">
+      <c r="AD45" s="94" t="n">
         <v>65.84</v>
       </c>
-      <c r="AA45" s="94" t="n">
-        <v>63.25</v>
-      </c>
-      <c r="AB45" s="94" t="n">
-        <v>63.25</v>
-      </c>
-      <c r="AC45" s="94" t="n">
-        <v>46.49</v>
-      </c>
-      <c r="AD45" s="94" t="n">
-        <v>60.14</v>
-      </c>
       <c r="AE45" s="94" t="n">
-        <v>60.14</v>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -11424,155 +11399,153 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="91" t="inlineStr">
+      <c r="B46" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C46" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D46" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E46" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="C46" s="91" t="inlineStr">
+      <c r="G46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D46" s="92" t="inlineStr">
+      <c r="H46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E46" s="92" t="inlineStr">
+      <c r="I46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F46" s="92" t="inlineStr">
+      <c r="J46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G46" s="92" t="inlineStr">
+      <c r="K46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H46" s="91" t="inlineStr">
+      <c r="L46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I46" s="91" t="inlineStr">
+      <c r="M46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J46" s="91" t="inlineStr">
+      <c r="N46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K46" s="91" t="inlineStr">
+      <c r="O46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L46" s="91" t="inlineStr">
+      <c r="P46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M46" s="91" t="inlineStr">
+      <c r="Q46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N46" s="91" t="inlineStr">
+      <c r="R46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O46" s="91" t="inlineStr">
+      <c r="S46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P46" s="91" t="inlineStr">
+      <c r="T46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q46" s="93" t="inlineStr">
+      <c r="U46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R46" s="92" t="inlineStr">
+      <c r="V46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S46" s="92" t="inlineStr">
+      <c r="W46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T46" s="91" t="inlineStr">
+      <c r="X46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U46" s="91" t="inlineStr">
+      <c r="Y46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V46" s="91" t="inlineStr">
+      <c r="Z46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W46" s="91" t="inlineStr">
+      <c r="AA46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X46" s="93" t="inlineStr">
+      <c r="AB46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y46" s="93" t="inlineStr">
+      <c r="AC46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z46" s="92" t="inlineStr">
+      <c r="AD46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA46" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB46" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC46" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD46" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE46" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
+      <c r="AE46" s="92" t="n">
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -11582,94 +11555,94 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="C47" s="94" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="D47" s="94" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="E47" s="94" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="F47" s="94" t="n">
         <v>13.89</v>
       </c>
-      <c r="C47" s="94" t="n">
+      <c r="G47" s="94" t="n">
         <v>12.36</v>
       </c>
-      <c r="D47" s="94" t="n">
+      <c r="H47" s="94" t="n">
         <v>10.02</v>
       </c>
-      <c r="E47" s="94" t="n">
+      <c r="I47" s="94" t="n">
         <v>8.960000000000001</v>
       </c>
-      <c r="F47" s="94" t="n">
+      <c r="J47" s="94" t="n">
         <v>9.92</v>
       </c>
-      <c r="G47" s="94" t="n">
+      <c r="K47" s="94" t="n">
         <v>9.92</v>
       </c>
-      <c r="H47" s="94" t="n">
+      <c r="L47" s="94" t="n">
         <v>10.12</v>
       </c>
-      <c r="I47" s="94" t="n">
+      <c r="M47" s="94" t="n">
         <v>9.68</v>
       </c>
-      <c r="J47" s="94" t="n">
+      <c r="N47" s="94" t="n">
         <v>8.34</v>
       </c>
-      <c r="K47" s="94" t="n">
+      <c r="O47" s="94" t="n">
         <v>7.86</v>
       </c>
-      <c r="L47" s="94" t="n">
+      <c r="P47" s="94" t="n">
         <v>6.34</v>
       </c>
-      <c r="M47" s="94" t="n">
+      <c r="Q47" s="94" t="n">
         <v>6.34</v>
       </c>
-      <c r="N47" s="94" t="n">
+      <c r="R47" s="94" t="n">
         <v>5.47</v>
       </c>
-      <c r="O47" s="94" t="n">
+      <c r="S47" s="94" t="n">
         <v>5.88</v>
       </c>
-      <c r="P47" s="94" t="n">
+      <c r="T47" s="94" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q47" s="94" t="n">
+      <c r="U47" s="94" t="n">
         <v>3.2</v>
       </c>
-      <c r="R47" s="94" t="n">
+      <c r="V47" s="94" t="n">
         <v>4.34</v>
       </c>
-      <c r="S47" s="94" t="n">
+      <c r="W47" s="94" t="n">
         <v>4.34</v>
       </c>
-      <c r="T47" s="94" t="n">
+      <c r="X47" s="94" t="n">
         <v>5.76</v>
       </c>
-      <c r="U47" s="94" t="n">
+      <c r="Y47" s="94" t="n">
         <v>5.58</v>
       </c>
-      <c r="V47" s="94" t="n">
+      <c r="Z47" s="94" t="n">
         <v>6.68</v>
       </c>
-      <c r="W47" s="94" t="n">
+      <c r="AA47" s="94" t="n">
         <v>5.82</v>
       </c>
-      <c r="X47" s="94" t="n">
+      <c r="AB47" s="94" t="n">
         <v>4.11</v>
       </c>
-      <c r="Y47" s="94" t="n">
+      <c r="AC47" s="94" t="n">
         <v>4.11</v>
       </c>
-      <c r="Z47" s="94" t="n">
+      <c r="AD47" s="94" t="n">
         <v>5.31</v>
       </c>
-      <c r="AA47" s="94" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AB47" s="94" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AC47" s="94" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AD47" s="94" t="n">
-        <v>4.01</v>
-      </c>
       <c r="AE47" s="94" t="n">
-        <v>4.01</v>
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -11679,94 +11652,94 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="C48" s="94" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="D48" s="94" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="E48" s="94" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="F48" s="94" t="n">
         <v>22.89</v>
       </c>
-      <c r="C48" s="94" t="n">
+      <c r="G48" s="94" t="n">
         <v>22.83</v>
       </c>
-      <c r="D48" s="94" t="n">
+      <c r="H48" s="94" t="n">
         <v>23.49</v>
       </c>
-      <c r="E48" s="94" t="n">
+      <c r="I48" s="94" t="n">
         <v>22.74</v>
       </c>
-      <c r="F48" s="94" t="n">
+      <c r="J48" s="94" t="n">
         <v>21.14</v>
       </c>
-      <c r="G48" s="94" t="n">
+      <c r="K48" s="94" t="n">
         <v>21.14</v>
       </c>
-      <c r="H48" s="94" t="n">
+      <c r="L48" s="94" t="n">
         <v>18.41</v>
       </c>
-      <c r="I48" s="94" t="n">
+      <c r="M48" s="94" t="n">
         <v>14.83</v>
       </c>
-      <c r="J48" s="94" t="n">
+      <c r="N48" s="94" t="n">
         <v>14.29</v>
       </c>
-      <c r="K48" s="94" t="n">
+      <c r="O48" s="94" t="n">
         <v>14.57</v>
       </c>
-      <c r="L48" s="94" t="n">
+      <c r="P48" s="94" t="n">
         <v>13.5</v>
       </c>
-      <c r="M48" s="94" t="n">
+      <c r="Q48" s="94" t="n">
         <v>13.5</v>
       </c>
-      <c r="N48" s="94" t="n">
+      <c r="R48" s="94" t="n">
         <v>12.88</v>
       </c>
-      <c r="O48" s="94" t="n">
+      <c r="S48" s="94" t="n">
         <v>11.9</v>
       </c>
-      <c r="P48" s="94" t="n">
+      <c r="T48" s="94" t="n">
         <v>9.23</v>
       </c>
-      <c r="Q48" s="94" t="n">
+      <c r="U48" s="94" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="R48" s="94" t="n">
+      <c r="V48" s="94" t="n">
         <v>11.24</v>
       </c>
-      <c r="S48" s="94" t="n">
+      <c r="W48" s="94" t="n">
         <v>11.24</v>
       </c>
-      <c r="T48" s="94" t="n">
+      <c r="X48" s="94" t="n">
         <v>10.69</v>
       </c>
-      <c r="U48" s="94" t="n">
+      <c r="Y48" s="94" t="n">
         <v>10.27</v>
       </c>
-      <c r="V48" s="94" t="n">
+      <c r="Z48" s="94" t="n">
         <v>9.84</v>
       </c>
-      <c r="W48" s="94" t="n">
+      <c r="AA48" s="94" t="n">
         <v>8.74</v>
       </c>
-      <c r="X48" s="94" t="n">
+      <c r="AB48" s="94" t="n">
         <v>6.18</v>
       </c>
-      <c r="Y48" s="94" t="n">
+      <c r="AC48" s="94" t="n">
         <v>6.18</v>
       </c>
-      <c r="Z48" s="94" t="n">
+      <c r="AD48" s="94" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="AA48" s="94" t="n">
-        <v>8.16</v>
-      </c>
-      <c r="AB48" s="94" t="n">
-        <v>8.16</v>
-      </c>
-      <c r="AC48" s="94" t="n">
-        <v>8.16</v>
-      </c>
-      <c r="AD48" s="94" t="n">
-        <v>9.59</v>
-      </c>
       <c r="AE48" s="94" t="n">
-        <v>9.59</v>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -11776,107 +11749,107 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
+        <v>54.37</v>
+      </c>
+      <c r="C49" s="94" t="n">
+        <v>87.03</v>
+      </c>
+      <c r="D49" s="94" t="n">
+        <v>87.03</v>
+      </c>
+      <c r="E49" s="94" t="n">
+        <v>87.03</v>
+      </c>
+      <c r="F49" s="94" t="n">
         <v>86.93000000000001</v>
       </c>
-      <c r="C49" s="94" t="n">
+      <c r="G49" s="94" t="n">
         <v>85.23</v>
       </c>
-      <c r="D49" s="94" t="n">
+      <c r="H49" s="94" t="n">
         <v>80.29000000000001</v>
       </c>
-      <c r="E49" s="94" t="n">
+      <c r="I49" s="94" t="n">
         <v>75.37</v>
       </c>
-      <c r="F49" s="94" t="n">
+      <c r="J49" s="94" t="n">
         <v>89.53</v>
       </c>
-      <c r="G49" s="94" t="n">
+      <c r="K49" s="94" t="n">
         <v>89.53</v>
       </c>
-      <c r="H49" s="94" t="n">
+      <c r="L49" s="94" t="n">
         <v>91.64</v>
       </c>
-      <c r="I49" s="94" t="n">
+      <c r="M49" s="94" t="n">
         <v>89.73</v>
       </c>
-      <c r="J49" s="94" t="n">
+      <c r="N49" s="94" t="n">
         <v>86.16</v>
       </c>
-      <c r="K49" s="94" t="n">
+      <c r="O49" s="94" t="n">
         <v>85.12</v>
       </c>
-      <c r="L49" s="94" t="n">
+      <c r="P49" s="94" t="n">
         <v>83.34999999999999</v>
       </c>
-      <c r="M49" s="94" t="n">
+      <c r="Q49" s="94" t="n">
         <v>83.34999999999999</v>
       </c>
-      <c r="N49" s="94" t="n">
+      <c r="R49" s="94" t="n">
         <v>76.81</v>
       </c>
-      <c r="O49" s="94" t="n">
+      <c r="S49" s="94" t="n">
         <v>74.04000000000001</v>
       </c>
-      <c r="P49" s="94" t="n">
+      <c r="T49" s="94" t="n">
         <v>58.54</v>
       </c>
-      <c r="Q49" s="94" t="n">
+      <c r="U49" s="94" t="n">
         <v>46.37</v>
       </c>
-      <c r="R49" s="94" t="n">
+      <c r="V49" s="94" t="n">
         <v>54.22</v>
       </c>
-      <c r="S49" s="94" t="n">
+      <c r="W49" s="94" t="n">
         <v>54.22</v>
       </c>
-      <c r="T49" s="94" t="n">
+      <c r="X49" s="94" t="n">
         <v>65.81999999999999</v>
       </c>
-      <c r="U49" s="94" t="n">
+      <c r="Y49" s="94" t="n">
         <v>67.31999999999999</v>
       </c>
-      <c r="V49" s="94" t="n">
+      <c r="Z49" s="94" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="W49" s="94" t="n">
+      <c r="AA49" s="94" t="n">
         <v>62.55</v>
       </c>
-      <c r="X49" s="94" t="n">
+      <c r="AB49" s="94" t="n">
         <v>39.09</v>
       </c>
-      <c r="Y49" s="94" t="n">
+      <c r="AC49" s="94" t="n">
         <v>39.09</v>
       </c>
-      <c r="Z49" s="94" t="n">
+      <c r="AD49" s="94" t="n">
         <v>48.84</v>
       </c>
-      <c r="AA49" s="94" t="n">
-        <v>35.85</v>
-      </c>
-      <c r="AB49" s="94" t="n">
-        <v>35.85</v>
-      </c>
-      <c r="AC49" s="94" t="n">
-        <v>35.85</v>
-      </c>
-      <c r="AD49" s="94" t="n">
-        <v>41.58</v>
-      </c>
       <c r="AE49" s="94" t="n">
-        <v>41.58</v>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：</t>
+          <t>今日买报：us500:RS2:15.04&lt;=22;ixic:RS2:11.59&lt;=38</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:75.39&gt;=73;vn:RS3:85.3&gt;=85;dax30:RNG60:13.89&gt;=10;dax30:RNG120:22.89&gt;=20</t>
+          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:74.2&gt;=73;dax30:RNG60:11.79&gt;=10;dax30:RNG120:20.75&gt;=20</t>
         </is>
       </c>
     </row>
@@ -15477,13 +15450,13 @@
       <c r="G2" s="36" t="n">
         <v>66</v>
       </c>
-      <c r="H2" s="96" t="n">
+      <c r="H2" s="97" t="n">
         <v>22.3514585</v>
       </c>
       <c r="I2" s="36" t="n">
         <v>7.06</v>
       </c>
-      <c r="J2" s="97">
+      <c r="J2" s="98">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -15515,13 +15488,13 @@
       <c r="G3" s="39" t="n">
         <v>73</v>
       </c>
-      <c r="H3" s="98" t="n">
+      <c r="H3" s="99" t="n">
         <v>35.0298984</v>
       </c>
       <c r="I3" s="39" t="n">
         <v>11.41</v>
       </c>
-      <c r="J3" s="97">
+      <c r="J3" s="98">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -15553,13 +15526,13 @@
       <c r="G4" s="39" t="n">
         <v>85</v>
       </c>
-      <c r="H4" s="98" t="n">
+      <c r="H4" s="99" t="n">
         <v>122.4911655</v>
       </c>
       <c r="I4" s="39" t="n">
         <v>76.98</v>
       </c>
-      <c r="J4" s="99">
+      <c r="J4" s="100">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -15591,13 +15564,13 @@
       <c r="G5" s="39" t="n">
         <v>96</v>
       </c>
-      <c r="H5" s="98" t="n">
+      <c r="H5" s="99" t="n">
         <v>136.13543</v>
       </c>
       <c r="I5" s="39" t="n">
         <v>100.05</v>
       </c>
-      <c r="J5" s="99">
+      <c r="J5" s="100">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -15629,13 +15602,13 @@
       <c r="G6" s="39" t="n">
         <v>95</v>
       </c>
-      <c r="H6" s="98" t="n">
+      <c r="H6" s="99" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I6" s="39" t="n">
         <v>44.37</v>
       </c>
-      <c r="J6" s="99">
+      <c r="J6" s="100">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -15667,13 +15640,13 @@
       <c r="G7" s="39" t="n">
         <v>86</v>
       </c>
-      <c r="H7" s="98" t="n">
+      <c r="H7" s="99" t="n">
         <v>123.8525927</v>
       </c>
       <c r="I7" s="39" t="n">
         <v>63.41</v>
       </c>
-      <c r="J7" s="99">
+      <c r="J7" s="100">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -15705,13 +15678,13 @@
       <c r="G8" s="39" t="n">
         <v>87</v>
       </c>
-      <c r="H8" s="98" t="n">
+      <c r="H8" s="99" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I8" s="39" t="n">
         <v>26.39</v>
       </c>
-      <c r="J8" s="99">
+      <c r="J8" s="100">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -15743,13 +15716,13 @@
       <c r="G9" s="39" t="n">
         <v>83</v>
       </c>
-      <c r="H9" s="98" t="n">
+      <c r="H9" s="99" t="n">
         <v>47.02060524</v>
       </c>
       <c r="I9" s="39" t="n">
         <v>37.82</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="100">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -15780,13 +15753,13 @@
       <c r="G10" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="H10" s="100" t="n">
+      <c r="H10" s="101" t="n">
         <v>27.8860732</v>
       </c>
       <c r="I10" s="24" t="n">
         <v>-10.97</v>
       </c>
-      <c r="J10" s="101" t="n">
+      <c r="J10" s="102" t="n">
         <v>0.278860732</v>
       </c>
     </row>
@@ -15817,13 +15790,13 @@
       <c r="G11" s="24" t="n">
         <v>93</v>
       </c>
-      <c r="H11" s="100" t="n">
+      <c r="H11" s="101" t="n">
         <v>17.4948656</v>
       </c>
       <c r="I11" s="24" t="n">
         <v>-7.7</v>
       </c>
-      <c r="J11" s="101">
+      <c r="J11" s="102">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -6342,152 +6342,152 @@
       </c>
       <c r="B1" s="77" t="inlineStr">
         <is>
+          <t>250204</t>
+        </is>
+      </c>
+      <c r="C1" s="77" t="inlineStr">
+        <is>
           <t>250203</t>
         </is>
       </c>
-      <c r="C1" s="77" t="inlineStr">
+      <c r="D1" s="77" t="inlineStr">
         <is>
           <t>250202</t>
         </is>
       </c>
-      <c r="D1" s="77" t="inlineStr">
+      <c r="E1" s="77" t="inlineStr">
         <is>
           <t>250201</t>
         </is>
       </c>
-      <c r="E1" s="77" t="inlineStr">
+      <c r="F1" s="77" t="inlineStr">
         <is>
           <t>250131</t>
         </is>
       </c>
-      <c r="F1" s="77" t="inlineStr">
+      <c r="G1" s="77" t="inlineStr">
         <is>
           <t>250130</t>
         </is>
       </c>
-      <c r="G1" s="77" t="inlineStr">
+      <c r="H1" s="77" t="inlineStr">
         <is>
           <t>250129</t>
         </is>
       </c>
-      <c r="H1" s="77" t="inlineStr">
+      <c r="I1" s="77" t="inlineStr">
         <is>
           <t>250128</t>
         </is>
       </c>
-      <c r="I1" s="77" t="inlineStr">
+      <c r="J1" s="77" t="inlineStr">
         <is>
           <t>250127</t>
         </is>
       </c>
-      <c r="J1" s="77" t="inlineStr">
+      <c r="K1" s="77" t="inlineStr">
         <is>
           <t>250126</t>
         </is>
       </c>
-      <c r="K1" s="77" t="inlineStr">
+      <c r="L1" s="77" t="inlineStr">
         <is>
           <t>250124</t>
         </is>
       </c>
-      <c r="L1" s="77" t="inlineStr">
+      <c r="M1" s="77" t="inlineStr">
         <is>
           <t>250123</t>
         </is>
       </c>
-      <c r="M1" s="77" t="inlineStr">
+      <c r="N1" s="77" t="inlineStr">
         <is>
           <t>250122</t>
         </is>
       </c>
-      <c r="N1" s="77" t="inlineStr">
+      <c r="O1" s="77" t="inlineStr">
         <is>
           <t>250121</t>
         </is>
       </c>
-      <c r="O1" s="77" t="inlineStr">
+      <c r="P1" s="77" t="inlineStr">
         <is>
           <t>250120</t>
         </is>
       </c>
-      <c r="P1" s="77" t="inlineStr">
+      <c r="Q1" s="77" t="inlineStr">
         <is>
           <t>250119</t>
         </is>
       </c>
-      <c r="Q1" s="77" t="inlineStr">
+      <c r="R1" s="77" t="inlineStr">
         <is>
           <t>250117</t>
         </is>
       </c>
-      <c r="R1" s="77" t="inlineStr">
+      <c r="S1" s="77" t="inlineStr">
         <is>
           <t>250116</t>
         </is>
       </c>
-      <c r="S1" s="77" t="inlineStr">
+      <c r="T1" s="77" t="inlineStr">
         <is>
           <t>250115</t>
         </is>
       </c>
-      <c r="T1" s="77" t="inlineStr">
+      <c r="U1" s="77" t="inlineStr">
         <is>
           <t>250114</t>
         </is>
       </c>
-      <c r="U1" s="77" t="inlineStr">
+      <c r="V1" s="77" t="inlineStr">
         <is>
           <t>250113</t>
         </is>
       </c>
-      <c r="V1" s="77" t="inlineStr">
+      <c r="W1" s="77" t="inlineStr">
         <is>
           <t>250112</t>
         </is>
       </c>
-      <c r="W1" s="77" t="inlineStr">
+      <c r="X1" s="77" t="inlineStr">
         <is>
           <t>250110</t>
         </is>
       </c>
-      <c r="X1" s="77" t="inlineStr">
+      <c r="Y1" s="77" t="inlineStr">
         <is>
           <t>250109</t>
         </is>
       </c>
-      <c r="Y1" s="77" t="inlineStr">
+      <c r="Z1" s="77" t="inlineStr">
         <is>
           <t>250108</t>
         </is>
       </c>
-      <c r="Z1" s="77" t="inlineStr">
+      <c r="AA1" s="77" t="inlineStr">
         <is>
           <t>250107</t>
         </is>
       </c>
-      <c r="AA1" s="77" t="inlineStr">
+      <c r="AB1" s="77" t="inlineStr">
         <is>
           <t>250106</t>
         </is>
       </c>
-      <c r="AB1" s="77" t="inlineStr">
+      <c r="AC1" s="77" t="inlineStr">
         <is>
           <t>250105</t>
         </is>
       </c>
-      <c r="AC1" s="77" t="inlineStr">
+      <c r="AD1" s="77" t="inlineStr">
         <is>
           <t>250103</t>
         </is>
       </c>
-      <c r="AD1" s="77" t="inlineStr">
+      <c r="AE1" s="77" t="inlineStr">
         <is>
           <t>250102</t>
-        </is>
-      </c>
-      <c r="AE1" s="77" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
@@ -6547,103 +6547,105 @@
           <t>red</t>
         </is>
       </c>
-      <c r="L2" s="92" t="inlineStr">
+      <c r="L2" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M2" s="93" t="inlineStr">
+      <c r="N2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N2" s="92" t="inlineStr">
+      <c r="O2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O2" s="92" t="inlineStr">
+      <c r="P2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P2" s="92" t="inlineStr">
+      <c r="Q2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q2" s="92" t="inlineStr">
+      <c r="R2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R2" s="92" t="inlineStr">
+      <c r="S2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S2" s="92" t="inlineStr">
+      <c r="T2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T2" s="92" t="inlineStr">
+      <c r="U2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U2" s="92" t="inlineStr">
+      <c r="V2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V2" s="93" t="inlineStr">
+      <c r="W2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W2" s="93" t="inlineStr">
+      <c r="X2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X2" s="92" t="inlineStr">
+      <c r="Y2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y2" s="92" t="inlineStr">
+      <c r="Z2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z2" s="92" t="inlineStr">
+      <c r="AA2" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA2" s="93" t="inlineStr">
+      <c r="AB2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB2" s="93" t="inlineStr">
+      <c r="AC2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC2" s="93" t="inlineStr">
+      <c r="AD2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD2" s="93" t="inlineStr">
+      <c r="AE2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
-      </c>
-      <c r="AE2" s="92" t="n">
-        <v/>
       </c>
     </row>
     <row r="3">
@@ -6677,70 +6679,70 @@
         <v>-0.65</v>
       </c>
       <c r="J3" s="94" t="n">
-        <v>-0.83</v>
+        <v>-0.65</v>
       </c>
       <c r="K3" s="94" t="n">
         <v>-0.83</v>
       </c>
       <c r="L3" s="94" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="M3" s="94" t="n">
         <v>-1.1</v>
       </c>
-      <c r="M3" s="94" t="n">
+      <c r="N3" s="94" t="n">
         <v>-2.21</v>
       </c>
-      <c r="N3" s="94" t="n">
+      <c r="O3" s="94" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O3" s="94" t="n">
+      <c r="P3" s="94" t="n">
         <v>-1.68</v>
-      </c>
-      <c r="P3" s="94" t="n">
-        <v>-1.17</v>
       </c>
       <c r="Q3" s="94" t="n">
         <v>-1.17</v>
       </c>
       <c r="R3" s="94" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="S3" s="94" t="n">
         <v>-2.02</v>
       </c>
-      <c r="S3" s="94" t="n">
+      <c r="T3" s="94" t="n">
         <v>-1.79</v>
       </c>
-      <c r="T3" s="94" t="n">
+      <c r="U3" s="94" t="n">
         <v>-0.83</v>
       </c>
-      <c r="U3" s="94" t="n">
+      <c r="V3" s="94" t="n">
         <v>-3.09</v>
-      </c>
-      <c r="V3" s="94" t="n">
-        <v>-0.03</v>
       </c>
       <c r="W3" s="94" t="n">
         <v>-0.03</v>
       </c>
       <c r="X3" s="94" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="Y3" s="94" t="n">
         <v>0.26</v>
       </c>
-      <c r="Y3" s="94" t="n">
+      <c r="Z3" s="94" t="n">
         <v>0.9</v>
       </c>
-      <c r="Z3" s="94" t="n">
+      <c r="AA3" s="94" t="n">
         <v>-1.66</v>
       </c>
-      <c r="AA3" s="94" t="n">
+      <c r="AB3" s="94" t="n">
         <v>-0.34</v>
-      </c>
-      <c r="AB3" s="94" t="n">
-        <v>-2.74</v>
       </c>
       <c r="AC3" s="94" t="n">
         <v>-2.74</v>
       </c>
       <c r="AD3" s="94" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="AE3" s="94" t="n">
         <v>0.11</v>
-      </c>
-      <c r="AE3" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="4">
@@ -6774,70 +6776,70 @@
         <v>10.61</v>
       </c>
       <c r="J4" s="94" t="n">
-        <v>12.97</v>
+        <v>10.61</v>
       </c>
       <c r="K4" s="94" t="n">
         <v>12.97</v>
       </c>
       <c r="L4" s="94" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="M4" s="94" t="n">
         <v>11.7</v>
       </c>
-      <c r="M4" s="94" t="n">
+      <c r="N4" s="94" t="n">
         <v>11.16</v>
       </c>
-      <c r="N4" s="94" t="n">
+      <c r="O4" s="94" t="n">
         <v>12.33</v>
       </c>
-      <c r="O4" s="94" t="n">
+      <c r="P4" s="94" t="n">
         <v>11.8</v>
-      </c>
-      <c r="P4" s="94" t="n">
-        <v>11.2</v>
       </c>
       <c r="Q4" s="94" t="n">
         <v>11.2</v>
       </c>
       <c r="R4" s="94" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="S4" s="94" t="n">
         <v>9.17</v>
       </c>
-      <c r="S4" s="94" t="n">
+      <c r="T4" s="94" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="T4" s="94" t="n">
+      <c r="U4" s="94" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="U4" s="94" t="n">
+      <c r="V4" s="94" t="n">
         <v>6.68</v>
-      </c>
-      <c r="V4" s="94" t="n">
-        <v>6.46</v>
       </c>
       <c r="W4" s="94" t="n">
         <v>6.46</v>
       </c>
       <c r="X4" s="94" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="Y4" s="94" t="n">
         <v>7.98</v>
       </c>
-      <c r="Y4" s="94" t="n">
+      <c r="Z4" s="94" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="Z4" s="94" t="n">
+      <c r="AA4" s="94" t="n">
         <v>8.73</v>
       </c>
-      <c r="AA4" s="94" t="n">
+      <c r="AB4" s="94" t="n">
         <v>9.1</v>
-      </c>
-      <c r="AB4" s="94" t="n">
-        <v>8.52</v>
       </c>
       <c r="AC4" s="94" t="n">
         <v>8.52</v>
       </c>
       <c r="AD4" s="94" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="AE4" s="94" t="n">
         <v>11.64</v>
-      </c>
-      <c r="AE4" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="5">
@@ -6871,70 +6873,70 @@
         <v>67.42</v>
       </c>
       <c r="J5" s="94" t="n">
-        <v>71.19</v>
+        <v>67.42</v>
       </c>
       <c r="K5" s="94" t="n">
         <v>71.19</v>
       </c>
       <c r="L5" s="94" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="M5" s="94" t="n">
         <v>50.98</v>
       </c>
-      <c r="M5" s="94" t="n">
+      <c r="N5" s="94" t="n">
         <v>25.28</v>
       </c>
-      <c r="N5" s="94" t="n">
+      <c r="O5" s="94" t="n">
         <v>65.31999999999999</v>
       </c>
-      <c r="O5" s="94" t="n">
+      <c r="P5" s="94" t="n">
         <v>69.8</v>
-      </c>
-      <c r="P5" s="94" t="n">
-        <v>67.65000000000001</v>
       </c>
       <c r="Q5" s="94" t="n">
         <v>67.65000000000001</v>
       </c>
       <c r="R5" s="94" t="n">
+        <v>67.65000000000001</v>
+      </c>
+      <c r="S5" s="94" t="n">
         <v>63.76</v>
       </c>
-      <c r="S5" s="94" t="n">
+      <c r="T5" s="94" t="n">
         <v>58.67</v>
       </c>
-      <c r="T5" s="94" t="n">
+      <c r="U5" s="94" t="n">
         <v>68.65000000000001</v>
       </c>
-      <c r="U5" s="94" t="n">
+      <c r="V5" s="94" t="n">
         <v>8.279999999999999</v>
-      </c>
-      <c r="V5" s="94" t="n">
-        <v>9.460000000000001</v>
       </c>
       <c r="W5" s="94" t="n">
         <v>9.460000000000001</v>
       </c>
       <c r="X5" s="94" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="Y5" s="94" t="n">
         <v>19.81</v>
       </c>
-      <c r="Y5" s="94" t="n">
+      <c r="Z5" s="94" t="n">
         <v>29.11</v>
       </c>
-      <c r="Z5" s="94" t="n">
+      <c r="AA5" s="94" t="n">
         <v>28.48</v>
       </c>
-      <c r="AA5" s="94" t="n">
+      <c r="AB5" s="94" t="n">
         <v>4.01</v>
-      </c>
-      <c r="AB5" s="94" t="n">
-        <v>4.21</v>
       </c>
       <c r="AC5" s="94" t="n">
         <v>4.21</v>
       </c>
       <c r="AD5" s="94" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AE5" s="94" t="n">
         <v>6.55</v>
-      </c>
-      <c r="AE5" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="6">
@@ -6983,113 +6985,115 @@
           <t>green</t>
         </is>
       </c>
-      <c r="J6" s="91" t="inlineStr">
+      <c r="J6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K6" s="91" t="inlineStr">
+      <c r="L6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L6" s="93" t="inlineStr">
+      <c r="M6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M6" s="91" t="inlineStr">
+      <c r="N6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N6" s="91" t="inlineStr">
+      <c r="O6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O6" s="92" t="inlineStr">
+      <c r="P6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P6" s="92" t="inlineStr">
+      <c r="Q6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q6" s="92" t="inlineStr">
+      <c r="R6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R6" s="93" t="inlineStr">
+      <c r="S6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S6" s="91" t="inlineStr">
+      <c r="T6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T6" s="91" t="inlineStr">
+      <c r="U6" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U6" s="92" t="inlineStr">
+      <c r="V6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V6" s="92" t="inlineStr">
+      <c r="W6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W6" s="92" t="inlineStr">
+      <c r="X6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X6" s="92" t="inlineStr">
+      <c r="Y6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y6" s="92" t="inlineStr">
+      <c r="Z6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z6" s="92" t="inlineStr">
+      <c r="AA6" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA6" s="93" t="inlineStr">
+      <c r="AB6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB6" s="93" t="inlineStr">
+      <c r="AC6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC6" s="93" t="inlineStr">
+      <c r="AD6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD6" s="93" t="inlineStr">
+      <c r="AE6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
-      </c>
-      <c r="AE6" s="92" t="n">
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -7123,70 +7127,70 @@
         <v>1.63</v>
       </c>
       <c r="J7" s="94" t="n">
-        <v>0.55</v>
+        <v>1.63</v>
       </c>
       <c r="K7" s="94" t="n">
         <v>0.55</v>
       </c>
       <c r="L7" s="94" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M7" s="94" t="n">
         <v>0.76</v>
       </c>
-      <c r="M7" s="94" t="n">
+      <c r="N7" s="94" t="n">
         <v>-0</v>
       </c>
-      <c r="N7" s="94" t="n">
+      <c r="O7" s="94" t="n">
         <v>-1.04</v>
       </c>
-      <c r="O7" s="94" t="n">
+      <c r="P7" s="94" t="n">
         <v>-2.32</v>
-      </c>
-      <c r="P7" s="94" t="n">
-        <v>-1.2</v>
       </c>
       <c r="Q7" s="94" t="n">
         <v>-1.2</v>
       </c>
       <c r="R7" s="94" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="S7" s="94" t="n">
         <v>-2.32</v>
       </c>
-      <c r="S7" s="94" t="n">
+      <c r="T7" s="94" t="n">
         <v>-0.83</v>
       </c>
-      <c r="T7" s="94" t="n">
+      <c r="U7" s="94" t="n">
         <v>-1.86</v>
       </c>
-      <c r="U7" s="94" t="n">
+      <c r="V7" s="94" t="n">
         <v>-2.7</v>
-      </c>
-      <c r="V7" s="94" t="n">
-        <v>8.130000000000001</v>
       </c>
       <c r="W7" s="94" t="n">
         <v>8.130000000000001</v>
       </c>
       <c r="X7" s="94" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="Y7" s="94" t="n">
         <v>9.789999999999999</v>
       </c>
-      <c r="Y7" s="94" t="n">
+      <c r="Z7" s="94" t="n">
         <v>7.38</v>
       </c>
-      <c r="Z7" s="94" t="n">
+      <c r="AA7" s="94" t="n">
         <v>4.27</v>
       </c>
-      <c r="AA7" s="94" t="n">
+      <c r="AB7" s="94" t="n">
         <v>4.43</v>
-      </c>
-      <c r="AB7" s="94" t="n">
-        <v>-1.29</v>
       </c>
       <c r="AC7" s="94" t="n">
         <v>-1.29</v>
       </c>
       <c r="AD7" s="94" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="AE7" s="94" t="n">
         <v>-4.26</v>
-      </c>
-      <c r="AE7" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="8">
@@ -7220,70 +7224,70 @@
         <v>28.48</v>
       </c>
       <c r="J8" s="94" t="n">
-        <v>37.3</v>
+        <v>28.48</v>
       </c>
       <c r="K8" s="94" t="n">
         <v>37.3</v>
       </c>
       <c r="L8" s="94" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="M8" s="94" t="n">
         <v>36.53</v>
       </c>
-      <c r="M8" s="94" t="n">
+      <c r="N8" s="94" t="n">
         <v>35.49</v>
       </c>
-      <c r="N8" s="94" t="n">
+      <c r="O8" s="94" t="n">
         <v>36.76</v>
       </c>
-      <c r="O8" s="94" t="n">
+      <c r="P8" s="94" t="n">
         <v>35.74</v>
-      </c>
-      <c r="P8" s="94" t="n">
-        <v>33.95</v>
       </c>
       <c r="Q8" s="94" t="n">
         <v>33.95</v>
       </c>
       <c r="R8" s="94" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="S8" s="94" t="n">
         <v>27.18</v>
       </c>
-      <c r="S8" s="94" t="n">
+      <c r="T8" s="94" t="n">
         <v>30.45</v>
       </c>
-      <c r="T8" s="94" t="n">
+      <c r="U8" s="94" t="n">
         <v>33.5</v>
       </c>
-      <c r="U8" s="94" t="n">
+      <c r="V8" s="94" t="n">
         <v>30.62</v>
-      </c>
-      <c r="V8" s="94" t="n">
-        <v>29.85</v>
       </c>
       <c r="W8" s="94" t="n">
         <v>29.85</v>
       </c>
       <c r="X8" s="94" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="Y8" s="94" t="n">
         <v>34.31</v>
       </c>
-      <c r="Y8" s="94" t="n">
+      <c r="Z8" s="94" t="n">
         <v>34.35</v>
       </c>
-      <c r="Z8" s="94" t="n">
+      <c r="AA8" s="94" t="n">
         <v>34.47</v>
       </c>
-      <c r="AA8" s="94" t="n">
+      <c r="AB8" s="94" t="n">
         <v>32.14</v>
-      </c>
-      <c r="AB8" s="94" t="n">
-        <v>32.67</v>
       </c>
       <c r="AC8" s="94" t="n">
         <v>32.67</v>
       </c>
       <c r="AD8" s="94" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="AE8" s="94" t="n">
         <v>37.96</v>
-      </c>
-      <c r="AE8" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="9">
@@ -7317,70 +7321,70 @@
         <v>35.78</v>
       </c>
       <c r="J9" s="94" t="n">
-        <v>56.52</v>
+        <v>35.78</v>
       </c>
       <c r="K9" s="94" t="n">
         <v>56.52</v>
       </c>
       <c r="L9" s="94" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="M9" s="94" t="n">
         <v>45.32</v>
       </c>
-      <c r="M9" s="94" t="n">
+      <c r="N9" s="94" t="n">
         <v>57.96</v>
       </c>
-      <c r="N9" s="94" t="n">
+      <c r="O9" s="94" t="n">
         <v>59.34</v>
       </c>
-      <c r="O9" s="94" t="n">
+      <c r="P9" s="94" t="n">
         <v>51.65</v>
-      </c>
-      <c r="P9" s="94" t="n">
-        <v>49.39</v>
       </c>
       <c r="Q9" s="94" t="n">
         <v>49.39</v>
       </c>
       <c r="R9" s="94" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="S9" s="94" t="n">
         <v>40.47</v>
       </c>
-      <c r="S9" s="94" t="n">
+      <c r="T9" s="94" t="n">
         <v>59.12</v>
       </c>
-      <c r="T9" s="94" t="n">
+      <c r="U9" s="94" t="n">
         <v>63.67</v>
       </c>
-      <c r="U9" s="94" t="n">
+      <c r="V9" s="94" t="n">
         <v>34.88</v>
-      </c>
-      <c r="V9" s="94" t="n">
-        <v>32.56</v>
       </c>
       <c r="W9" s="94" t="n">
         <v>32.56</v>
       </c>
       <c r="X9" s="94" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="Y9" s="94" t="n">
         <v>40.33</v>
       </c>
-      <c r="Y9" s="94" t="n">
+      <c r="Z9" s="94" t="n">
         <v>43.12</v>
       </c>
-      <c r="Z9" s="94" t="n">
+      <c r="AA9" s="94" t="n">
         <v>43.39</v>
       </c>
-      <c r="AA9" s="94" t="n">
+      <c r="AB9" s="94" t="n">
         <v>16.15</v>
-      </c>
-      <c r="AB9" s="94" t="n">
-        <v>16.9</v>
       </c>
       <c r="AC9" s="94" t="n">
         <v>16.9</v>
       </c>
       <c r="AD9" s="94" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AE9" s="94" t="n">
         <v>20.18</v>
-      </c>
-      <c r="AE9" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="10">
@@ -7429,113 +7433,115 @@
           <t>green</t>
         </is>
       </c>
-      <c r="J10" s="91" t="inlineStr">
+      <c r="J10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K10" s="91" t="inlineStr">
+      <c r="L10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L10" s="91" t="inlineStr">
+      <c r="M10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M10" s="91" t="inlineStr">
+      <c r="N10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N10" s="91" t="inlineStr">
+      <c r="O10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O10" s="91" t="inlineStr">
+      <c r="P10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P10" s="91" t="inlineStr">
+      <c r="Q10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q10" s="91" t="inlineStr">
+      <c r="R10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R10" s="92" t="inlineStr">
+      <c r="S10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S10" s="92" t="inlineStr">
+      <c r="T10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T10" s="91" t="inlineStr">
+      <c r="U10" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U10" s="92" t="inlineStr">
+      <c r="V10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V10" s="92" t="inlineStr">
+      <c r="W10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W10" s="92" t="inlineStr">
+      <c r="X10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X10" s="92" t="inlineStr">
+      <c r="Y10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y10" s="92" t="inlineStr">
+      <c r="Z10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z10" s="92" t="inlineStr">
+      <c r="AA10" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA10" s="93" t="inlineStr">
+      <c r="AB10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB10" s="93" t="inlineStr">
+      <c r="AC10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC10" s="93" t="inlineStr">
+      <c r="AD10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD10" s="93" t="inlineStr">
+      <c r="AE10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
-      </c>
-      <c r="AE10" s="92" t="n">
-        <v/>
       </c>
     </row>
     <row r="11">
@@ -7569,70 +7575,70 @@
         <v>-2.82</v>
       </c>
       <c r="J11" s="94" t="n">
-        <v>-1.97</v>
+        <v>-2.82</v>
       </c>
       <c r="K11" s="94" t="n">
         <v>-1.97</v>
       </c>
       <c r="L11" s="94" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="M11" s="94" t="n">
         <v>-2.71</v>
       </c>
-      <c r="M11" s="94" t="n">
+      <c r="N11" s="94" t="n">
         <v>-3.5</v>
       </c>
-      <c r="N11" s="94" t="n">
+      <c r="O11" s="94" t="n">
         <v>-5.24</v>
       </c>
-      <c r="O11" s="94" t="n">
+      <c r="P11" s="94" t="n">
         <v>-5.99</v>
-      </c>
-      <c r="P11" s="94" t="n">
-        <v>-4.96</v>
       </c>
       <c r="Q11" s="94" t="n">
         <v>-4.96</v>
       </c>
       <c r="R11" s="94" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="S11" s="94" t="n">
         <v>-6.98</v>
       </c>
-      <c r="S11" s="94" t="n">
+      <c r="T11" s="94" t="n">
         <v>-8.08</v>
       </c>
-      <c r="T11" s="94" t="n">
+      <c r="U11" s="94" t="n">
         <v>-6.09</v>
       </c>
-      <c r="U11" s="94" t="n">
+      <c r="V11" s="94" t="n">
         <v>-9.69</v>
-      </c>
-      <c r="V11" s="94" t="n">
-        <v>-2.86</v>
       </c>
       <c r="W11" s="94" t="n">
         <v>-2.86</v>
       </c>
       <c r="X11" s="94" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="Y11" s="94" t="n">
         <v>-1.44</v>
       </c>
-      <c r="Y11" s="94" t="n">
+      <c r="Z11" s="94" t="n">
         <v>-3.72</v>
       </c>
-      <c r="Z11" s="94" t="n">
+      <c r="AA11" s="94" t="n">
         <v>-5.89</v>
       </c>
-      <c r="AA11" s="94" t="n">
+      <c r="AB11" s="94" t="n">
         <v>-4.13</v>
-      </c>
-      <c r="AB11" s="94" t="n">
-        <v>-8.9</v>
       </c>
       <c r="AC11" s="94" t="n">
         <v>-8.9</v>
       </c>
       <c r="AD11" s="94" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="AE11" s="94" t="n">
         <v>-9.630000000000001</v>
-      </c>
-      <c r="AE11" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="12">
@@ -7666,70 +7672,70 @@
         <v>22.25</v>
       </c>
       <c r="J12" s="94" t="n">
-        <v>30.1</v>
+        <v>22.25</v>
       </c>
       <c r="K12" s="94" t="n">
         <v>30.1</v>
       </c>
       <c r="L12" s="94" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="M12" s="94" t="n">
         <v>27.98</v>
       </c>
-      <c r="M12" s="94" t="n">
+      <c r="N12" s="94" t="n">
         <v>26.6</v>
       </c>
-      <c r="N12" s="94" t="n">
+      <c r="O12" s="94" t="n">
         <v>28.46</v>
       </c>
-      <c r="O12" s="94" t="n">
+      <c r="P12" s="94" t="n">
         <v>27.49</v>
-      </c>
-      <c r="P12" s="94" t="n">
-        <v>23.68</v>
       </c>
       <c r="Q12" s="94" t="n">
         <v>23.68</v>
       </c>
       <c r="R12" s="94" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="S12" s="94" t="n">
         <v>18.99</v>
       </c>
-      <c r="S12" s="94" t="n">
+      <c r="T12" s="94" t="n">
         <v>18.11</v>
       </c>
-      <c r="T12" s="94" t="n">
+      <c r="U12" s="94" t="n">
         <v>20.84</v>
       </c>
-      <c r="U12" s="94" t="n">
+      <c r="V12" s="94" t="n">
         <v>16.86</v>
-      </c>
-      <c r="V12" s="94" t="n">
-        <v>16.44</v>
       </c>
       <c r="W12" s="94" t="n">
         <v>16.44</v>
       </c>
       <c r="X12" s="94" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="Y12" s="94" t="n">
         <v>20.18</v>
       </c>
-      <c r="Y12" s="94" t="n">
+      <c r="Z12" s="94" t="n">
         <v>19.29</v>
       </c>
-      <c r="Z12" s="94" t="n">
+      <c r="AA12" s="94" t="n">
         <v>20.37</v>
       </c>
-      <c r="AA12" s="94" t="n">
+      <c r="AB12" s="94" t="n">
         <v>21.99</v>
-      </c>
-      <c r="AB12" s="94" t="n">
-        <v>22.02</v>
       </c>
       <c r="AC12" s="94" t="n">
         <v>22.02</v>
       </c>
       <c r="AD12" s="94" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="AE12" s="94" t="n">
         <v>26.5</v>
-      </c>
-      <c r="AE12" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="13">
@@ -7763,70 +7769,70 @@
         <v>31.12</v>
       </c>
       <c r="J13" s="94" t="n">
-        <v>77.11</v>
+        <v>31.12</v>
       </c>
       <c r="K13" s="94" t="n">
         <v>77.11</v>
       </c>
       <c r="L13" s="94" t="n">
+        <v>77.11</v>
+      </c>
+      <c r="M13" s="94" t="n">
         <v>55.59</v>
       </c>
-      <c r="M13" s="94" t="n">
+      <c r="N13" s="94" t="n">
         <v>66.94</v>
       </c>
-      <c r="N13" s="94" t="n">
+      <c r="O13" s="94" t="n">
         <v>83.7</v>
       </c>
-      <c r="O13" s="94" t="n">
+      <c r="P13" s="94" t="n">
         <v>81.64</v>
-      </c>
-      <c r="P13" s="94" t="n">
-        <v>68.69</v>
       </c>
       <c r="Q13" s="94" t="n">
         <v>68.69</v>
       </c>
       <c r="R13" s="94" t="n">
+        <v>68.69</v>
+      </c>
+      <c r="S13" s="94" t="n">
         <v>60.87</v>
       </c>
-      <c r="S13" s="94" t="n">
+      <c r="T13" s="94" t="n">
         <v>54.48</v>
       </c>
-      <c r="T13" s="94" t="n">
+      <c r="U13" s="94" t="n">
         <v>78.59</v>
       </c>
-      <c r="U13" s="94" t="n">
+      <c r="V13" s="94" t="n">
         <v>21.44</v>
-      </c>
-      <c r="V13" s="94" t="n">
-        <v>9.02</v>
       </c>
       <c r="W13" s="94" t="n">
         <v>9.02</v>
       </c>
       <c r="X13" s="94" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="Y13" s="94" t="n">
         <v>18.81</v>
       </c>
-      <c r="Y13" s="94" t="n">
+      <c r="Z13" s="94" t="n">
         <v>14.94</v>
       </c>
-      <c r="Z13" s="94" t="n">
+      <c r="AA13" s="94" t="n">
         <v>20.9</v>
       </c>
-      <c r="AA13" s="94" t="n">
+      <c r="AB13" s="94" t="n">
         <v>2.46</v>
-      </c>
-      <c r="AB13" s="94" t="n">
-        <v>2.51</v>
       </c>
       <c r="AC13" s="94" t="n">
         <v>2.51</v>
       </c>
       <c r="AD13" s="94" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AE13" s="94" t="n">
         <v>3.75</v>
-      </c>
-      <c r="AE13" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="14">
@@ -7835,153 +7841,155 @@
           <t>hk50:EIDE</t>
         </is>
       </c>
-      <c r="B14" s="92" t="inlineStr">
+      <c r="B14" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C14" s="91" t="inlineStr">
+      <c r="D14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D14" s="91" t="inlineStr">
+      <c r="E14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E14" s="91" t="inlineStr">
+      <c r="F14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F14" s="91" t="inlineStr">
+      <c r="G14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G14" s="91" t="inlineStr">
+      <c r="H14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H14" s="91" t="inlineStr">
+      <c r="I14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I14" s="91" t="inlineStr">
+      <c r="J14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J14" s="91" t="inlineStr">
+      <c r="K14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K14" s="91" t="inlineStr">
+      <c r="L14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L14" s="92" t="inlineStr">
+      <c r="M14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M14" s="92" t="inlineStr">
+      <c r="N14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N14" s="91" t="inlineStr">
+      <c r="O14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O14" s="91" t="inlineStr">
+      <c r="P14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P14" s="91" t="inlineStr">
+      <c r="Q14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q14" s="91" t="inlineStr">
+      <c r="R14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R14" s="91" t="inlineStr">
+      <c r="S14" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S14" s="92" t="inlineStr">
+      <c r="T14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T14" s="92" t="inlineStr">
+      <c r="U14" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U14" s="93" t="inlineStr">
+      <c r="V14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V14" s="93" t="inlineStr">
+      <c r="W14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W14" s="93" t="inlineStr">
+      <c r="X14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X14" s="93" t="inlineStr">
+      <c r="Y14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y14" s="93" t="inlineStr">
+      <c r="Z14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z14" s="93" t="inlineStr">
+      <c r="AA14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA14" s="93" t="inlineStr">
+      <c r="AB14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB14" s="93" t="inlineStr">
+      <c r="AC14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC14" s="93" t="inlineStr">
+      <c r="AD14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD14" s="93" t="inlineStr">
+      <c r="AE14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
-      </c>
-      <c r="AE14" s="92" t="n">
-        <v/>
       </c>
     </row>
     <row r="15">
@@ -7991,10 +7999,10 @@
         </is>
       </c>
       <c r="B15" s="94" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="C15" s="94" t="n">
         <v>-1.41</v>
-      </c>
-      <c r="C15" s="94" t="n">
-        <v>-0.45</v>
       </c>
       <c r="D15" s="94" t="n">
         <v>-0.45</v>
@@ -8012,73 +8020,73 @@
         <v>-0.45</v>
       </c>
       <c r="I15" s="94" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="J15" s="94" t="n">
         <v>-0.9</v>
-      </c>
-      <c r="J15" s="94" t="n">
-        <v>-3.07</v>
       </c>
       <c r="K15" s="94" t="n">
         <v>-3.07</v>
       </c>
       <c r="L15" s="94" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="M15" s="94" t="n">
         <v>-4.36</v>
       </c>
-      <c r="M15" s="94" t="n">
+      <c r="N15" s="94" t="n">
         <v>-3.94</v>
       </c>
-      <c r="N15" s="94" t="n">
+      <c r="O15" s="94" t="n">
         <v>-1.87</v>
       </c>
-      <c r="O15" s="94" t="n">
+      <c r="P15" s="94" t="n">
         <v>-4.02</v>
-      </c>
-      <c r="P15" s="94" t="n">
-        <v>-4.46</v>
       </c>
       <c r="Q15" s="94" t="n">
         <v>-4.46</v>
       </c>
       <c r="R15" s="94" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="S15" s="94" t="n">
         <v>-4.67</v>
       </c>
-      <c r="S15" s="94" t="n">
+      <c r="T15" s="94" t="n">
         <v>-7.3</v>
       </c>
-      <c r="T15" s="94" t="n">
+      <c r="U15" s="94" t="n">
         <v>-4.28</v>
       </c>
-      <c r="U15" s="94" t="n">
+      <c r="V15" s="94" t="n">
         <v>-6.96</v>
-      </c>
-      <c r="V15" s="94" t="n">
-        <v>-6.17</v>
       </c>
       <c r="W15" s="94" t="n">
         <v>-6.17</v>
       </c>
       <c r="X15" s="94" t="n">
+        <v>-6.17</v>
+      </c>
+      <c r="Y15" s="94" t="n">
         <v>-8.779999999999999</v>
       </c>
-      <c r="Y15" s="94" t="n">
+      <c r="Z15" s="94" t="n">
         <v>-9.279999999999999</v>
       </c>
-      <c r="Z15" s="94" t="n">
+      <c r="AA15" s="94" t="n">
         <v>-5.76</v>
       </c>
-      <c r="AA15" s="94" t="n">
+      <c r="AB15" s="94" t="n">
         <v>-5.92</v>
-      </c>
-      <c r="AB15" s="94" t="n">
-        <v>-14.46</v>
       </c>
       <c r="AC15" s="94" t="n">
         <v>-14.46</v>
       </c>
       <c r="AD15" s="94" t="n">
+        <v>-14.46</v>
+      </c>
+      <c r="AE15" s="94" t="n">
         <v>-13.69</v>
-      </c>
-      <c r="AE15" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="16">
@@ -8088,10 +8096,10 @@
         </is>
       </c>
       <c r="B16" s="94" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="C16" s="94" t="n">
         <v>21.07</v>
-      </c>
-      <c r="C16" s="94" t="n">
-        <v>19.35</v>
       </c>
       <c r="D16" s="94" t="n">
         <v>19.35</v>
@@ -8109,73 +8117,73 @@
         <v>19.35</v>
       </c>
       <c r="I16" s="94" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="J16" s="94" t="n">
         <v>16.72</v>
-      </c>
-      <c r="J16" s="94" t="n">
-        <v>15.69</v>
       </c>
       <c r="K16" s="94" t="n">
         <v>15.69</v>
       </c>
       <c r="L16" s="94" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="M16" s="94" t="n">
         <v>15.87</v>
       </c>
-      <c r="M16" s="94" t="n">
+      <c r="N16" s="94" t="n">
         <v>14.74</v>
       </c>
-      <c r="N16" s="94" t="n">
+      <c r="O16" s="94" t="n">
         <v>18.13</v>
       </c>
-      <c r="O16" s="94" t="n">
+      <c r="P16" s="94" t="n">
         <v>17.18</v>
-      </c>
-      <c r="P16" s="94" t="n">
-        <v>13.13</v>
       </c>
       <c r="Q16" s="94" t="n">
         <v>13.13</v>
       </c>
       <c r="R16" s="94" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="S16" s="94" t="n">
         <v>11.76</v>
       </c>
-      <c r="S16" s="94" t="n">
+      <c r="T16" s="94" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="T16" s="94" t="n">
+      <c r="U16" s="94" t="n">
         <v>10.35</v>
       </c>
-      <c r="U16" s="94" t="n">
+      <c r="V16" s="94" t="n">
         <v>6.16</v>
-      </c>
-      <c r="V16" s="94" t="n">
-        <v>7.47</v>
       </c>
       <c r="W16" s="94" t="n">
         <v>7.47</v>
       </c>
       <c r="X16" s="94" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="Y16" s="94" t="n">
         <v>8.529999999999999</v>
       </c>
-      <c r="Y16" s="94" t="n">
+      <c r="Z16" s="94" t="n">
         <v>7.02</v>
       </c>
-      <c r="Z16" s="94" t="n">
+      <c r="AA16" s="94" t="n">
         <v>6.31</v>
       </c>
-      <c r="AA16" s="94" t="n">
+      <c r="AB16" s="94" t="n">
         <v>10.41</v>
-      </c>
-      <c r="AB16" s="94" t="n">
-        <v>13.1</v>
       </c>
       <c r="AC16" s="94" t="n">
         <v>13.1</v>
       </c>
       <c r="AD16" s="94" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="AE16" s="94" t="n">
         <v>11.98</v>
-      </c>
-      <c r="AE16" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="17">
@@ -8185,10 +8193,10 @@
         </is>
       </c>
       <c r="B17" s="94" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="C17" s="94" t="n">
         <v>74.2</v>
-      </c>
-      <c r="C17" s="94" t="n">
-        <v>75.39</v>
       </c>
       <c r="D17" s="94" t="n">
         <v>75.39</v>
@@ -8206,73 +8214,73 @@
         <v>75.39</v>
       </c>
       <c r="I17" s="94" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="J17" s="94" t="n">
         <v>74.31</v>
-      </c>
-      <c r="J17" s="94" t="n">
-        <v>69.52</v>
       </c>
       <c r="K17" s="94" t="n">
         <v>69.52</v>
       </c>
       <c r="L17" s="94" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="M17" s="94" t="n">
         <v>50.12</v>
       </c>
-      <c r="M17" s="94" t="n">
+      <c r="N17" s="94" t="n">
         <v>55.82</v>
       </c>
-      <c r="N17" s="94" t="n">
+      <c r="O17" s="94" t="n">
         <v>86.87</v>
       </c>
-      <c r="O17" s="94" t="n">
+      <c r="P17" s="94" t="n">
         <v>82.95</v>
-      </c>
-      <c r="P17" s="94" t="n">
-        <v>70.41</v>
       </c>
       <c r="Q17" s="94" t="n">
         <v>70.41</v>
       </c>
       <c r="R17" s="94" t="n">
+        <v>70.41</v>
+      </c>
+      <c r="S17" s="94" t="n">
         <v>67.17</v>
       </c>
-      <c r="S17" s="94" t="n">
+      <c r="T17" s="94" t="n">
         <v>51.86</v>
       </c>
-      <c r="T17" s="94" t="n">
+      <c r="U17" s="94" t="n">
         <v>46.63</v>
       </c>
-      <c r="U17" s="94" t="n">
+      <c r="V17" s="94" t="n">
         <v>7.26</v>
-      </c>
-      <c r="V17" s="94" t="n">
-        <v>10.43</v>
       </c>
       <c r="W17" s="94" t="n">
         <v>10.43</v>
       </c>
       <c r="X17" s="94" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="Y17" s="94" t="n">
         <v>15.01</v>
       </c>
-      <c r="Y17" s="94" t="n">
+      <c r="Z17" s="94" t="n">
         <v>16.18</v>
       </c>
-      <c r="Z17" s="94" t="n">
+      <c r="AA17" s="94" t="n">
         <v>21.65</v>
       </c>
-      <c r="AA17" s="94" t="n">
+      <c r="AB17" s="94" t="n">
         <v>34.02</v>
-      </c>
-      <c r="AB17" s="94" t="n">
-        <v>39.01</v>
       </c>
       <c r="AC17" s="94" t="n">
         <v>39.01</v>
       </c>
       <c r="AD17" s="94" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="AE17" s="94" t="n">
         <v>22.83</v>
-      </c>
-      <c r="AE17" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="18">
@@ -8286,148 +8294,150 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C18" s="92" t="inlineStr">
+      <c r="C18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D18" s="92" t="inlineStr">
+      <c r="E18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E18" s="92" t="inlineStr">
+      <c r="F18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F18" s="92" t="inlineStr">
+      <c r="G18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G18" s="92" t="inlineStr">
+      <c r="H18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H18" s="92" t="inlineStr">
+      <c r="I18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I18" s="92" t="inlineStr">
+      <c r="J18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J18" s="91" t="inlineStr">
+      <c r="K18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K18" s="91" t="inlineStr">
+      <c r="L18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L18" s="91" t="inlineStr">
+      <c r="M18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M18" s="91" t="inlineStr">
+      <c r="N18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N18" s="91" t="inlineStr">
+      <c r="O18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O18" s="91" t="inlineStr">
+      <c r="P18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P18" s="91" t="inlineStr">
+      <c r="Q18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q18" s="91" t="inlineStr">
+      <c r="R18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R18" s="91" t="inlineStr">
+      <c r="S18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S18" s="91" t="inlineStr">
+      <c r="T18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T18" s="92" t="inlineStr">
+      <c r="U18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U18" s="93" t="inlineStr">
+      <c r="V18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V18" s="93" t="inlineStr">
+      <c r="W18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W18" s="93" t="inlineStr">
+      <c r="X18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X18" s="92" t="inlineStr">
+      <c r="Y18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y18" s="92" t="inlineStr">
+      <c r="Z18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z18" s="93" t="inlineStr">
+      <c r="AA18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA18" s="91" t="inlineStr">
+      <c r="AB18" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB18" s="92" t="inlineStr">
+      <c r="AC18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC18" s="92" t="inlineStr">
+      <c r="AD18" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD18" s="93" t="inlineStr">
+      <c r="AE18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
-      </c>
-      <c r="AE18" s="92" t="n">
-        <v/>
       </c>
     </row>
     <row r="19">
@@ -8440,7 +8450,7 @@
         <v>4.93</v>
       </c>
       <c r="C19" s="94" t="n">
-        <v>5.44</v>
+        <v>4.93</v>
       </c>
       <c r="D19" s="94" t="n">
         <v>5.44</v>
@@ -8449,34 +8459,34 @@
         <v>5.44</v>
       </c>
       <c r="F19" s="94" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="G19" s="94" t="n">
         <v>6.41</v>
       </c>
-      <c r="G19" s="94" t="n">
+      <c r="H19" s="94" t="n">
         <v>3.88</v>
       </c>
-      <c r="H19" s="94" t="n">
+      <c r="I19" s="94" t="n">
         <v>4.03</v>
       </c>
-      <c r="I19" s="94" t="n">
+      <c r="J19" s="94" t="n">
         <v>3.24</v>
-      </c>
-      <c r="J19" s="94" t="n">
-        <v>5.05</v>
       </c>
       <c r="K19" s="94" t="n">
         <v>5.05</v>
       </c>
       <c r="L19" s="94" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="M19" s="94" t="n">
         <v>5.32</v>
       </c>
-      <c r="M19" s="94" t="n">
+      <c r="N19" s="94" t="n">
         <v>4.98</v>
       </c>
-      <c r="N19" s="94" t="n">
+      <c r="O19" s="94" t="n">
         <v>3.38</v>
-      </c>
-      <c r="O19" s="94" t="n">
-        <v>2.44</v>
       </c>
       <c r="P19" s="94" t="n">
         <v>2.44</v>
@@ -8485,46 +8495,46 @@
         <v>2.44</v>
       </c>
       <c r="R19" s="94" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="S19" s="94" t="n">
         <v>1.24</v>
       </c>
-      <c r="S19" s="94" t="n">
+      <c r="T19" s="94" t="n">
         <v>1.86</v>
       </c>
-      <c r="T19" s="94" t="n">
+      <c r="U19" s="94" t="n">
         <v>0.01</v>
       </c>
-      <c r="U19" s="94" t="n">
+      <c r="V19" s="94" t="n">
         <v>0.36</v>
-      </c>
-      <c r="V19" s="94" t="n">
-        <v>-0.5600000000000001</v>
       </c>
       <c r="W19" s="94" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="X19" s="94" t="n">
-        <v>1.78</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="Y19" s="94" t="n">
         <v>1.78</v>
       </c>
       <c r="Z19" s="94" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA19" s="94" t="n">
         <v>2.23</v>
       </c>
-      <c r="AA19" s="94" t="n">
+      <c r="AB19" s="94" t="n">
         <v>3.17</v>
-      </c>
-      <c r="AB19" s="94" t="n">
-        <v>3.33</v>
       </c>
       <c r="AC19" s="94" t="n">
         <v>3.33</v>
       </c>
       <c r="AD19" s="94" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AE19" s="94" t="n">
         <v>3.03</v>
-      </c>
-      <c r="AE19" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="20">
@@ -8537,7 +8547,7 @@
         <v>12.17</v>
       </c>
       <c r="C20" s="94" t="n">
-        <v>13.56</v>
+        <v>12.17</v>
       </c>
       <c r="D20" s="94" t="n">
         <v>13.56</v>
@@ -8546,34 +8556,34 @@
         <v>13.56</v>
       </c>
       <c r="F20" s="94" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="G20" s="94" t="n">
         <v>16.76</v>
       </c>
-      <c r="G20" s="94" t="n">
+      <c r="H20" s="94" t="n">
         <v>15.25</v>
       </c>
-      <c r="H20" s="94" t="n">
+      <c r="I20" s="94" t="n">
         <v>16.99</v>
       </c>
-      <c r="I20" s="94" t="n">
+      <c r="J20" s="94" t="n">
         <v>12.45</v>
-      </c>
-      <c r="J20" s="94" t="n">
-        <v>12.02</v>
       </c>
       <c r="K20" s="94" t="n">
         <v>12.02</v>
       </c>
       <c r="L20" s="94" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="M20" s="94" t="n">
         <v>10.8</v>
       </c>
-      <c r="M20" s="94" t="n">
+      <c r="N20" s="94" t="n">
         <v>11.96</v>
       </c>
-      <c r="N20" s="94" t="n">
+      <c r="O20" s="94" t="n">
         <v>10.72</v>
-      </c>
-      <c r="O20" s="94" t="n">
-        <v>9.85</v>
       </c>
       <c r="P20" s="94" t="n">
         <v>9.85</v>
@@ -8582,46 +8592,46 @@
         <v>9.85</v>
       </c>
       <c r="R20" s="94" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="S20" s="94" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="S20" s="94" t="n">
+      <c r="T20" s="94" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="T20" s="94" t="n">
+      <c r="U20" s="94" t="n">
         <v>5.17</v>
       </c>
-      <c r="U20" s="94" t="n">
+      <c r="V20" s="94" t="n">
         <v>4.88</v>
-      </c>
-      <c r="V20" s="94" t="n">
-        <v>5.85</v>
       </c>
       <c r="W20" s="94" t="n">
         <v>5.85</v>
       </c>
       <c r="X20" s="94" t="n">
-        <v>6.74</v>
+        <v>5.85</v>
       </c>
       <c r="Y20" s="94" t="n">
         <v>6.74</v>
       </c>
       <c r="Z20" s="94" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="AA20" s="94" t="n">
         <v>5.74</v>
       </c>
-      <c r="AA20" s="94" t="n">
+      <c r="AB20" s="94" t="n">
         <v>5.44</v>
-      </c>
-      <c r="AB20" s="94" t="n">
-        <v>5.53</v>
       </c>
       <c r="AC20" s="94" t="n">
         <v>5.53</v>
       </c>
       <c r="AD20" s="94" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="AE20" s="94" t="n">
         <v>4.51</v>
-      </c>
-      <c r="AE20" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="21">
@@ -8634,7 +8644,7 @@
         <v>15.04</v>
       </c>
       <c r="C21" s="94" t="n">
-        <v>35.39</v>
+        <v>15.04</v>
       </c>
       <c r="D21" s="94" t="n">
         <v>35.39</v>
@@ -8643,34 +8653,34 @@
         <v>35.39</v>
       </c>
       <c r="F21" s="94" t="n">
+        <v>35.39</v>
+      </c>
+      <c r="G21" s="94" t="n">
         <v>64.51000000000001</v>
       </c>
-      <c r="G21" s="94" t="n">
+      <c r="H21" s="94" t="n">
         <v>37.99</v>
       </c>
-      <c r="H21" s="94" t="n">
+      <c r="I21" s="94" t="n">
         <v>56.94</v>
       </c>
-      <c r="I21" s="94" t="n">
+      <c r="J21" s="94" t="n">
         <v>16.07</v>
-      </c>
-      <c r="J21" s="94" t="n">
-        <v>67.48999999999999</v>
       </c>
       <c r="K21" s="94" t="n">
         <v>67.48999999999999</v>
       </c>
       <c r="L21" s="94" t="n">
+        <v>67.48999999999999</v>
+      </c>
+      <c r="M21" s="94" t="n">
         <v>98.41</v>
       </c>
-      <c r="M21" s="94" t="n">
+      <c r="N21" s="94" t="n">
         <v>97.23999999999999</v>
       </c>
-      <c r="N21" s="94" t="n">
+      <c r="O21" s="94" t="n">
         <v>95.22</v>
-      </c>
-      <c r="O21" s="94" t="n">
-        <v>90.06</v>
       </c>
       <c r="P21" s="94" t="n">
         <v>90.06</v>
@@ -8679,46 +8689,46 @@
         <v>90.06</v>
       </c>
       <c r="R21" s="94" t="n">
+        <v>90.06</v>
+      </c>
+      <c r="S21" s="94" t="n">
         <v>74.65000000000001</v>
       </c>
-      <c r="S21" s="94" t="n">
+      <c r="T21" s="94" t="n">
         <v>89.31999999999999</v>
       </c>
-      <c r="T21" s="94" t="n">
+      <c r="U21" s="94" t="n">
         <v>34.87</v>
       </c>
-      <c r="U21" s="94" t="n">
+      <c r="V21" s="94" t="n">
         <v>22.53</v>
-      </c>
-      <c r="V21" s="94" t="n">
-        <v>10.95</v>
       </c>
       <c r="W21" s="94" t="n">
         <v>10.95</v>
       </c>
       <c r="X21" s="94" t="n">
-        <v>42.53</v>
+        <v>10.95</v>
       </c>
       <c r="Y21" s="94" t="n">
         <v>42.53</v>
       </c>
       <c r="Z21" s="94" t="n">
+        <v>42.53</v>
+      </c>
+      <c r="AA21" s="94" t="n">
         <v>32.72</v>
       </c>
-      <c r="AA21" s="94" t="n">
+      <c r="AB21" s="94" t="n">
         <v>84.81999999999999</v>
-      </c>
-      <c r="AB21" s="94" t="n">
-        <v>74.91</v>
       </c>
       <c r="AC21" s="94" t="n">
         <v>74.91</v>
       </c>
       <c r="AD21" s="94" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="AE21" s="94" t="n">
         <v>6.03</v>
-      </c>
-      <c r="AE21" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="22">
@@ -8762,118 +8772,120 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="I22" s="91" t="inlineStr">
+      <c r="I22" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J22" s="91" t="inlineStr">
+      <c r="K22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K22" s="91" t="inlineStr">
+      <c r="L22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L22" s="91" t="inlineStr">
+      <c r="M22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M22" s="91" t="inlineStr">
+      <c r="N22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N22" s="91" t="inlineStr">
+      <c r="O22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O22" s="91" t="inlineStr">
+      <c r="P22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P22" s="91" t="inlineStr">
+      <c r="Q22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q22" s="91" t="inlineStr">
+      <c r="R22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R22" s="91" t="inlineStr">
+      <c r="S22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S22" s="91" t="inlineStr">
+      <c r="T22" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T22" s="92" t="inlineStr">
+      <c r="U22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U22" s="92" t="inlineStr">
+      <c r="V22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V22" s="93" t="inlineStr">
+      <c r="W22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W22" s="93" t="inlineStr">
+      <c r="X22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X22" s="92" t="inlineStr">
+      <c r="Y22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y22" s="92" t="inlineStr">
+      <c r="Z22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z22" s="92" t="inlineStr">
+      <c r="AA22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA22" s="92" t="inlineStr">
+      <c r="AB22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB22" s="92" t="inlineStr">
+      <c r="AC22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC22" s="92" t="inlineStr">
+      <c r="AD22" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD22" s="93" t="inlineStr">
+      <c r="AE22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
-      </c>
-      <c r="AE22" s="92" t="n">
-        <v/>
       </c>
     </row>
     <row r="23">
@@ -8886,7 +8898,7 @@
         <v>6.29</v>
       </c>
       <c r="C23" s="94" t="n">
-        <v>5.93</v>
+        <v>6.29</v>
       </c>
       <c r="D23" s="94" t="n">
         <v>5.93</v>
@@ -8895,34 +8907,34 @@
         <v>5.93</v>
       </c>
       <c r="F23" s="94" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="G23" s="94" t="n">
         <v>7.47</v>
       </c>
-      <c r="G23" s="94" t="n">
+      <c r="H23" s="94" t="n">
         <v>6.1</v>
       </c>
-      <c r="H23" s="94" t="n">
+      <c r="I23" s="94" t="n">
         <v>6.2</v>
       </c>
-      <c r="I23" s="94" t="n">
+      <c r="J23" s="94" t="n">
         <v>5.49</v>
-      </c>
-      <c r="J23" s="94" t="n">
-        <v>5.48</v>
       </c>
       <c r="K23" s="94" t="n">
         <v>5.48</v>
       </c>
       <c r="L23" s="94" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="M23" s="94" t="n">
         <v>5.17</v>
       </c>
-      <c r="M23" s="94" t="n">
+      <c r="N23" s="94" t="n">
         <v>3.86</v>
       </c>
-      <c r="N23" s="94" t="n">
+      <c r="O23" s="94" t="n">
         <v>2.56</v>
-      </c>
-      <c r="O23" s="94" t="n">
-        <v>1.3</v>
       </c>
       <c r="P23" s="94" t="n">
         <v>1.3</v>
@@ -8931,46 +8943,46 @@
         <v>1.3</v>
       </c>
       <c r="R23" s="94" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" s="94" t="n">
         <v>-0.28</v>
       </c>
-      <c r="S23" s="94" t="n">
+      <c r="T23" s="94" t="n">
         <v>-0.04</v>
       </c>
-      <c r="T23" s="94" t="n">
+      <c r="U23" s="94" t="n">
         <v>-1.3</v>
       </c>
-      <c r="U23" s="94" t="n">
+      <c r="V23" s="94" t="n">
         <v>-1.04</v>
-      </c>
-      <c r="V23" s="94" t="n">
-        <v>-2.62</v>
       </c>
       <c r="W23" s="94" t="n">
         <v>-2.62</v>
       </c>
       <c r="X23" s="94" t="n">
-        <v>-0.53</v>
+        <v>-2.62</v>
       </c>
       <c r="Y23" s="94" t="n">
         <v>-0.53</v>
       </c>
       <c r="Z23" s="94" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="AA23" s="94" t="n">
         <v>0.17</v>
       </c>
-      <c r="AA23" s="94" t="n">
+      <c r="AB23" s="94" t="n">
         <v>0.46</v>
-      </c>
-      <c r="AB23" s="94" t="n">
-        <v>1.55</v>
       </c>
       <c r="AC23" s="94" t="n">
         <v>1.55</v>
       </c>
       <c r="AD23" s="94" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE23" s="94" t="n">
         <v>1.04</v>
-      </c>
-      <c r="AE23" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="24">
@@ -8983,7 +8995,7 @@
         <v>12.47</v>
       </c>
       <c r="C24" s="94" t="n">
-        <v>12.92</v>
+        <v>12.47</v>
       </c>
       <c r="D24" s="94" t="n">
         <v>12.92</v>
@@ -8992,34 +9004,34 @@
         <v>12.92</v>
       </c>
       <c r="F24" s="94" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="G24" s="94" t="n">
         <v>15.78</v>
       </c>
-      <c r="G24" s="94" t="n">
+      <c r="H24" s="94" t="n">
         <v>14.66</v>
       </c>
-      <c r="H24" s="94" t="n">
+      <c r="I24" s="94" t="n">
         <v>15.88</v>
       </c>
-      <c r="I24" s="94" t="n">
+      <c r="J24" s="94" t="n">
         <v>12.52</v>
-      </c>
-      <c r="J24" s="94" t="n">
-        <v>10.1</v>
       </c>
       <c r="K24" s="94" t="n">
         <v>10.1</v>
       </c>
       <c r="L24" s="94" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="M24" s="94" t="n">
         <v>9.109999999999999</v>
       </c>
-      <c r="M24" s="94" t="n">
+      <c r="N24" s="94" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="N24" s="94" t="n">
+      <c r="O24" s="94" t="n">
         <v>8.6</v>
-      </c>
-      <c r="O24" s="94" t="n">
-        <v>7.14</v>
       </c>
       <c r="P24" s="94" t="n">
         <v>7.14</v>
@@ -9028,46 +9040,46 @@
         <v>7.14</v>
       </c>
       <c r="R24" s="94" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="S24" s="94" t="n">
         <v>8.06</v>
       </c>
-      <c r="S24" s="94" t="n">
+      <c r="T24" s="94" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="T24" s="94" t="n">
+      <c r="U24" s="94" t="n">
         <v>5.35</v>
       </c>
-      <c r="U24" s="94" t="n">
+      <c r="V24" s="94" t="n">
         <v>4.66</v>
-      </c>
-      <c r="V24" s="94" t="n">
-        <v>4.1</v>
       </c>
       <c r="W24" s="94" t="n">
         <v>4.1</v>
       </c>
       <c r="X24" s="94" t="n">
-        <v>4.84</v>
+        <v>4.1</v>
       </c>
       <c r="Y24" s="94" t="n">
         <v>4.84</v>
       </c>
       <c r="Z24" s="94" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="AA24" s="94" t="n">
         <v>3.23</v>
       </c>
-      <c r="AA24" s="94" t="n">
+      <c r="AB24" s="94" t="n">
         <v>4.28</v>
-      </c>
-      <c r="AB24" s="94" t="n">
-        <v>6.27</v>
       </c>
       <c r="AC24" s="94" t="n">
         <v>6.27</v>
       </c>
       <c r="AD24" s="94" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="AE24" s="94" t="n">
         <v>5.98</v>
-      </c>
-      <c r="AE24" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="25">
@@ -9080,7 +9092,7 @@
         <v>32.81</v>
       </c>
       <c r="C25" s="94" t="n">
-        <v>41.24</v>
+        <v>32.81</v>
       </c>
       <c r="D25" s="94" t="n">
         <v>41.24</v>
@@ -9089,34 +9101,34 @@
         <v>41.24</v>
       </c>
       <c r="F25" s="94" t="n">
+        <v>41.24</v>
+      </c>
+      <c r="G25" s="94" t="n">
         <v>77.98</v>
       </c>
-      <c r="G25" s="94" t="n">
+      <c r="H25" s="94" t="n">
         <v>68.69</v>
       </c>
-      <c r="H25" s="94" t="n">
+      <c r="I25" s="94" t="n">
         <v>89</v>
       </c>
-      <c r="I25" s="94" t="n">
+      <c r="J25" s="94" t="n">
         <v>86.3</v>
-      </c>
-      <c r="J25" s="94" t="n">
-        <v>79.05</v>
       </c>
       <c r="K25" s="94" t="n">
         <v>79.05</v>
       </c>
       <c r="L25" s="94" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="M25" s="94" t="n">
         <v>95.43000000000001</v>
       </c>
-      <c r="M25" s="94" t="n">
+      <c r="N25" s="94" t="n">
         <v>92.37</v>
       </c>
-      <c r="N25" s="94" t="n">
+      <c r="O25" s="94" t="n">
         <v>91.09999999999999</v>
-      </c>
-      <c r="O25" s="94" t="n">
-        <v>83.62</v>
       </c>
       <c r="P25" s="94" t="n">
         <v>83.62</v>
@@ -9125,46 +9137,46 @@
         <v>83.62</v>
       </c>
       <c r="R25" s="94" t="n">
+        <v>83.62</v>
+      </c>
+      <c r="S25" s="94" t="n">
         <v>74.87</v>
       </c>
-      <c r="S25" s="94" t="n">
+      <c r="T25" s="94" t="n">
         <v>80.75</v>
       </c>
-      <c r="T25" s="94" t="n">
+      <c r="U25" s="94" t="n">
         <v>58.29</v>
       </c>
-      <c r="U25" s="94" t="n">
+      <c r="V25" s="94" t="n">
         <v>44.79</v>
-      </c>
-      <c r="V25" s="94" t="n">
-        <v>15.07</v>
       </c>
       <c r="W25" s="94" t="n">
         <v>15.07</v>
       </c>
       <c r="X25" s="94" t="n">
-        <v>49.78</v>
+        <v>15.07</v>
       </c>
       <c r="Y25" s="94" t="n">
         <v>49.78</v>
       </c>
       <c r="Z25" s="94" t="n">
+        <v>49.78</v>
+      </c>
+      <c r="AA25" s="94" t="n">
         <v>34.31</v>
       </c>
-      <c r="AA25" s="94" t="n">
+      <c r="AB25" s="94" t="n">
         <v>52.18</v>
-      </c>
-      <c r="AB25" s="94" t="n">
-        <v>54.91</v>
       </c>
       <c r="AC25" s="94" t="n">
         <v>54.91</v>
       </c>
       <c r="AD25" s="94" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="AE25" s="94" t="n">
         <v>15.8</v>
-      </c>
-      <c r="AE25" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="26">
@@ -9193,133 +9205,135 @@
           <t>green</t>
         </is>
       </c>
-      <c r="F26" s="92" t="inlineStr">
+      <c r="F26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G26" s="93" t="inlineStr">
+      <c r="H26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H26" s="92" t="inlineStr">
+      <c r="I26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I26" s="93" t="inlineStr">
+      <c r="J26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J26" s="91" t="inlineStr">
+      <c r="K26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K26" s="91" t="inlineStr">
+      <c r="L26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L26" s="91" t="inlineStr">
+      <c r="M26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M26" s="91" t="inlineStr">
+      <c r="N26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N26" s="91" t="inlineStr">
+      <c r="O26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O26" s="91" t="inlineStr">
+      <c r="P26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P26" s="91" t="inlineStr">
+      <c r="Q26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q26" s="91" t="inlineStr">
+      <c r="R26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R26" s="92" t="inlineStr">
+      <c r="S26" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S26" s="91" t="inlineStr">
+      <c r="T26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T26" s="93" t="inlineStr">
+      <c r="U26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U26" s="93" t="inlineStr">
+      <c r="V26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V26" s="93" t="inlineStr">
+      <c r="W26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W26" s="93" t="inlineStr">
+      <c r="X26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X26" s="93" t="inlineStr">
+      <c r="Y26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y26" s="93" t="inlineStr">
+      <c r="Z26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z26" s="93" t="inlineStr">
+      <c r="AA26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA26" s="91" t="inlineStr">
+      <c r="AB26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB26" s="91" t="inlineStr">
+      <c r="AC26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC26" s="91" t="inlineStr">
+      <c r="AD26" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD26" s="93" t="inlineStr">
+      <c r="AE26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
-      </c>
-      <c r="AE26" s="92" t="n">
-        <v/>
       </c>
     </row>
     <row r="27">
@@ -9332,7 +9346,7 @@
         <v>6.67</v>
       </c>
       <c r="C27" s="94" t="n">
-        <v>7.61</v>
+        <v>6.67</v>
       </c>
       <c r="D27" s="94" t="n">
         <v>7.61</v>
@@ -9341,34 +9355,34 @@
         <v>7.61</v>
       </c>
       <c r="F27" s="94" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="G27" s="94" t="n">
         <v>8.77</v>
       </c>
-      <c r="G27" s="94" t="n">
+      <c r="H27" s="94" t="n">
         <v>5.51</v>
       </c>
-      <c r="H27" s="94" t="n">
+      <c r="I27" s="94" t="n">
         <v>5.46</v>
       </c>
-      <c r="I27" s="94" t="n">
+      <c r="J27" s="94" t="n">
         <v>4.17</v>
-      </c>
-      <c r="J27" s="94" t="n">
-        <v>7.75</v>
       </c>
       <c r="K27" s="94" t="n">
         <v>7.75</v>
       </c>
       <c r="L27" s="94" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="M27" s="94" t="n">
         <v>8.9</v>
       </c>
-      <c r="M27" s="94" t="n">
+      <c r="N27" s="94" t="n">
         <v>9.48</v>
       </c>
-      <c r="N27" s="94" t="n">
+      <c r="O27" s="94" t="n">
         <v>6.37</v>
-      </c>
-      <c r="O27" s="94" t="n">
-        <v>5.88</v>
       </c>
       <c r="P27" s="94" t="n">
         <v>5.88</v>
@@ -9377,46 +9391,46 @@
         <v>5.88</v>
       </c>
       <c r="R27" s="94" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="S27" s="94" t="n">
         <v>4.59</v>
       </c>
-      <c r="S27" s="94" t="n">
+      <c r="T27" s="94" t="n">
         <v>6.19</v>
       </c>
-      <c r="T27" s="94" t="n">
+      <c r="U27" s="94" t="n">
         <v>3.69</v>
       </c>
-      <c r="U27" s="94" t="n">
+      <c r="V27" s="94" t="n">
         <v>4.22</v>
-      </c>
-      <c r="V27" s="94" t="n">
-        <v>3.56</v>
       </c>
       <c r="W27" s="94" t="n">
         <v>3.56</v>
       </c>
       <c r="X27" s="94" t="n">
-        <v>6.19</v>
+        <v>3.56</v>
       </c>
       <c r="Y27" s="94" t="n">
         <v>6.19</v>
       </c>
       <c r="Z27" s="94" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="AA27" s="94" t="n">
         <v>6.61</v>
       </c>
-      <c r="AA27" s="94" t="n">
+      <c r="AB27" s="94" t="n">
         <v>8.6</v>
-      </c>
-      <c r="AB27" s="94" t="n">
-        <v>7.91</v>
       </c>
       <c r="AC27" s="94" t="n">
         <v>7.91</v>
       </c>
       <c r="AD27" s="94" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="AE27" s="94" t="n">
         <v>7.57</v>
-      </c>
-      <c r="AE27" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="28">
@@ -9429,7 +9443,7 @@
         <v>15.81</v>
       </c>
       <c r="C28" s="94" t="n">
-        <v>17.81</v>
+        <v>15.81</v>
       </c>
       <c r="D28" s="94" t="n">
         <v>17.81</v>
@@ -9438,34 +9452,34 @@
         <v>17.81</v>
       </c>
       <c r="F28" s="94" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="G28" s="94" t="n">
         <v>21.52</v>
       </c>
-      <c r="G28" s="94" t="n">
+      <c r="H28" s="94" t="n">
         <v>19.95</v>
       </c>
-      <c r="H28" s="94" t="n">
+      <c r="I28" s="94" t="n">
         <v>21.81</v>
       </c>
-      <c r="I28" s="94" t="n">
+      <c r="J28" s="94" t="n">
         <v>15.29</v>
-      </c>
-      <c r="J28" s="94" t="n">
-        <v>16.05</v>
       </c>
       <c r="K28" s="94" t="n">
         <v>16.05</v>
       </c>
       <c r="L28" s="94" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="M28" s="94" t="n">
         <v>13.95</v>
       </c>
-      <c r="M28" s="94" t="n">
+      <c r="N28" s="94" t="n">
         <v>16.69</v>
       </c>
-      <c r="N28" s="94" t="n">
+      <c r="O28" s="94" t="n">
         <v>13.74</v>
-      </c>
-      <c r="O28" s="94" t="n">
-        <v>13.09</v>
       </c>
       <c r="P28" s="94" t="n">
         <v>13.09</v>
@@ -9474,46 +9488,46 @@
         <v>13.09</v>
       </c>
       <c r="R28" s="94" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="S28" s="94" t="n">
         <v>12.55</v>
       </c>
-      <c r="S28" s="94" t="n">
+      <c r="T28" s="94" t="n">
         <v>12.51</v>
       </c>
-      <c r="T28" s="94" t="n">
+      <c r="U28" s="94" t="n">
         <v>5.82</v>
       </c>
-      <c r="U28" s="94" t="n">
+      <c r="V28" s="94" t="n">
         <v>6</v>
-      </c>
-      <c r="V28" s="94" t="n">
-        <v>8.09</v>
       </c>
       <c r="W28" s="94" t="n">
         <v>8.09</v>
       </c>
       <c r="X28" s="94" t="n">
-        <v>9</v>
+        <v>8.09</v>
       </c>
       <c r="Y28" s="94" t="n">
         <v>9</v>
       </c>
       <c r="Z28" s="94" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA28" s="94" t="n">
         <v>8.289999999999999</v>
       </c>
-      <c r="AA28" s="94" t="n">
+      <c r="AB28" s="94" t="n">
         <v>7.32</v>
-      </c>
-      <c r="AB28" s="94" t="n">
-        <v>6.22</v>
       </c>
       <c r="AC28" s="94" t="n">
         <v>6.22</v>
       </c>
       <c r="AD28" s="94" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="AE28" s="94" t="n">
         <v>4.8</v>
-      </c>
-      <c r="AE28" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="29">
@@ -9526,7 +9540,7 @@
         <v>11.59</v>
       </c>
       <c r="C29" s="94" t="n">
-        <v>39.04</v>
+        <v>11.59</v>
       </c>
       <c r="D29" s="94" t="n">
         <v>39.04</v>
@@ -9535,34 +9549,34 @@
         <v>39.04</v>
       </c>
       <c r="F29" s="94" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="G29" s="94" t="n">
         <v>53.71</v>
       </c>
-      <c r="G29" s="94" t="n">
+      <c r="H29" s="94" t="n">
         <v>44.16</v>
       </c>
-      <c r="H29" s="94" t="n">
+      <c r="I29" s="94" t="n">
         <v>55.99</v>
       </c>
-      <c r="I29" s="94" t="n">
+      <c r="J29" s="94" t="n">
         <v>8.699999999999999</v>
-      </c>
-      <c r="J29" s="94" t="n">
-        <v>54.41</v>
       </c>
       <c r="K29" s="94" t="n">
         <v>54.41</v>
       </c>
       <c r="L29" s="94" t="n">
+        <v>54.41</v>
+      </c>
+      <c r="M29" s="94" t="n">
         <v>94.87</v>
       </c>
-      <c r="M29" s="94" t="n">
+      <c r="N29" s="94" t="n">
         <v>93.84999999999999</v>
       </c>
-      <c r="N29" s="94" t="n">
+      <c r="O29" s="94" t="n">
         <v>85.8</v>
-      </c>
-      <c r="O29" s="94" t="n">
-        <v>78.89</v>
       </c>
       <c r="P29" s="94" t="n">
         <v>78.89</v>
@@ -9571,46 +9585,46 @@
         <v>78.89</v>
       </c>
       <c r="R29" s="94" t="n">
+        <v>78.89</v>
+      </c>
+      <c r="S29" s="94" t="n">
         <v>51.88</v>
       </c>
-      <c r="S29" s="94" t="n">
+      <c r="T29" s="94" t="n">
         <v>83.56</v>
       </c>
-      <c r="T29" s="94" t="n">
+      <c r="U29" s="94" t="n">
         <v>6.54</v>
       </c>
-      <c r="U29" s="94" t="n">
+      <c r="V29" s="94" t="n">
         <v>8.380000000000001</v>
-      </c>
-      <c r="V29" s="94" t="n">
-        <v>10.96</v>
       </c>
       <c r="W29" s="94" t="n">
         <v>10.96</v>
       </c>
       <c r="X29" s="94" t="n">
-        <v>32.97</v>
+        <v>10.96</v>
       </c>
       <c r="Y29" s="94" t="n">
         <v>32.97</v>
       </c>
       <c r="Z29" s="94" t="n">
+        <v>32.97</v>
+      </c>
+      <c r="AA29" s="94" t="n">
         <v>34.13</v>
       </c>
-      <c r="AA29" s="94" t="n">
+      <c r="AB29" s="94" t="n">
         <v>88.52</v>
-      </c>
-      <c r="AB29" s="94" t="n">
-        <v>76.26000000000001</v>
       </c>
       <c r="AC29" s="94" t="n">
         <v>76.26000000000001</v>
       </c>
       <c r="AD29" s="94" t="n">
+        <v>76.26000000000001</v>
+      </c>
+      <c r="AE29" s="94" t="n">
         <v>5.68</v>
-      </c>
-      <c r="AE29" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="30">
@@ -9629,128 +9643,130 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D30" s="91" t="inlineStr">
+      <c r="D30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E30" s="91" t="inlineStr">
+      <c r="F30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F30" s="91" t="inlineStr">
+      <c r="G30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G30" s="92" t="inlineStr">
+      <c r="H30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H30" s="93" t="inlineStr">
+      <c r="I30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I30" s="92" t="inlineStr">
+      <c r="J30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J30" s="91" t="inlineStr">
+      <c r="K30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K30" s="91" t="inlineStr">
+      <c r="L30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L30" s="91" t="inlineStr">
+      <c r="M30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M30" s="91" t="inlineStr">
+      <c r="N30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N30" s="91" t="inlineStr">
+      <c r="O30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O30" s="92" t="inlineStr">
+      <c r="P30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P30" s="93" t="inlineStr">
+      <c r="Q30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q30" s="93" t="inlineStr">
+      <c r="R30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R30" s="93" t="inlineStr">
+      <c r="S30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S30" s="93" t="inlineStr">
+      <c r="T30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T30" s="93" t="inlineStr">
+      <c r="U30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U30" s="93" t="inlineStr">
+      <c r="V30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V30" s="93" t="inlineStr">
+      <c r="W30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W30" s="93" t="inlineStr">
+      <c r="X30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X30" s="92" t="inlineStr">
+      <c r="Y30" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y30" s="91" t="inlineStr">
+      <c r="Z30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z30" s="91" t="inlineStr">
+      <c r="AA30" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA30" s="93" t="inlineStr">
+      <c r="AB30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
-      </c>
-      <c r="AB30" s="92" t="n">
-        <v/>
       </c>
       <c r="AC30" s="92" t="n">
         <v/>
@@ -9769,64 +9785,64 @@
         </is>
       </c>
       <c r="B31" s="94" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="C31" s="94" t="n">
         <v>0.12</v>
       </c>
-      <c r="C31" s="94" t="n">
+      <c r="D31" s="94" t="n">
         <v>1.56</v>
-      </c>
-      <c r="D31" s="94" t="n">
-        <v>3.99</v>
       </c>
       <c r="E31" s="94" t="n">
         <v>3.99</v>
       </c>
       <c r="F31" s="94" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="G31" s="94" t="n">
         <v>1.11</v>
       </c>
-      <c r="G31" s="94" t="n">
+      <c r="H31" s="94" t="n">
         <v>0.35</v>
       </c>
-      <c r="H31" s="94" t="n">
+      <c r="I31" s="94" t="n">
         <v>0.29</v>
       </c>
-      <c r="I31" s="94" t="n">
+      <c r="J31" s="94" t="n">
         <v>2.49</v>
-      </c>
-      <c r="J31" s="94" t="n">
-        <v>5.32</v>
       </c>
       <c r="K31" s="94" t="n">
         <v>5.32</v>
       </c>
       <c r="L31" s="94" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="M31" s="94" t="n">
         <v>4.76</v>
       </c>
-      <c r="M31" s="94" t="n">
+      <c r="N31" s="94" t="n">
         <v>4.05</v>
       </c>
-      <c r="N31" s="94" t="n">
+      <c r="O31" s="94" t="n">
         <v>1.6</v>
       </c>
-      <c r="O31" s="94" t="n">
+      <c r="P31" s="94" t="n">
         <v>-0.13</v>
-      </c>
-      <c r="P31" s="94" t="n">
-        <v>-1.36</v>
       </c>
       <c r="Q31" s="94" t="n">
         <v>-1.36</v>
       </c>
       <c r="R31" s="94" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="S31" s="94" t="n">
         <v>-0.87</v>
       </c>
-      <c r="S31" s="94" t="n">
+      <c r="T31" s="94" t="n">
         <v>-1.88</v>
       </c>
-      <c r="T31" s="94" t="n">
+      <c r="U31" s="94" t="n">
         <v>-3.6</v>
-      </c>
-      <c r="U31" s="94" t="n">
-        <v>-1.05</v>
       </c>
       <c r="V31" s="94" t="n">
         <v>-1.05</v>
@@ -9835,19 +9851,19 @@
         <v>-1.05</v>
       </c>
       <c r="X31" s="94" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="Y31" s="94" t="n">
         <v>0.57</v>
       </c>
-      <c r="Y31" s="94" t="n">
+      <c r="Z31" s="94" t="n">
         <v>1.79</v>
       </c>
-      <c r="Z31" s="94" t="n">
+      <c r="AA31" s="94" t="n">
         <v>2.94</v>
       </c>
-      <c r="AA31" s="94" t="n">
+      <c r="AB31" s="94" t="n">
         <v>-0.07000000000000001</v>
-      </c>
-      <c r="AB31" s="94" t="n">
-        <v/>
       </c>
       <c r="AC31" s="94" t="n">
         <v/>
@@ -9866,64 +9882,64 @@
         </is>
       </c>
       <c r="B32" s="94" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="C32" s="94" t="n">
         <v>9.98</v>
       </c>
-      <c r="C32" s="94" t="n">
+      <c r="D32" s="94" t="n">
         <v>10.95</v>
-      </c>
-      <c r="D32" s="94" t="n">
-        <v>12.78</v>
       </c>
       <c r="E32" s="94" t="n">
         <v>12.78</v>
       </c>
       <c r="F32" s="94" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="G32" s="94" t="n">
         <v>13.95</v>
       </c>
-      <c r="G32" s="94" t="n">
+      <c r="H32" s="94" t="n">
         <v>25.29</v>
       </c>
-      <c r="H32" s="94" t="n">
+      <c r="I32" s="94" t="n">
         <v>8.65</v>
       </c>
-      <c r="I32" s="94" t="n">
+      <c r="J32" s="94" t="n">
         <v>3.78</v>
-      </c>
-      <c r="J32" s="94" t="n">
-        <v>2.12</v>
       </c>
       <c r="K32" s="94" t="n">
         <v>2.12</v>
       </c>
       <c r="L32" s="94" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M32" s="94" t="n">
         <v>3.72</v>
       </c>
-      <c r="M32" s="94" t="n">
+      <c r="N32" s="94" t="n">
         <v>3.06</v>
       </c>
-      <c r="N32" s="94" t="n">
+      <c r="O32" s="94" t="n">
         <v>3.61</v>
       </c>
-      <c r="O32" s="94" t="n">
+      <c r="P32" s="94" t="n">
         <v>2.73</v>
-      </c>
-      <c r="P32" s="94" t="n">
-        <v>-1.8</v>
       </c>
       <c r="Q32" s="94" t="n">
         <v>-1.8</v>
       </c>
       <c r="R32" s="94" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="S32" s="94" t="n">
         <v>-2.58</v>
       </c>
-      <c r="S32" s="94" t="n">
+      <c r="T32" s="94" t="n">
         <v>-2.92</v>
       </c>
-      <c r="T32" s="94" t="n">
+      <c r="U32" s="94" t="n">
         <v>-3.97</v>
-      </c>
-      <c r="U32" s="94" t="n">
-        <v>-2.33</v>
       </c>
       <c r="V32" s="94" t="n">
         <v>-2.33</v>
@@ -9932,19 +9948,19 @@
         <v>-2.33</v>
       </c>
       <c r="X32" s="94" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="Y32" s="94" t="n">
         <v>-3.63</v>
       </c>
-      <c r="Y32" s="94" t="n">
+      <c r="Z32" s="94" t="n">
         <v>-3.14</v>
       </c>
-      <c r="Z32" s="94" t="n">
+      <c r="AA32" s="94" t="n">
         <v>-2.69</v>
       </c>
-      <c r="AA32" s="94" t="n">
+      <c r="AB32" s="94" t="n">
         <v>-6.91</v>
-      </c>
-      <c r="AB32" s="94" t="n">
-        <v/>
       </c>
       <c r="AC32" s="94" t="n">
         <v/>
@@ -9963,64 +9979,64 @@
         </is>
       </c>
       <c r="B33" s="94" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="C33" s="94" t="n">
         <v>37.3</v>
       </c>
-      <c r="C33" s="94" t="n">
+      <c r="D33" s="94" t="n">
         <v>38.95</v>
-      </c>
-      <c r="D33" s="94" t="n">
-        <v>54.66</v>
       </c>
       <c r="E33" s="94" t="n">
         <v>54.66</v>
       </c>
       <c r="F33" s="94" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="G33" s="94" t="n">
         <v>53.61</v>
       </c>
-      <c r="G33" s="94" t="n">
+      <c r="H33" s="94" t="n">
         <v>51.93</v>
       </c>
-      <c r="H33" s="94" t="n">
+      <c r="I33" s="94" t="n">
         <v>44.81</v>
       </c>
-      <c r="I33" s="94" t="n">
+      <c r="J33" s="94" t="n">
         <v>54.76</v>
-      </c>
-      <c r="J33" s="94" t="n">
-        <v>63.06</v>
       </c>
       <c r="K33" s="94" t="n">
         <v>63.06</v>
       </c>
       <c r="L33" s="94" t="n">
+        <v>63.06</v>
+      </c>
+      <c r="M33" s="94" t="n">
         <v>63.69</v>
       </c>
-      <c r="M33" s="94" t="n">
+      <c r="N33" s="94" t="n">
         <v>59.51</v>
       </c>
-      <c r="N33" s="94" t="n">
+      <c r="O33" s="94" t="n">
         <v>49.22</v>
       </c>
-      <c r="O33" s="94" t="n">
+      <c r="P33" s="94" t="n">
         <v>46.79</v>
-      </c>
-      <c r="P33" s="94" t="n">
-        <v>37.14</v>
       </c>
       <c r="Q33" s="94" t="n">
         <v>37.14</v>
       </c>
       <c r="R33" s="94" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="S33" s="94" t="n">
         <v>38.82</v>
       </c>
-      <c r="S33" s="94" t="n">
+      <c r="T33" s="94" t="n">
         <v>36.1</v>
       </c>
-      <c r="T33" s="94" t="n">
+      <c r="U33" s="94" t="n">
         <v>36.44</v>
-      </c>
-      <c r="U33" s="94" t="n">
-        <v>45.43</v>
       </c>
       <c r="V33" s="94" t="n">
         <v>45.43</v>
@@ -10029,19 +10045,19 @@
         <v>45.43</v>
       </c>
       <c r="X33" s="94" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="Y33" s="94" t="n">
         <v>52.04</v>
       </c>
-      <c r="Y33" s="94" t="n">
+      <c r="Z33" s="94" t="n">
         <v>58.96</v>
       </c>
-      <c r="Z33" s="94" t="n">
+      <c r="AA33" s="94" t="n">
         <v>60.92</v>
       </c>
-      <c r="AA33" s="94" t="n">
+      <c r="AB33" s="94" t="n">
         <v>49.64</v>
-      </c>
-      <c r="AB33" s="94" t="n">
-        <v/>
       </c>
       <c r="AC33" s="94" t="n">
         <v/>
@@ -10059,153 +10075,155 @@
           <t>vn:EIDE</t>
         </is>
       </c>
-      <c r="B34" s="92" t="inlineStr">
+      <c r="B34" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C34" s="91" t="inlineStr">
+      <c r="D34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D34" s="91" t="inlineStr">
+      <c r="E34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E34" s="91" t="inlineStr">
+      <c r="F34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F34" s="91" t="inlineStr">
+      <c r="G34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G34" s="91" t="inlineStr">
+      <c r="H34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H34" s="91" t="inlineStr">
+      <c r="I34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I34" s="91" t="inlineStr">
+      <c r="J34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J34" s="91" t="inlineStr">
+      <c r="K34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K34" s="91" t="inlineStr">
+      <c r="L34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L34" s="91" t="inlineStr">
+      <c r="M34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M34" s="92" t="inlineStr">
+      <c r="N34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N34" s="92" t="inlineStr">
+      <c r="O34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O34" s="91" t="inlineStr">
+      <c r="P34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P34" s="91" t="inlineStr">
+      <c r="Q34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q34" s="91" t="inlineStr">
+      <c r="R34" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R34" s="92" t="inlineStr">
+      <c r="S34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S34" s="92" t="inlineStr">
+      <c r="T34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T34" s="93" t="inlineStr">
+      <c r="U34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U34" s="93" t="inlineStr">
+      <c r="V34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V34" s="93" t="inlineStr">
+      <c r="W34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W34" s="93" t="inlineStr">
+      <c r="X34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X34" s="93" t="inlineStr">
+      <c r="Y34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y34" s="93" t="inlineStr">
+      <c r="Z34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z34" s="93" t="inlineStr">
+      <c r="AA34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA34" s="93" t="inlineStr">
+      <c r="AB34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB34" s="93" t="inlineStr">
+      <c r="AC34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC34" s="93" t="inlineStr">
+      <c r="AD34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD34" s="92" t="inlineStr">
+      <c r="AE34" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
-      </c>
-      <c r="AE34" s="92" t="n">
-        <v/>
       </c>
     </row>
     <row r="35">
@@ -10215,10 +10233,10 @@
         </is>
       </c>
       <c r="B35" s="94" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C35" s="94" t="n">
         <v>-0.15</v>
-      </c>
-      <c r="C35" s="94" t="n">
-        <v>0.05</v>
       </c>
       <c r="D35" s="94" t="n">
         <v>0.05</v>
@@ -10245,64 +10263,64 @@
         <v>0.05</v>
       </c>
       <c r="L35" s="94" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M35" s="94" t="n">
         <v>0.08</v>
       </c>
-      <c r="M35" s="94" t="n">
+      <c r="N35" s="94" t="n">
         <v>-1.53</v>
       </c>
-      <c r="N35" s="94" t="n">
+      <c r="O35" s="94" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="O35" s="94" t="n">
+      <c r="P35" s="94" t="n">
         <v>-0.25</v>
-      </c>
-      <c r="P35" s="94" t="n">
-        <v>-0.66</v>
       </c>
       <c r="Q35" s="94" t="n">
         <v>-0.66</v>
       </c>
       <c r="R35" s="94" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="S35" s="94" t="n">
         <v>-2.25</v>
       </c>
-      <c r="S35" s="94" t="n">
+      <c r="T35" s="94" t="n">
         <v>-2.65</v>
       </c>
-      <c r="T35" s="94" t="n">
+      <c r="U35" s="94" t="n">
         <v>-3.96</v>
       </c>
-      <c r="U35" s="94" t="n">
+      <c r="V35" s="94" t="n">
         <v>-3.87</v>
-      </c>
-      <c r="V35" s="94" t="n">
-        <v>-4.36</v>
       </c>
       <c r="W35" s="94" t="n">
         <v>-4.36</v>
       </c>
       <c r="X35" s="94" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="Y35" s="94" t="n">
         <v>-2.63</v>
       </c>
-      <c r="Y35" s="94" t="n">
+      <c r="Z35" s="94" t="n">
         <v>-2.35</v>
       </c>
-      <c r="Z35" s="94" t="n">
+      <c r="AA35" s="94" t="n">
         <v>-3.06</v>
       </c>
-      <c r="AA35" s="94" t="n">
+      <c r="AB35" s="94" t="n">
         <v>-3.26</v>
-      </c>
-      <c r="AB35" s="94" t="n">
-        <v>-2.47</v>
       </c>
       <c r="AC35" s="94" t="n">
         <v>-2.47</v>
       </c>
       <c r="AD35" s="94" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="AE35" s="94" t="n">
         <v>-0.95</v>
-      </c>
-      <c r="AE35" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="36">
@@ -10312,10 +10330,10 @@
         </is>
       </c>
       <c r="B36" s="94" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="C36" s="94" t="n">
         <v>3.06</v>
-      </c>
-      <c r="C36" s="94" t="n">
-        <v>4.53</v>
       </c>
       <c r="D36" s="94" t="n">
         <v>4.53</v>
@@ -10342,64 +10360,64 @@
         <v>4.53</v>
       </c>
       <c r="L36" s="94" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="M36" s="94" t="n">
         <v>6.02</v>
       </c>
-      <c r="M36" s="94" t="n">
+      <c r="N36" s="94" t="n">
         <v>0.48</v>
       </c>
-      <c r="N36" s="94" t="n">
+      <c r="O36" s="94" t="n">
         <v>1.56</v>
       </c>
-      <c r="O36" s="94" t="n">
+      <c r="P36" s="94" t="n">
         <v>-0.16</v>
-      </c>
-      <c r="P36" s="94" t="n">
-        <v>0.33</v>
       </c>
       <c r="Q36" s="94" t="n">
         <v>0.33</v>
       </c>
       <c r="R36" s="94" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="S36" s="94" t="n">
         <v>-0.34</v>
       </c>
-      <c r="S36" s="94" t="n">
+      <c r="T36" s="94" t="n">
         <v>-0.48</v>
       </c>
-      <c r="T36" s="94" t="n">
+      <c r="U36" s="94" t="n">
         <v>-0.33</v>
       </c>
-      <c r="U36" s="94" t="n">
+      <c r="V36" s="94" t="n">
         <v>-0.23</v>
-      </c>
-      <c r="V36" s="94" t="n">
-        <v>-0.11</v>
       </c>
       <c r="W36" s="94" t="n">
         <v>-0.11</v>
       </c>
       <c r="X36" s="94" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="Y36" s="94" t="n">
         <v>-0.71</v>
       </c>
-      <c r="Y36" s="94" t="n">
+      <c r="Z36" s="94" t="n">
         <v>-1.09</v>
       </c>
-      <c r="Z36" s="94" t="n">
+      <c r="AA36" s="94" t="n">
         <v>-2.16</v>
       </c>
-      <c r="AA36" s="94" t="n">
+      <c r="AB36" s="94" t="n">
         <v>-1.76</v>
-      </c>
-      <c r="AB36" s="94" t="n">
-        <v>-2.08</v>
       </c>
       <c r="AC36" s="94" t="n">
         <v>-2.08</v>
       </c>
       <c r="AD36" s="94" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="AE36" s="94" t="n">
         <v>-0.79</v>
-      </c>
-      <c r="AE36" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="37">
@@ -10409,10 +10427,10 @@
         </is>
       </c>
       <c r="B37" s="94" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="C37" s="94" t="n">
         <v>47.07</v>
-      </c>
-      <c r="C37" s="94" t="n">
-        <v>85.3</v>
       </c>
       <c r="D37" s="94" t="n">
         <v>85.3</v>
@@ -10439,64 +10457,64 @@
         <v>85.3</v>
       </c>
       <c r="L37" s="94" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="M37" s="94" t="n">
         <v>80.56</v>
       </c>
-      <c r="M37" s="94" t="n">
+      <c r="N37" s="94" t="n">
         <v>39.31</v>
       </c>
-      <c r="N37" s="94" t="n">
+      <c r="O37" s="94" t="n">
         <v>55.71</v>
       </c>
-      <c r="O37" s="94" t="n">
+      <c r="P37" s="94" t="n">
         <v>76.36</v>
-      </c>
-      <c r="P37" s="94" t="n">
-        <v>75.59</v>
       </c>
       <c r="Q37" s="94" t="n">
         <v>75.59</v>
       </c>
       <c r="R37" s="94" t="n">
+        <v>75.59</v>
+      </c>
+      <c r="S37" s="94" t="n">
         <v>63.48</v>
       </c>
-      <c r="S37" s="94" t="n">
+      <c r="T37" s="94" t="n">
         <v>47.6</v>
       </c>
-      <c r="T37" s="94" t="n">
+      <c r="U37" s="94" t="n">
         <v>21.39</v>
       </c>
-      <c r="U37" s="94" t="n">
+      <c r="V37" s="94" t="n">
         <v>30.94</v>
-      </c>
-      <c r="V37" s="94" t="n">
-        <v>9.859999999999999</v>
       </c>
       <c r="W37" s="94" t="n">
         <v>9.859999999999999</v>
       </c>
       <c r="X37" s="94" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="Y37" s="94" t="n">
         <v>24.76</v>
       </c>
-      <c r="Y37" s="94" t="n">
+      <c r="Z37" s="94" t="n">
         <v>37.84</v>
       </c>
-      <c r="Z37" s="94" t="n">
+      <c r="AA37" s="94" t="n">
         <v>14.49</v>
       </c>
-      <c r="AA37" s="94" t="n">
+      <c r="AB37" s="94" t="n">
         <v>11.22</v>
-      </c>
-      <c r="AB37" s="94" t="n">
-        <v>17.28</v>
       </c>
       <c r="AC37" s="94" t="n">
         <v>17.28</v>
       </c>
       <c r="AD37" s="94" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="AE37" s="94" t="n">
         <v>51.04</v>
-      </c>
-      <c r="AE37" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="38">
@@ -10530,129 +10548,129 @@
           <t>red</t>
         </is>
       </c>
-      <c r="G38" s="92" t="inlineStr">
+      <c r="G38" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H38" s="92" t="inlineStr">
+      <c r="I38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I38" s="93" t="inlineStr">
+      <c r="J38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J38" s="92" t="inlineStr">
+      <c r="K38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K38" s="92" t="inlineStr">
+      <c r="L38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L38" s="92" t="inlineStr">
+      <c r="M38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M38" s="92" t="inlineStr">
+      <c r="N38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N38" s="93" t="inlineStr">
+      <c r="O38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O38" s="92" t="inlineStr">
+      <c r="P38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P38" s="92" t="inlineStr">
+      <c r="Q38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q38" s="92" t="inlineStr">
+      <c r="R38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R38" s="92" t="inlineStr">
+      <c r="S38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S38" s="92" t="inlineStr">
+      <c r="T38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T38" s="93" t="inlineStr">
+      <c r="U38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U38" s="93" t="inlineStr">
+      <c r="V38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V38" s="93" t="inlineStr">
+      <c r="W38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W38" s="93" t="inlineStr">
+      <c r="X38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X38" s="93" t="inlineStr">
+      <c r="Y38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y38" s="92" t="inlineStr">
+      <c r="Z38" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z38" s="93" t="inlineStr">
+      <c r="AA38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA38" s="93" t="inlineStr">
+      <c r="AB38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB38" s="91" t="inlineStr">
+      <c r="AC38" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC38" s="91" t="inlineStr">
+      <c r="AD38" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD38" s="91" t="inlineStr">
+      <c r="AE38" s="91" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AE38" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -10663,94 +10681,94 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="C39" s="94" t="n">
         <v>-2.96</v>
-      </c>
-      <c r="C39" s="94" t="n">
-        <v>-3.57</v>
       </c>
       <c r="D39" s="94" t="n">
         <v>-3.57</v>
       </c>
       <c r="E39" s="94" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="F39" s="94" t="n">
         <v>-2.49</v>
       </c>
-      <c r="F39" s="94" t="n">
+      <c r="G39" s="94" t="n">
         <v>-2.57</v>
       </c>
-      <c r="G39" s="94" t="n">
+      <c r="H39" s="94" t="n">
         <v>-4</v>
       </c>
-      <c r="H39" s="94" t="n">
+      <c r="I39" s="94" t="n">
         <v>-4.39</v>
       </c>
-      <c r="I39" s="94" t="n">
+      <c r="J39" s="94" t="n">
         <v>-5.72</v>
-      </c>
-      <c r="J39" s="94" t="n">
-        <v>-5.2</v>
       </c>
       <c r="K39" s="94" t="n">
         <v>-5.2</v>
       </c>
       <c r="L39" s="94" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="M39" s="94" t="n">
         <v>-4.36</v>
       </c>
-      <c r="M39" s="94" t="n">
+      <c r="N39" s="94" t="n">
         <v>-3.77</v>
       </c>
-      <c r="N39" s="94" t="n">
+      <c r="O39" s="94" t="n">
         <v>-5.28</v>
       </c>
-      <c r="O39" s="94" t="n">
+      <c r="P39" s="94" t="n">
         <v>-3.76</v>
-      </c>
-      <c r="P39" s="94" t="n">
-        <v>-4.49</v>
       </c>
       <c r="Q39" s="94" t="n">
         <v>-4.49</v>
       </c>
       <c r="R39" s="94" t="n">
+        <v>-4.49</v>
+      </c>
+      <c r="S39" s="94" t="n">
         <v>-5.06</v>
       </c>
-      <c r="S39" s="94" t="n">
+      <c r="T39" s="94" t="n">
         <v>-5.54</v>
       </c>
-      <c r="T39" s="94" t="n">
+      <c r="U39" s="94" t="n">
         <v>-5.56</v>
       </c>
-      <c r="U39" s="94" t="n">
+      <c r="V39" s="94" t="n">
         <v>-6.35</v>
-      </c>
-      <c r="V39" s="94" t="n">
-        <v>-5.43</v>
       </c>
       <c r="W39" s="94" t="n">
         <v>-5.43</v>
       </c>
       <c r="X39" s="94" t="n">
+        <v>-5.43</v>
+      </c>
+      <c r="Y39" s="94" t="n">
         <v>-5.31</v>
       </c>
-      <c r="Y39" s="94" t="n">
+      <c r="Z39" s="94" t="n">
         <v>-3.97</v>
       </c>
-      <c r="Z39" s="94" t="n">
+      <c r="AA39" s="94" t="n">
         <v>-4.18</v>
       </c>
-      <c r="AA39" s="94" t="n">
+      <c r="AB39" s="94" t="n">
         <v>-4.3</v>
-      </c>
-      <c r="AB39" s="94" t="n">
-        <v>-2.95</v>
       </c>
       <c r="AC39" s="94" t="n">
         <v>-2.95</v>
       </c>
       <c r="AD39" s="94" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="AE39" s="94" t="n">
         <v>-1.36</v>
-      </c>
-      <c r="AE39" s="94" t="n">
-        <v>-3.89</v>
       </c>
     </row>
     <row r="40">
@@ -10760,94 +10778,94 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="C40" s="94" t="n">
         <v>-2.43</v>
-      </c>
-      <c r="C40" s="94" t="n">
-        <v>-1.84</v>
       </c>
       <c r="D40" s="94" t="n">
         <v>-1.84</v>
       </c>
       <c r="E40" s="94" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="F40" s="94" t="n">
         <v>-2.7</v>
       </c>
-      <c r="F40" s="94" t="n">
+      <c r="G40" s="94" t="n">
         <v>-3.7</v>
       </c>
-      <c r="G40" s="94" t="n">
+      <c r="H40" s="94" t="n">
         <v>-2.98</v>
       </c>
-      <c r="H40" s="94" t="n">
+      <c r="I40" s="94" t="n">
         <v>-4.49</v>
       </c>
-      <c r="I40" s="94" t="n">
+      <c r="J40" s="94" t="n">
         <v>-4.11</v>
-      </c>
-      <c r="J40" s="94" t="n">
-        <v>-3.26</v>
       </c>
       <c r="K40" s="94" t="n">
         <v>-3.26</v>
       </c>
       <c r="L40" s="94" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="M40" s="94" t="n">
         <v>-5.51</v>
       </c>
-      <c r="M40" s="94" t="n">
+      <c r="N40" s="94" t="n">
         <v>-6.67</v>
       </c>
-      <c r="N40" s="94" t="n">
+      <c r="O40" s="94" t="n">
         <v>-7.22</v>
       </c>
-      <c r="O40" s="94" t="n">
+      <c r="P40" s="94" t="n">
         <v>-5.38</v>
-      </c>
-      <c r="P40" s="94" t="n">
-        <v>-5.82</v>
       </c>
       <c r="Q40" s="94" t="n">
         <v>-5.82</v>
       </c>
       <c r="R40" s="94" t="n">
+        <v>-5.82</v>
+      </c>
+      <c r="S40" s="94" t="n">
         <v>-5.27</v>
       </c>
-      <c r="S40" s="94" t="n">
+      <c r="T40" s="94" t="n">
         <v>-4.14</v>
       </c>
-      <c r="T40" s="94" t="n">
+      <c r="U40" s="94" t="n">
         <v>-4.55</v>
       </c>
-      <c r="U40" s="94" t="n">
+      <c r="V40" s="94" t="n">
         <v>-5.1</v>
-      </c>
-      <c r="V40" s="94" t="n">
-        <v>-3.88</v>
       </c>
       <c r="W40" s="94" t="n">
         <v>-3.88</v>
       </c>
       <c r="X40" s="94" t="n">
+        <v>-3.88</v>
+      </c>
+      <c r="Y40" s="94" t="n">
         <v>-3.7</v>
       </c>
-      <c r="Y40" s="94" t="n">
+      <c r="Z40" s="94" t="n">
         <v>-3.93</v>
       </c>
-      <c r="Z40" s="94" t="n">
+      <c r="AA40" s="94" t="n">
         <v>-3.12</v>
       </c>
-      <c r="AA40" s="94" t="n">
+      <c r="AB40" s="94" t="n">
         <v>-3.35</v>
-      </c>
-      <c r="AB40" s="94" t="n">
-        <v>-1.61</v>
       </c>
       <c r="AC40" s="94" t="n">
         <v>-1.61</v>
       </c>
       <c r="AD40" s="94" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="AE40" s="94" t="n">
         <v>0.06</v>
-      </c>
-      <c r="AE40" s="94" t="n">
-        <v>-1.77</v>
       </c>
     </row>
     <row r="41">
@@ -10857,94 +10875,94 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
+        <v>60.96</v>
+      </c>
+      <c r="C41" s="94" t="n">
         <v>51.83</v>
-      </c>
-      <c r="C41" s="94" t="n">
-        <v>55.73</v>
       </c>
       <c r="D41" s="94" t="n">
         <v>55.73</v>
       </c>
       <c r="E41" s="94" t="n">
+        <v>55.73</v>
+      </c>
+      <c r="F41" s="94" t="n">
         <v>55.68</v>
       </c>
-      <c r="F41" s="94" t="n">
+      <c r="G41" s="94" t="n">
         <v>48.37</v>
       </c>
-      <c r="G41" s="94" t="n">
+      <c r="H41" s="94" t="n">
         <v>45.92</v>
       </c>
-      <c r="H41" s="94" t="n">
+      <c r="I41" s="94" t="n">
         <v>38.59</v>
       </c>
-      <c r="I41" s="94" t="n">
+      <c r="J41" s="94" t="n">
         <v>31.52</v>
-      </c>
-      <c r="J41" s="94" t="n">
-        <v>37.51</v>
       </c>
       <c r="K41" s="94" t="n">
         <v>37.51</v>
       </c>
       <c r="L41" s="94" t="n">
+        <v>37.51</v>
+      </c>
+      <c r="M41" s="94" t="n">
         <v>40.26</v>
       </c>
-      <c r="M41" s="94" t="n">
+      <c r="N41" s="94" t="n">
         <v>38.85</v>
       </c>
-      <c r="N41" s="94" t="n">
+      <c r="O41" s="94" t="n">
         <v>31.71</v>
       </c>
-      <c r="O41" s="94" t="n">
+      <c r="P41" s="94" t="n">
         <v>41.13</v>
-      </c>
-      <c r="P41" s="94" t="n">
-        <v>34.71</v>
       </c>
       <c r="Q41" s="94" t="n">
         <v>34.71</v>
       </c>
       <c r="R41" s="94" t="n">
+        <v>34.71</v>
+      </c>
+      <c r="S41" s="94" t="n">
         <v>38.21</v>
       </c>
-      <c r="S41" s="94" t="n">
+      <c r="T41" s="94" t="n">
         <v>33.68</v>
       </c>
-      <c r="T41" s="94" t="n">
+      <c r="U41" s="94" t="n">
         <v>30.45</v>
       </c>
-      <c r="U41" s="94" t="n">
+      <c r="V41" s="94" t="n">
         <v>28.07</v>
-      </c>
-      <c r="V41" s="94" t="n">
-        <v>34.68</v>
       </c>
       <c r="W41" s="94" t="n">
         <v>34.68</v>
       </c>
       <c r="X41" s="94" t="n">
+        <v>34.68</v>
+      </c>
+      <c r="Y41" s="94" t="n">
         <v>36.46</v>
       </c>
-      <c r="Y41" s="94" t="n">
+      <c r="Z41" s="94" t="n">
         <v>40.56</v>
       </c>
-      <c r="Z41" s="94" t="n">
+      <c r="AA41" s="94" t="n">
         <v>40.95</v>
       </c>
-      <c r="AA41" s="94" t="n">
+      <c r="AB41" s="94" t="n">
         <v>38.45</v>
-      </c>
-      <c r="AB41" s="94" t="n">
-        <v>48.38</v>
       </c>
       <c r="AC41" s="94" t="n">
         <v>48.38</v>
       </c>
       <c r="AD41" s="94" t="n">
+        <v>48.38</v>
+      </c>
+      <c r="AE41" s="94" t="n">
         <v>55.82</v>
-      </c>
-      <c r="AE41" s="94" t="n">
-        <v>39</v>
       </c>
     </row>
     <row r="42">
@@ -10993,113 +11011,115 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="J42" s="91" t="inlineStr">
+      <c r="J42" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K42" s="91" t="inlineStr">
+      <c r="L42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L42" s="91" t="inlineStr">
+      <c r="M42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M42" s="91" t="inlineStr">
+      <c r="N42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N42" s="91" t="inlineStr">
+      <c r="O42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O42" s="91" t="inlineStr">
+      <c r="P42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P42" s="91" t="inlineStr">
+      <c r="Q42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q42" s="91" t="inlineStr">
+      <c r="R42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R42" s="91" t="inlineStr">
+      <c r="S42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S42" s="91" t="inlineStr">
+      <c r="T42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T42" s="92" t="inlineStr">
+      <c r="U42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U42" s="92" t="inlineStr">
+      <c r="V42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V42" s="92" t="inlineStr">
+      <c r="W42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W42" s="92" t="inlineStr">
+      <c r="X42" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X42" s="91" t="inlineStr">
+      <c r="Y42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y42" s="91" t="inlineStr">
+      <c r="Z42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z42" s="91" t="inlineStr">
+      <c r="AA42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA42" s="91" t="inlineStr">
+      <c r="AB42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB42" s="93" t="inlineStr">
+      <c r="AC42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC42" s="93" t="inlineStr">
+      <c r="AD42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD42" s="91" t="inlineStr">
+      <c r="AE42" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
-      </c>
-      <c r="AE42" s="92" t="n">
-        <v/>
       </c>
     </row>
     <row r="43">
@@ -11112,7 +11132,7 @@
         <v>6.59</v>
       </c>
       <c r="C43" s="94" t="n">
-        <v>7.33</v>
+        <v>6.59</v>
       </c>
       <c r="D43" s="94" t="n">
         <v>7.33</v>
@@ -11121,82 +11141,82 @@
         <v>7.33</v>
       </c>
       <c r="F43" s="94" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="G43" s="94" t="n">
         <v>7.73</v>
       </c>
-      <c r="G43" s="94" t="n">
+      <c r="H43" s="94" t="n">
         <v>6.25</v>
       </c>
-      <c r="H43" s="94" t="n">
+      <c r="I43" s="94" t="n">
         <v>7.44</v>
       </c>
-      <c r="I43" s="94" t="n">
+      <c r="J43" s="94" t="n">
         <v>6.44</v>
-      </c>
-      <c r="J43" s="94" t="n">
-        <v>5.55</v>
       </c>
       <c r="K43" s="94" t="n">
         <v>5.55</v>
       </c>
       <c r="L43" s="94" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="M43" s="94" t="n">
         <v>4.44</v>
       </c>
-      <c r="M43" s="94" t="n">
+      <c r="N43" s="94" t="n">
         <v>4.53</v>
       </c>
-      <c r="N43" s="94" t="n">
+      <c r="O43" s="94" t="n">
         <v>3.57</v>
       </c>
-      <c r="O43" s="94" t="n">
+      <c r="P43" s="94" t="n">
         <v>3.15</v>
-      </c>
-      <c r="P43" s="94" t="n">
-        <v>2.32</v>
       </c>
       <c r="Q43" s="94" t="n">
         <v>2.32</v>
       </c>
       <c r="R43" s="94" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S43" s="94" t="n">
         <v>1.31</v>
       </c>
-      <c r="S43" s="94" t="n">
+      <c r="T43" s="94" t="n">
         <v>-1.82</v>
       </c>
-      <c r="T43" s="94" t="n">
+      <c r="U43" s="94" t="n">
         <v>-2.11</v>
       </c>
-      <c r="U43" s="94" t="n">
+      <c r="V43" s="94" t="n">
         <v>-1.11</v>
-      </c>
-      <c r="V43" s="94" t="n">
-        <v>-1.21</v>
       </c>
       <c r="W43" s="94" t="n">
         <v>-1.21</v>
       </c>
       <c r="X43" s="94" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="Y43" s="94" t="n">
         <v>-1.47</v>
       </c>
-      <c r="Y43" s="94" t="n">
+      <c r="Z43" s="94" t="n">
         <v>-1.66</v>
       </c>
-      <c r="Z43" s="94" t="n">
+      <c r="AA43" s="94" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="AA43" s="94" t="n">
+      <c r="AB43" s="94" t="n">
         <v>-1.51</v>
-      </c>
-      <c r="AB43" s="94" t="n">
-        <v>-3.18</v>
       </c>
       <c r="AC43" s="94" t="n">
         <v>-3.18</v>
       </c>
       <c r="AD43" s="94" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="AE43" s="94" t="n">
         <v>-2.41</v>
-      </c>
-      <c r="AE43" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="44">
@@ -11209,7 +11229,7 @@
         <v>7.11</v>
       </c>
       <c r="C44" s="94" t="n">
-        <v>9.27</v>
+        <v>7.11</v>
       </c>
       <c r="D44" s="94" t="n">
         <v>9.27</v>
@@ -11218,82 +11238,82 @@
         <v>9.27</v>
       </c>
       <c r="F44" s="94" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="G44" s="94" t="n">
         <v>9.529999999999999</v>
       </c>
-      <c r="G44" s="94" t="n">
+      <c r="H44" s="94" t="n">
         <v>8.289999999999999</v>
       </c>
-      <c r="H44" s="94" t="n">
+      <c r="I44" s="94" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="I44" s="94" t="n">
+      <c r="J44" s="94" t="n">
         <v>8.82</v>
-      </c>
-      <c r="J44" s="94" t="n">
-        <v>11.19</v>
       </c>
       <c r="K44" s="94" t="n">
         <v>11.19</v>
       </c>
       <c r="L44" s="94" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="M44" s="94" t="n">
         <v>10.4</v>
       </c>
-      <c r="M44" s="94" t="n">
+      <c r="N44" s="94" t="n">
         <v>8.08</v>
       </c>
-      <c r="N44" s="94" t="n">
+      <c r="O44" s="94" t="n">
         <v>5.43</v>
       </c>
-      <c r="O44" s="94" t="n">
+      <c r="P44" s="94" t="n">
         <v>2.68</v>
-      </c>
-      <c r="P44" s="94" t="n">
-        <v>3.14</v>
       </c>
       <c r="Q44" s="94" t="n">
         <v>3.14</v>
       </c>
       <c r="R44" s="94" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="S44" s="94" t="n">
         <v>2.56</v>
       </c>
-      <c r="S44" s="94" t="n">
+      <c r="T44" s="94" t="n">
         <v>-0.57</v>
       </c>
-      <c r="T44" s="94" t="n">
+      <c r="U44" s="94" t="n">
         <v>-0.05</v>
       </c>
-      <c r="U44" s="94" t="n">
+      <c r="V44" s="94" t="n">
         <v>-1.4</v>
-      </c>
-      <c r="V44" s="94" t="n">
-        <v>-2.21</v>
       </c>
       <c r="W44" s="94" t="n">
         <v>-2.21</v>
       </c>
       <c r="X44" s="94" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="Y44" s="94" t="n">
         <v>-1.73</v>
       </c>
-      <c r="Y44" s="94" t="n">
+      <c r="Z44" s="94" t="n">
         <v>-1.09</v>
       </c>
-      <c r="Z44" s="94" t="n">
+      <c r="AA44" s="94" t="n">
         <v>-1.28</v>
       </c>
-      <c r="AA44" s="94" t="n">
+      <c r="AB44" s="94" t="n">
         <v>-1.65</v>
-      </c>
-      <c r="AB44" s="94" t="n">
-        <v>-3.93</v>
       </c>
       <c r="AC44" s="94" t="n">
         <v>-3.93</v>
       </c>
       <c r="AD44" s="94" t="n">
+        <v>-3.93</v>
+      </c>
+      <c r="AE44" s="94" t="n">
         <v>-3.13</v>
-      </c>
-      <c r="AE44" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="45">
@@ -11306,7 +11326,7 @@
         <v>48.42</v>
       </c>
       <c r="C45" s="94" t="n">
-        <v>80.51000000000001</v>
+        <v>48.42</v>
       </c>
       <c r="D45" s="94" t="n">
         <v>80.51000000000001</v>
@@ -11315,82 +11335,82 @@
         <v>80.51000000000001</v>
       </c>
       <c r="F45" s="94" t="n">
+        <v>80.51000000000001</v>
+      </c>
+      <c r="G45" s="94" t="n">
         <v>79.54000000000001</v>
       </c>
-      <c r="G45" s="94" t="n">
+      <c r="H45" s="94" t="n">
         <v>69.76000000000001</v>
       </c>
-      <c r="H45" s="94" t="n">
+      <c r="I45" s="94" t="n">
         <v>80.88</v>
       </c>
-      <c r="I45" s="94" t="n">
+      <c r="J45" s="94" t="n">
         <v>84.89</v>
-      </c>
-      <c r="J45" s="94" t="n">
-        <v>93.34</v>
       </c>
       <c r="K45" s="94" t="n">
         <v>93.34</v>
       </c>
       <c r="L45" s="94" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="M45" s="94" t="n">
         <v>92.31999999999999</v>
       </c>
-      <c r="M45" s="94" t="n">
+      <c r="N45" s="94" t="n">
         <v>90.48999999999999</v>
       </c>
-      <c r="N45" s="94" t="n">
+      <c r="O45" s="94" t="n">
         <v>87.65000000000001</v>
       </c>
-      <c r="O45" s="94" t="n">
+      <c r="P45" s="94" t="n">
         <v>85.73</v>
-      </c>
-      <c r="P45" s="94" t="n">
-        <v>84.51000000000001</v>
       </c>
       <c r="Q45" s="94" t="n">
         <v>84.51000000000001</v>
       </c>
       <c r="R45" s="94" t="n">
+        <v>84.51000000000001</v>
+      </c>
+      <c r="S45" s="94" t="n">
         <v>80.23</v>
       </c>
-      <c r="S45" s="94" t="n">
+      <c r="T45" s="94" t="n">
         <v>62.6</v>
       </c>
-      <c r="T45" s="94" t="n">
+      <c r="U45" s="94" t="n">
         <v>51.62</v>
       </c>
-      <c r="U45" s="94" t="n">
+      <c r="V45" s="94" t="n">
         <v>48.02</v>
-      </c>
-      <c r="V45" s="94" t="n">
-        <v>52.7</v>
       </c>
       <c r="W45" s="94" t="n">
         <v>52.7</v>
       </c>
       <c r="X45" s="94" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="Y45" s="94" t="n">
         <v>66.38</v>
       </c>
-      <c r="Y45" s="94" t="n">
+      <c r="Z45" s="94" t="n">
         <v>61.23</v>
       </c>
-      <c r="Z45" s="94" t="n">
+      <c r="AA45" s="94" t="n">
         <v>69.54000000000001</v>
       </c>
-      <c r="AA45" s="94" t="n">
+      <c r="AB45" s="94" t="n">
         <v>65.06</v>
-      </c>
-      <c r="AB45" s="94" t="n">
-        <v>37.52</v>
       </c>
       <c r="AC45" s="94" t="n">
         <v>37.52</v>
       </c>
       <c r="AD45" s="94" t="n">
+        <v>37.52</v>
+      </c>
+      <c r="AE45" s="94" t="n">
         <v>65.84</v>
-      </c>
-      <c r="AE45" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="46">
@@ -11419,133 +11439,135 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="F46" s="91" t="inlineStr">
+      <c r="F46" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G46" s="91" t="inlineStr">
+      <c r="H46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H46" s="92" t="inlineStr">
+      <c r="I46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I46" s="92" t="inlineStr">
+      <c r="J46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J46" s="92" t="inlineStr">
+      <c r="K46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K46" s="92" t="inlineStr">
+      <c r="L46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L46" s="91" t="inlineStr">
+      <c r="M46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M46" s="91" t="inlineStr">
+      <c r="N46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N46" s="91" t="inlineStr">
+      <c r="O46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O46" s="91" t="inlineStr">
+      <c r="P46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P46" s="91" t="inlineStr">
+      <c r="Q46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q46" s="91" t="inlineStr">
+      <c r="R46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R46" s="91" t="inlineStr">
+      <c r="S46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S46" s="91" t="inlineStr">
+      <c r="T46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T46" s="91" t="inlineStr">
+      <c r="U46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U46" s="93" t="inlineStr">
+      <c r="V46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V46" s="92" t="inlineStr">
+      <c r="W46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W46" s="92" t="inlineStr">
+      <c r="X46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X46" s="91" t="inlineStr">
+      <c r="Y46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y46" s="91" t="inlineStr">
+      <c r="Z46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z46" s="91" t="inlineStr">
+      <c r="AA46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA46" s="91" t="inlineStr">
+      <c r="AB46" s="91" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB46" s="93" t="inlineStr">
+      <c r="AC46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC46" s="93" t="inlineStr">
+      <c r="AD46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD46" s="92" t="inlineStr">
+      <c r="AE46" s="92" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
-      </c>
-      <c r="AE46" s="92" t="n">
-        <v/>
       </c>
     </row>
     <row r="47">
@@ -11555,10 +11577,10 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>11.79</v>
+        <v>11.91</v>
       </c>
       <c r="C47" s="94" t="n">
-        <v>12.86</v>
+        <v>11.91</v>
       </c>
       <c r="D47" s="94" t="n">
         <v>12.86</v>
@@ -11567,82 +11589,82 @@
         <v>12.86</v>
       </c>
       <c r="F47" s="94" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="G47" s="94" t="n">
         <v>13.89</v>
       </c>
-      <c r="G47" s="94" t="n">
+      <c r="H47" s="94" t="n">
         <v>12.36</v>
       </c>
-      <c r="H47" s="94" t="n">
+      <c r="I47" s="94" t="n">
         <v>10.02</v>
       </c>
-      <c r="I47" s="94" t="n">
+      <c r="J47" s="94" t="n">
         <v>8.960000000000001</v>
-      </c>
-      <c r="J47" s="94" t="n">
-        <v>9.92</v>
       </c>
       <c r="K47" s="94" t="n">
         <v>9.92</v>
       </c>
       <c r="L47" s="94" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="M47" s="94" t="n">
         <v>10.12</v>
       </c>
-      <c r="M47" s="94" t="n">
+      <c r="N47" s="94" t="n">
         <v>9.68</v>
       </c>
-      <c r="N47" s="94" t="n">
+      <c r="O47" s="94" t="n">
         <v>8.34</v>
       </c>
-      <c r="O47" s="94" t="n">
+      <c r="P47" s="94" t="n">
         <v>7.86</v>
-      </c>
-      <c r="P47" s="94" t="n">
-        <v>6.34</v>
       </c>
       <c r="Q47" s="94" t="n">
         <v>6.34</v>
       </c>
       <c r="R47" s="94" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="S47" s="94" t="n">
         <v>5.47</v>
       </c>
-      <c r="S47" s="94" t="n">
+      <c r="T47" s="94" t="n">
         <v>5.88</v>
       </c>
-      <c r="T47" s="94" t="n">
+      <c r="U47" s="94" t="n">
         <v>4.03</v>
       </c>
-      <c r="U47" s="94" t="n">
+      <c r="V47" s="94" t="n">
         <v>3.2</v>
-      </c>
-      <c r="V47" s="94" t="n">
-        <v>4.34</v>
       </c>
       <c r="W47" s="94" t="n">
         <v>4.34</v>
       </c>
       <c r="X47" s="94" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="Y47" s="94" t="n">
         <v>5.76</v>
       </c>
-      <c r="Y47" s="94" t="n">
+      <c r="Z47" s="94" t="n">
         <v>5.58</v>
       </c>
-      <c r="Z47" s="94" t="n">
+      <c r="AA47" s="94" t="n">
         <v>6.68</v>
       </c>
-      <c r="AA47" s="94" t="n">
+      <c r="AB47" s="94" t="n">
         <v>5.82</v>
-      </c>
-      <c r="AB47" s="94" t="n">
-        <v>4.11</v>
       </c>
       <c r="AC47" s="94" t="n">
         <v>4.11</v>
       </c>
       <c r="AD47" s="94" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AE47" s="94" t="n">
         <v>5.31</v>
-      </c>
-      <c r="AE47" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="48">
@@ -11652,10 +11674,10 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>20.75</v>
+        <v>20.88</v>
       </c>
       <c r="C48" s="94" t="n">
-        <v>22.62</v>
+        <v>20.88</v>
       </c>
       <c r="D48" s="94" t="n">
         <v>22.62</v>
@@ -11664,82 +11686,82 @@
         <v>22.62</v>
       </c>
       <c r="F48" s="94" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="G48" s="94" t="n">
         <v>22.89</v>
       </c>
-      <c r="G48" s="94" t="n">
+      <c r="H48" s="94" t="n">
         <v>22.83</v>
       </c>
-      <c r="H48" s="94" t="n">
+      <c r="I48" s="94" t="n">
         <v>23.49</v>
       </c>
-      <c r="I48" s="94" t="n">
+      <c r="J48" s="94" t="n">
         <v>22.74</v>
-      </c>
-      <c r="J48" s="94" t="n">
-        <v>21.14</v>
       </c>
       <c r="K48" s="94" t="n">
         <v>21.14</v>
       </c>
       <c r="L48" s="94" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="M48" s="94" t="n">
         <v>18.41</v>
       </c>
-      <c r="M48" s="94" t="n">
+      <c r="N48" s="94" t="n">
         <v>14.83</v>
       </c>
-      <c r="N48" s="94" t="n">
+      <c r="O48" s="94" t="n">
         <v>14.29</v>
       </c>
-      <c r="O48" s="94" t="n">
+      <c r="P48" s="94" t="n">
         <v>14.57</v>
-      </c>
-      <c r="P48" s="94" t="n">
-        <v>13.5</v>
       </c>
       <c r="Q48" s="94" t="n">
         <v>13.5</v>
       </c>
       <c r="R48" s="94" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="S48" s="94" t="n">
         <v>12.88</v>
       </c>
-      <c r="S48" s="94" t="n">
+      <c r="T48" s="94" t="n">
         <v>11.9</v>
       </c>
-      <c r="T48" s="94" t="n">
+      <c r="U48" s="94" t="n">
         <v>9.23</v>
       </c>
-      <c r="U48" s="94" t="n">
+      <c r="V48" s="94" t="n">
         <v>9.380000000000001</v>
-      </c>
-      <c r="V48" s="94" t="n">
-        <v>11.24</v>
       </c>
       <c r="W48" s="94" t="n">
         <v>11.24</v>
       </c>
       <c r="X48" s="94" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="Y48" s="94" t="n">
         <v>10.69</v>
       </c>
-      <c r="Y48" s="94" t="n">
+      <c r="Z48" s="94" t="n">
         <v>10.27</v>
       </c>
-      <c r="Z48" s="94" t="n">
+      <c r="AA48" s="94" t="n">
         <v>9.84</v>
       </c>
-      <c r="AA48" s="94" t="n">
+      <c r="AB48" s="94" t="n">
         <v>8.74</v>
-      </c>
-      <c r="AB48" s="94" t="n">
-        <v>6.18</v>
       </c>
       <c r="AC48" s="94" t="n">
         <v>6.18</v>
       </c>
       <c r="AD48" s="94" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="AE48" s="94" t="n">
         <v>8.039999999999999</v>
-      </c>
-      <c r="AE48" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="49">
@@ -11749,10 +11771,10 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>54.37</v>
+        <v>55.85</v>
       </c>
       <c r="C49" s="94" t="n">
-        <v>87.03</v>
+        <v>55.85</v>
       </c>
       <c r="D49" s="94" t="n">
         <v>87.03</v>
@@ -11761,82 +11783,82 @@
         <v>87.03</v>
       </c>
       <c r="F49" s="94" t="n">
+        <v>87.03</v>
+      </c>
+      <c r="G49" s="94" t="n">
         <v>86.93000000000001</v>
       </c>
-      <c r="G49" s="94" t="n">
+      <c r="H49" s="94" t="n">
         <v>85.23</v>
       </c>
-      <c r="H49" s="94" t="n">
+      <c r="I49" s="94" t="n">
         <v>80.29000000000001</v>
       </c>
-      <c r="I49" s="94" t="n">
+      <c r="J49" s="94" t="n">
         <v>75.37</v>
-      </c>
-      <c r="J49" s="94" t="n">
-        <v>89.53</v>
       </c>
       <c r="K49" s="94" t="n">
         <v>89.53</v>
       </c>
       <c r="L49" s="94" t="n">
+        <v>89.53</v>
+      </c>
+      <c r="M49" s="94" t="n">
         <v>91.64</v>
       </c>
-      <c r="M49" s="94" t="n">
+      <c r="N49" s="94" t="n">
         <v>89.73</v>
       </c>
-      <c r="N49" s="94" t="n">
+      <c r="O49" s="94" t="n">
         <v>86.16</v>
       </c>
-      <c r="O49" s="94" t="n">
+      <c r="P49" s="94" t="n">
         <v>85.12</v>
-      </c>
-      <c r="P49" s="94" t="n">
-        <v>83.34999999999999</v>
       </c>
       <c r="Q49" s="94" t="n">
         <v>83.34999999999999</v>
       </c>
       <c r="R49" s="94" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="S49" s="94" t="n">
         <v>76.81</v>
       </c>
-      <c r="S49" s="94" t="n">
+      <c r="T49" s="94" t="n">
         <v>74.04000000000001</v>
       </c>
-      <c r="T49" s="94" t="n">
+      <c r="U49" s="94" t="n">
         <v>58.54</v>
       </c>
-      <c r="U49" s="94" t="n">
+      <c r="V49" s="94" t="n">
         <v>46.37</v>
-      </c>
-      <c r="V49" s="94" t="n">
-        <v>54.22</v>
       </c>
       <c r="W49" s="94" t="n">
         <v>54.22</v>
       </c>
       <c r="X49" s="94" t="n">
+        <v>54.22</v>
+      </c>
+      <c r="Y49" s="94" t="n">
         <v>65.81999999999999</v>
       </c>
-      <c r="Y49" s="94" t="n">
+      <c r="Z49" s="94" t="n">
         <v>67.31999999999999</v>
       </c>
-      <c r="Z49" s="94" t="n">
+      <c r="AA49" s="94" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="AA49" s="94" t="n">
+      <c r="AB49" s="94" t="n">
         <v>62.55</v>
-      </c>
-      <c r="AB49" s="94" t="n">
-        <v>39.09</v>
       </c>
       <c r="AC49" s="94" t="n">
         <v>39.09</v>
       </c>
       <c r="AD49" s="94" t="n">
+        <v>39.09</v>
+      </c>
+      <c r="AE49" s="94" t="n">
         <v>48.84</v>
-      </c>
-      <c r="AE49" s="94" t="n">
-        <v/>
       </c>
     </row>
     <row r="51">
@@ -11849,7 +11871,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:74.2&gt;=73;dax30:RNG60:11.79&gt;=10;dax30:RNG120:20.75&gt;=20</t>
+          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:89.8&gt;=73;dax30:RNG60:11.91&gt;=10;dax30:RNG120:20.88&gt;=20</t>
         </is>
       </c>
     </row>

--- a/report_2501.xlsx
+++ b/report_2501.xlsx
@@ -800,7 +800,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1063,7 +1063,6 @@
     <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8289,9 +8288,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B18" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C18" s="93" t="inlineStr">
@@ -8447,7 +8446,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>4.93</v>
+        <v>4.41</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>4.93</v>
@@ -8544,7 +8543,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>12.17</v>
+        <v>12.98</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>12.17</v>
@@ -8635,13 +8634,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="96" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>15.04</v>
+        <v>59.23</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>15.04</v>
@@ -8895,7 +8894,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>6.29</v>
+        <v>5.53</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>6.29</v>
@@ -8992,7 +8991,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>12.47</v>
+        <v>13.21</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>12.47</v>
@@ -9089,7 +9088,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>32.81</v>
+        <v>49.68</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>32.81</v>
@@ -9185,9 +9184,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B26" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C26" s="93" t="inlineStr">
@@ -9343,7 +9342,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>6.67</v>
+        <v>6.59</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>6.67</v>
@@ -9440,7 +9439,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>15.81</v>
+        <v>17.12</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>15.81</v>
@@ -9531,13 +9530,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="96" t="inlineStr">
+      <c r="A29" s="76" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>11.59</v>
+        <v>65.53</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>11.59</v>
@@ -10681,7 +10680,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-1.68</v>
+        <v>-1.14</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>-2.96</v>
@@ -10778,7 +10777,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>-1.2</v>
+        <v>-0.65</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>-2.43</v>
@@ -10875,7 +10874,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>60.96</v>
+        <v>64.06</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>51.83</v>
@@ -11129,7 +11128,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>6.59</v>
+        <v>6.47</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>6.59</v>
@@ -11226,7 +11225,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>7.11</v>
+        <v>6.51</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>7.11</v>
@@ -11323,7 +11322,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>48.42</v>
+        <v>59.36</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>48.42</v>
@@ -11577,7 +11576,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>11.91</v>
+        <v>11.68</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>11.91</v>
@@ -11674,7 +11673,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>20.88</v>
+        <v>20.74</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>20.88</v>
@@ -11771,7 +11770,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>55.85</v>
+        <v>60.21</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>55.85</v>
@@ -11864,14 +11863,14 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：us500:RS2:15.04&lt;=22;ixic:RS2:11.59&lt;=38</t>
+          <t>今日买报：</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:89.8&gt;=73;dax30:RNG60:11.91&gt;=10;dax30:RNG120:20.88&gt;=20</t>
+          <t>今日卖报：sh:RS3:67.42&gt;=66;hk50:RS4:89.8&gt;=73;dax30:RNG60:11.68&gt;=10;dax30:RNG120:20.74&gt;=20</t>
         </is>
       </c>
     </row>
@@ -15472,13 +15471,13 @@
       <c r="G2" s="36" t="n">
         <v>66</v>
       </c>
-      <c r="H2" s="97" t="n">
+      <c r="H2" s="96" t="n">
         <v>22.3514585</v>
       </c>
       <c r="I2" s="36" t="n">
         <v>7.06</v>
       </c>
-      <c r="J2" s="98">
+      <c r="J2" s="97">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -15510,13 +15509,13 @@
       <c r="G3" s="39" t="n">
         <v>73</v>
       </c>
-      <c r="H3" s="99" t="n">
+      <c r="H3" s="98" t="n">
         <v>35.0298984</v>
       </c>
       <c r="I3" s="39" t="n">
         <v>11.41</v>
       </c>
-      <c r="J3" s="98">
+      <c r="J3" s="97">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -15548,13 +15547,13 @@
       <c r="G4" s="39" t="n">
         <v>85</v>
       </c>
-      <c r="H4" s="99" t="n">
+      <c r="H4" s="98" t="n">
         <v>122.4911655</v>
       </c>
       <c r="I4" s="39" t="n">
         <v>76.98</v>
       </c>
-      <c r="J4" s="100">
+      <c r="J4" s="99">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -15586,13 +15585,13 @@
       <c r="G5" s="39" t="n">
         <v>96</v>
       </c>
-      <c r="H5" s="99" t="n">
+      <c r="H5" s="98" t="n">
         <v>136.13543</v>
       </c>
       <c r="I5" s="39" t="n">
         <v>100.05</v>
       </c>
-      <c r="J5" s="100">
+      <c r="J5" s="99">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -15624,13 +15623,13 @@
       <c r="G6" s="39" t="n">
         <v>95</v>
       </c>
-      <c r="H6" s="99" t="n">
+      <c r="H6" s="98" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I6" s="39" t="n">
         <v>44.37</v>
       </c>
-      <c r="J6" s="100">
+      <c r="J6" s="99">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -15662,13 +15661,13 @@
       <c r="G7" s="39" t="n">
         <v>86</v>
       </c>
-      <c r="H7" s="99" t="n">
+      <c r="H7" s="98" t="n">
         <v>123.8525927</v>
       </c>
       <c r="I7" s="39" t="n">
         <v>63.41</v>
       </c>
-      <c r="J7" s="100">
+      <c r="J7" s="99">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -15700,13 +15699,13 @@
       <c r="G8" s="39" t="n">
         <v>87</v>
       </c>
-      <c r="H8" s="99" t="n">
+      <c r="H8" s="98" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I8" s="39" t="n">
         <v>26.39</v>
       </c>
-      <c r="J8" s="100">
+      <c r="J8" s="99">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -15738,13 +15737,13 @@
       <c r="G9" s="39" t="n">
         <v>83</v>
       </c>
-      <c r="H9" s="99" t="n">
+      <c r="H9" s="98" t="n">
         <v>47.02060524</v>
       </c>
       <c r="I9" s="39" t="n">
         <v>37.82</v>
       </c>
-      <c r="J9" s="100">
+      <c r="J9" s="99">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -15775,13 +15774,13 @@
       <c r="G10" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="H10" s="101" t="n">
+      <c r="H10" s="100" t="n">
         <v>27.8860732</v>
       </c>
       <c r="I10" s="24" t="n">
         <v>-10.97</v>
       </c>
-      <c r="J10" s="102" t="n">
+      <c r="J10" s="101" t="n">
         <v>0.278860732</v>
       </c>
     </row>
@@ -15812,13 +15811,13 @@
       <c r="G11" s="24" t="n">
         <v>93</v>
       </c>
-      <c r="H11" s="101" t="n">
+      <c r="H11" s="100" t="n">
         <v>17.4948656</v>
       </c>
       <c r="I11" s="24" t="n">
         <v>-7.7</v>
       </c>
-      <c r="J11" s="102">
+      <c r="J11" s="101">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>
